--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,20 +449,25 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Products</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Comment 1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Comment 2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Comment 3</t>
         </is>
@@ -499,20 +504,25 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Windows</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>50.000¥. Moq-1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>50.000¥. Moq-1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>50.000¥. Moq-1</t>
         </is>
@@ -529,20 +539,25 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Windows</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>500 pcs price 58 usd</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>1000 pcs price 120 usd</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>1000 pcs price 38 USD</t>
         </is>
@@ -579,20 +594,25 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Windows</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>80$</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>70$</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>300 yuan</t>
         </is>
@@ -629,20 +649,25 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Smart</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>500pcs / $100USD for pcs</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>50pcs / $50USD for pcs</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>20pcs / $100USD for pcs</t>
         </is>
@@ -675,20 +700,25 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Windows</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Custom order</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Custom order</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Custom order</t>
         </is>
@@ -725,20 +755,25 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>170 to 335 usd</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>100 to up</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>100 to up usd</t>
         </is>
@@ -755,20 +790,25 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Coatings</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>Super</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Super</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Super</t>
         </is>
@@ -801,20 +841,25 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -847,20 +892,25 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Wall sheet , 200 rmb per meter , 2000 mtr,</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Handles , 500 moq , 100 rmb per handle</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
         </is>
@@ -897,20 +947,25 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 uni</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Price: 1200 – 3500 CNY per unit depending on materials and security specificatio</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. M</t>
         </is>
@@ -943,20 +998,25 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Furnishing</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>Хорошее, 400rmb</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Хорошее , 1500rmb</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Нормальное</t>
         </is>
@@ -977,20 +1037,25 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>$176, MOQ 50, very good!</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>$55, MOQ100pcs, good</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>$30, MOQ 10pcs, nice</t>
         </is>
@@ -1027,20 +1092,25 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Doors</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>1000 yuan 1 square</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>150 rmb</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>570 rmb</t>
         </is>
@@ -1077,20 +1147,25 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>620 super</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>1500 super</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>130 super</t>
         </is>
@@ -1127,20 +1202,25 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>$32, MOQ 300, good</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>¥3000, MoQ 1pcs, very good</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>¥17, Moq 50, good</t>
         </is>
@@ -1177,20 +1257,25 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>600 RMB Great, very cheap</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>800 rmb, little high</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>3400, Good price</t>
         </is>
@@ -1219,20 +1304,25 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Coatings</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>10$</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>69$</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>50-85$</t>
         </is>
@@ -1261,20 +1351,25 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>￥1000 good</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>¥ 500 good</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>￥ 300 good</t>
         </is>
@@ -1303,20 +1398,25 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>300 rmb and more. Good quality and good price. Small quantity</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>33$ for 1 pcs. Good quality and quantity</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Good quality and quantity. 140 rmb 1 pcs.</t>
         </is>
@@ -1341,20 +1441,25 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>Good 👍</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>1570</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>5800</t>
         </is>
@@ -1391,20 +1496,25 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>130 yuan</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>20000usd</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>500yuan</t>
         </is>
@@ -1441,20 +1551,25 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>MOQ 100, 47 rnb per piece</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>MOQ 50, 200 rnb per</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>MOQ 10, 845 per piece</t>
         </is>
@@ -1491,20 +1606,25 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Building</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>1pcs. Start from 60rmb. Novative technology</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>From 1pc. Natural materials.</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>1250rmb. MOQ 1 pc</t>
         </is>
@@ -1541,20 +1661,25 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>399</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>199</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>1410</t>
         </is>
@@ -1591,20 +1716,25 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>229</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>680</t>
         </is>
@@ -1641,20 +1771,25 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>150 yuan, 100, good range of products</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>800usd, very nice, good quality product</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Set of furniture is very good quality, I like the company has also a showroom in</t>
         </is>
@@ -1675,20 +1810,25 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>The price starts from three thousand yuan, the consultant showed all the functio</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>The price starts from three thousand yuan, the consultant showed all the functio</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>I couldn't tell you the price for smart pens right away, but they said they woul</t>
         </is>
@@ -1721,20 +1861,25 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>1410</t>
         </is>
@@ -1767,20 +1912,25 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Smart</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не р</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>330 юаней. 500 штук минималка . Качественный , магнитный умный переключатель с е</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно за</t>
         </is>
@@ -1817,20 +1967,25 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного </t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количест</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккур</t>
         </is>
@@ -1867,20 +2022,25 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>2900 usd</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1917,20 +2077,25 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product a</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>MOQ 1, they got samples. 8000usd. Very well made product, trendy and popular. Th</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable</t>
         </is>
@@ -1967,20 +2132,25 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>600</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -2017,20 +2187,25 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>0.6 usd/m2</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Under negotiation, great opportunities</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>1-5 usd/l</t>
         </is>
@@ -2063,20 +2238,25 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>679 rmb</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>59 rmb</t>
         </is>
@@ -2101,20 +2281,25 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>249RMB</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>6000RMB</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>2000RMB&amp;gt;</t>
         </is>
@@ -2147,20 +2332,25 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
           <t>MOQ - 5000 and price - 7000 dollars</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>4000$</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>3000 dollars</t>
         </is>
@@ -2193,20 +2383,25 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>The price cheap, merchant very friendly</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>The price more cheaper, good quality</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Good merchant, perfect products</t>
         </is>
@@ -2243,20 +2438,25 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>160 RMB/ pcs The prices are attractive and he wants me to represent their produc</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>15 RMB the product is interesting</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>nearly $15,000 for this production line</t>
         </is>
@@ -2293,20 +2493,25 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>249</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>749</t>
         </is>
@@ -2343,20 +2548,25 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>5000 USD</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>3000 USD</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>3000 USD</t>
         </is>
@@ -2381,20 +2591,25 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Doors</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t>6000 RMB. I like the way they explain everything about their product.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Smart home system 2000 RMB. They have showed us how the smart home system works.</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>249 RMB. They have fully described their products.</t>
         </is>
@@ -2423,20 +2638,25 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Doors</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
           <t>6000RMB，积极，详细地告诉了一切</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>249RMB , 价格很便宜</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>2000 RMB</t>
         </is>
@@ -2469,20 +2689,25 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Coatings</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>400rmb /m2 good meeting</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>350 rmb/m2</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>MOQ 5000 pieces</t>
         </is>
@@ -2515,20 +2740,25 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Coatings</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
           <t>400rmb/m2</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>350rmb/m2</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>MOQ 5000 pieces</t>
         </is>
@@ -2565,20 +2795,25 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
           <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>3000 / MOQ 1 Inside view is luxury, i love it</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>20 / MOQ 100 Nice worker answered all questions</t>
         </is>
@@ -2611,20 +2846,25 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Building</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>80 rmb for 230 meter</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>1560 rmb for whole item</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>4600 rmb</t>
         </is>
@@ -2641,20 +2881,25 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
@@ -2675,20 +2920,25 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
           <t>50 Yuan 50g (The taste is authentic and aroma is really good</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>150 Yuan, 1 bottle. ( Taste is strong and good</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Haven't discussed the prices. Just got the company name list for future referenc</t>
         </is>
@@ -2725,20 +2975,25 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
           <t>2085</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>2147</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>2223</t>
         </is>
@@ -2775,20 +3030,25 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
           <t>250¥/м3</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>4500¥</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>8790$</t>
         </is>
@@ -2825,20 +3085,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Furnishing</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
           <t>300¥ 300pcs</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>50¥ 1000pcs</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>500$ 100psc</t>
         </is>
@@ -2875,20 +3140,25 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
           <t>4500¥</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>8790$</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>250¥/m3</t>
         </is>
@@ -2921,20 +3191,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Doors</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>1p, 10000$m2, very beautiful big red door</t>
         </is>
@@ -2971,20 +3246,25 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Doors</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t>1 container (400 square meters), 60 dollars for 1 square meters</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Moq is 1 door, 530 RMB for 1 door</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>14400 dollars, moq - 1</t>
         </is>
@@ -3017,20 +3297,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>Doors</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>1 товаров</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается </t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается </t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t xml:space="preserve">Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается </t>
         </is>
@@ -3063,20 +3348,25 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Furnishing</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>100 RMB per sample. The taste is very good</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>150 RMB per sample. The taste is very good</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>250 RMB per sample. The taste is very good</t>
         </is>
@@ -3097,20 +3387,25 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
           <t>498rmb/unit. I like the green tea in white color. First time to see colorless te</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>They have tea perfume bar, which was amazing, moreover, i also love their snacks</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>The 中国好水 brand water was really good. They are using deep water instead of shall</t>
         </is>
@@ -3147,20 +3442,25 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
           <t>I will explore their catalog and website, choose products, then'll make an inqui</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>I will explore their catalog and website, choose products, then'll make an inqui</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>I will explore their catalog and website, choose products, then'll make an inqui</t>
         </is>
@@ -3197,20 +3497,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Furnishing</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>1050</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>550</t>
         </is>
@@ -3227,20 +3532,25 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
           <t>Prices are go and packing and Verstaliy is more</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>The taste anaroma is good of this product then anyother</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>the product prices are very good. looks attractive</t>
         </is>
@@ -3273,20 +3583,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Furnishing</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
           <t>820 rmb moq 100</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>650 moq 300</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>560 moq 200</t>
         </is>
@@ -3323,20 +3638,25 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>2.5 RMB per unit, MOQ is 500 pieces. The plastic material was high quality and c</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this com</t>
         </is>
@@ -3369,20 +3689,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Furnishing</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
           <t>1299, MOQ 200. I like the company and people there . Very friendly and know thei</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>5000rmb MOQ 50</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>1500 rmb MOQ 100</t>
         </is>
@@ -3415,20 +3740,25 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
           <t>Black matt tap water $20</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>109</t>
         </is>
@@ -3465,20 +3795,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
           <t>9$</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>13.25$</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>8.83$</t>
         </is>
@@ -3507,20 +3842,25 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
           <t>640 PCs, 3.72 RMB very good</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>30 PCs, 420 RMB, need check quality</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>10 PCs, 1150 RMB, very good</t>
         </is>
@@ -3553,20 +3893,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3603,20 +3948,25 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
           <t>Depend on item</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>Depend of quantity</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>100/square meter</t>
         </is>
@@ -3653,20 +4003,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Building</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
           <t>RMB 15705 MOQ5; pleasant impression</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>MOQ5 25799 RMB</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>RMB 19479; MOQ 1</t>
         </is>
@@ -3703,20 +4058,25 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
@@ -3753,20 +4113,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
           <t>2000$, can be customized, very convenient</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>38$, very unique</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>2050 rmb, very interesting, convenient to use for pets</t>
         </is>
@@ -3795,20 +4160,25 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
           <t>25 rmb, 1 box, like this product</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>34 rmb, 1000, normal</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>40 rmb, 2000, very good</t>
         </is>
@@ -3845,20 +4215,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
           <t>1 container 250 rmb</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>1 container 500 rmb</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>1 container 700 rmb</t>
         </is>
@@ -3895,20 +4270,25 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
           <t>Жду коммерческое предложение. Компания понравилась</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Цена зависит от обьема, от 3 юаней, расходники</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>Прайс отправят, от 100ед, хорошая компания</t>
         </is>

--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,40 +434,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Products</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Comment 1</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Comment 2</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Comment 3</t>
         </is>
@@ -489,40 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>crystal@sunhohiglobal.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>+86-137 0262 5097</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>www.sunhohiwindow.com</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>20th Floor, Building A1, Full International Financial Center, No. 28, Haiwu Road, Guicheng Street, Nanhai District, Foshan City, Guangdong Province, China</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Windows</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>50.000¥. Moq-1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>50.000¥. Moq-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>50.000¥. Moq-1</t>
         </is>
@@ -537,27 +547,28 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Windows</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>500 pcs price 58 usd</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>1000 pcs price 120 usd</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>1000 pcs price 38 USD</t>
         </is>
@@ -579,40 +590,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>export01@gznewhoo.com</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>+86-198-7837-3626</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>www.gznewhoo.com</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Building 7, Hongyu Smart Industrial Park, No. 333 Juhuashi Avenue, Huadu District, Guangzhou</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Windows</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>80$</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>70$</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>300 yuan</t>
         </is>
@@ -634,40 +650,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>kim.lok@bweetech.com</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>186-5759-0678</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>www.bweetech.com</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Smart</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>500pcs / $100USD for pcs</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>50pcs / $50USD for pcs</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>20pcs / $100USD for pcs</t>
         </is>
@@ -689,36 +710,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>sales5@deiouxwindows.com</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>+86-13392246940</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>WWW.DEIOUXWINDOWS.COM</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Windows</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>Custom order</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Custom order</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Custom order</t>
         </is>
@@ -740,40 +766,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>market@smarteklock.com</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>+86-15889896019</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>www.smarteklock.com</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City, Guangdong, China 528415</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>170 to 335 usd</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>100 to up</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>100 to up usd</t>
         </is>
@@ -788,27 +819,28 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Coatings</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Super</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Super</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Super</t>
         </is>
@@ -830,36 +862,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>sales03@cn-xindong.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>0086-182 5765 3405</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -881,36 +918,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>sales09@ouhuadec.comkindell1771@gmail.com962460055@qq.com</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>13326792105</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>佛山市南海区大沥谭边工业区虹岭一路一号（2号厂房）</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Wall sheet , 200 rmb per meter , 2000 mtr,</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Handles , 500 moq , 100 rmb per handle</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
         </is>
@@ -932,40 +974,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>jinjian19@jinjianlock.com</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>15057304393</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>www.jinjianlock.com</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>温州市瓯海区郭溪街道智能锁具产业园(1号楼)1号</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 uni</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Price: 1200 – 3500 CNY per unit depending on materials and security specificatio</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. M</t>
         </is>
@@ -985,38 +1032,39 @@
           <t>赖华芳</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
         <is>
           <t>13727479513, 400-8339513</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Furnishing</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>3 товаров</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Хорошее, 400rmb</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Хорошее , 1500rmb</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Нормальное</t>
         </is>
@@ -1028,36 +1076,57 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中山市福乐门智能科技有限公司</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+          <t>CHINA GUANGCHAO CONTAINER HOUSE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>陈洁玲 Rowling</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>014@cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>+86 189 2997 1329</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>www.cgchcontainer.com</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Doors</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>$176, MOQ 50, very good!</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>$55, MOQ100pcs, good</t>
+          <t>1000 yuan 1 square</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>$30, MOQ 10pcs, nice</t>
+          <t>150 rmb</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>570 rmb</t>
         </is>
       </c>
     </row>
@@ -1067,52 +1136,57 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHINA GUANGCHAO CONTAINER HOUSE</t>
+          <t>广东招材建材科技有限公司</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>陈洁玲 Rowling</t>
+          <t>黎桃桃</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>+86 189 2997 1329</t>
+          <t>toto.liblun@gmail.com</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>www.cgchcontainer.com</t>
+          <t>+8618934320539</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+          <t>www.liblun.com</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Doors</t>
+          <t>广东省佛山市南海区罗村社区新下村5号厂房</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1000 yuan 1 square</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>150 rmb</t>
+          <t>620 super</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>570 rmb</t>
+          <t>1500 super</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>130 super</t>
         </is>
       </c>
     </row>
@@ -1122,52 +1196,57 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>广东招材建材科技有限公司</t>
+          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co., Ltd.)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>黎桃桃</t>
+          <t>欧阳玉滢 (Sonia Ouyang)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>+8618934320539</t>
+          <t>sonia.ouyang@wireking.com</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>www.liblun.com</t>
+          <t>+86-13392758223</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区罗村社区新下村5号厂房</t>
+          <t>www.wireking.com</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Decoration</t>
+          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>620 super</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1500 super</t>
+          <t>$32, MOQ 300, good</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>130 super</t>
+          <t>¥3000, MoQ 1pcs, very good</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>¥17, Moq 50, good</t>
         </is>
       </c>
     </row>
@@ -1177,52 +1256,57 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co., Ltd.)</t>
+          <t>佛山市悠派家居科技有限公司</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>欧阳玉滢 (Sonia Ouyang)</t>
+          <t>黄伟业</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>+86-13392758223</t>
+          <t>Yea@LGPKB.com</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>www.wireking.com</t>
+          <t>13825596371</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
+          <t>www.LGPKB.com</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>$32, MOQ 300, good</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>¥3000, MoQ 1pcs, very good</t>
+          <t>600 RMB Great, very cheap</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>¥17, Moq 50, good</t>
+          <t>800 rmb, little high</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>3400, Good price</t>
         </is>
       </c>
     </row>
@@ -1232,52 +1316,49 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>佛山市悠派家居科技有限公司</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>黄伟业</t>
-        </is>
-      </c>
+          <t>常州市永春保温材料有限公司</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13825596371</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>www.LGPKB.com</t>
-        </is>
-      </c>
+          <t>yongchun1208@163.com</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
+          <t>www.ycbwcl.1688.com</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>江苏省常州市</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Coatings</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>600 RMB Great, very cheap</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>800 rmb, little high</t>
+          <t>10$</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3400, Good price</t>
+          <t>69$</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>50-85$</t>
         </is>
       </c>
     </row>
@@ -1287,44 +1368,49 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>常州市永春保温材料有限公司</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>杭州班昇</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>陈卓敏 Ruby</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>295608376@qq.com</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>www.ycbwcl.1688.com</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>江苏省常州市</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Coatings</t>
-        </is>
-      </c>
+          <t>+86 13556688832</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10$</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>69$</t>
+          <t>￥1000 good</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>50-85$</t>
+          <t>¥ 500 good</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>￥ 300 good</t>
         </is>
       </c>
     </row>
@@ -1334,44 +1420,45 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>杭州班昇</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>陈卓敏 Ruby</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>+86 13556688832</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>江门市新阳刚智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>135 3666 7789, 400-9090-518</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Decoration</t>
+          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>￥1000 good</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>¥ 500 good</t>
+          <t>300 rmb and more. Good quality and good price. Small quantity</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>￥ 300 good</t>
+          <t>33$ for 1 pcs. Good quality and quantity</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Good quality and quantity. 140 rmb 1 pcs.</t>
         </is>
       </c>
     </row>
@@ -1381,44 +1468,45 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>江门市新阳刚智能科技有限公司</t>
+          <t>三强地毯 (THREE-STRONG CARPET)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>135 3666 7789, 400-9090-518</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
+          <t>hengsheng_carpet@163.com</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0769-89807692</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>300 rmb and more. Good quality and good price. Small quantity</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>33$ for 1 pcs. Good quality and quantity</t>
+          <t>Good 👍</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Good quality and quantity. 140 rmb 1 pcs.</t>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>5800</t>
         </is>
       </c>
     </row>
@@ -1428,40 +1516,57 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>三强地毯 (THREE-STRONG CARPET)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>Zhejiang Kehon Intelligent Science &amp; Technology Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sammi Shi</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0769-89807692</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+          <t>sales01@kehon.cn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>+86 156 8948 5097</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>www.kehon.cn</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Good 👍</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>130 yuan</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>20000usd</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>500yuan</t>
         </is>
       </c>
     </row>
@@ -1471,52 +1576,57 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zhejiang Kehon Intelligent Science &amp; Technology Co., Ltd.</t>
+          <t>CAE SANITARY FITTINGS INDUSTRY CO., LTD. GUANGDONG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sammi Shi</t>
+          <t>Josie Guan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>+86 156 8948 5097</t>
+          <t>cae@china-cae.com</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>www.kehon.cn</t>
+          <t>+86-13702279135</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
+          <t>www.china-cae.com</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>No.62-64, Xingda Rd., Shagang Dist., ShuikouTown, Kaiping; Guangdong, P.R.Of China. PC: 529321</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>130 yuan</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20000usd</t>
+          <t>MOQ 100, 47 rnb per piece</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>500yuan</t>
+          <t>MOQ 50, 200 rnb per</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>MOQ 10, 845 per piece</t>
         </is>
       </c>
     </row>
@@ -1526,52 +1636,57 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CAE SANITARY FITTINGS INDUSTRY CO., LTD. GUANGDONG</t>
+          <t>利亚德光电股份有限公司</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Josie Guan</t>
+          <t>金厚强</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>+86-13702279135</t>
+          <t>jinhouqiang@leyard.com</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>www.china-cae.com</t>
+          <t>13510009569, 18829341125, 400-8592-666</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>No.62-64, Xingda Rd., Shagang Dist., ShuikouTown, Kaiping; Guangdong, P.R.Of China. PC: 529321</t>
+          <t>www.leyard.com</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>北京市海淀区颐和园路北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号利亚德南方产业园A栋</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Building</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MOQ 100, 47 rnb per piece</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>MOQ 50, 200 rnb per</t>
+          <t>1pcs. Start from 60rmb. Novative technology</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>MOQ 10, 845 per piece</t>
+          <t>From 1pc. Natural materials.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1250rmb. MOQ 1 pc</t>
         </is>
       </c>
     </row>
@@ -1581,52 +1696,57 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>利亚德光电股份有限公司</t>
+          <t>广州传祺时代智能科技有限公司</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>金厚强</t>
+          <t>洪美兰</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13510009569, 18829341125, 400-8592-666</t>
+          <t>jiang@chuangqitimes.com</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>www.leyard.com</t>
+          <t>13450298606</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>北京市海淀区颐和园路北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号利亚德南方产业园A栋</t>
+          <t>www.chuangqitimes.com</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Building</t>
+          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1pcs. Start from 60rmb. Novative technology</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>From 1pc. Natural materials.</t>
+          <t>329</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1250rmb. MOQ 1 pc</t>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>680</t>
         </is>
       </c>
     </row>
@@ -1636,52 +1756,57 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Zhejiang Kehon Intelligent Science &amp; Technology Co.,Ltd.</t>
+          <t>Guangdong CAE Sanitary Fittings Co., Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Janice Kuan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>+86 157 5573 4990</t>
+          <t>jack@cae.com.cn</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>www.kehon.cn</t>
+          <t>+86-750-2713118</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
+          <t>www.cae.cn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>No.22, 2nd Phase, Shuikou Sanitary Ware Industrial Park, Kaiping, Guangdong, China</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>150 yuan, 100, good range of products</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>800usd, very nice, good quality product</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Set of furniture is very good quality, I like the company has also a showroom in</t>
         </is>
       </c>
     </row>
@@ -1691,52 +1816,53 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>广州传祺时代智能科技有限公司</t>
+          <t>JNOD 基诺德</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>洪美兰</t>
+          <t>周信朋 Joe Zhou</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13450298606</t>
+          <t>sales02@jnodwater.com</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>www.chuangqitimes.com</t>
+          <t>+86 199 2825 2201</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+          <t>www.jnodwater.com</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>199</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1410</t>
         </is>
       </c>
     </row>
@@ -1746,52 +1872,53 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Guangdong CAE Sanitary Fittings Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Janice Kuan</t>
-        </is>
-      </c>
+          <t>榜威电子科技（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>+86-750-2713118</t>
+          <t>service@bweetech.com</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>www.cae.cn</t>
+          <t>021-57715805</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>No.22, 2nd Phase, Shuikou Sanitary Ware Industrial Park, Kaiping, Guangdong, China</t>
+          <t>www.bweetech.com</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>上海市闵行区新骏环路188号15号楼南5层A501室</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Smart</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>150 yuan, 100, good range of products</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>800usd, very nice, good quality product</t>
+          <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не р</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Set of furniture is very good quality, I like the company has also a showroom in</t>
+          <t>330 юаней. 500 штук минималка . Качественный , магнитный умный переключатель с е</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно за</t>
         </is>
       </c>
     </row>
@@ -1801,36 +1928,57 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>THOR索而</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+          <t>Suzhou Acousound New Material Technology Inc.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Yolanda He</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>acousound02@polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>+86-18018121056</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>The price starts from three thousand yuan, the consultant showed all the functio</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>The price starts from three thousand yuan, the consultant showed all the functio</t>
+          <t xml:space="preserve">Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного </t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>I couldn't tell you the price for smart pens right away, but they said they woul</t>
+          <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количест</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккур</t>
         </is>
       </c>
     </row>
@@ -1840,48 +1988,57 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JNOD 基诺德</t>
+          <t>诺奥(福建)环保家居用品有限公司</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>周信朋 Joe Zhou</t>
+          <t>蔡绿缘</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>+86 199 2825 2201</t>
+          <t>wendyyian@163.com</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>www.jnodwater.com</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>0086-13599917696</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>www.fjnuoao.cn</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>2900 usd</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1891,48 +2048,57 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>榜威电子科技（上海）有限公司</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>Guangzhou Sunrans Sanitary Ware Co., Ltd / Guangzhou Sunrans New Energy Technology Co., Ltd</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>021-57715805</t>
+          <t>william@sunrans.com</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>www.bweetech.com</t>
+          <t>+86 134 1613 9887</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>上海市闵行区新骏环路188号15号楼南5层A501室</t>
+          <t>http://www.sunrans.com</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Smart</t>
+          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не р</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>330 юаней. 500 штук минималка . Качественный , магнитный умный переключатель с е</t>
+          <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product a</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно за</t>
+          <t>MOQ 1, they got samples. 8000usd. Very well made product, trendy and popular. Th</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable</t>
         </is>
       </c>
     </row>
@@ -1942,52 +2108,57 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Suzhou Acousound New Material Technology Inc.</t>
+          <t>IFUN PARK &amp; TIPTOPFUN AMUSEMENT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yolanda He</t>
+          <t>Ivy Zhou</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>+86-18018121056</t>
+          <t>ivy@ifunpark.com</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>www.polyacoustic.com</t>
+          <t>+86 133 0238 5758</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+          <t>www.ifunpark.com / www.ifunamusement.com</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>Decoration</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного </t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количест</t>
+          <t>600</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккур</t>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -1997,52 +2168,57 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>诺奥(福建)环保家居用品有限公司</t>
+          <t>RENQIU TUOXIN BUILDING MATERIALS CO., LTD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>蔡绿缘</t>
+          <t>Emily Li</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0086-13599917696</t>
+          <t>tuoxinlqm@outlook.com</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>www.fjnuoao.cn</t>
+          <t>+86 19831737599</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
+          <t>https://www.tuoxinfiberglassmesh.com/</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2900 usd</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0.6 usd/m2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Under negotiation, great opportunities</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1-5 usd/l</t>
         </is>
       </c>
     </row>
@@ -2052,52 +2228,53 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Guangzhou Sunrans Sanitary Ware Co., Ltd / Guangzhou Sunrans New Energy Technology Co., Ltd</t>
+          <t>安居福智能门</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>罗加玲</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>+86 134 1613 9887</t>
+          <t>1040857731@qq.com</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>http://www.sunrans.com</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
-        </is>
-      </c>
+          <t>18928121650</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>广东省中山市东凤镇</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product a</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>MOQ 1, they got samples. 8000usd. Very well made product, trendy and popular. Th</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable</t>
+          <t>679 rmb</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>59 rmb</t>
         </is>
       </c>
     </row>
@@ -2107,52 +2284,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IFUN PARK &amp; TIPTOPFUN AMUSEMENT</t>
+          <t>东方喜卡</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ivy Zhou</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>+86 133 0238 5758</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>www.ifunpark.com / www.ifunamusement.com</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Decoration</t>
-        </is>
-      </c>
+          <t>果果</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>249RMB</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>6000RMB</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2000RMB&amp;gt;</t>
         </is>
       </c>
     </row>
@@ -2162,52 +2328,53 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RENQIU TUOXIN BUILDING MATERIALS CO., LTD</t>
+          <t>GUANGDONG TUOXUN INTELLIGENT TECHNOLOGY CO., LTD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Emily Li</t>
+          <t>Wing</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>+86 19831737599</t>
+          <t>wuyunying08@gmail.com</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.tuoxinfiberglassmesh.com/</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
-        </is>
-      </c>
+          <t>189-2984-9818</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
+          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.6 usd/m2</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Under negotiation, great opportunities</t>
+          <t>MOQ - 5000 and price - 7000 dollars</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1-5 usd/l</t>
+          <t>4000$</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>3000 dollars</t>
         </is>
       </c>
     </row>
@@ -2217,48 +2384,53 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>安居福智能门</t>
+          <t>佛山市方泓五金建材有限公司</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>罗加玲</t>
+          <t>陈施志凯</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>18928121650</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>广东省中山市东凤镇</t>
-        </is>
-      </c>
+          <t>108455453@qq.com</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>+86 134 3318 1558</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
+          <t>中国广东省佛山市南海区里水镇大步工业区13号</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>679 rmb</t>
+          <t>The price cheap, merchant very friendly</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>59 rmb</t>
+          <t>The price more cheaper, good quality</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Good merchant, perfect products</t>
         </is>
       </c>
     </row>
@@ -2268,40 +2440,57 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>东方喜卡</t>
+          <t>Gaocheng</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>果果</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>叶小龙/Dustin Ye</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>yedustin@gmail.com</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>+86-188 5861 0008</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>www.cngaocheng.cn</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>浙江省三门县浦坝港镇沿海工业城 (Coastal Industrial City, Pubagang Town, Sanmen, Taizhou City, Zhejiang Pro., China)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>249RMB</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6000RMB</t>
+          <t>160 RMB/ pcs The prices are attractive and he wants me to represent their produc</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2000RMB&amp;gt;</t>
+          <t>15 RMB the product is interesting</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>nearly $15,000 for this production line</t>
         </is>
       </c>
     </row>
@@ -2311,48 +2500,57 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GUANGDONG TUOXUN INTELLIGENT TECHNOLOGY CO., LTD</t>
+          <t>ZHEJIANG DOUBLE-LIN VALVES CO., LTD.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wing</t>
+          <t>Dream Lin</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>189-2984-9818</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>sale15@double-lin.com</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>86-13710718529, 86-020-66837727</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
+          <t>www.double-lin.com</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>MOQ - 5000 and price - 7000 dollars</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4000$</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3000 dollars</t>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>749</t>
         </is>
       </c>
     </row>
@@ -2362,48 +2560,57 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>佛山市方泓五金建材有限公司</t>
+          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.LTD.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>陈施志凯</t>
+          <t>Eric Huang</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>+86 134 3318 1558</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>464565801@qq.com</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>13813551160, 0519-88784050</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>中国广东省佛山市南海区里水镇大步工业区13号</t>
+          <t>www.ycpanel.com</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>#28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>The price cheap, merchant very friendly</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>The price more cheaper, good quality</t>
+          <t>5000 USD</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Good merchant, perfect products</t>
+          <t>3000 USD</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>3000 USD</t>
         </is>
       </c>
     </row>
@@ -2413,52 +2620,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gaocheng</t>
+          <t>优品声学吸音隔音</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>叶小龙/Dustin Ye</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>+86-188 5861 0008</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>www.cngaocheng.cn</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>浙江省三门县浦坝港镇沿海工业城 (Coastal Industrial City, Pubagang Town, Sanmen, Taizhou City, Zhejiang Pro., China)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
+          <t>杨伟杰</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Doors</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>160 RMB/ pcs The prices are attractive and he wants me to represent their produc</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>15 RMB the product is interesting</t>
+          <t>6000 RMB. I like the way they explain everything about their product.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>nearly $15,000 for this production line</t>
+          <t>Smart home system 2000 RMB. They have showed us how the smart home system works.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>249 RMB. They have fully described their products.</t>
         </is>
       </c>
     </row>
@@ -2468,52 +2664,45 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ZHEJIANG DOUBLE-LIN VALVES CO., LTD.</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Dream Lin</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>86-13710718529, 86-020-66837727</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>www.double-lin.com</t>
-        </is>
-      </c>
+          <t>广州市优品声学科技有限公司</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
+          <t>www.gzypsx.com</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>广东省广州市番禺区石碁镇文边路28号二栋二层</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Doors</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>6000RMB，积极，详细地告诉了一切</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>249RMB , 价格很便宜</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2000 RMB</t>
         </is>
       </c>
     </row>
@@ -2523,52 +2712,53 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.LTD.</t>
+          <t>贵州佑远木业有限公司</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eric Huang</t>
+          <t>颜加伟</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13813551160, 0519-88784050</t>
+          <t>1164199388@qq.com</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>www.ycpanel.com</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>#28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
-        </is>
-      </c>
+          <t>133 9983 5678</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Decoration</t>
+          <t>贵州省赤水市成渝（赤水）家具产业园A3-2</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Coatings</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5000 USD</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>3000 USD</t>
+          <t>400rmb /m2 good meeting</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>3000 USD</t>
+          <t>350 rmb/m2</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>MOQ 5000 pieces</t>
         </is>
       </c>
     </row>
@@ -2578,40 +2768,57 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>优品声学吸音隔音</t>
+          <t>MOERSHU 摩尔舒卫浴</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杨伟杰</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+          <t>Thea</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>moershu3@moershu.com</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>13957622087</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>www.moershu.com</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Doors</t>
+          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6000 RMB. I like the way they explain everything about their product.</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Smart home system 2000 RMB. They have showed us how the smart home system works.</t>
+          <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>249 RMB. They have fully described their products.</t>
+          <t>3000 / MOQ 1 Inside view is luxury, i love it</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>20 / MOQ 100 Nice worker answered all questions</t>
         </is>
       </c>
     </row>
@@ -2621,44 +2828,53 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>广州市优品声学科技有限公司</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+          <t>江西荣科新型材料有限公司 (JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Lucy Zeng (曾露)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>lucy@rongkedecor.com</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>www.gzypsx.com</t>
+          <t>+86-13134020034</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区石碁镇文边路28号二栋二层</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Doors</t>
-        </is>
-      </c>
+          <t>https://www.amerdecor.com/</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Building</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6000RMB，积极，详细地告诉了一切</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>249RMB , 价格很便宜</t>
+          <t>80 rmb for 230 meter</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2000 RMB</t>
+          <t>1560 rmb for whole item</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4600 rmb</t>
         </is>
       </c>
     </row>
@@ -2666,50 +2882,35 @@
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>贵州佑远木业有限公司</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>颜加伟</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>133 9983 5678</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>贵州省赤水市成渝（赤水）家具产业园A3-2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Coatings</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>400rmb /m2 good meeting</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>350 rmb/m2</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>MOQ 5000 pieces</t>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -2719,48 +2920,53 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>贵州佑远木业有限公司</t>
+          <t>江西瑞京鸿兴实业有限公司</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>颜加伟</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>133 9983 5678</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>朱友群</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>13763963598</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>贵州省赤水市成渝(赤水)家居产业园A3-2</t>
+          <t>www.jx-wpc.com</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Coatings</t>
+          <t>江西省瑞金市经济开发区创业一路东侧</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>General</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>400rmb/m2</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>350rmb/m2</t>
+          <t>250¥/м3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>MOQ 5000 pieces</t>
+          <t>4500¥</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>8790$</t>
         </is>
       </c>
     </row>
@@ -2770,52 +2976,57 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MOERSHU 摩尔舒卫浴</t>
+          <t>ciarra</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thea</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13957622087</t>
+          <t>linda.lu@ciarrahome.com</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>www.moershu.com</t>
+          <t>+86 1882 9964 960 / +86 1343 2639 580</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
+          <t>www.ciarrahome.com</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Furnishing</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3000 / MOQ 1 Inside view is luxury, i love it</t>
+          <t>300¥ 300pcs</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>20 / MOQ 100 Nice worker answered all questions</t>
+          <t>50¥ 1000pcs</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>500$ 100psc</t>
         </is>
       </c>
     </row>
@@ -2825,48 +3036,57 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>江西荣科新型材料有限公司 (JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD)</t>
+          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lucy Zeng (曾露)</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>+86-13134020034</t>
+          <t>victor@ck-bath.com</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://www.amerdecor.com/</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>18656330093</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://ck-bath.com/</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Building</t>
+          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>80 rmb for 230 meter</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1560 rmb for whole item</t>
+          <t>4500¥</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>4600 rmb</t>
+          <t>8790$</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>250¥/m3</t>
         </is>
       </c>
     </row>
@@ -2874,34 +3094,55 @@
       <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>佛山市旌晨铝门窗有限公司</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>胡光辉</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1525423805@qq.com</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>18128752879</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>佛山市狮山镇谭边工业区崩岗头路四号之一</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Doors</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1p, 10000$m2, very beautiful big red door</t>
         </is>
       </c>
     </row>
@@ -2911,36 +3152,57 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>东风汽车</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+          <t>河南贝迪塑业有限公司 (HENAN BEIDI PLASTIC INDUSTRY CO., LTD.)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>代桂菊 (Cathy Dai)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>cathy@hnbeidi.com</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>+86 151 3737 2072</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>www.baydeegroup.com</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>中国河南省鹤壁市 (HEBI CITY, HENAN PROVINCE, CHINA)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Doors</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50 Yuan 50g (The taste is authentic and aroma is really good</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>150 Yuan, 1 bottle. ( Taste is strong and good</t>
+          <t>1 container (400 square meters), 60 dollars for 1 square meters</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Haven't discussed the prices. Just got the company name list for future referenc</t>
+          <t>Moq is 1 door, 530 RMB for 1 door</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>14400 dollars, moq - 1</t>
         </is>
       </c>
     </row>
@@ -2950,52 +3212,49 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.,LTD.</t>
+          <t>景德镇窑珍陶瓷</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eric Huang</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>13813551160</t>
-        </is>
-      </c>
+          <t>徐云霞</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>www.ycpanel.com</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>#28. Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
-        </is>
-      </c>
+          <t>13697981203</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Decoration</t>
+          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Furnishing</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>100 RMB per sample. The taste is very good</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>150 RMB per sample. The taste is very good</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>250 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -3005,52 +3264,57 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>江西瑞京鸿兴实业有限公司</t>
+          <t>聖羅蘭·衛浴 (Sannora)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>朱友群</t>
+          <t>ALLEN XU (许熙平)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13763963598</t>
+          <t>sales5@sannora.com</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>www.jx-wpc.com</t>
+          <t>+86 137 0224 0244</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>江西省瑞金市经济开发区创业一路东侧</t>
+          <t>www.sannora.com</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Tangxia Ind. Zone, Shishan Town, Nanhai Dist., Foshan, Guangdong, China</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>250¥/м3</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>4500¥</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inqui</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8790$</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inqui</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>I will explore their catalog and website, choose products, then'll make an inqui</t>
         </is>
       </c>
     </row>
@@ -3060,52 +3324,57 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ciarra</t>
+          <t>ZHEJIANG SEATING TECHNOLOGY CO., LTD.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>May Zhang</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>+86 1882 9964 960 / +86 1343 2639 580</t>
+          <t>sales5@anjeurostilefurniture.com</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>www.ciarrahome.com</t>
+          <t>+86 182 5727 1590</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
+          <t>www.zjseating.com</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>Furnishing</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>300¥ 300pcs</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>50¥ 1000pcs</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>500$ 100psc</t>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>550</t>
         </is>
       </c>
     </row>
@@ -3113,54 +3382,35 @@
       <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Anne</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>18656330093</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://ck-bath.com/</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4500¥</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>8790$</t>
+          <t>Prices are go and packing and Verstaliy is more</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>250¥/m3</t>
+          <t>The taste anaroma is good of this product then anyother</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>the product prices are very good. looks attractive</t>
         </is>
       </c>
     </row>
@@ -3170,48 +3420,57 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>佛山市旌晨铝门窗有限公司</t>
+          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>胡光辉</t>
+          <t>Pacao Yin</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>18128752879</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>pin@pingaolao.com</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>(0086)13903035682 / (0086)0769-86378283</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>佛山市狮山镇谭边工业区崩岗头路四号之一</t>
+          <t>www.pingaolao.com / https://dgpingao.1688.com</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Doors</t>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
+          <t>2.5 RMB per unit, MOQ is 500 pieces. The plastic material was high quality and c</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1p, 10000$m2, very beautiful big red door</t>
+          <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this com</t>
         </is>
       </c>
     </row>
@@ -3221,52 +3480,57 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>河南贝迪塑业有限公司 (HENAN BEIDI PLASTIC INDUSTRY CO., LTD.)</t>
+          <t>Chongnuo(Shandong)NewMaterial Co.,Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>代桂菊 (Cathy Dai)</t>
+          <t>Daisy</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>+86 151 3737 2072</t>
+          <t>sales06@chongnuo-floors.com</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>www.baydeegroup.com</t>
+          <t>+86 19906379675</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>中国河南省鹤壁市 (HEBI CITY, HENAN PROVINCE, CHINA)</t>
+          <t>www.chongnuo-floors.com</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Doors</t>
+          <t>Qingyun County, Dezhou City, China</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1 container (400 square meters), 60 dollars for 1 square meters</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Moq is 1 door, 530 RMB for 1 door</t>
+          <t>9$</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>14400 dollars, moq - 1</t>
+          <t>13.25$</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>8.83$</t>
         </is>
       </c>
     </row>
@@ -3276,48 +3540,45 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>佛山市旌晨铝门窗有限公司</t>
+          <t>ZHE JIANG TIANYAN HOLDING LTD</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>张广帅</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>13726358587, 400-9155262</t>
-        </is>
-      </c>
+          <t>NICOLE</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>佛山市狮山镇谭边工业区顾岗头路四号之一</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Doors</t>
+          <t>TAIZHOU, ZHEJIANG</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается </t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается </t>
+          <t>640 PCs, 3.72 RMB very good</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается </t>
+          <t>30 PCs, 420 RMB, need check quality</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>10 PCs, 1150 RMB, very good</t>
         </is>
       </c>
     </row>
@@ -3327,48 +3588,53 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>景德镇窑珍陶瓷</t>
+          <t>中国广东柜邦精密金属制品有限公司 (China Guangdong Guibang Precision Metal Products Co.Ltd)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>徐云霞</t>
+          <t>唐一智 (JUNIOR)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>13697981203</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
-        </is>
-      </c>
+          <t>13621417@QQ.COM</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>+86-156-2562-1155</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Furnishing</t>
+          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>100 RMB per sample. The taste is very good</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>150 RMB per sample. The taste is very good</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>250 RMB per sample. The taste is very good</t>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -3378,36 +3644,57 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>湖北龙王垭茶业有限公司</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+          <t>广东亚当斯金属精密制造有限公司 (Guangdong Adams Metal Precision Manufacturing Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Kelly Liang 梁凯莹</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>kelly@adamsmetal.com.cn</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>+86-180-2935-2895 / +86-757-25331912</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>www.adamsmetal.com.cn</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>498rmb/unit. I like the green tea in white color. First time to see colorless te</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>They have tea perfume bar, which was amazing, moreover, i also love their snacks</t>
+          <t>Depend on item</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>The 中国好水 brand water was really good. They are using deep water instead of shall</t>
+          <t>Depend of quantity</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>100/square meter</t>
         </is>
       </c>
     </row>
@@ -3417,52 +3704,57 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>聖羅蘭·衛浴 (Sannora)</t>
+          <t>多彩帐篷 (DUOCAI TENT)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ALLEN XU (许熙平)</t>
+          <t>Jimmy 黄锦民</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>+86 137 0224 0244</t>
+          <t>sales003@sdduocaizp.com</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>www.sannora.com</t>
+          <t>+86-766-8298662, (86)133 2294 8506</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tangxia Ind. Zone, Shishan Town, Nanhai Dist., Foshan, Guangdong, China</t>
+          <t>www.dc-tent.com, www.sdduocaizp.com</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>广东省云浮市云安区佛山(云浮)产业转移工业园86号 / No.86 Foshan(Yunfu) Industrial transfer park, Yunan, Yunfu, Guangdong, China</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Building</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inqui</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inqui</t>
+          <t>RMB 15705 MOQ5; pleasant impression</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inqui</t>
+          <t>MOQ5 25799 RMB</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>RMB 19479; MOQ 1</t>
         </is>
       </c>
     </row>
@@ -3472,52 +3764,57 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ZHEJIANG SEATING TECHNOLOGY CO., LTD.</t>
+          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd.)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>May Zhang</t>
+          <t>孟少美 (Elie Meng)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>+86 182 5727 1590</t>
+          <t>boilide.hinge@163.comxujianzhai1987@qq.com13621417@qq.comtff@hbtfjs.comkelly@adamsmetal.com.cnjane@dirock.cn</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>www.zjseating.com</t>
+          <t>13103196326</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
+          <t>www.hbtfjs.com</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Furnishing</t>
+          <t>河北省隆尧县公子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -3525,34 +3822,59 @@
       <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>广州蒙娜丽莎卫浴股份有限公司</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>伍乐彤</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>monalisa702@monalisa.cn</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>86 13711117863</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>www.monalisa.cn</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>广州市花都区花东镇港头工业区4号</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Prices are go and packing and Verstaliy is more</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>The taste anaroma is good of this product then anyother</t>
+          <t>2000$, can be customized, very convenient</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>the product prices are very good. looks attractive</t>
+          <t>38$, very unique</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2050 rmb, very interesting, convenient to use for pets</t>
         </is>
       </c>
     </row>
@@ -3562,48 +3884,45 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>佛山市同路匠人家具有限公司</t>
+          <t>广西中晨木业有限公司 (Guangxi Zhongchen Wood Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>蒙玉婷</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>13160953218</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区龙江镇联盟路三路3号9513家具总部</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Furnishing</t>
-        </is>
-      </c>
+          <t>张爱彬 (Zhang Aibin)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>+86 18178085851</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>820 rmb moq 100</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>650 moq 300</t>
+          <t>25 rmb, 1 box, like this product</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>560 moq 200</t>
+          <t>34 rmb, 1000, normal</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>40 rmb, 2000, very good</t>
         </is>
       </c>
     </row>
@@ -3613,52 +3932,57 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
+          <t>浙江安吉双虎竹木业有限公司</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pacao Yin</t>
+          <t>周瑶琳</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>(0086)13903035682 / (0086)0769-86378283</t>
+          <t>lisa.nordi@nuodibm.com</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>www.pingaolao.com / https://dgpingao.1688.com</t>
+          <t>+86-137 3822 8209</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+          <t>www.tigerbamboo.com / www.nuodibm.com</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2.5 RMB per unit, MOQ is 500 pieces. The plastic material was high quality and c</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping</t>
+          <t>1 container 250 rmb</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this com</t>
+          <t>1 container 500 rmb</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>1 container 700 rmb</t>
         </is>
       </c>
     </row>
@@ -3668,627 +3992,55 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>佛山市同路匠人家具有限公司</t>
+          <t>宏宇集团 (HONGYU GROUP)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>肖汝兰</t>
+          <t>Melina 王玲</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>18675197017</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+          <t>lina@hongyugroup.com</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>+86 13827702216</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区龙江镇联盟嘉园三路3号9513家具总部</t>
+          <t>en.hongyugroup.com</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Furnishing</t>
+          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>3 товаров</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1299, MOQ 200. I like the company and people there . Very friendly and know thei</t>
+          <t>3 товаров</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>5000rmb MOQ 50</t>
+          <t>Жду коммерческое предложение. Компания понравилась</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>1500 rmb MOQ 100</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>浙江鑫东洁具有限公司 (ZHEJIANG XINDONG SANITARY WARE CO., LTD.)</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>冯晶晶 Joanna</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>0086-159 9067 6107</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Black matt tap water $20</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Chongnuo(Shandong)NewMaterial Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Daisy</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>+86 19906379675</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>www.chongnuo-floors.com</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Qingyun County, Dezhou City, China</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Decoration</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>9$</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>13.25$</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>8.83$</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>ZHE JIANG TIANYAN HOLDING LTD</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>NICOLE</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>TAIZHOU, ZHEJIANG</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>640 PCs, 3.72 RMB very good</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>30 PCs, 420 RMB, need check quality</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>10 PCs, 1150 RMB, very good</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>中国广东柜邦精密金属制品有限公司 (China Guangdong Guibang Precision Metal Products Co.Ltd)</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>唐一智 (JUNIOR)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>+86-156-2562-1155</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>广东亚当斯金属精密制造有限公司 (Guangdong Adams Metal Precision Manufacturing Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Kelly Liang 梁凯莹</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>+86-180-2935-2895 / +86-757-25331912</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>www.adamsmetal.com.cn</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Depend on item</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Depend of quantity</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>100/square meter</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>多彩帐篷 (DUOCAI TENT)</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Jimmy 黄锦民</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>+86-766-8298662, (86)133 2294 8506</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>www.dc-tent.com, www.sdduocaizp.com</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>广东省云浮市云安区佛山(云浮)产业转移工业园86号 / No.86 Foshan(Yunfu) Industrial transfer park, Yunan, Yunfu, Guangdong, China</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>RMB 15705 MOQ5; pleasant impression</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>MOQ5 25799 RMB</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>RMB 19479; MOQ 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>孟少美 (Elie Meng)</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>13103196326</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>www.hbtfjs.com</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>河北省隆尧县公子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>广州蒙娜丽莎卫浴股份有限公司</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>伍乐彤</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>86 13711117863</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>www.monalisa.cn</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>广州市花都区花东镇港头工业区4号</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2000$, can be customized, very convenient</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>38$, very unique</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>2050 rmb, very interesting, convenient to use for pets</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>广西中晨木业有限公司 (Guangxi Zhongchen Wood Industry Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>张爱彬 (Zhang Aibin)</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>+86 18178085851</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Decoration</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>25 rmb, 1 box, like this product</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>34 rmb, 1000, normal</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>40 rmb, 2000, very good</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>浙江安吉双虎竹木业有限公司</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>周瑶琳</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>+86-137 3822 8209</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>www.tigerbamboo.com / www.nuodibm.com</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Decoration</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1 container 250 rmb</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>1 container 500 rmb</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>1 container 700 rmb</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>宏宇集团 (HONGYU GROUP)</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Melina 王玲</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>+86 13827702216</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>en.hongyugroup.com</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Decoration</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>3 товаров</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Жду коммерческое предложение. Компания понравилась</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
           <t>Цена зависит от обьема, от 3 юаней, расходники</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>Прайс отправят, от 100ед, хорошая компания</t>
         </is>

--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I182"/>
+  <dimension ref="A1:I229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Super | 620 super</t>
+          <t>Super</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>130 super</t>
+          <t>620 super</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>$32, MOQ 300, good</t>
+          <t>1500 super</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>¥3000, MoQ 1pcs, very good</t>
+          <t>130 super</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>¥17, Moq 50, good</t>
+          <t>$32, MOQ 300, good</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>600 RMB Great, very cheap</t>
+          <t>¥3000, MoQ 1pcs, very good</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>800 rmb, little high</t>
+          <t>¥17, Moq 50, good</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3400, Good price</t>
+          <t>600 RMB Great, very cheap</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10$</t>
+          <t>800 rmb, little high</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>69$</t>
+          <t>3400, Good price</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50-85$</t>
+          <t>10$</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>￥1000 good</t>
+          <t>69$</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>¥ 500 good</t>
+          <t>50-85$</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>￥ 300 good</t>
+          <t>￥1000 good</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>300 rmb and more. Good quality and good price. Small quantity</t>
+          <t>¥ 500 good</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>33$ for 1 pcs. Good quality and quantity</t>
+          <t>￥ 300 good</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Good quality and quantity. 140 rmb 1 pcs.</t>
+          <t>300 rmb and more. Good quality and good price. Small quantity</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Good 👍</t>
+          <t>33$ for 1 pcs. Good quality and quantity</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>Good quality and quantity. 140 rmb 1 pcs.</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>Good 👍</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>130 yuan | 1410</t>
+          <t>1570</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>20000usd</t>
+          <t>5800</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>500yuan</t>
+          <t>130 yuan</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>MOQ 100, 47 rnb per piece</t>
+          <t>20000usd</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>MOQ 50, 200 rnb per</t>
+          <t>500yuan</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>MOQ 10, 845 per piece | 800usd, very nice, good quality product</t>
+          <t>MOQ 100, 47 rnb per piece</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1pcs. Start from 60rmb. Novative technology</t>
+          <t>MOQ 50, 200 rnb per</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>From 1pc. Natural materials.</t>
+          <t>MOQ 10, 845 per piece</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1250rmb. MOQ 1 pc</t>
+          <t>1pcs. Start from 60rmb. Novative technology</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>From 1pc. Natural materials.</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1410 | 199</t>
+          <t>1250rmb. MOQ 1 pc</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>399</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>199</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>1410</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>150 yuan, 100, good range of products</t>
+          <t>329</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
+          <t>229</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+          <t>680</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+          <t>150 yuan, 100, good range of products</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>I couldn't tell you the price for smart pens right away, but they said they would send a catalogue with prices to Wechat</t>
+          <t>800usd, very nice, good quality product</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет пр</t>
+          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>330 юаней. 500 штук минималка . Качественный , магнитный умный переключатель с емкой батареей . Опять же проблема с ПО .</t>
+          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
+          <t>I couldn't tell you the price for smart pens right away, but they said they would send a catalogue with prices to Wechat</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного метра 150 юаней сказала примерно. Не до </t>
+          <t>199</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккура</t>
+          <t>320</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккуратно. Хорошее решение для сушки белья и </t>
+          <t>1410</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет пр</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very go</t>
+          <t>330 юаней. 500 штук минималка . Качественный , магнитный умный переключатель с емкой батареей . Опять же проблема с ПО .</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
+          <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>600</t>
+          <t xml:space="preserve">Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного метра 150 юаней сказала примерно. Не до </t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккура</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккуратно. Хорошее решение для сушки белья и </t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>0.6 usd/m2</t>
+          <t>2900 usd</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Under negotiation, great opportunities</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1-5 usd/l</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very go</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>679 rmb</t>
+          <t>MOQ 1, they got samples. 8000usd. Very well made product, trendy and popular. This capsules houses very affordable.</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>59 rmb</t>
+          <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>249RMB</t>
+          <t>600</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>6000RMB</t>
+          <t>500</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2000RMB&amp;gt;</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>MOQ - 5000 and price - 7000 dollars | 3000 USD | 2147</t>
+          <t>0.6 usd/m2</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>3000 dollars</t>
+          <t>Under negotiation, great opportunities</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>The price cheap, merchant very friendly</t>
+          <t>1-5 usd/l</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>The price more cheaper, good quality</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Good merchant, perfect products</t>
+          <t>679 rmb</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
+          <t>59 rmb</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>15 RMB the product is interesting</t>
+          <t>249RMB</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>nearly $15,000 for this production line</t>
+          <t>6000RMB</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>2000RMB&amp;gt;</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>MOQ - 5000 and price - 7000 dollars</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>5000 USD | 2085 | 2223</t>
+          <t>4000$</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>6000 RMB. I like the way they explain everything about their product.</t>
+          <t>3000 dollars</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
+          <t>The price cheap, merchant very friendly</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>249 RMB. They have fully described their products. | 249RMB , 价格很便宜</t>
+          <t>The price more cheaper, good quality</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>6000RMB，积极，详细地告诉了一切</t>
+          <t>Good merchant, perfect products</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2000 RMB</t>
+          <t>160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>400rmb /m2 good meeting | 400rmb/m2</t>
+          <t>15 RMB the product is interesting</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>350 rmb/m2 | 350rmb/m2</t>
+          <t>nearly $15,000 for this production line</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>20 / MOQ 100 Nice worker answered all questions</t>
+          <t>249</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>80 rmb for 230 meter</t>
+          <t>749</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1560 rmb for whole item</t>
+          <t>5000 USD</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>4600 rmb</t>
+          <t>3000 USD</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>3000 USD</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>6000 RMB. I like the way they explain everything about their product.</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>50 Yuan 50g (The taste is authentic and aroma is really good</t>
+          <t>249 RMB. They have fully described their products.</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>250¥/м3 | 250¥/m3</t>
+          <t>6000RMB，积极，详细地告诉了一切</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>4500¥ | 4500¥</t>
+          <t>249RMB , 价格很便宜</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>300¥ 300pcs</t>
+          <t>2000 RMB</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>50¥ 1000pcs</t>
+          <t>400rmb /m2 good meeting</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>500$ 100psc</t>
+          <t>350 rmb/m2</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
+          <t>MOQ 5000 pieces</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
+          <t>400rmb/m2</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
+          <t>350rmb/m2</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
+          <t>MOQ 5000 pieces</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>100 RMB per sample. The taste is very good</t>
+          <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>150 RMB per sample. The taste is very good</t>
+          <t>3000 / MOQ 1 Inside view is luxury, i love it</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>250 RMB per sample. The taste is very good</t>
+          <t>20 / MOQ 100 Nice worker answered all questions</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>498rmb/unit. I like the green tea in white color. First time to see colorless tea and it was amazing, i will recommend i</t>
+          <t>80 rmb for 230 meter</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea. | The 中国好水 brand water w</t>
+          <t>1560 rmb for whole item</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>4600 rmb</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>50 Yuan 50g (The taste is authentic and aroma is really good</t>
         </is>
       </c>
     </row>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Prices are go and packing and Verstaliy is more</t>
+          <t>150 Yuan, 1 bottle. ( Taste is strong and good</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>The taste anaroma is good of this product then anyother</t>
+          <t>Haven't discussed the prices. Just got the company name list for future reference</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>the product prices are very good. looks attractive</t>
+          <t>2085</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>650 moq 300</t>
+          <t>2147</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>560 moq 200</t>
+          <t>2223</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
+          <t>250¥/м3</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
+          <t>4500¥</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>20 | Жду коммерческое предложение. Компания понравилась</t>
+          <t>8790$</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>300¥ 300pcs</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>9$</t>
+          <t>50¥ 1000pcs</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>13.25$</t>
+          <t>500$ 100psc</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>8.83$</t>
+          <t>4500¥</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>640 PCs, 3.72 RMB very good</t>
+          <t>8790$</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>30 PCs, 420 RMB, need check quality</t>
+          <t>250¥/m3</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>10 PCs, 1150 RMB, very good</t>
+          <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1p, 10000$m2, very beautiful big red door</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1 container (400 square meters), 60 dollars for 1 square meters</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Depend on item</t>
+          <t>Moq is 1 door, 530 RMB for 1 door</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Depend of quantity</t>
+          <t>14400 dollars, moq - 1</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>100/square meter</t>
+          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>RMB 15705 MOQ5; pleasant impression</t>
+          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
         </is>
       </c>
     </row>
@@ -6795,7 +6795,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>MOQ5 25799 RMB</t>
+          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>RMB 19479; MOQ 1</t>
+          <t>100 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>150 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>250 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>498rmb/unit. I like the green tea in white color. First time to see colorless tea and it was amazing, i will recommend i</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2000$, can be customized, very convenient</t>
+          <t>They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>38$, very unique</t>
+          <t>The 中国好水 brand water was really good. They are using deep water instead of shallow water (used by nongfu), and trace min</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2050 rmb, very interesting, convenient to use for pets</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>25 rmb, 1 box, like this product | 1 container 500 rmb</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7188,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>34 rmb, 1000, normal</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>40 rmb, 2000, very good</t>
+          <t>1100</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>1 container 250 rmb</t>
+          <t>1050</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Цена зависит от обьема, от 3 юаней, расходники</t>
+          <t>550</t>
         </is>
       </c>
     </row>
@@ -7348,9 +7348,984 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
+          <t>Prices are go and packing and Verstaliy is more</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>The taste anaroma is good of this product then anyother</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>the product prices are very good. looks attractive</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>820 rmb moq 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>650 moq 300</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>560 moq 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>2.5 RMB per unit, MOQ is 500 pieces. The plastic material was high quality and company was willing to provide samples on</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1299, MOQ 200. I like the company and people there . Very friendly and know their products very good . I would be happy </t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>5000rmb MOQ 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>1500 rmb MOQ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Black matt tap water $20</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>9$</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>13.25$</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>8.83$</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>640 PCs, 3.72 RMB very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>30 PCs, 420 RMB, need check quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>10 PCs, 1150 RMB, very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Depend on item</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Depend of quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>100/square meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>RMB 15705 MOQ5; pleasant impression</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>MOQ5 25799 RMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>RMB 19479; MOQ 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>2000$, can be customized, very convenient</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>38$, very unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>2050 rmb, very interesting, convenient to use for pets</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>25 rmb, 1 box, like this product</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>34 rmb, 1000, normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>40 rmb, 2000, very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>1 container 250 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>1 container 500 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>1 container 700 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Жду коммерческое предложение. Компания понравилась</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Цена зависит от обьема, от 3 юаней, расходники</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
           <t>Прайс отправят, от 100ед, хорошая компания</t>
         </is>
       </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I229"/>
+  <dimension ref="A1:I183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,11 +590,7 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Supplier_Row3_1</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -647,7 +643,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -836,7 +832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -861,7 +857,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1046,7 +1042,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1132,7 +1128,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1145,11 +1141,7 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Supplier_Row8_1</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1444,7 +1436,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1530,7 +1522,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1575,7 +1567,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1657,7 +1649,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Furniture &amp; Custom Home</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1739,7 +1731,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Furniture &amp; Custom Home</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1995,7 +1987,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>620 super</t>
+          <t>130 super</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2028,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1500 super</t>
+          <t>$32, MOQ 300, good</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2073,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>130 super</t>
+          <t>¥3000, MoQ 1pcs, very good</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2118,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>$32, MOQ 300, good</t>
+          <t>¥17, Moq 50, good</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2163,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>¥3000, MoQ 1pcs, very good</t>
+          <t>600 RMB Great, very cheap</t>
         </is>
       </c>
     </row>
@@ -2179,11 +2171,7 @@
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Supplier_Row17_2</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -2196,7 +2184,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>¥17, Moq 50, good</t>
+          <t>800 rmb, little high</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2213,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>600 RMB Great, very cheap</t>
+          <t>3400, Good price</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2254,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>800 rmb, little high</t>
+          <t>10$</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2299,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3400, Good price</t>
+          <t>69$</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2340,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10$</t>
+          <t>50-85$</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2377,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>69$</t>
+          <t>￥1000 good</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2422,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>50-85$</t>
+          <t>¥ 500 good</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2467,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>￥1000 good</t>
+          <t>￥ 300 good</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2500,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>¥ 500 good</t>
+          <t>300 rmb and more. Good quality and good price. Small quantity</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2545,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>￥ 300 good</t>
+          <t>33$ for 1 pcs. Good quality and quantity</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2578,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>300 rmb and more. Good quality and good price. Small quantity</t>
+          <t>Good quality and quantity. 140 rmb 1 pcs.</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2611,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>33$ for 1 pcs. Good quality and quantity</t>
+          <t>Good 👍</t>
         </is>
       </c>
     </row>
@@ -2631,11 +2619,7 @@
       <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Supplier_Row21_2</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
@@ -2648,7 +2632,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Good quality and quantity. 140 rmb 1 pcs.</t>
+          <t>1570</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2677,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Good 👍</t>
+          <t>5800</t>
         </is>
       </c>
     </row>
@@ -2733,12 +2717,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>130 yuan</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2767,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>20000usd</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2812,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>130 yuan</t>
+          <t>500yuan</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2857,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>20000usd</t>
+          <t>MOQ 100, 47 rnb per piece</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2898,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>500yuan</t>
+          <t>MOQ 50, 200 rnb per</t>
         </is>
       </c>
     </row>
@@ -2954,12 +2938,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Furniture &amp; Custom Home</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>MOQ 100, 47 rnb per piece</t>
+          <t>MOQ 10, 845 per piece</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2983,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>MOQ 50, 200 rnb per</t>
+          <t>1pcs. Start from 60rmb. Novative technology</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3013,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>MOQ 10, 845 per piece</t>
+          <t>From 1pc. Natural materials.</t>
         </is>
       </c>
     </row>
@@ -3049,12 +3033,12 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Furniture &amp; Custom Home</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1pcs. Start from 60rmb. Novative technology</t>
+          <t>1250rmb. MOQ 1 pc</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3058,12 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>From 1pc. Natural materials.</t>
+          <t>199</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3104,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1250rmb. MOQ 1 pc</t>
+          <t>1410</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3144,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>329</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3190,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>229</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3222,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>680</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3272,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>150 yuan, 100, good range of products</t>
         </is>
       </c>
     </row>
@@ -3328,12 +3312,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Furniture &amp; Custom Home</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3342,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
         </is>
       </c>
     </row>
@@ -3394,12 +3378,12 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>150 yuan, 100, good range of products</t>
+          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
         </is>
       </c>
     </row>
@@ -3407,11 +3391,7 @@
       <c r="A78" t="n">
         <v>77</v>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Supplier_Row28_3</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -3419,12 +3399,12 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>800usd, very nice, good quality product</t>
+          <t>I couldn't tell you the price for smart pens right away, but they said they would send a catalogue with prices to Wechat</t>
         </is>
       </c>
     </row>
@@ -3432,11 +3412,7 @@
       <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Supplier_Row29_2</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -3449,7 +3425,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
+          <t>320</t>
         </is>
       </c>
     </row>
@@ -3485,12 +3461,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+          <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет пр</t>
         </is>
       </c>
     </row>
@@ -3498,11 +3474,7 @@
       <c r="A81" t="n">
         <v>80</v>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Supplier_Row30_2</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -3515,7 +3487,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+          <t>330 юаней. 500 штук минималка . Качественный , магнитный умный переключатель с емкой батареей . Опять же проблема с ПО .</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3528,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>I couldn't tell you the price for smart pens right away, but they said they would send a catalogue with prices to Wechat</t>
+          <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3573,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>199</t>
+          <t xml:space="preserve">Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного метра 150 юаней сказала примерно. Не до </t>
         </is>
       </c>
     </row>
@@ -3638,7 +3610,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккура</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3635,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t xml:space="preserve">От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккуратно. Хорошее решение для сушки белья и </t>
         </is>
       </c>
     </row>
@@ -3708,7 +3680,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет пр</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3725,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>330 юаней. 500 штук минималка . Качественный , магнитный умный переключатель с емкой батареей . Опять же проблема с ПО .</t>
+          <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very go</t>
         </is>
       </c>
     </row>
@@ -3761,11 +3733,7 @@
       <c r="A88" t="n">
         <v>87</v>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Supplier_Row33_3</t>
-        </is>
-      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
@@ -3782,7 +3750,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
+          <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3795,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного метра 150 юаней сказала примерно. Не до </t>
+          <t>600</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3820,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккура</t>
+          <t>500</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3845,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккуратно. Хорошее решение для сушки белья и </t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3890,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2900 usd</t>
+          <t>0.6 usd/m2</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3935,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Under negotiation, great opportunities</t>
         </is>
       </c>
     </row>
@@ -4004,7 +3972,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1-5 usd/l</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4005,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very go</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4030,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>MOQ 1, they got samples. 8000usd. Very well made product, trendy and popular. This capsules houses very affordable.</t>
+          <t>679 rmb</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4059,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
+          <t>59 rmb</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4088,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>249RMB</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4129,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>6000RMB</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4162,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2000RMB&amp;gt;</t>
         </is>
       </c>
     </row>
@@ -4230,12 +4198,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>0.6 usd/m2</t>
+          <t>MOQ - 5000 and price - 7000 dollars</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4248,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Under negotiation, great opportunities</t>
+          <t>3000 dollars</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4289,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1-5 usd/l</t>
+          <t>The price cheap, merchant very friendly</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4330,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>The price more cheaper, good quality</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4375,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>679 rmb</t>
+          <t>Good merchant, perfect products</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4420,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>59 rmb</t>
+          <t>160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4465,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>249RMB</t>
+          <t>15 RMB the product is interesting</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4510,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>6000RMB</t>
+          <t>nearly $15,000 for this production line</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4555,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2000RMB&amp;gt;</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4596,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>MOQ - 5000 and price - 7000 dollars</t>
+          <t>749</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4641,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>4000$</t>
+          <t>5000 USD</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4670,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>3000 dollars</t>
+          <t>6000 RMB. I like the way they explain everything about their product.</t>
         </is>
       </c>
     </row>
@@ -4730,12 +4698,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>The price cheap, merchant very friendly</t>
+          <t>Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
         </is>
       </c>
     </row>
@@ -4763,12 +4731,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Furniture &amp; Custom Home</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>The price more cheaper, good quality</t>
+          <t>249 RMB. They have fully described their products.</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4769,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Good merchant, perfect products</t>
+          <t>6000RMB，积极，详细地告诉了一切</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4798,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
+          <t>2000 RMB</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4839,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>15 RMB the product is interesting</t>
+          <t>400rmb /m2 good meeting</t>
         </is>
       </c>
     </row>
@@ -4903,12 +4871,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Furniture &amp; Custom Home</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>nearly $15,000 for this production line</t>
+          <t>350 rmb/m2</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4921,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4957,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>20 / MOQ 100 Nice worker answered all questions</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5003,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>80 rmb for 230 meter</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5044,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>5000 USD</t>
+          <t>1560 rmb for whole item</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5089,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>3000 USD</t>
+          <t>4600 rmb</t>
         </is>
       </c>
     </row>
@@ -5129,11 +5097,7 @@
       <c r="A124" t="n">
         <v>123</v>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Supplier_Row49_1</t>
-        </is>
-      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
@@ -5146,7 +5110,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>3000 USD</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -5154,11 +5118,7 @@
       <c r="A125" t="n">
         <v>124</v>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Supplier_Row49_2</t>
-        </is>
-      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
@@ -5171,7 +5131,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>6000 RMB. I like the way they explain everything about their product.</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -5179,11 +5139,7 @@
       <c r="A126" t="n">
         <v>125</v>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Supplier_Row49_3</t>
-        </is>
-      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
@@ -5196,7 +5152,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5177,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>249 RMB. They have fully described their products.</t>
+          <t>50 Yuan 50g (The taste is authentic and aroma is really good</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5218,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>6000RMB，积极，详细地告诉了一切</t>
+          <t>250¥/м3</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5263,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>249RMB , 价格很便宜</t>
+          <t>4500¥</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5308,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2000 RMB</t>
+          <t>300¥ 300pcs</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5349,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>400rmb /m2 good meeting</t>
+          <t>50¥ 1000pcs</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5394,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>350 rmb/m2</t>
+          <t>500$ 100psc</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5435,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>MOQ 5000 pieces</t>
+          <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5475,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>400rmb/m2</t>
+          <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5509,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>350rmb/m2</t>
+          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5534,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>MOQ 5000 pieces</t>
+          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5571,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
+          <t>100 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5608,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>3000 / MOQ 1 Inside view is luxury, i love it</t>
+          <t>150 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5633,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>20 / MOQ 100 Nice worker answered all questions</t>
+          <t>250 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5658,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>80 rmb for 230 meter</t>
+          <t>498rmb/unit. I like the green tea in white color. First time to see colorless tea and it was amazing, i will recommend i</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5691,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1560 rmb for whole item</t>
+          <t>They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5736,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>4600 rmb</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5777,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5818,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5863,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>1100</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5908,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>50 Yuan 50g (The taste is authentic and aroma is really good</t>
+          <t>1050</t>
         </is>
       </c>
     </row>
@@ -5977,7 +5933,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>150 Yuan, 1 bottle. ( Taste is strong and good</t>
+          <t>Prices are go and packing and Verstaliy is more</t>
         </is>
       </c>
     </row>
@@ -6002,7 +5958,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Haven't discussed the prices. Just got the company name list for future reference</t>
+          <t>The taste anaroma is good of this product then anyother</t>
         </is>
       </c>
     </row>
@@ -6027,7 +5983,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>the product prices are very good. looks attractive</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6024,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>650 moq 300</t>
         </is>
       </c>
     </row>
@@ -6076,11 +6032,7 @@
       <c r="A151" t="n">
         <v>150</v>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Supplier_Row63_3</t>
-        </is>
-      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
@@ -6093,7 +6045,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>560 moq 200</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6086,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>250¥/м3</t>
+          <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6123,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>4500¥</t>
+          <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6168,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8790$</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -6224,11 +6176,7 @@
       <c r="A155" t="n">
         <v>154</v>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Supplier_Row66_3</t>
-        </is>
-      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
@@ -6241,7 +6189,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>300¥ 300pcs</t>
+          <t>109</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6234,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>50¥ 1000pcs</t>
+          <t>9$</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6271,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>500$ 100psc</t>
+          <t>13.25$</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6312,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>4500¥</t>
+          <t>8.83$</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6345,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>8790$</t>
+          <t>640 PCs, 3.72 RMB very good</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6386,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>250¥/m3</t>
+          <t>30 PCs, 420 RMB, need check quality</t>
         </is>
       </c>
     </row>
@@ -6446,11 +6394,7 @@
       <c r="A161" t="n">
         <v>160</v>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Supplier_Row68_3</t>
-        </is>
-      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
@@ -6463,7 +6407,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
+          <t>10 PCs, 1150 RMB, very good</t>
         </is>
       </c>
     </row>
@@ -6499,12 +6443,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6489,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>1p, 10000$m2, very beautiful big red door</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6530,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>1 container (400 square meters), 60 dollars for 1 square meters</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -6626,12 +6570,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Moq is 1 door, 530 RMB for 1 door</t>
+          <t>Depend on item</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6604,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>14400 dollars, moq - 1</t>
+          <t>Depend of quantity</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6644,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
+          <t>100/square meter</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6694,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
+          <t>RMB 15705 MOQ5; pleasant impression</t>
         </is>
       </c>
     </row>
@@ -6795,7 +6739,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
+          <t>MOQ5 25799 RMB</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6784,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>100 RMB per sample. The taste is very good</t>
+          <t>RMB 19479; MOQ 1</t>
         </is>
       </c>
     </row>
@@ -6880,12 +6824,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>150 RMB per sample. The taste is very good</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6874,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>250 RMB per sample. The taste is very good</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -6970,12 +6914,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>498rmb/unit. I like the green tea in white color. First time to see colorless tea and it was amazing, i will recommend i</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -7020,7 +6964,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
+          <t>2000$, can be customized, very convenient</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7009,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>The 中国好水 brand water was really good. They are using deep water instead of shallow water (used by nongfu), and trace min</t>
+          <t>38$, very unique</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7054,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>2050 rmb, very interesting, convenient to use for pets</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7087,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>25 rmb, 1 box, like this product</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7132,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>34 rmb, 1000, normal</t>
         </is>
       </c>
     </row>
@@ -7228,12 +7172,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>40 rmb, 2000, very good</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7222,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1 container 250 rmb</t>
         </is>
       </c>
     </row>
@@ -7288,32 +7232,32 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ZHEJIANG TIANYAN HOLDING CO.,LTD.</t>
+          <t>宏宇集团 HONGYU GROUP</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Nicole</t>
+          <t>Melina 王玲</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ty11@cntianyan.com</t>
+          <t>lina@hongyugroup.com</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>+86-15867028552</t>
+          <t>+86 13827702216</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>www.cntianyan.com</t>
+          <t>en.hongyugroup.com</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Chengjiang industrial zone,huangyan district taizhou,zhejiang,china</t>
+          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -7323,7 +7267,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>Жду коммерческое предложение. Компания понравилась</t>
         </is>
       </c>
     </row>
@@ -7333,14 +7277,34 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>BANRUGE / KING LIYE</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
+          <t>ZHEJIANG TIANYAN HOLDING CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ty11@cntianyan.com</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>+86-15867028552</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>www.cntianyan.com</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Chengjiang industrial zone,huangyan district taizhou,zhejiang,china</t>
+        </is>
+      </c>
       <c r="H182" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -7348,7 +7312,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Prices are go and packing and Verstaliy is more</t>
+          <t>Цена зависит от обьема, от 3 юаней, расходники</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7320,11 @@
       <c r="A183" t="n">
         <v>182</v>
       </c>
-      <c r="B183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>BANRUGE / KING LIYE</t>
+        </is>
+      </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
@@ -7364,968 +7332,14 @@
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>The taste anaroma is good of this product then anyother</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>183</v>
-      </c>
-      <c r="B184" t="inlineStr"/>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>the product prices are very good. looks attractive</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>184</v>
-      </c>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>820 rmb moq 100</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>185</v>
-      </c>
-      <c r="B186" t="inlineStr"/>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>650 moq 300</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>186</v>
-      </c>
-      <c r="B187" t="inlineStr"/>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>560 moq 200</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>187</v>
-      </c>
-      <c r="B188" t="inlineStr"/>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>2.5 RMB per unit, MOQ is 500 pieces. The plastic material was high quality and company was willing to provide samples on</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>188</v>
-      </c>
-      <c r="B189" t="inlineStr"/>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>189</v>
-      </c>
-      <c r="B190" t="inlineStr"/>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>190</v>
-      </c>
-      <c r="B191" t="inlineStr"/>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1299, MOQ 200. I like the company and people there . Very friendly and know their products very good . I would be happy </t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>191</v>
-      </c>
-      <c r="B192" t="inlineStr"/>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>5000rmb MOQ 50</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>192</v>
-      </c>
-      <c r="B193" t="inlineStr"/>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>1500 rmb MOQ 100</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>193</v>
-      </c>
-      <c r="B194" t="inlineStr"/>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>Black matt tap water $20</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>194</v>
-      </c>
-      <c r="B195" t="inlineStr"/>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>195</v>
-      </c>
-      <c r="B196" t="inlineStr"/>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>196</v>
-      </c>
-      <c r="B197" t="inlineStr"/>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>9$</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>197</v>
-      </c>
-      <c r="B198" t="inlineStr"/>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>13.25$</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>198</v>
-      </c>
-      <c r="B199" t="inlineStr"/>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>8.83$</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>199</v>
-      </c>
-      <c r="B200" t="inlineStr"/>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>640 PCs, 3.72 RMB very good</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>200</v>
-      </c>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>30 PCs, 420 RMB, need check quality</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>201</v>
-      </c>
-      <c r="B202" t="inlineStr"/>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>10 PCs, 1150 RMB, very good</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>202</v>
-      </c>
-      <c r="B203" t="inlineStr"/>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>203</v>
-      </c>
-      <c r="B204" t="inlineStr"/>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>204</v>
-      </c>
-      <c r="B205" t="inlineStr"/>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>205</v>
-      </c>
-      <c r="B206" t="inlineStr"/>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>Depend on item</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>206</v>
-      </c>
-      <c r="B207" t="inlineStr"/>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>Depend of quantity</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
-        <v>207</v>
-      </c>
-      <c r="B208" t="inlineStr"/>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>100/square meter</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
-        <v>208</v>
-      </c>
-      <c r="B209" t="inlineStr"/>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>RMB 15705 MOQ5; pleasant impression</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>209</v>
-      </c>
-      <c r="B210" t="inlineStr"/>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>MOQ5 25799 RMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>210</v>
-      </c>
-      <c r="B211" t="inlineStr"/>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>RMB 19479; MOQ 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>211</v>
-      </c>
-      <c r="B212" t="inlineStr"/>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>212</v>
-      </c>
-      <c r="B213" t="inlineStr"/>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>213</v>
-      </c>
-      <c r="B214" t="inlineStr"/>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>214</v>
-      </c>
-      <c r="B215" t="inlineStr"/>
-      <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>2000$, can be customized, very convenient</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>215</v>
-      </c>
-      <c r="B216" t="inlineStr"/>
-      <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>38$, very unique</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>216</v>
-      </c>
-      <c r="B217" t="inlineStr"/>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>2050 rmb, very interesting, convenient to use for pets</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="n">
-        <v>217</v>
-      </c>
-      <c r="B218" t="inlineStr"/>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>25 rmb, 1 box, like this product</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
-        <v>218</v>
-      </c>
-      <c r="B219" t="inlineStr"/>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>34 rmb, 1000, normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
-        <v>219</v>
-      </c>
-      <c r="B220" t="inlineStr"/>
-      <c r="C220" t="inlineStr"/>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>40 rmb, 2000, very good</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
-        <v>220</v>
-      </c>
-      <c r="B221" t="inlineStr"/>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>1 container 250 rmb</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
-        <v>221</v>
-      </c>
-      <c r="B222" t="inlineStr"/>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>1 container 500 rmb</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
-        <v>222</v>
-      </c>
-      <c r="B223" t="inlineStr"/>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>1 container 700 rmb</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
-        <v>223</v>
-      </c>
-      <c r="B224" t="inlineStr"/>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>Жду коммерческое предложение. Компания понравилась</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
-        <v>224</v>
-      </c>
-      <c r="B225" t="inlineStr"/>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>Цена зависит от обьема, от 3 юаней, расходники</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
-        <v>225</v>
-      </c>
-      <c r="B226" t="inlineStr"/>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
           <t>Прайс отправят, от 100ед, хорошая компания</t>
         </is>
       </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
-        <v>226</v>
-      </c>
-      <c r="B227" t="inlineStr"/>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
-        <v>227</v>
-      </c>
-      <c r="B228" t="inlineStr"/>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" t="n">
-        <v>228</v>
-      </c>
-      <c r="B229" t="inlineStr"/>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,12 +467,36 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sunhohi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Crystal Wong</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>crystal@sunhohiglobal.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>+86-137 0262 5097</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>www.sunhohiwindow.com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Marketing Center: 20th Floor, Building A1, Full International Financial Center, No. 28, Haiwu Road, Guicheng Street, Nanhai District, Foshan City, Guangdong Province, China; Factory: Zhenxing 3rd Road, Xincheng Town, Xinxing County, Yunfu City, Guangdong Province, China</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -480,7 +504,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>500 pcs price 58 usd</t>
+          <t>50.000¥. Moq-1</t>
         </is>
       </c>
     </row>
@@ -490,22 +514,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HDL</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>Guangdong Fuson Windoor Industry Co., Ltd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Eileen Yip (叶颖怡)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>export09@fusonwindoor.com</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>+86 18028156982</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>www.fusonwindoor.com</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fuxuan Office Building, 2nd Longhu Rd, High Tech District, Zhaoqing City, Guangdong Province</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20pcs / $100USD for pcs</t>
+          <t>50.000¥. Moq-1</t>
         </is>
       </c>
     </row>
@@ -513,20 +557,32 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>开平艺和门业有限公司</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>张硕怡 (Stoney)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>134 1416 0636</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>50.000¥. Moq-1</t>
         </is>
       </c>
     </row>
@@ -547,7 +603,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>800 rmb, little high</t>
+          <t>500 pcs price 58 usd</t>
         </is>
       </c>
     </row>
@@ -557,18 +613,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>艾锐特</t>
+          <t>河南贝迪塑业有限公司 (Henan Beidi Plastic Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>冯蕾</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>Jane Li (李蓉娟)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jane@hncrown.com</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+86 187 3917 6242 / 86-0372-6270170</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>www.baydeegroup.com / www.hnbeidi.com</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>中国·河南省鹤壁市 (Hebi City, Henan Province, China)</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -576,7 +648,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3400, Good price</t>
+          <t>1000 pcs price 38 USD</t>
         </is>
       </c>
     </row>
@@ -584,12 +656,36 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Guangzhou NewHoo Technology Co. Ltd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tony</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>export01@gznewhoo.com</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+86-198-7837-3626</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>www.gznewhoo.com</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Building 7, Hongyu Smart Industrial Park, No. 333 Juhuashi Avenue, Huadu District, Guangzhou</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -597,7 +693,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>80$</t>
         </is>
       </c>
     </row>
@@ -607,42 +703,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CAE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Jack Guan</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>jack@cae.cn</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>+86-750-8119338</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>www.cae.cn</t>
-        </is>
-      </c>
+          <t>旭博卫浴</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
+          <t>福建省南安市</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150 yuan, 100, good range of products</t>
+          <t>70$</t>
         </is>
       </c>
     </row>
@@ -650,7 +730,11 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>旭博恒温</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -658,12 +742,12 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>I couldn't tell you the price for smart pens right away, but they said they would send a catalogue with prices to Wechat</t>
+          <t>300 yuan</t>
         </is>
       </c>
     </row>
@@ -671,20 +755,44 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>榜威电子科技（上海）有限公司 (Bweetech Electronics Technology (Shanghai) Co., Ltd)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>骆剑 (Kim Lok)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>kim.lok@bweetech.com</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>186-5759-0678</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>www.bweetech.com</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>500pcs / $100USD for pcs</t>
         </is>
       </c>
     </row>
@@ -692,7 +800,11 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>深圳市塞恩斯电子有限公司 (Sands Evermore Electronic)</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -700,12 +812,12 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>330 юаней. 500 штук минималка . Качественный , магнитный умный переключатель с емкой батареей . Опять же проблема с ПО .</t>
+          <t>50pcs / $50USD for pcs</t>
         </is>
       </c>
     </row>
@@ -713,14 +825,14 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HDL</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>15916159866</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -730,7 +842,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
+          <t>20pcs / $100USD for pcs</t>
         </is>
       </c>
     </row>
@@ -740,22 +852,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>欧派</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+          <t>DEIOUX WINDOWS &amp; DOORS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CANDICE CHOU</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sales5@deiouxwindows.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>+86-13392246940</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>679 rmb</t>
+          <t>Custom order</t>
         </is>
       </c>
     </row>
@@ -763,20 +891,40 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>China Warren Windows and Doors Co., Ltd.</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>info@warrenwindows.com</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>+86-400-811-0300</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>www.warrenwindows.com</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Room 1007, Block B, Wangjing SOHO, Chaoyang District, Beijing, China</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Custom order</t>
         </is>
       </c>
     </row>
@@ -784,20 +932,32 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Matthew window&amp;door</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>张小洪 (Matthew / Kevin)</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Foshan, Guangdong</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Custom order</t>
         </is>
       </c>
     </row>
@@ -805,20 +965,44 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Zhongshan Smartek Security Technology Co.,LTD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tim Pan</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>market@smarteklock.com</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>+86-15889896019</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>www.smarteklock.com</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City Guangdong, China 528415</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>170 to 335 usd</t>
         </is>
       </c>
     </row>
@@ -828,13 +1012,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>武夷星</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+          <t>HDL Automation Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Krystal Wei</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>krystal@hdlautomation.com</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>+86 19512956186</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>www.hdlautomation.com</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
@@ -843,7 +1043,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>250 RMB per sample. The taste is very good</t>
+          <t>100 to up</t>
         </is>
       </c>
     </row>
@@ -851,20 +1051,44 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ningbo AIFEIBAO Intelligent Security Co., Ltd</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sean Xiao</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>sales@aifeibao.com</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0086 198 1730 8681</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>www.afbsafe.com</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No.1 Donghu Rd., Daxie Development Zone, Ningbo, China (315812)</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>560 moq 200</t>
+          <t>100 to up usd</t>
         </is>
       </c>
     </row>
@@ -885,7 +1109,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>Super</t>
         </is>
       </c>
     </row>
@@ -893,12 +1117,28 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>佛山市普辉亚科技有限公司 (Foshan Pu Huiya Technology Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>邹隆鹏</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>15818099349</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -906,7 +1146,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10 PCs, 1150 RMB, very good</t>
+          <t>Super</t>
         </is>
       </c>
     </row>
@@ -914,52 +1154,5993 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>广东招材建材科技有限公司</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>黎桃桃</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>toto.liblun@gmail.com</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>+8618934320539</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>www.liblun.com</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Super</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>浙江鑫东洁具有限公司 (ZHEJIANG XINDONG SANITARY WARE CO., LTD.)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>曾燕燕 Elyn</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>sales03@cn-xindong.com</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0086-182 5765 3405, 0086-576-87493988</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>杭州南博装饰材料有限公司</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>王小忠</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>浙江省杭州市临平区运河街道育士路53-1号</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>台州旭升卫浴股份有限公司</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>应杨军</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3572780651@qq.com</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>13511470999</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>www.xs88.cn</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>浙江省台州市台州湾新区海虹大道228#</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NIFO 耐孚</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>顾鹏</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>962460053@qq.com</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>13326792105</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Wall sheet , 200 rmb per meter , 2000 mtr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Zhejiang Oushe Home Improvement And New Materials Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Davis Dong 董伟杰</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>sales05@authoe.com</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>+86-18906831082</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Jiaxing/Hongkong</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Handles , 500 moq , 100 rmb per handle</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JIN OGMEI</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Alex Xing</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>kindeli1771@gmail.com</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>+86-18302200384</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Shijiazhuang City, Hebei Province</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>温州金锏智能锁具有限公司</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>张丽</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>jinjian19@jinjianlock.com</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>15067804393</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>www.jinjianlock.com</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>上海世灿国际贸易有限公司</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>杨苗</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>yangm618@163.com</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>138 1618 4706</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>http://www.shicanchina.com</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>上海市浦东新区商城路889号C3-B06</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Doors &amp; Windows</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models an</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>COLOMAC DECOR</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Aaron Liu</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>aaron@ccolomac.com</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>+86-0371-66350801, +86 15936292861</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>www.ccolomac.com</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Smart Home &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>佛山市同路匠人家具有限公司</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>赖华芳</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>13727479513, 400-8339513</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Home Furnishing</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Хорошее, 400rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>固豪木业 | SUNDIN尚鼎</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Clément / 付雄豪</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>clement.fu@cqsdmy.com</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>+(86) 19112691557</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>www.guhaogroup.com / www.cqsdmy.com</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Хорошее , 1500rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>佛山市嘉豪飞度家具有限公司 (FOSHAN KAHO FIT FURNITURE CO., LTD.)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>周灿灿</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>15986196312@163.com</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>159 1909 0393, +86-757-2339 1505</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Home Furnishing</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Нормальное</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>中山市福乐门智能科技有限公司 / 中山市乐帝智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Doors &amp; Windows</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>$176, MOQ 50, very good!</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Suzhou Acousound New Material Technology Inc.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Yolanda He</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>acousound07@polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>+86-18068038050</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>$55, MOQ100pcs, good</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>特斯豹工具</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>$30, MOQ 10pcs, nice</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CGCH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>陈洁玲 Rowling</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>014@cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>+86 189 2997 1329</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>www.cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1000 yuan 1 square</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>广东省中山名谷屋木门厂</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>罗美玲</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>180 0760 4399</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Doors &amp; Windows</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>150 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>multishades</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sophia</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>sophia@multishades.com.cn</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0086-15918713187, 0086-757-86780865</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>www.multishades.com.cn</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Office: Room 1501, CITIC Plaza, No.233, Tianhebei Road, Guangzhou City, Guangdong Province, China; Factory: 1 Shengshi Road, Shibei Industrial Park, Shishan Town, Foshan City, Guangdong Province, China</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>570 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>超友皮革家居</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1561767</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>130 super</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co.,Ltd)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>欧阳玉滢 (Sonia Ouyang)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>sonia.ouyang@wireking.com</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>+86-13392758223</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>$32, MOQ 300, good</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PTA DOOR Automation (Hunan Tianan Door Technology Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Eva Leng</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>eva@ptadoor.com</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>+86 19848080478, +44 7704 561086</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>global.ptadoor.com</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Xincheng technology park, Yuelu Avenue, Changsha Hunan China</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Doors &amp; Windows</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>¥3000, MoQ 1pcs, very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>丰顺县泰雅达实业有限公司</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>徐小俊</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>281431686@qq.com</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>13802731123</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://taiyada1688.1688.com/</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>广东省丰顺县汤坑镇太平北路</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>¥17, Moq 50, good</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>佛山市悠派家居科技有限公司</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>黄伟业</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Yea@LGPKB.com</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>13825596371</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>www.LGPKB.com</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>600 RMB Great, very cheap</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>800 rmb, little high</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>艾锐特</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>冯蕾</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3400, Good price</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>常州市永春保温材料有限公司 (Changzhou Yongchun Thermal Insulation Materials Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>yc@ycbycl.com</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0519-88931168</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>www.ycbycl.com</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>江苏省常州市天宁区郑陆镇工业集中区</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10$</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>诺奥(福建)环保家居用品有限公司</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>曾令贵</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>513573190@qq.com</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>86-13585642723 / 0596-8273388-8083</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>www.fjnuoao.cn</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>69$</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>大音声学 (DAYIN ACOUSTICS)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>唐佳豪 (Vance)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>+86 18925924350</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>www.dayinacoustics.com</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>佛山市南海区里水镇赤山大道32号 (No.32 Chishan Avenue, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>50-85$</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>杭州班昇</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>陈卓敏 Ruby</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>295608376@qq.com</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>+86 13556688832</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>￥1000 good</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FOSHAN SINCERE BUILDING MATERIALS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Crystal 刘晓艺</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>crystal@sincerechina.net</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>86-15815992213</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>www.sincerechina.net</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>佛山市禅城区南庄镇季华西路中国陶瓷产业总部基地西区C07-C08栋 (China Ceramics Industry Headquaters Block No.C07-08, West Area, West Jihua Road, Nanzhuang, Foshan, China)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>¥ 500 good</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Xiamen Golden Ricky Industry &amp; Trade Co.,Ltd</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Joan Liu</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>joan@goldenrickyhpl.com</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>+86 13599525074</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Https://goldenrickyhpl.com</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Xiamen City, Fujian, China</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>￥ 300 good</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>江门市新阳刚智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>135 3666 7789, 400-9090-518</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Doors &amp; Windows</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>300 rmb and more. Good quality and good price. Small quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>河南蓝健陶瓷有限公司</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>王闻浠</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>lanjanweiyu@163.com</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>+86-13569915996</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>www.lanjan.com</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>河南省长葛市石固镇梁庄工业园区</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>33$ for 1 pcs. Good quality and quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>沃澜 (WOTUA)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Dion Sun</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>3座104号</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Good quality and quantity. 140 rmb 1 pcs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>三强地毯</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>hengsheng_carpet@163.com</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0769-89807692</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Home Furnishing</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Good 👍</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Higold Group Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Willer Zhou</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>sale31@higold.com.cn</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>+86 158 2865 5891</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>www.higoldhardware.com</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>No.36 Shunye East Rd, Xingtan, Shunde, Foshan 528325, Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5800</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Zhejiang Kehon Intelligent Science &amp; Technology Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Sammi Shi</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>sales01@kehon.cn</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>+86 156 8948 5097, 0578-3271096</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>www.kehon.cn</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Smart Home &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>130 yuan</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Guangdong Wanbang Modular Building Co., Ltd</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Richie Wang</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>richie.wang@wbhouse.com</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>+86 137 1002 1675</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>www.gdwbprefabhouse.com</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Guangdong Factory: No.5, No. 161 Ganghe Avenue, Gaoming District, Foshan city, Guangdong, CHINA; Fujian Factory: Provincial Highway 308, Yunrong Township, Minqing County, Fuzhou City, Fujian Province, CHINA.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20000usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Guhao Group | SEAJOIN</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Owen Li</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>owen.li@seajoinhouse.com</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>(86) 133 9501 1076</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>www.seajoinhouse.com</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Chongqing, China / Ho Chi Minh City, Vietnam</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>500yuan</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CAE SANITARY FITTINGS INDUSTRY CO., LTD. GUANGDONG</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Josie Guan</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>cae@china-cae.com</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>+86-13702279135</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>www.china-cae.com</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>No.62-64, Xingda Rd., Shagang Dist., Shuikou Town, Kaiping, Guangdong, P.R.Of China.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>MOQ 100, 47 rnb per piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>盐城格子匠家居有限公司</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>董华</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>418897056@qq.com</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>13914649982, 18951488133</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>MOQ 50, 200 rnb per</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SUOFEIYA HOME COLLECTION CO., LTD</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Jasmine Guan 管敏秀</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>jasmine@suofeiyahome.com</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>+86 147 7520 2759</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.sofeyiahome.com</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>MOQ 10, 845 per piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>利亚德光电股份有限公司 Leyard Optoelectronic Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>金厚强 Jin Houqiang</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>jinhouqiang@leyard.com</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>13510009569, 18829341125, 400-8592-666</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>www.leyard.com</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Smart Home &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1pcs. Start from 60rmb. Novative technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>林商学社</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>From 1pc. Natural materials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>佛山市威尔信保险柜有限公司 (Foshan Weierxin Safe Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1250rmb. MOQ 1 pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SAKURA 樱花智能锁</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Smart Home &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>JNOD 基诺德</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>周信朋 Joe Zhou</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>sales02@jnodwater.com</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>+86 199 2825 2201, +86-757-2361 7920</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>www.jnodwater.com</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>广州传祺时代智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>洪美兰</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>jiang@chuangqitimes.com</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>13450298606, 020-82511901</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>www.chuangqitimes.com</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Smart Home &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>RUIKANG</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>sales08@ruikang-cn.com</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>+86 18028330648, +86 18022073939</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>松下电器设备(中国)有限公司</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>潘禹</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>13691864691</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Smart Home &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CAE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Jack Guan</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>jack@cae.cn</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>+86-750-8119338</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>www.cae.cn</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Cabinetry</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>150 yuan, 100, good range of products</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>广东富矿智能家居有限公司 (Guangdong Fukuang Intelligent Home Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>余赛银 (Yu Saiyin)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>109786129@qq.com</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>+86 13660529010</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>kingliye.com</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>佛山市南海区里广路二号碧桂园金沙国际广场1201室 (Room 1201, Building 10, Jinsha International Plaza No.2 Liguang Road, Nanhai District, Foshan City)</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Home Furnishing</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>THOR 索而</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>肇庆合生雅居智能家居有限公司 (Zhaoqing Hesheng Yaju Intelligent Home Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Winni 何玲玲</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>helingling@gdhsyj.com</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>+86 18924564942</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>WWW.HOPSOONER.COM</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Smart Home &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Smart Home &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>I couldn't tell you the price for smart pens right away, but they said they would send a catalogue with prices to Wechat</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>视威电子科技（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>service@3weitech.com</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>021-57715805</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>www.3weitech.com</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>上海市闵行区新骏环路188号11号楼A座518室</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет пр</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>330 юаней. 500 штук минималка . Качественный , магнитный умный переключатель с емкой батареей . Опять же проблема с ПО .</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>爱舒床垫集团有限公司</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>王鹏</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1319129904@qq.com</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>189-2324-7677</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>www.asnug.com</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>soundbox</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>劉奕紫 Cathy</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>sales19@soundbox.hk</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>+86 137 6339 3059</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккура</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>顶固集团</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккуратно. Хорошее решение для сушки белья и </t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Shenzhen Kingston Sanitary Ware Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Felicity</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>sales09@spakingston.com</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>+86-18025851458</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>www.spakingston.com</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Kingston Company, JiangJun Road, Qiuchang, Huiyang, Huizhou, China</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Guangzhou Sunrans Sanitary Ware Co., Ltd / Guangzhou Sunrans New Energy Technology Co., Ltd</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>william@sunrans.com</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>+86 134 1613 9887, +86-20-26231998</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>http://www.sunrans.com</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very go</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>15916159866</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>IFUN PARK &amp; TIPTOPFUN AMUSEMENT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ivy Zhou</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ivy@ifunpark.com</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>+86 133 0238 5758</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>www.ifunpark.com / www.ifunamusement.com</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Weyth 惠特</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D.DELI 德利智能门锁</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Doors &amp; Windows</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>RENQIU TUOXIN BUILDING MATERIALS CO., LTD</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Emily Li</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>tuoxinlqm@outlook.com</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>+86 19831737599</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://www.tuoxinfiberglassmesh.com/</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0.6 usd/m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>河南威兰得建筑科技有限公司</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>王虎旗</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>hectorwang1982@gmail.com</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>86 18638546565</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>www.weilandeglobal.com</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>河南省郑州市曲梁工业园188号</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Under negotiation, great opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>江门市新会区致恒科技材料有限公司</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>曹双林 (Edith Cao)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>13286132534, 400-0750-889</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>广东省江门市蓬江区迎宾大道西23号之129</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Doors &amp; Windows</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1-5 usd/l</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>安居福智能门 (ANJUFU INTELLIGENT GATE)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>罗如玲</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>广东省中山市东凤镇</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Doors &amp; Windows</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>欧派</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>679 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>永康市鸿钰门业有限公司</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>浙江省永康市长城工业区</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Doors &amp; Windows</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>59 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>东方喜卡</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>果果</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>249RMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>优品声学 (YP ACOUSTICS)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>李尚声 (Shangsheng Li)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>15915975597@163.com</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>15915974406</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>6000RMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>双龙智科</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2000RMB&amp;gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>GUANGDONG TUOXUN INTELLIGENT TECHNOLOGY CO., LTD</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Wing</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>wuyunying08@gmail.com</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>189-2984-9818, 0758-8578545</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Smart Home &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>MOQ - 5000 and price - 7000 dollars</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>佛山市方泓五金建材有限公司 (Foshan Fangheng Hardware Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>陈施志凯 (CHEN SHI ZHI KAI)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>108455453@qq.com</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>+86 134 3318 1558, 0757-8560 9159</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>The price cheap, merchant very friendly</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Countermast Technology (Dalian) Company Limited</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>sales.countermast.china@countermast.com</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>400-100-2228</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>www.countermast.cn</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Building No.7, Zhongqing Industrial Park, Dalian free trade zone, Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>The price more cheaper, good quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>广州蒙娜丽莎控股集团有限公司, 广州蒙娜丽莎卫浴股份有限公司</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>严金霞</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>monalisa38@monalisa.cn</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>+86 13711113746, 400 020 1818, +86 20-28607711</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>www.monalisa.cn</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>广州市花都区花东镇港头工业区4号</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Good merchant, perfect products</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>高成 (Gaocheng)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>叶小龙/Dustin Ye</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>yedustin@gmail.com</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>+86-188 5861 0008</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>www.cngaocheng.cn</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>浙江省三门县浦坝港镇沿海工业城 (COASTAL INDUSTRIAL CITY, PUBAGANG TOWN, SANMEN, TAIZHOU CITY, ZHEJIANG PRO., CHINA)</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD. / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Pacao Yin</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>pin@pingaolao.com</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>(0086)13903035682, (0086)0769-86378283, (0086)0769-86377522</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>15 RMB the product is interesting</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>浙江瑞鑫环保设备有限公司</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>吴仁余</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>294217488@qq.com</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>13967444542, 0579-82889122</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>www.jhrxhb.com</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>浙江省金华市婺城区罗店镇北山路精工工业园</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>nearly $15,000 for this production line</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ZHEJIANG DOUBLE-LIN VALVES CO., LTD.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Dream Lin</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>sale15@double-lin.com</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>86-020-66837727, 86-13710718529</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>www.double-lin.com</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>苏州市富尔达科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>袁佳磊</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>18652449601</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>www.cnfrd.cn</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>江苏省太仓市港区临江路1号</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Eric Huang</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>464565801@qq.com</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>13813551160 / 0519-88784050</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>www.ycpanel.com</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>No.28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>5000 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>优品声学</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>杨伟杰</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>6000 RMB. I like the way they explain everything about their product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>双龙中科</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Smart Home &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>深圳市家为安智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>186-0205-8898 / 400-608-0098</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>广东省佛山市南海区里水镇</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Home Furnishing</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>249 RMB. They have fully described their products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>广州市优品声学科技有限公司</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>www.gzypsx.com</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>广东省广州市番禺区南村镇南村西路138号德意创意园二层</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>6000RMB，积极，详细地告诉了一切</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>科维尔 (VIR)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>市长城工业区</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2000 RMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>贵州佑远木业有限公司</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>颜加伟</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1164199388@qq.com</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>133 9983 5678</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>400rmb /m2 good meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>广西豪庭家具有限公司 (Guangxi Haoting Furniture Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>高学梅</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>17687627315</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Home Furnishing</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>350 rmb/m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Moershu (摩尔舒卫浴)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Thea</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>moershu3@moershu.com</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>13957622087</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>www.moershu.com</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Hangzhou Sciener Smart Technology Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Zoey Zhang</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>zoey@sciener.com</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>+86 178-5768-8782</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Smart Home &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>20 / MOQ 100 Nice worker answered all questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>江西荣科新型材料有限公司 / JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Lucy Zeng (曾露)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>lucy@rongkedecor.com</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>+86-13134020034</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://www.amerdecor.com/</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>80 rmb for 230 meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SANNORA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>王冠</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>+86 13229297183</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>WWW.SANNORA.COM; WWW.SANNORA-BATH.COM</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1560 rmb for whole item</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Kaiping Gold Medal Sanitary Ware Co.,Ltd. / Guangdong Aosman Sanitary Ware Co.,Ltd</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Sophia Deng (邓小艳)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>sophiadeng@china-gold.cn</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>+181 3838 6948</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>http://www.china-gold.cn, http://www.aosman.cn</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>198 Siqian Xi Road, Shuikou, Kaiping 529300, Guangdong PR.China</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>4600 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>东风汽车</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>50 Yuan 50g (The taste is authentic and aroma is really good</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>江西瑞京鸿兴实业有限公司</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>朱支群</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>13763963598</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>www.jx-wpc.com</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>江西省瑞金市经济开发区创业一路东侧</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>250¥/м3</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Anne</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>victor@ck-bath.com</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>18656330093</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://ck-bath.com/</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>4500¥</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ciarra</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>linda.lu@ciarrahome.com</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>+86 1882 9964 960, +86 1343 2639 580</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>www.ciarrahome.com</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>300¥ 300pcs</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Yekalon Mills</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Viola Liu</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>wood6@sennorwell.com</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>(86) 158 8931 1832</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>50¥ 1000pcs</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ideal Sanitary Ware Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Amy Liu 刘建美</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>export@ideal-china.net</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>+86 (0) 757 8558 9299</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>www.ideal-sanitary.com</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>No.3 Hexi Road of Shashui, Yanghe Town, Gaoming District, Foshan City, Guangdong Province, 528515 - P.R.China.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>500$ 100psc</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>佛山市旌晨铝门窗有限公司</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>胡光辉</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>1525423805@qq.com</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>18128752879</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>佛山狮山镇谭边工业区崩岗头路四号之一</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Doors &amp; Windows</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>佛山市乾泽科技有限公司</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>陈可樑</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>hw-hardware@qian-ze.com</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>180 3863 7238</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>www.honeywell-hardware.com</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>广东省佛山市三水区云东海街道宝盛路2号1座三层（合和建筑五金园区北门）</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Doors &amp; Windows</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ARTY 艺和</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>广东 · 开平</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>景德镇窑珍陶瓷</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>徐云霞</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>13697981203</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>100 RMB per sample. The taste is very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>苏州东山茶厂 (Suzhou Dongshan Biluochun Tea Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0512-66281146</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>www.dsteaf.com</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>江苏省苏州市吴中区东山镇 (Dongshan Town, Wuzhong District, Suzhou City)</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>150 RMB per sample. The taste is very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>武夷星</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>250 RMB per sample. The taste is very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>湖北龙王垭茶业有限公司</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>498rmb/unit. I like the green tea in white color. First time to see colorless tea and it was amazing, i will recommend i</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>知和香馆</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>15926183211</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>福建永春达埔</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>San Nora (聖羅蘭·衛浴)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ALLEN XU (许熙平)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>sales@sannora.com</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>+86 137 0263 0244, +86-757-86438259</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>WWW.SANNORA.COM, WWW.SANNORA-BATH.COM</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>TANBIAN IND. ZONE, SHISHAN TOWN, NANHAI DIST., FOSHAN, GUANGDONG, CHINA</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PTAT | 帕兰蒂诺</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Joy Yang</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>joy@rans.group</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>+86-13757430301</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>www.ptat.cn</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>万磊建筑涂料有限公司</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>万磊市场部</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>186-8825-1404, 4000-147-187</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>http://www.fswanlei.com</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Coatings &amp; Paints</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ZHEJIANG SEATING TECHNOLOGY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>May Zhang</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>sales5@anjeurostilefurniture.com</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>+86 182 5727 1590</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>www.zjseating.com</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Chaozhou Lefu Sanitary Ware Technology Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>lucy@lefucz.com</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>+0086 18098114370</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>www.lefucz.com</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Lefu Sanitary Ware, Sheweikeng, Dengtang Town, Chaoan District, Chaozhou City, Guangdong Province, China</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>胡沛能 / Oliver Hu</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>oliver@wireking.com</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>+86-13802465791</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>宜昌毛尖</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Prices are go and packing and Verstaliy is more</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>湖北龙王娅茶业有限公司</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>The taste anaroma is good of this product then anyother</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>正山堂 (ZHENG SHAN TANG)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>the product prices are very good. looks attractive</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>560 moq 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>浙江雅柔装饰材料有限公司 (Zhejiang Yarou Decoration Material Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>sale01@yarouwallpaper.com.cn</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>+86-18069994326, +86-18069994377</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://www.yarouwallpaper.com.cn/</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>浙江省金华市义乌市福田街道涌金大道87号厂房二楼 (No. 1, Factory 2, Yongjin Avenue 87, Futian Subdistrict, Yiwu City, Jinhua City, Zhejiang Province)</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>淄博永顺装饰材料有限公司</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>戴艳辉</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>18830173388</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>石家庄市正定县曙光路49号东标和聚居</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>宏宇集团 (HONGYU GROUP)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Melina 王玲</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>lina@hongyugroup.com</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>+86 13827702216</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>en.hongyugroup.com</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Chongnuo(Shandong)NewMaterial Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Daisy</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>sales06@chongnuo-floors.com</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>+86 19906379675</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>www.chongnuo-floors.com</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>QingyunCounty,DezhouCity,China</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>9$</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>上海德翔木业有限公司 (Shanghai Dexiang Wood Industry Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>崔强 (Cui Qiang)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>513437660@qq.com</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>+8618901960431</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>13.25$</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>中材(邯郸)新材料有限公司 (China National Building Materials (Handan) New Materials Co.,Ltd.)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Wangfeng</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2523911877@qq.com</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>13233648687</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>8.83$</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Zhejiang Tianyan Holding Ltd</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Taizhou, Zhejiang</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>640 PCs, 3.72 RMB very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Foshan Cofesu Sanitary Ware Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>sales@cofesu.com</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>+86 181 2821 2128</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>www.cofesu.com</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Foshan, Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>30 PCs, 420 RMB, need check quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>10 PCs, 1150 RMB, very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>中国广东柜邦精密金属制品有限公司 (China Guangdong Guibang Precision Metal Products Co.Ltd)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>唐一智 (JUNIOR)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>13621417@qq.com</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>+86-156-2562-1155</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Jieyang Yagegu Hardware Products Co., LTD</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Zoya</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2291828903@qq.com</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>+86 132 8810 6615</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>广东启宏盛精密五金制品有限公司 (GUANGDONG QIHONGSHENG PRECISION HARDWARE PRODUCTS CO., LTD)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>邓美君 Jessica</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>bailide_hinge@163.com</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>+86 13823419116 / 0758-8565117</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>广东亚当斯金属精密制造有限公司 (Guangdong Adams Metal Precision Manufacturing Co.,Ltd)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Kelly Liang (梁凯莹)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>kelly@adamsmetal.com.cn</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>+86-180-2935-2895 / +86-757-25331912</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>www.adamsmetal.com.cn</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Depend on item</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>明德 (Mingde)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>www.mingde-china.com</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Depend of quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>佛山市顺德区腾徽精密智造有限公司 (FoShan ShunDe TengHui Precision Intelligent Manufacturing Co., Ltd)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>刘婉莹 Carol Liu</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>tenghuihardware@126.com</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>+86 133 1836 4599</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>www.teehve.cn</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区勒流街道众涌村港口路以西8-9号之二 (No.8-9, West of GangKou Road, Zhongchong Village, Leliu Town, Shunde District, Foshan City, Guangdong, China)</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Smart Home &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>100/square meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>DUOCAI TENT (多彩帐蓬)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Jimmy 黄锦民</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>sales003@sdduocaizp.com</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>(86)133 2294 8506, +86-766-8298662</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>www.dc-tent.com, www.sdduocaizp.com</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>云浮市云安区佛山(云浮)产业转移工业园86号 (No.86 Foshan(Yunfu) Industrial transfer park, yunan, yunfu, Guangdong China)</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>RMB 15705 MOQ5; pleasant impression</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>佛山市路乐户外制品有限公司 (FOSHAN RULER OUTDOOR HARDWARES CO.,LTD)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Marco Lau (刘嘉乐)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>RULERAWNING07@163.COM</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>+86 13129016338</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>WWW.RULER-AWNING.COM</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>END OF ROAD SHATANXIAN, SHASHUI INDUSTRIAL ZONE, SONGGANG TOWN, SHISHAN DISTRICT, FOSHAN CITY, GUANGDONG PROVINCE, CHINA, 528200</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Doors &amp; Windows</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>MOQ5 25799 RMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Avant Sports Industrial Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Jay Zhou</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>jay@avant.com.cn</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>+86-13128980150, +86-755-2968-8357</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>www.avantseating.com</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Avant Industrial Park, Zhoushi Road, Bao'an, Shenzhen, Guangdong Province, China</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>RMB 19479; MOQ 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>孟少美 (Elite Meng)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ttf@hbtfjs.com</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>+86-13103196326</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>www.hbtfjs.com</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>河北省隆尧县东谷子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>揭阳市新骏业五金制品有限公司 (JIEYANG XINJUNYE HARDWARE PRODUCTS CO., LTD)</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>林树丹 (Lin Shudan)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>linshdong@qq.com</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>13751676456</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>www.xinjunye.com</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>广东省揭阳市揭东区锡场工业区 (Xichang Industrial Zone, Jiedong District, Jieyang City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>广州蒙娜丽莎控股集团有限公司 / 广州蒙娜丽莎卫浴股份有限公司</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>伍乐彤</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>monalisa702@monalisa.cn</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>86 13711117863, 400 020 1818, 86 20-28607722, 86 20-28607788</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>www.monalisa.cn</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>广州市花都区花东镇港头工业区4号</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2000$, can be customized, very convenient</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>中山藝進不銹鋼裝飾制品有限公司 (ZHONGSHAN YIJIN STAINLESS STEEL DECORATION CO., LTD.)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Anson Yuen</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>info@hugemount.com</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>150 1954 6322 / 86-760-88702663</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>www.yijin.com</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>中国广东省中山市港口镇石特社区穗安工业区迎富2路1号 (NO.1, Ying Fu 2 Road, Sui An Gong Ye Qu, Gang Kou Zhen Shi Te She Qu, Zhongshan City, Guangdong Province, P.R.China)</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Coatings &amp; Paints</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>38$, very unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>宣城市宠爱卫浴有限公司 (CHONGAI SANITARY WARE CO., LTD.)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Lucy (卢美珍)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>export@vnsmilo.com</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>+86-13757322119</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>www.vnsmilo.com</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Xuancheng City Anhui, CHINA</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Bath &amp; Sanitary</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>2050 rmb, very interesting, convenient to use for pets</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>广西中晨木业有限公司 (Guangxi Zhongchen Wood Industry Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>张爱彬 (Zhang Aibin)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>+86 18178085851</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>25 rmb, 1 box, like this product</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>NINGBO YUSHENG HOME TECH CO., LTD. (宁波裕盛家居科技有限公司)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Tequila Xu (徐孟杰)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>marketing@cxyushun.com, tequila8xu@gmail.com</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0086-13819449988, +86 574 63190388</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>www.cxys8.com</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>中国浙江慈溪市杨梅大道南路1518号 (NO.1518, YANGMEI AVENUE SOUTH ROAD, CIXI CITY, ZHEJIANG, CHINA)</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>34 rmb, 1000, normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>河北建华锁业有限公司 (Hebei Jianhua Lock Industry Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>刘芳 (Jane Liu)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>jane@dirock.cn</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>187 1377 2087</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>http://www.dirock.cn</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>河北省泊头市寺门村镇后牛屯</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>40 rmb, 2000, very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>浙江安吉双虎竹木业有限公司 / 安吉诺迪新材料有限公司</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>周瑶琳</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>lisa.nordi@nuodibm.com</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>+86-137 3822 8209</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>www.tigerbamboo.com / www.nuodibm.com</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>1 container 250 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>马世晓 (Amelia Ma)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>tf@hbtfjs.com, mashixiaomsx@163.com</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>15097968589, 0319-6581195</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>www.hbtfjs.com</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>河北省隆尧县公子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1 container 700 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>BANRUGE / KING LIYE</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Home Furnishing</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Прайс отправят, от 100ед, хорошая компания</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I180"/>
+  <dimension ref="A1:I164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,12 +590,36 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>河南贝迪塑业有限公司 (Henan Beidi Plastic Industry Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Jane Li (李蓉娟)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Jane@hncrown.com</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+86 187 3917 6242 / 86-0372-6270170</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>www.baydeegroup.com / www.hnbeidi.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>中国·河南省鹤壁市 (Hebi City, Henan Province, China)</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -603,7 +627,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>500 pcs price 58 usd</t>
+          <t>1000 pcs price 38 USD</t>
         </is>
       </c>
     </row>
@@ -613,32 +637,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>河南贝迪塑业有限公司 (Henan Beidi Plastic Industry Co., Ltd.)</t>
+          <t>Guangzhou NewHoo Technology Co. Ltd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jane Li (李蓉娟)</t>
+          <t>Tony</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jane@hncrown.com</t>
+          <t>export01@gznewhoo.com</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+86 187 3917 6242 / 86-0372-6270170</t>
+          <t>+86-198-7837-3626</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>www.baydeegroup.com / www.hnbeidi.com</t>
+          <t>www.gznewhoo.com</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>中国·河南省鹤壁市 (Hebi City, Henan Province, China)</t>
+          <t>Building 7, Hongyu Smart Industrial Park, No. 333 Juhuashi Avenue, Huadu District, Guangzhou</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -648,7 +672,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1000 pcs price 38 USD</t>
+          <t>80$</t>
         </is>
       </c>
     </row>
@@ -658,42 +682,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Guangzhou NewHoo Technology Co. Ltd</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Tony</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>export01@gznewhoo.com</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>+86-198-7837-3626</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>www.gznewhoo.com</t>
-        </is>
-      </c>
+          <t>旭博卫浴</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Building 7, Hongyu Smart Industrial Park, No. 333 Juhuashi Avenue, Huadu District, Guangzhou</t>
+          <t>福建省南安市</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80$</t>
+          <t>70$</t>
         </is>
       </c>
     </row>
@@ -703,26 +711,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>旭博卫浴</t>
+          <t>旭博恒温</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>福建省南安市</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>70$</t>
+          <t>300 yuan</t>
         </is>
       </c>
     </row>
@@ -732,22 +736,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>旭博恒温</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>榜威电子科技（上海）有限公司 (Bweetech Electronics Technology (Shanghai) Co., Ltd)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>骆剑 (Kim Lok)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>kim.lok@bweetech.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>186-5759-0678</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>www.bweetech.com</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>300 yuan</t>
+          <t>500pcs / $100USD for pcs</t>
         </is>
       </c>
     </row>
@@ -757,34 +781,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>榜威电子科技（上海）有限公司 (Bweetech Electronics Technology (Shanghai) Co., Ltd)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>骆剑 (Kim Lok)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>kim.lok@bweetech.com</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>186-5759-0678</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>www.bweetech.com</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
-        </is>
-      </c>
+          <t>深圳市塞恩斯电子有限公司 (Sands Evermore Electronic)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Smart Home &amp; Lighting</t>
@@ -792,7 +796,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>500pcs / $100USD for pcs</t>
+          <t>50pcs / $50USD for pcs</t>
         </is>
       </c>
     </row>
@@ -802,7 +806,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>深圳市塞恩斯电子有限公司 (Sands Evermore Electronic)</t>
+          <t>HDL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -812,12 +816,12 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50pcs / $50USD for pcs</t>
+          <t>20pcs / $100USD for pcs</t>
         </is>
       </c>
     </row>
@@ -827,22 +831,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HDL</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>DEIOUX WINDOWS &amp; DOORS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CANDICE CHOU</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>sales5@deiouxwindows.com</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>+86-13392246940</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20pcs / $100USD for pcs</t>
+          <t>Custom order</t>
         </is>
       </c>
     </row>
@@ -852,30 +872,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEIOUX WINDOWS &amp; DOORS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>CANDICE CHOU</t>
-        </is>
-      </c>
+          <t>China Warren Windows and Doors Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sales5@deiouxwindows.com</t>
+          <t>info@warrenwindows.com</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+86-13392246940</t>
+          <t>+86-400-811-0300</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>www.warrenwindows.com</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Room 1007, Block B, Wangjing SOHO, Chaoyang District, Beijing, China</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
@@ -893,28 +913,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>China Warren Windows and Doors Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>info@warrenwindows.com</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>+86-400-811-0300</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>www.warrenwindows.com</t>
-        </is>
-      </c>
+          <t>Matthew window&amp;door</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>张小洪 (Matthew / Kevin)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Room 1007, Block B, Wangjing SOHO, Chaoyang District, Beijing, China</t>
+          <t>Foshan, Guangdong</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -934,30 +946,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Matthew window&amp;door</t>
+          <t>Zhongshan Smartek Security Technology Co.,LTD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>张小洪 (Matthew / Kevin)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>Tim Pan</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>market@smarteklock.com</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>+86-15889896019</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>www.smarteklock.com</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Foshan, Guangdong</t>
+          <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City Guangdong, China 528415</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Custom order</t>
+          <t>170 to 335 usd</t>
         </is>
       </c>
     </row>
@@ -967,42 +991,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Zhongshan Smartek Security Technology Co.,LTD</t>
+          <t>HDL Automation Co., Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tim Pan</t>
+          <t>Krystal Wei</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>market@smarteklock.com</t>
+          <t>krystal@hdlautomation.com</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+86-15889896019</t>
+          <t>+86 19512956186</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>www.smarteklock.com</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City Guangdong, China 528415</t>
-        </is>
-      </c>
+          <t>www.hdlautomation.com</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>170 to 335 usd</t>
+          <t>100 to up</t>
         </is>
       </c>
     </row>
@@ -1012,38 +1032,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HDL Automation Co., Ltd.</t>
+          <t>Ningbo AIFEIBAO Intelligent Security Co., Ltd</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Krystal Wei</t>
+          <t>Sean Xiao</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>krystal@hdlautomation.com</t>
+          <t>sales@aifeibao.com</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>+86 19512956186</t>
+          <t>0086 198 1730 8681</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>www.hdlautomation.com</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>www.afbsafe.com</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No.1 Donghu Rd., Daxie Development Zone, Ningbo, China (315812)</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100 to up</t>
+          <t>100 to up usd</t>
         </is>
       </c>
     </row>
@@ -1053,42 +1077,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ningbo AIFEIBAO Intelligent Security Co., Ltd</t>
+          <t>佛山市普辉亚科技有限公司 (Foshan Pu Huiya Technology Co., Ltd.)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sean Xiao</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>sales@aifeibao.com</t>
-        </is>
-      </c>
+          <t>邹隆鹏</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0086 198 1730 8681</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>www.afbsafe.com</t>
-        </is>
-      </c>
+          <t>15818099349</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No.1 Donghu Rd., Daxie Development Zone, Ningbo, China (315812)</t>
+          <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100 to up usd</t>
+          <t>Super</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1112,36 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>广东招材建材科技有限公司</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>黎桃桃</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>toto.liblun@gmail.com</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>+8618934320539</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>www.liblun.com</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1119,34 +1159,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>佛山市普辉亚科技有限公司 (Foshan Pu Huiya Technology Co., Ltd.)</t>
+          <t>浙江鑫东洁具有限公司 (ZHEJIANG XINDONG SANITARY WARE CO., LTD.)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>邹隆鹏</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>曾燕燕 Elyn</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>sales03@cn-xindong.com</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15818099349</t>
+          <t>0086-182 5765 3405, 0086-576-87493988</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
+          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -1156,32 +1200,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>广东招材建材科技有限公司</t>
+          <t>杭州南博装饰材料有限公司</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>黎桃桃</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>toto.liblun@gmail.com</t>
-        </is>
-      </c>
+          <t>王小忠</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>+8618934320539</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>www.liblun.com</t>
-        </is>
-      </c>
+          <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
+          <t>浙江省杭州市临平区运河街道育士路53-1号</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1191,7 +1227,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -1201,28 +1237,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>浙江鑫东洁具有限公司 (ZHEJIANG XINDONG SANITARY WARE CO., LTD.)</t>
+          <t>台州旭升卫浴股份有限公司</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>曾燕燕 Elyn</t>
+          <t>应杨军</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>sales03@cn-xindong.com</t>
+          <t>3572780651@qq.com</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0086-182 5765 3405, 0086-576-87493988</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>13511470999</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>www.xs88.cn</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
+          <t>浙江省台州市台州湾新区海虹大道228#</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1232,7 +1272,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -1242,24 +1282,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>杭州南博装饰材料有限公司</t>
+          <t>NIFO 耐孚</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>王小忠</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>顾鹏</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>962460053@qq.com</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
+          <t>13326792105</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区运河街道育士路53-1号</t>
+          <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1269,7 +1313,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Wall sheet , 200 rmb per meter , 2000 mtr,</t>
         </is>
       </c>
     </row>
@@ -1279,42 +1323,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台州旭升卫浴股份有限公司</t>
+          <t>Zhejiang Oushe Home Improvement And New Materials Co., Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>应杨军</t>
+          <t>Davis Dong 董伟杰</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3572780651@qq.com</t>
+          <t>sales05@authoe.com</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13511470999</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>www.xs88.cn</t>
-        </is>
-      </c>
+          <t>+86-18906831082</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>浙江省台州市台州湾新区海虹大道228#</t>
+          <t>Jiaxing/Hongkong</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Handles , 500 moq , 100 rmb per handle</t>
         </is>
       </c>
     </row>
@@ -1324,28 +1364,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NIFO 耐孚</t>
+          <t>JIN OGMEI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>顾鹏</t>
+          <t>Alex Xing</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>962460053@qq.com</t>
+          <t>kindeli1771@gmail.com</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13326792105</t>
+          <t>+86-18302200384</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
+          <t>Shijiazhuang City, Hebei Province</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1355,7 +1395,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Wall sheet , 200 rmb per meter , 2000 mtr,</t>
+          <t>Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
         </is>
       </c>
     </row>
@@ -1365,28 +1405,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Zhejiang Oushe Home Improvement And New Materials Co., Ltd.</t>
+          <t>温州金锏智能锁具有限公司</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Davis Dong 董伟杰</t>
+          <t>张丽</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>sales05@authoe.com</t>
+          <t>jinjian19@jinjianlock.com</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>+86-18906831082</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>15067804393</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>www.jinjianlock.com</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Jiaxing/Hongkong</t>
+          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1396,7 +1440,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Handles , 500 moq , 100 rmb per handle</t>
+          <t>Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1450,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JIN OGMEI</t>
+          <t>上海世灿国际贸易有限公司</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alex Xing</t>
+          <t>杨苗</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>kindeli1771@gmail.com</t>
+          <t>yangm618@163.com</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>+86-18302200384</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>138 1618 4706</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>http://www.shicanchina.com</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Shijiazhuang City, Hebei Province</t>
+          <t>上海市浦东新区商城路889号C3-B06</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
+          <t>Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models an</t>
         </is>
       </c>
     </row>
@@ -1447,42 +1495,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>温州金锏智能锁具有限公司</t>
+          <t>COLOMAC DECOR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>张丽</t>
+          <t>Aaron Liu</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jinjian19@jinjianlock.com</t>
+          <t>aaron@ccolomac.com</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15067804393</t>
+          <t>+86-0371-66350801, +86 15936292861</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>www.jinjianlock.com</t>
+          <t>www.ccolomac.com</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号</t>
+          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for</t>
+          <t>Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 10</t>
         </is>
       </c>
     </row>
@@ -1492,42 +1540,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>上海世灿国际贸易有限公司</t>
+          <t>佛山市同路匠人家具有限公司</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杨苗</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>yangm618@163.com</t>
-        </is>
-      </c>
+          <t>赖华芳</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>138 1618 4706</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>http://www.shicanchina.com</t>
-        </is>
-      </c>
+          <t>13727479513, 400-8339513</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>上海市浦东新区商城路889号C3-B06</t>
+          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models an</t>
+          <t>Хорошее, 400rmb</t>
         </is>
       </c>
     </row>
@@ -1537,42 +1577,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>COLOMAC DECOR</t>
+          <t>固豪木业 | SUNDIN尚鼎</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Aaron Liu</t>
+          <t>Clément / 付雄豪</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>aaron@ccolomac.com</t>
+          <t>clement.fu@cqsdmy.com</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>+86-0371-66350801, +86 15936292861</t>
+          <t>+(86) 19112691557</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>www.ccolomac.com</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
-        </is>
-      </c>
+          <t>www.guhaogroup.com / www.cqsdmy.com</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 10</t>
+          <t>Хорошее , 1500rmb</t>
         </is>
       </c>
     </row>
@@ -1582,24 +1618,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>佛山市同路匠人家具有限公司</t>
+          <t>佛山市嘉豪飞度家具有限公司 (FOSHAN KAHO FIT FURNITURE CO., LTD.)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>赖华芳</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>周灿灿</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>15986196312@163.com</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13727479513, 400-8339513</t>
+          <t>159 1909 0393, +86-757-2339 1505</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
+          <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1609,7 +1649,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Хорошее, 400rmb</t>
+          <t>Нормальное</t>
         </is>
       </c>
     </row>
@@ -1619,38 +1659,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>固豪木业 | SUNDIN尚鼎</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Clément / 付雄豪</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>clement.fu@cqsdmy.com</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>+(86) 19112691557</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>www.guhaogroup.com / www.cqsdmy.com</t>
-        </is>
-      </c>
+          <t>中山市福乐门智能科技有限公司 / 中山市乐帝智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Хорошее , 1500rmb</t>
+          <t>$176, MOQ 50, very good!</t>
         </is>
       </c>
     </row>
@@ -1660,38 +1684,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>佛山市嘉豪飞度家具有限公司 (FOSHAN KAHO FIT FURNITURE CO., LTD.)</t>
+          <t>Suzhou Acousound New Material Technology Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>周灿灿</t>
+          <t>Yolanda He</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15986196312@163.com</t>
+          <t>acousound07@polyacoustic.com</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>159 1909 0393, +86-757-2339 1505</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>+86-18068038050</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
+          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Нормальное</t>
+          <t>$55, MOQ100pcs, good</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1729,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>中山市福乐门智能科技有限公司 / 中山市乐帝智能科技有限公司</t>
+          <t>特斯豹工具</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -1711,12 +1739,12 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>$176, MOQ 50, very good!</t>
+          <t>$30, MOQ 10pcs, nice</t>
         </is>
       </c>
     </row>
@@ -1726,32 +1754,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Suzhou Acousound New Material Technology Inc.</t>
+          <t>CGCH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yolanda He</t>
+          <t>陈洁玲 Rowling</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>acousound07@polyacoustic.com</t>
+          <t>014@cgchcontainer.com</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>+86-18068038050</t>
+          <t>+86 189 2997 1329</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>www.polyacoustic.com</t>
+          <t>www.cgchcontainer.com</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1761,7 +1789,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>$55, MOQ100pcs, good</t>
+          <t>1000 yuan 1 square</t>
         </is>
       </c>
     </row>
@@ -1771,22 +1799,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>特斯豹工具</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>广东省中山名谷屋木门厂</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>罗美玲</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>180 0760 4399</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>$30, MOQ 10pcs, nice</t>
+          <t>150 rmb</t>
         </is>
       </c>
     </row>
@@ -1796,32 +1836,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CGCH</t>
+          <t>multishades</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>陈洁玲 Rowling</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>014@cgchcontainer.com</t>
+          <t>sophia@multishades.com.cn</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>+86 189 2997 1329</t>
+          <t>0086-15918713187, 0086-757-86780865</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>www.cgchcontainer.com</t>
+          <t>www.multishades.com.cn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+          <t>Office: Room 1501, CITIC Plaza, No.233, Tianhebei Road, Guangzhou City, Guangdong Province, China; Factory: 1 Shengshi Road, Shibei Industrial Park, Shishan Town, Foshan City, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1831,7 +1871,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1000 yuan 1 square</t>
+          <t>570 rmb</t>
         </is>
       </c>
     </row>
@@ -1841,34 +1881,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>广东省中山名谷屋木门厂</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>罗美玲</t>
-        </is>
-      </c>
+          <t>超友皮革家居</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>180 0760 4399</t>
+          <t>1561767</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>150 rmb</t>
+          <t>130 super</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1910,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>multishades</t>
+          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co.,Ltd)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>欧阳玉滢 (Sonia Ouyang)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>sophia@multishades.com.cn</t>
+          <t>sonia.ouyang@wireking.com</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0086-15918713187, 0086-757-86780865</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>www.multishades.com.cn</t>
-        </is>
-      </c>
+          <t>+86-13392758223</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Office: Room 1501, CITIC Plaza, No.233, Tianhebei Road, Guangzhou City, Guangdong Province, China; Factory: 1 Shengshi Road, Shibei Industrial Park, Shishan Town, Foshan City, Guangdong Province, China</t>
+          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1913,7 +1941,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>570 rmb</t>
+          <t>$32, MOQ 300, good</t>
         </is>
       </c>
     </row>
@@ -1923,26 +1951,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>超友皮革家居</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+          <t>PTA DOOR Automation (Hunan Tianan Door Technology Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Eva Leng</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>eva@ptadoor.com</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1561767</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+          <t>+86 19848080478, +44 7704 561086</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>global.ptadoor.com</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Xincheng technology park, Yuelu Avenue, Changsha Hunan China</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>130 super</t>
+          <t>¥3000, MoQ 1pcs, very good</t>
         </is>
       </c>
     </row>
@@ -1952,28 +1996,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co.,Ltd)</t>
+          <t>丰顺县泰雅达实业有限公司</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>欧阳玉滢 (Sonia Ouyang)</t>
+          <t>徐小俊</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sonia.ouyang@wireking.com</t>
+          <t>281431686@qq.com</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>+86-13392758223</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>13802731123</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://taiyada1688.1688.com/</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
+          <t>广东省丰顺县汤坑镇太平北路</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1983,7 +2031,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>$32, MOQ 300, good</t>
+          <t>¥17, Moq 50, good</t>
         </is>
       </c>
     </row>
@@ -1993,42 +2041,42 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PTA DOOR Automation (Hunan Tianan Door Technology Co., Ltd.)</t>
+          <t>佛山市悠派家居科技有限公司</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eva Leng</t>
+          <t>黄伟业</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>eva@ptadoor.com</t>
+          <t>Yea@LGPKB.com</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>+86 19848080478, +44 7704 561086</t>
+          <t>13825596371</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>global.ptadoor.com</t>
+          <t>www.LGPKB.com</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Xincheng technology park, Yuelu Avenue, Changsha Hunan China</t>
+          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¥3000, MoQ 1pcs, very good</t>
+          <t>600 RMB Great, very cheap</t>
         </is>
       </c>
     </row>
@@ -2038,34 +2086,18 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>丰顺县泰雅达实业有限公司</t>
+          <t>艾锐特</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>徐小俊</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>281431686@qq.com</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>13802731123</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>https://taiyada1688.1688.com/</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>广东省丰顺县汤坑镇太平北路</t>
-        </is>
-      </c>
+          <t>冯蕾</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2073,7 +2105,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>¥17, Moq 50, good</t>
+          <t>3400, Good price</t>
         </is>
       </c>
     </row>
@@ -2083,32 +2115,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>佛山市悠派家居科技有限公司</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>黄伟业</t>
-        </is>
-      </c>
+          <t>常州市永春保温材料有限公司 (Changzhou Yongchun Thermal Insulation Materials Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Yea@LGPKB.com</t>
+          <t>yc@ycbycl.com</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13825596371</t>
+          <t>0519-88931168</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>www.LGPKB.com</t>
+          <t>www.ycbycl.com</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
+          <t>江苏省常州市天宁区郑陆镇工业集中区</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2118,7 +2146,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>600 RMB Great, very cheap</t>
+          <t>10$</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2154,36 @@
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>诺奥(福建)环保家居用品有限公司</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>曾令贵</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>513573190@qq.com</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>86-13585642723 / 0596-8273388-8083</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>www.fjnuoao.cn</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2139,7 +2191,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>800 rmb, little high</t>
+          <t>69$</t>
         </is>
       </c>
     </row>
@@ -2149,18 +2201,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>艾锐特</t>
+          <t>大音声学 (DAYIN ACOUSTICS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>冯蕾</t>
+          <t>唐佳豪 (Vance)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>+86 18925924350</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>www.dayinacoustics.com</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>佛山市南海区里水镇赤山大道32号 (No.32 Chishan Avenue, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2168,7 +2232,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3400, Good price</t>
+          <t>50-85$</t>
         </is>
       </c>
     </row>
@@ -2178,30 +2242,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>常州市永春保温材料有限公司 (Changzhou Yongchun Thermal Insulation Materials Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>杭州班昇</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>陈卓敏 Ruby</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>yc@ycbycl.com</t>
+          <t>295608376@qq.com</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0519-88931168</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>www.ycbycl.com</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>江苏省常州市天宁区郑陆镇工业集中区</t>
-        </is>
-      </c>
+          <t>+86 13556688832</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2209,7 +2269,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10$</t>
+          <t>￥1000 good</t>
         </is>
       </c>
     </row>
@@ -2219,32 +2279,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>诺奥(福建)环保家居用品有限公司</t>
+          <t>FOSHAN SINCERE BUILDING MATERIALS CO., LTD.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>曾令贵</t>
+          <t>Crystal 刘晓艺</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>513573190@qq.com</t>
+          <t>crystal@sincerechina.net</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>86-13585642723 / 0596-8273388-8083</t>
+          <t>86-15815992213</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>www.fjnuoao.cn</t>
+          <t>www.sincerechina.net</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
+          <t>佛山市禅城区南庄镇季华西路中国陶瓷产业总部基地西区C07-C08栋 (China Ceramics Industry Headquaters Block No.C07-08, West Area, West Jihua Road, Nanzhuang, Foshan, China)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2254,7 +2314,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>69$</t>
+          <t>¥ 500 good</t>
         </is>
       </c>
     </row>
@@ -2264,28 +2324,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>大音声学 (DAYIN ACOUSTICS)</t>
+          <t>Xiamen Golden Ricky Industry &amp; Trade Co.,Ltd</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>唐佳豪 (Vance)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Joan Liu</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>joan@goldenrickyhpl.com</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>+86 18925924350</t>
+          <t>+86 13599525074</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>www.dayinacoustics.com</t>
+          <t>Https://goldenrickyhpl.com</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>佛山市南海区里水镇赤山大道32号 (No.32 Chishan Avenue, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+          <t>Xiamen City, Fujian, China</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2295,7 +2359,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50-85$</t>
+          <t>￥ 300 good</t>
         </is>
       </c>
     </row>
@@ -2305,34 +2369,30 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>杭州班昇</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>陈卓敏 Ruby</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>295608376@qq.com</t>
-        </is>
-      </c>
+          <t>江门市新阳刚智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>+86 13556688832</t>
+          <t>135 3666 7789, 400-9090-518</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>￥1000 good</t>
+          <t>300 rmb and more. Good quality and good price. Small quantity</t>
         </is>
       </c>
     </row>
@@ -2342,32 +2402,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FOSHAN SINCERE BUILDING MATERIALS CO., LTD.</t>
+          <t>河南蓝健陶瓷有限公司</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Crystal 刘晓艺</t>
+          <t>王闻浠</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>crystal@sincerechina.net</t>
+          <t>lanjanweiyu@163.com</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>86-15815992213</t>
+          <t>+86-13569915996</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>www.sincerechina.net</t>
+          <t>www.lanjan.com</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇季华西路中国陶瓷产业总部基地西区C07-C08栋 (China Ceramics Industry Headquaters Block No.C07-08, West Area, West Jihua Road, Nanzhuang, Foshan, China)</t>
+          <t>河南省长葛市石固镇梁庄工业园区</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2377,7 +2437,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>¥ 500 good</t>
+          <t>33$ for 1 pcs. Good quality and quantity</t>
         </is>
       </c>
     </row>
@@ -2387,32 +2447,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Xiamen Golden Ricky Industry &amp; Trade Co.,Ltd</t>
+          <t>沃澜 (WOTUA)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Joan Liu</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>joan@goldenrickyhpl.com</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>+86 13599525074</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Https://goldenrickyhpl.com</t>
-        </is>
-      </c>
+          <t>Dion Sun</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Xiamen City, Fujian, China</t>
+          <t>3座104号</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2422,7 +2470,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>￥ 300 good</t>
+          <t>Good quality and quantity. 140 rmb 1 pcs.</t>
         </is>
       </c>
     </row>
@@ -2432,30 +2480,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>江门市新阳刚智能科技有限公司</t>
+          <t>三强地毯</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>hengsheng_carpet@163.com</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>135 3666 7789, 400-9090-518</t>
+          <t>0769-89807692</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>300 rmb and more. Good quality and good price. Small quantity</t>
+          <t>Good 👍</t>
         </is>
       </c>
     </row>
@@ -2465,32 +2513,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>河南蓝健陶瓷有限公司</t>
+          <t>Higold Group Co., Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>王闻浠</t>
+          <t>Willer Zhou</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>lanjanweiyu@163.com</t>
+          <t>sale31@higold.com.cn</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>+86-13569915996</t>
+          <t>+86 158 2865 5891</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>www.lanjan.com</t>
+          <t>www.higoldhardware.com</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>河南省长葛市石固镇梁庄工业园区</t>
+          <t>No.36 Shunye East Rd, Xingtan, Shunde, Foshan 528325, Guangdong, China</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2500,7 +2548,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>33$ for 1 pcs. Good quality and quantity</t>
+          <t>5800</t>
         </is>
       </c>
     </row>
@@ -2510,30 +2558,42 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>沃澜 (WOTUA)</t>
+          <t>Zhejiang Kehon Intelligent Science &amp; Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dion Sun</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+          <t>Sammi Shi</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>sales01@kehon.cn</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>+86 156 8948 5097, 0578-3271096</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>www.kehon.cn</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3座104号</t>
+          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Good quality and quantity. 140 rmb 1 pcs.</t>
+          <t>130 yuan</t>
         </is>
       </c>
     </row>
@@ -2543,30 +2603,42 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>三强地毯</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>Guangdong Wanbang Modular Building Co., Ltd</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Richie Wang</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>hengsheng_carpet@163.com</t>
+          <t>richie.wang@wbhouse.com</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0769-89807692</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+          <t>+86 137 1002 1675</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>www.gdwbprefabhouse.com</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Guangdong Factory: No.5, No. 161 Ganghe Avenue, Gaoming District, Foshan city, Guangdong, CHINA; Fujian Factory: Provincial Highway 308, Yunrong Township, Minqing County, Fuzhou City, Fujian Province, CHINA.</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Good 👍</t>
+          <t>20000usd</t>
         </is>
       </c>
     </row>
@@ -2574,12 +2646,36 @@
       <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Guhao Group | SEAJOIN</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Owen Li</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>owen.li@seajoinhouse.com</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>(86) 133 9501 1076</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>www.seajoinhouse.com</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Chongqing, China / Ho Chi Minh City, Vietnam</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2587,7 +2683,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>500yuan</t>
         </is>
       </c>
     </row>
@@ -2597,42 +2693,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Higold Group Co., Ltd.</t>
+          <t>CAE SANITARY FITTINGS INDUSTRY CO., LTD. GUANGDONG</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Willer Zhou</t>
+          <t>Josie Guan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>sale31@higold.com.cn</t>
+          <t>cae@china-cae.com</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>+86 158 2865 5891</t>
+          <t>+86-13702279135</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>www.higoldhardware.com</t>
+          <t>www.china-cae.com</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>No.36 Shunye East Rd, Xingtan, Shunde, Foshan 528325, Guangdong, China</t>
+          <t>No.62-64, Xingda Rd., Shagang Dist., Shuikou Town, Kaiping, Guangdong, P.R.Of China.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>MOQ 100, 47 rnb per piece</t>
         </is>
       </c>
     </row>
@@ -2642,42 +2738,38 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Zhejiang Kehon Intelligent Science &amp; Technology Co., Ltd.</t>
+          <t>盐城格子匠家居有限公司</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sammi Shi</t>
+          <t>董华</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>sales01@kehon.cn</t>
+          <t>418897056@qq.com</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>+86 156 8948 5097, 0578-3271096</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>www.kehon.cn</t>
-        </is>
-      </c>
+          <t>13914649982, 18951488133</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
+          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>130 yuan</t>
+          <t>MOQ 50, 200 rnb per</t>
         </is>
       </c>
     </row>
@@ -2687,32 +2779,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Guangdong Wanbang Modular Building Co., Ltd</t>
+          <t>SUOFEIYA HOME COLLECTION CO., LTD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richie Wang</t>
+          <t>Jasmine Guan 管敏秀</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>richie.wang@wbhouse.com</t>
+          <t>jasmine@suofeiyahome.com</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>+86 137 1002 1675</t>
+          <t>+86 147 7520 2759</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>www.gdwbprefabhouse.com</t>
+          <t>https://www.sofeyiahome.com</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Guangdong Factory: No.5, No. 161 Ganghe Avenue, Gaoming District, Foshan city, Guangdong, CHINA; Fujian Factory: Provincial Highway 308, Yunrong Township, Minqing County, Fuzhou City, Fujian Province, CHINA.</t>
+          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2722,7 +2814,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20000usd</t>
+          <t>MOQ 10, 845 per piece</t>
         </is>
       </c>
     </row>
@@ -2732,42 +2824,42 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Guhao Group | SEAJOIN</t>
+          <t>利亚德光电股份有限公司 Leyard Optoelectronic Co., Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Owen Li</t>
+          <t>金厚强 Jin Houqiang</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>owen.li@seajoinhouse.com</t>
+          <t>jinhouqiang@leyard.com</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(86) 133 9501 1076</t>
+          <t>13510009569, 18829341125, 400-8592-666</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>www.seajoinhouse.com</t>
+          <t>www.leyard.com</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chongqing, China / Ho Chi Minh City, Vietnam</t>
+          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>500yuan</t>
+          <t>1pcs. Start from 60rmb. Novative technology</t>
         </is>
       </c>
     </row>
@@ -2777,42 +2869,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CAE SANITARY FITTINGS INDUSTRY CO., LTD. GUANGDONG</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Josie Guan</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>cae@china-cae.com</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>+86-13702279135</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>www.china-cae.com</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>No.62-64, Xingda Rd., Shagang Dist., Shuikou Town, Kaiping, Guangdong, P.R.Of China.</t>
-        </is>
-      </c>
+          <t>林商学社</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MOQ 100, 47 rnb per piece</t>
+          <t>From 1pc. Natural materials.</t>
         </is>
       </c>
     </row>
@@ -2822,30 +2894,14 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>盐城格子匠家居有限公司</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>董华</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>418897056@qq.com</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>13914649982, 18951488133</t>
-        </is>
-      </c>
+          <t>佛山市威尔信保险柜有限公司 (Foshan Weierxin Safe Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2853,7 +2909,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>MOQ 50, 200 rnb per</t>
+          <t>1250rmb. MOQ 1 pc</t>
         </is>
       </c>
     </row>
@@ -2863,42 +2919,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SUOFEIYA HOME COLLECTION CO., LTD</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Jasmine Guan 管敏秀</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>jasmine@suofeiyahome.com</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>+86 147 7520 2759</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>https://www.sofeyiahome.com</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
-        </is>
-      </c>
+          <t>SAKURA 樱花智能锁</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>MOQ 10, 845 per piece</t>
+          <t>199</t>
         </is>
       </c>
     </row>
@@ -2908,42 +2944,38 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>利亚德光电股份有限公司 Leyard Optoelectronic Co., Ltd.</t>
+          <t>JNOD 基诺德</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>金厚强 Jin Houqiang</t>
+          <t>周信朋 Joe Zhou</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jinhouqiang@leyard.com</t>
+          <t>sales02@jnodwater.com</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13510009569, 18829341125, 400-8592-666</t>
+          <t>+86 199 2825 2201, +86-757-2361 7920</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>www.leyard.com</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋</t>
-        </is>
-      </c>
+          <t>www.jnodwater.com</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1pcs. Start from 60rmb. Novative technology</t>
+          <t>1410</t>
         </is>
       </c>
     </row>
@@ -2953,22 +2985,42 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>林商学社</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+          <t>广州传祺时代智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>洪美兰</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>jiang@chuangqitimes.com</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>13450298606, 020-82511901</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>www.chuangqitimes.com</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>From 1pc. Natural materials.</t>
+          <t>329</t>
         </is>
       </c>
     </row>
@@ -2978,14 +3030,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>佛山市威尔信保险柜有限公司 (Foshan Weierxin Safe Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+          <t>RUIKANG</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>sales08@ruikang-cn.com</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>+86 18028330648, +86 18022073939</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2993,7 +3061,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1250rmb. MOQ 1 pc</t>
+          <t>229</t>
         </is>
       </c>
     </row>
@@ -3003,14 +3071,26 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SAKURA 樱花智能锁</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>松下电器设备(中国)有限公司</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>潘禹</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>13691864691</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Smart Home &amp; Lighting</t>
@@ -3018,7 +3098,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>680</t>
         </is>
       </c>
     </row>
@@ -3028,30 +3108,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JNOD 基诺德</t>
+          <t>CAE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>周信朋 Joe Zhou</t>
+          <t>Jack Guan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>sales02@jnodwater.com</t>
+          <t>jack@cae.cn</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>+86 199 2825 2201, +86-757-2361 7920</t>
+          <t>+86-750-8119338</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>www.jnodwater.com</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>www.cae.cn</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3059,7 +3143,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>150 yuan, 100, good range of products</t>
         </is>
       </c>
     </row>
@@ -3069,42 +3153,42 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>广州传祺时代智能科技有限公司</t>
+          <t>广东富矿智能家居有限公司 (Guangdong Fukuang Intelligent Home Co., Ltd.)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>洪美兰</t>
+          <t>余赛银 (Yu Saiyin)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jiang@chuangqitimes.com</t>
+          <t>109786129@qq.com</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>13450298606, 020-82511901</t>
+          <t>+86 13660529010</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>www.chuangqitimes.com</t>
+          <t>kingliye.com</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
+          <t>佛山市南海区里广路二号碧桂园金沙国际广场1201室 (Room 1201, Building 10, Jinsha International Plaza No.2 Liguang Road, Nanhai District, Foshan City)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
         </is>
       </c>
     </row>
@@ -3114,30 +3198,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RUIKANG</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Jacky</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>sales08@ruikang-cn.com</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>+86 18028330648, +86 18022073939</t>
-        </is>
-      </c>
+          <t>THOR 索而</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3145,7 +3213,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
         </is>
       </c>
     </row>
@@ -3155,26 +3223,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>松下电器设备(中国)有限公司</t>
+          <t>肇庆合生雅居智能家居有限公司 (Zhaoqing Hesheng Yaju Intelligent Home Co., Ltd.)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>潘禹</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Winni 何玲玲</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>helingling@gdhsyj.com</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>13691864691</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
-        </is>
-      </c>
+          <t>+86 18924564942</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>WWW.HOPSOONER.COM</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Smart Home &amp; Lighting</t>
@@ -3182,7 +3254,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
         </is>
       </c>
     </row>
@@ -3192,42 +3264,38 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CAE</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Jack Guan</t>
-        </is>
-      </c>
+          <t>视威电子科技（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>jack@cae.cn</t>
+          <t>service@3weitech.com</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>+86-750-8119338</t>
+          <t>021-57715805</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>www.cae.cn</t>
+          <t>www.3weitech.com</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
+          <t>上海市闵行区新骏环路188号11号楼A座518室</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kitchen &amp; Cabinetry</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>150 yuan, 100, good range of products</t>
+          <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет пр</t>
         </is>
       </c>
     </row>
@@ -3237,42 +3305,38 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>广东富矿智能家居有限公司 (Guangdong Fukuang Intelligent Home Co., Ltd.)</t>
+          <t>爱舒床垫集团有限公司</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>余赛银 (Yu Saiyin)</t>
+          <t>王鹏</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>109786129@qq.com</t>
+          <t>1319129904@qq.com</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>+86 13660529010</t>
+          <t>189-2324-7677</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>kingliye.com</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>佛山市南海区里广路二号碧桂园金沙国际广场1201室 (Room 1201, Building 10, Jinsha International Plaza No.2 Liguang Road, Nanhai District, Foshan City)</t>
-        </is>
-      </c>
+          <t>www.asnug.com</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
+          <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3346,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>THOR 索而</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+          <t>soundbox</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>劉奕紫 Cathy</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>sales19@soundbox.hk</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>+86 137 6339 3059</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
@@ -3297,7 +3373,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+          <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккура</t>
         </is>
       </c>
     </row>
@@ -3307,38 +3383,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>肇庆合生雅居智能家居有限公司 (Zhaoqing Hesheng Yaju Intelligent Home Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Winni 何玲玲</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>helingling@gdhsyj.com</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>+86 18924564942</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>WWW.HOPSOONER.COM</t>
-        </is>
-      </c>
+          <t>顶固集团</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+          <t xml:space="preserve">От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккуратно. Хорошее решение для сушки белья и </t>
         </is>
       </c>
     </row>
@@ -3346,20 +3406,44 @@
       <c r="A77" t="n">
         <v>76</v>
       </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Shenzhen Kingston Sanitary Ware Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Felicity</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>sales09@spakingston.com</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>+86-18025851458</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>www.spakingston.com</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Kingston Company, JiangJun Road, Qiuchang, Huiyang, Huizhou, China</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>I couldn't tell you the price for smart pens right away, but they said they would send a catalogue with prices to Wechat</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -3367,20 +3451,44 @@
       <c r="A78" t="n">
         <v>77</v>
       </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Guangzhou Sunrans Sanitary Ware Co., Ltd / Guangzhou Sunrans New Energy Technology Co., Ltd</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>william@sunrans.com</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>+86 134 1613 9887, +86-20-26231998</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>http://www.sunrans.com</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very go</t>
         </is>
       </c>
     </row>
@@ -3388,32 +3496,16 @@
       <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>视威电子科技（上海）有限公司</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>service@3weitech.com</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>021-57715805</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>www.3weitech.com</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>上海市闵行区新骏环路188号11号楼A座518室</t>
-        </is>
-      </c>
+          <t>15916159866</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3421,7 +3513,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет пр</t>
+          <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
         </is>
       </c>
     </row>
@@ -3429,12 +3521,36 @@
       <c r="A80" t="n">
         <v>79</v>
       </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>IFUN PARK &amp; TIPTOPFUN AMUSEMENT</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ivy Zhou</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ivy@ifunpark.com</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>+86 133 0238 5758</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>www.ifunpark.com / www.ifunamusement.com</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3442,7 +3558,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>330 юаней. 500 штук минималка . Качественный , магнитный умный переключатель с емкой батареей . Опять же проблема с ПО .</t>
+          <t>600</t>
         </is>
       </c>
     </row>
@@ -3452,29 +3568,13 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>爱舒床垫集团有限公司</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>王鹏</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1319129904@qq.com</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>189-2324-7677</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>www.asnug.com</t>
-        </is>
-      </c>
+          <t>Weyth 惠特</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
@@ -3483,7 +3583,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
+          <t>500</t>
         </is>
       </c>
     </row>
@@ -3493,34 +3593,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>soundbox</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>劉奕紫 Cathy</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>sales19@soundbox.hk</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>+86 137 6339 3059</t>
-        </is>
-      </c>
+          <t>D.DELI 德利智能门锁</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккура</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -3530,14 +3618,34 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>顶固集团</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
+          <t>RENQIU TUOXIN BUILDING MATERIALS CO., LTD</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Emily Li</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>tuoxinlqm@outlook.com</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>+86 19831737599</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://www.tuoxinfiberglassmesh.com/</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3545,7 +3653,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккуратно. Хорошее решение для сушки белья и </t>
+          <t>0.6 usd/m2</t>
         </is>
       </c>
     </row>
@@ -3555,42 +3663,42 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shenzhen Kingston Sanitary Ware Co., Ltd.</t>
+          <t>河南威兰得建筑科技有限公司</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Felicity</t>
+          <t>王虎旗</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>sales09@spakingston.com</t>
+          <t>hectorwang1982@gmail.com</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>+86-18025851458</t>
+          <t>86 18638546565</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>www.spakingston.com</t>
+          <t>www.weilandeglobal.com</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Kingston Company, JiangJun Road, Qiuchang, Huiyang, Huizhou, China</t>
+          <t>河南省郑州市曲梁工业园188号</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Under negotiation, great opportunities</t>
         </is>
       </c>
     </row>
@@ -3600,42 +3708,34 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Guangzhou Sunrans Sanitary Ware Co., Ltd / Guangzhou Sunrans New Energy Technology Co., Ltd</t>
+          <t>江门市新会区致恒科技材料有限公司</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>William</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>william@sunrans.com</t>
-        </is>
-      </c>
+          <t>曹双林 (Edith Cao)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>+86 134 1613 9887, +86-20-26231998</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>http://www.sunrans.com</t>
-        </is>
-      </c>
+          <t>13286132534, 400-0750-889</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
+          <t>广东省江门市蓬江区迎宾大道西23号之129</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very go</t>
+          <t>1-5 usd/l</t>
         </is>
       </c>
     </row>
@@ -3643,24 +3743,32 @@
       <c r="A86" t="n">
         <v>85</v>
       </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>安居福智能门 (ANJUFU INTELLIGENT GATE)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>罗如玲</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>15916159866</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>广东省中山市东凤镇</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -3670,34 +3778,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IFUN PARK &amp; TIPTOPFUN AMUSEMENT</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ivy Zhou</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>ivy@ifunpark.com</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>+86 133 0238 5758</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>www.ifunpark.com / www.ifunamusement.com</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
-        </is>
-      </c>
+          <t>欧派</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3705,7 +3793,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>679 rmb</t>
         </is>
       </c>
     </row>
@@ -3715,22 +3803,26 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Weyth 惠特</t>
+          <t>永康市鸿钰门业有限公司</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>浙江省永康市长城工业区</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>59 rmb</t>
         </is>
       </c>
     </row>
@@ -3740,22 +3832,26 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>D.DELI 德利智能门锁</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>东方喜卡</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>果果</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>249RMB</t>
         </is>
       </c>
     </row>
@@ -3765,32 +3861,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RENQIU TUOXIN BUILDING MATERIALS CO., LTD</t>
+          <t>优品声学 (YP ACOUSTICS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Emily Li</t>
+          <t>李尚声 (Shangsheng Li)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>tuoxinlqm@outlook.com</t>
+          <t>15915975597@163.com</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>+86 19831737599</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>https://www.tuoxinfiberglassmesh.com/</t>
-        </is>
-      </c>
+          <t>15915974406</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
+          <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3800,7 +3892,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>0.6 usd/m2</t>
+          <t>6000RMB</t>
         </is>
       </c>
     </row>
@@ -3810,32 +3902,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>河南威兰得建筑科技有限公司</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>王虎旗</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>hectorwang1982@gmail.com</t>
-        </is>
-      </c>
+          <t>双龙智科</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>86 18638546565</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>www.weilandeglobal.com</t>
-        </is>
-      </c>
+          <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>河南省郑州市曲梁工业园188号</t>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3845,7 +3925,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Under negotiation, great opportunities</t>
+          <t>2000RMB&amp;gt;</t>
         </is>
       </c>
     </row>
@@ -3855,34 +3935,38 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>江门市新会区致恒科技材料有限公司</t>
+          <t>GUANGDONG TUOXUN INTELLIGENT TECHNOLOGY CO., LTD</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>曹双林 (Edith Cao)</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>Wing</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>wuyunying08@gmail.com</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>13286132534, 400-0750-889</t>
+          <t>189-2984-9818, 0758-8578545</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>广东省江门市蓬江区迎宾大道西23号之129</t>
+          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1-5 usd/l</t>
+          <t>MOQ - 5000 and price - 7000 dollars</t>
         </is>
       </c>
     </row>
@@ -3892,30 +3976,38 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>安居福智能门 (ANJUFU INTELLIGENT GATE)</t>
+          <t>佛山市方泓五金建材有限公司 (Foshan Fangheng Hardware Co., Ltd.)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>罗如玲</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+          <t>陈施志凯 (CHEN SHI ZHI KAI)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>108455453@qq.com</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>+86 134 3318 1558, 0757-8560 9159</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>广东省中山市东凤镇</t>
+          <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>The price cheap, merchant very friendly</t>
         </is>
       </c>
     </row>
@@ -3925,14 +4017,30 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>欧派</t>
+          <t>Countermast Technology (Dalian) Company Limited</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>sales.countermast.china@countermast.com</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>400-100-2228</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>www.countermast.cn</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Building No.7, Zhongqing Industrial Park, Dalian free trade zone, Liaoning, China</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3940,7 +4048,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>679 rmb</t>
+          <t>The price more cheaper, good quality</t>
         </is>
       </c>
     </row>
@@ -3950,26 +4058,42 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>永康市鸿钰门业有限公司</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+          <t>广州蒙娜丽莎控股集团有限公司, 广州蒙娜丽莎卫浴股份有限公司</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>严金霞</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>monalisa38@monalisa.cn</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>+86 13711113746, 400 020 1818, +86 20-28607711</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>www.monalisa.cn</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>浙江省永康市长城工业区</t>
+          <t>广州市花都区花东镇港头工业区4号</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>59 rmb</t>
+          <t>Good merchant, perfect products</t>
         </is>
       </c>
     </row>
@@ -3979,18 +4103,34 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>东方喜卡</t>
+          <t>高成 (Gaocheng)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>果果</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+          <t>叶小龙/Dustin Ye</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>yedustin@gmail.com</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>+86-188 5861 0008</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>www.cngaocheng.cn</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>浙江省三门县浦坝港镇沿海工业城 (COASTAL INDUSTRIAL CITY, PUBAGANG TOWN, SANMEN, TAIZHOU CITY, ZHEJIANG PRO., CHINA)</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3998,7 +4138,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>249RMB</t>
+          <t>160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
         </is>
       </c>
     </row>
@@ -4008,38 +4148,42 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>优品声学 (YP ACOUSTICS)</t>
+          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD. / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>李尚声 (Shangsheng Li)</t>
+          <t>Pacao Yin</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>15915975597@163.com</t>
+          <t>pin@pingaolao.com</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>15915974406</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
+          <t>(0086)13903035682, (0086)0769-86378283, (0086)0769-86377522</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>6000RMB</t>
+          <t>15 RMB the product is interesting</t>
         </is>
       </c>
     </row>
@@ -4049,20 +4193,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>双龙智科</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
+          <t>浙江瑞鑫环保设备有限公司</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>吴仁余</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>294217488@qq.com</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
+          <t>13967444542, 0579-82889122</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>www.jhrxhb.com</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>江苏省太仓市双凤镇陆江路1号</t>
+          <t>浙江省金华市婺城区罗店镇北山路精工工业园</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4072,7 +4228,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2000RMB&amp;gt;</t>
+          <t>nearly $15,000 for this production line</t>
         </is>
       </c>
     </row>
@@ -4082,38 +4238,42 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GUANGDONG TUOXUN INTELLIGENT TECHNOLOGY CO., LTD</t>
+          <t>ZHEJIANG DOUBLE-LIN VALVES CO., LTD.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wing</t>
+          <t>Dream Lin</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>wuyunying08@gmail.com</t>
+          <t>sale15@double-lin.com</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>189-2984-9818, 0758-8578545</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
+          <t>86-020-66837727, 86-13710718529</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>www.double-lin.com</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
+          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>MOQ - 5000 and price - 7000 dollars</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -4123,38 +4283,38 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>佛山市方泓五金建材有限公司 (Foshan Fangheng Hardware Co., Ltd.)</t>
+          <t>苏州市富尔达科技股份有限公司</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>陈施志凯 (CHEN SHI ZHI KAI)</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>108455453@qq.com</t>
-        </is>
-      </c>
+          <t>袁佳磊</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>+86 134 3318 1558, 0757-8560 9159</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
+          <t>18652449601</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>www.cnfrd.cn</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+          <t>江苏省太仓市港区临江路1号</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>The price cheap, merchant very friendly</t>
+          <t>749</t>
         </is>
       </c>
     </row>
@@ -4164,28 +4324,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Countermast Technology (Dalian) Company Limited</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Eric Huang</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>sales.countermast.china@countermast.com</t>
+          <t>464565801@qq.com</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>400-100-2228</t>
+          <t>13813551160 / 0519-88784050</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>www.countermast.cn</t>
+          <t>www.ycpanel.com</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Building No.7, Zhongqing Industrial Park, Dalian free trade zone, Liaoning, China</t>
+          <t>No.28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4195,7 +4359,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>The price more cheaper, good quality</t>
+          <t>5000 USD</t>
         </is>
       </c>
     </row>
@@ -4205,42 +4369,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>广州蒙娜丽莎控股集团有限公司, 广州蒙娜丽莎卫浴股份有限公司</t>
+          <t>优品声学</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>严金霞</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>monalisa38@monalisa.cn</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>+86 13711113746, 400 020 1818, +86 20-28607711</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>www.monalisa.cn</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>广州市花都区花东镇港头工业区4号</t>
-        </is>
-      </c>
+          <t>杨伟杰</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Good merchant, perfect products</t>
+          <t>6000 RMB. I like the way they explain everything about their product.</t>
         </is>
       </c>
     </row>
@@ -4250,42 +4398,30 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>高成 (Gaocheng)</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>叶小龙/Dustin Ye</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>yedustin@gmail.com</t>
-        </is>
-      </c>
+          <t>双龙中科</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>+86-188 5861 0008</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>www.cngaocheng.cn</t>
-        </is>
-      </c>
+          <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>浙江省三门县浦坝港镇沿海工业城 (COASTAL INDUSTRIAL CITY, PUBAGANG TOWN, SANMEN, TAIZHOU CITY, ZHEJIANG PRO., CHINA)</t>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
+          <t>Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
         </is>
       </c>
     </row>
@@ -4295,42 +4431,30 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD. / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Pacao Yin</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>pin@pingaolao.com</t>
-        </is>
-      </c>
+          <t>深圳市家为安智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>(0086)13903035682, (0086)0769-86378283, (0086)0769-86377522</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
-        </is>
-      </c>
+          <t>186-0205-8898 / 400-608-0098</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+          <t>广东省佛山市南海区里水镇</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>15 RMB the product is interesting</t>
+          <t>249 RMB. They have fully described their products.</t>
         </is>
       </c>
     </row>
@@ -4340,32 +4464,20 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>浙江瑞鑫环保设备有限公司</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>吴仁余</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>294217488@qq.com</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>13967444542, 0579-82889122</t>
-        </is>
-      </c>
+          <t>广州市优品声学科技有限公司</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>www.jhrxhb.com</t>
+          <t>www.gzypsx.com</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>浙江省金华市婺城区罗店镇北山路精工工业园</t>
+          <t>广东省广州市番禺区南村镇南村西路138号德意创意园二层</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4375,7 +4487,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>nearly $15,000 for this production line</t>
+          <t>6000RMB，积极，详细地告诉了一切</t>
         </is>
       </c>
     </row>
@@ -4385,32 +4497,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ZHEJIANG DOUBLE-LIN VALVES CO., LTD.</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Dream Lin</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>sale15@double-lin.com</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>86-020-66837727, 86-13710718529</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>www.double-lin.com</t>
-        </is>
-      </c>
+          <t>科维尔 (VIR)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
+          <t>市长城工业区</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4420,7 +4516,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>2000 RMB</t>
         </is>
       </c>
     </row>
@@ -4430,28 +4526,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>苏州市富尔达科技股份有限公司</t>
+          <t>贵州佑远木业有限公司</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>袁佳磊</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>颜加伟</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>1164199388@qq.com</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>18652449601</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>www.cnfrd.cn</t>
-        </is>
-      </c>
+          <t>133 9983 5678</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>江苏省太仓市港区临江路1号</t>
+          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4461,7 +4557,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>400rmb /m2 good meeting</t>
         </is>
       </c>
     </row>
@@ -4471,42 +4567,34 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.,LTD.</t>
+          <t>广西豪庭家具有限公司 (Guangxi Haoting Furniture Co., Ltd.)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Eric Huang</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>464565801@qq.com</t>
-        </is>
-      </c>
+          <t>高学梅</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>13813551160 / 0519-88784050</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>www.ycpanel.com</t>
-        </is>
-      </c>
+          <t>17687627315</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>No.28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>5000 USD</t>
+          <t>350 rmb/m2</t>
         </is>
       </c>
     </row>
@@ -4516,26 +4604,42 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>优品声学</t>
+          <t>Moershu (摩尔舒卫浴)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>杨伟杰</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+          <t>Thea</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>moershu3@moershu.com</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>13957622087</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>www.moershu.com</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>6000 RMB. I like the way they explain everything about their product.</t>
+          <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
         </is>
       </c>
     </row>
@@ -4545,20 +4649,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>双龙中科</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
+          <t>Hangzhou Sciener Smart Technology Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Zoey Zhang</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>zoey@sciener.com</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
+          <t>+86 178-5768-8782</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>江苏省太仓市双凤镇陆江路1号</t>
+          <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4568,7 +4680,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
+          <t>20 / MOQ 100 Nice worker answered all questions</t>
         </is>
       </c>
     </row>
@@ -4578,30 +4690,38 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>深圳市家为安智能科技有限公司</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
+          <t>江西荣科新型材料有限公司 / JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Lucy Zeng (曾露)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>lucy@rongkedecor.com</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>186-0205-8898 / 400-608-0098</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>广东省佛山市南海区里水镇</t>
-        </is>
-      </c>
+          <t>+86-13134020034</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://www.amerdecor.com/</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>249 RMB. They have fully described their products.</t>
+          <t>80 rmb for 230 meter</t>
         </is>
       </c>
     </row>
@@ -4611,20 +4731,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>广州市优品声学科技有限公司</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
+          <t>SANNORA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>王冠</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>+86 13229297183</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>www.gzypsx.com</t>
+          <t>WWW.SANNORA.COM; WWW.SANNORA-BATH.COM</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区南村镇南村西路138号德意创意园二层</t>
+          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4634,7 +4762,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>6000RMB，积极，详细地告诉了一切</t>
+          <t>1560 rmb for whole item</t>
         </is>
       </c>
     </row>
@@ -4644,26 +4772,42 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>科维尔 (VIR)</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+          <t>Kaiping Gold Medal Sanitary Ware Co.,Ltd. / Guangdong Aosman Sanitary Ware Co.,Ltd</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Sophia Deng (邓小艳)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>sophiadeng@china-gold.cn</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>+181 3838 6948</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>http://www.china-gold.cn, http://www.aosman.cn</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>市长城工业区</t>
+          <t>198 Siqian Xi Road, Shuikou, Kaiping 529300, Guangdong PR.China</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2000 RMB</t>
+          <t>4600 rmb</t>
         </is>
       </c>
     </row>
@@ -4673,30 +4817,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>贵州佑远木业有限公司</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>颜加伟</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>1164199388@qq.com</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>133 9983 5678</t>
-        </is>
-      </c>
+          <t>东风汽车</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -4704,7 +4832,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>400rmb /m2 good meeting</t>
+          <t>50 Yuan 50g (The taste is authentic and aroma is really good</t>
         </is>
       </c>
     </row>
@@ -4714,34 +4842,38 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>广西豪庭家具有限公司 (Guangxi Haoting Furniture Co., Ltd.)</t>
+          <t>江西瑞京鸿兴实业有限公司</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>高学梅</t>
+          <t>朱支群</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>17687627315</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
+          <t>13763963598</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>www.jx-wpc.com</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
+          <t>江西省瑞金市经济开发区创业一路东侧</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>350 rmb/m2</t>
+          <t>250¥/м3</t>
         </is>
       </c>
     </row>
@@ -4751,32 +4883,32 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Moershu (摩尔舒卫浴)</t>
+          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Thea</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>moershu3@moershu.com</t>
+          <t>victor@ck-bath.com</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>13957622087</t>
+          <t>18656330093</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>www.moershu.com</t>
+          <t>https://ck-bath.com/</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
+          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4786,7 +4918,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
+          <t>4500¥</t>
         </is>
       </c>
     </row>
@@ -4796,38 +4928,42 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Hangzhou Sciener Smart Technology Co.,Ltd.</t>
+          <t>ciarra</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Zoey Zhang</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>zoey@sciener.com</t>
+          <t>linda.lu@ciarrahome.com</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>+86 178-5768-8782</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
+          <t>+86 1882 9964 960, +86 1343 2639 580</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>www.ciarrahome.com</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
+          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>20 / MOQ 100 Nice worker answered all questions</t>
+          <t>300¥ 300pcs</t>
         </is>
       </c>
     </row>
@@ -4837,30 +4973,30 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>江西荣科新型材料有限公司 / JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.</t>
+          <t>Yekalon Mills</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Lucy Zeng (曾露)</t>
+          <t>Viola Liu</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>lucy@rongkedecor.com</t>
+          <t>wood6@sennorwell.com</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>+86-13134020034</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>https://www.amerdecor.com/</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr"/>
+          <t>(86) 158 8931 1832</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
+        </is>
+      </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -4868,7 +5004,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>80 rmb for 230 meter</t>
+          <t>50¥ 1000pcs</t>
         </is>
       </c>
     </row>
@@ -4878,38 +5014,42 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SANNORA</t>
+          <t>Ideal Sanitary Ware Co., Ltd.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>王冠</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>Amy Liu 刘建美</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>export@ideal-china.net</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>+86 13229297183</t>
+          <t>+86 (0) 757 8558 9299</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>WWW.SANNORA.COM; WWW.SANNORA-BATH.COM</t>
+          <t>www.ideal-sanitary.com</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区</t>
+          <t>No.3 Hexi Road of Shashui, Yanghe Town, Gaoming District, Foshan City, Guangdong Province, 528515 - P.R.China.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>1560 rmb for whole item</t>
+          <t>500$ 100psc</t>
         </is>
       </c>
     </row>
@@ -4919,42 +5059,38 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kaiping Gold Medal Sanitary Ware Co.,Ltd. / Guangdong Aosman Sanitary Ware Co.,Ltd</t>
+          <t>佛山市旌晨铝门窗有限公司</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sophia Deng (邓小艳)</t>
+          <t>胡光辉</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>sophiadeng@china-gold.cn</t>
+          <t>1525423805@qq.com</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>+181 3838 6948</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>http://www.china-gold.cn, http://www.aosman.cn</t>
-        </is>
-      </c>
+          <t>18128752879</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>198 Siqian Xi Road, Shuikou, Kaiping 529300, Guangdong PR.China</t>
+          <t>佛山狮山镇谭边工业区崩岗头路四号之一</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>4600 rmb</t>
+          <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
         </is>
       </c>
     </row>
@@ -4962,20 +5098,44 @@
       <c r="A121" t="n">
         <v>120</v>
       </c>
-      <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>佛山市乾泽科技有限公司</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>陈可樑</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>hw-hardware@qian-ze.com</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>180 3863 7238</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>www.honeywell-hardware.com</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>广东省佛山市三水区云东海街道宝盛路2号1座三层（合和建筑五金园区北门）</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
         </is>
       </c>
     </row>
@@ -4983,12 +5143,20 @@
       <c r="A122" t="n">
         <v>121</v>
       </c>
-      <c r="B122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ARTY 艺和</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>广东 · 开平</t>
+        </is>
+      </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -4996,7 +5164,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
         </is>
       </c>
     </row>
@@ -5004,12 +5172,28 @@
       <c r="A123" t="n">
         <v>122</v>
       </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>景德镇窑珍陶瓷</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>徐云霞</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>13697981203</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5017,7 +5201,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>100 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -5027,14 +5211,26 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>东风汽车</t>
+          <t>苏州东山茶厂 (Suzhou Dongshan Biluochun Tea Co., Ltd.)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>0512-66281146</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>www.dsteaf.com</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>江苏省苏州市吴中区东山镇 (Dongshan Town, Wuzhong District, Suzhou City)</t>
+        </is>
+      </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5042,7 +5238,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>50 Yuan 50g (The taste is authentic and aroma is really good</t>
+          <t>150 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -5052,30 +5248,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>江西瑞京鸿兴实业有限公司</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>朱支群</t>
-        </is>
-      </c>
+          <t>武夷星</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>13763963598</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>www.jx-wpc.com</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>江西省瑞金市经济开发区创业一路东侧</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5083,7 +5263,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>250¥/м3</t>
+          <t>250 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -5093,42 +5273,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Anne</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>victor@ck-bath.com</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>18656330093</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>https://ck-bath.com/</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
-        </is>
-      </c>
+          <t>湖北龙王垭茶业有限公司</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>4500¥</t>
+          <t>498rmb/unit. I like the green tea in white color. First time to see colorless tea and it was amazing, i will recommend i</t>
         </is>
       </c>
     </row>
@@ -5138,32 +5298,20 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ciarra</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Linda</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>linda.lu@ciarrahome.com</t>
-        </is>
-      </c>
+          <t>知和香馆</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>+86 1882 9964 960, +86 1343 2639 580</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>www.ciarrahome.com</t>
-        </is>
-      </c>
+          <t>15926183211</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
+          <t>福建永春达埔</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5173,7 +5321,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>300¥ 300pcs</t>
+          <t>They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
         </is>
       </c>
     </row>
@@ -5183,28 +5331,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Yekalon Mills</t>
+          <t>San Nora (聖羅蘭·衛浴)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Viola Liu</t>
+          <t>ALLEN XU (许熙平)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>wood6@sennorwell.com</t>
+          <t>sales@sannora.com</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(86) 158 8931 1832</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
+          <t>+86 137 0263 0244, +86-757-86438259</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>WWW.SANNORA.COM, WWW.SANNORA-BATH.COM</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
+          <t>TANBIAN IND. ZONE, SHISHAN TOWN, NANHAI DIST., FOSHAN, GUANGDONG, CHINA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5214,7 +5366,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>50¥ 1000pcs</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -5224,42 +5376,38 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ideal Sanitary Ware Co., Ltd.</t>
+          <t>PTAT | 帕兰蒂诺</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Amy Liu 刘建美</t>
+          <t>Joy Yang</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>export@ideal-china.net</t>
+          <t>joy@rans.group</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>+86 (0) 757 8558 9299</t>
+          <t>+86-13757430301</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>www.ideal-sanitary.com</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>No.3 Hexi Road of Shashui, Yanghe Town, Gaoming District, Foshan City, Guangdong Province, 528515 - P.R.China.</t>
-        </is>
-      </c>
+          <t>www.ptat.cn</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>500$ 100psc</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -5269,38 +5417,38 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>佛山市旌晨铝门窗有限公司</t>
+          <t>万磊建筑涂料有限公司</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>胡光辉</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>1525423805@qq.com</t>
-        </is>
-      </c>
+          <t>万磊市场部</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>18128752879</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
+          <t>186-8825-1404, 4000-147-187</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>http://www.fswanlei.com</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>佛山狮山镇谭边工业区崩岗头路四号之一</t>
+          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Coatings &amp; Paints</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -5310,42 +5458,42 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>佛山市乾泽科技有限公司</t>
+          <t>ZHEJIANG SEATING TECHNOLOGY CO., LTD.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>陈可樑</t>
+          <t>May Zhang</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>hw-hardware@qian-ze.com</t>
+          <t>sales5@anjeurostilefurniture.com</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>180 3863 7238</t>
+          <t>+86 182 5727 1590</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>www.honeywell-hardware.com</t>
+          <t>www.zjseating.com</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>广东省佛山市三水区云东海街道宝盛路2号1座三层（合和建筑五金园区北门）</t>
+          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
+          <t>1100</t>
         </is>
       </c>
     </row>
@@ -5355,26 +5503,42 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ARTY 艺和</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>Chaozhou Lefu Sanitary Ware Technology Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>lucy@lefucz.com</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>+0086 18098114370</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>www.lefucz.com</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>广东 · 开平</t>
+          <t>Lefu Sanitary Ware, Sheweikeng, Dengtang Town, Chaoan District, Chaozhou City, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
+          <t>1050</t>
         </is>
       </c>
     </row>
@@ -5384,24 +5548,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>景德镇窑珍陶瓷</t>
+          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co., Ltd.)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>徐云霞</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>胡沛能 / Oliver Hu</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>oliver@wireking.com</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>13697981203</t>
+          <t>+86-13802465791</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
+          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5411,7 +5579,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>100 RMB per sample. The taste is very good</t>
+          <t>550</t>
         </is>
       </c>
     </row>
@@ -5421,26 +5589,14 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>苏州东山茶厂 (Suzhou Dongshan Biluochun Tea Co., Ltd.)</t>
+          <t>宜昌毛尖</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>0512-66281146</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>www.dsteaf.com</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>江苏省苏州市吴中区东山镇 (Dongshan Town, Wuzhong District, Suzhou City)</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5448,7 +5604,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>150 RMB per sample. The taste is very good</t>
+          <t>Prices are go and packing and Verstaliy is more</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5614,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>武夷星</t>
+          <t>湖北龙王娅茶业有限公司</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -5473,7 +5629,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>250 RMB per sample. The taste is very good</t>
+          <t>The taste anaroma is good of this product then anyother</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5639,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>湖北龙王垭茶业有限公司</t>
+          <t>正山堂 (ZHENG SHAN TANG)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -5498,7 +5654,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>498rmb/unit. I like the green tea in white color. First time to see colorless tea and it was amazing, i will recommend i</t>
+          <t>the product prices are very good. looks attractive</t>
         </is>
       </c>
     </row>
@@ -5508,20 +5664,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>知和香馆</t>
+          <t>浙江雅柔装饰材料有限公司 (Zhejiang Yarou Decoration Material Co., Ltd.)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>sale01@yarouwallpaper.com.cn</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>15926183211</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
+          <t>+86-18069994326, +86-18069994377</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://www.yarouwallpaper.com.cn/</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>福建永春达埔</t>
+          <t>浙江省金华市义乌市福田街道涌金大道87号厂房二楼 (No. 1, Factory 2, Yongjin Avenue 87, Futian Subdistrict, Yiwu City, Jinhua City, Zhejiang Province)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5531,7 +5695,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
+          <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
         </is>
       </c>
     </row>
@@ -5541,32 +5705,24 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>San Nora (聖羅蘭·衛浴)</t>
+          <t>淄博永顺装饰材料有限公司</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ALLEN XU (许熙平)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>sales@sannora.com</t>
-        </is>
-      </c>
+          <t>戴艳辉</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>+86 137 0263 0244, +86-757-86438259</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>WWW.SANNORA.COM, WWW.SANNORA-BATH.COM</t>
-        </is>
-      </c>
+          <t>18830173388</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>TANBIAN IND. ZONE, SHISHAN TOWN, NANHAI DIST., FOSHAN, GUANGDONG, CHINA</t>
+          <t>石家庄市正定县曙光路49号东标和聚居</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5576,7 +5732,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
         </is>
       </c>
     </row>
@@ -5586,30 +5742,34 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PTAT | 帕兰蒂诺</t>
+          <t>宏宇集团 (HONGYU GROUP)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Joy Yang</t>
+          <t>Melina 王玲</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>joy@rans.group</t>
+          <t>lina@hongyugroup.com</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>+86-13757430301</t>
+          <t>+86 13827702216</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>www.ptat.cn</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr"/>
+          <t>en.hongyugroup.com</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
+        </is>
+      </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5617,7 +5777,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -5627,38 +5787,42 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>万磊建筑涂料有限公司</t>
+          <t>Chongnuo(Shandong)NewMaterial Co.,Ltd.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>万磊市场部</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
+          <t>Daisy</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>sales06@chongnuo-floors.com</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>186-8825-1404, 4000-147-187</t>
+          <t>+86 19906379675</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>http://www.fswanlei.com</t>
+          <t>www.chongnuo-floors.com</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区</t>
+          <t>QingyunCounty,DezhouCity,China</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Coatings &amp; Paints</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>9$</t>
         </is>
       </c>
     </row>
@@ -5668,34 +5832,26 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ZHEJIANG SEATING TECHNOLOGY CO., LTD.</t>
+          <t>上海德翔木业有限公司 (Shanghai Dexiang Wood Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>May Zhang</t>
+          <t>崔强 (Cui Qiang)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>sales5@anjeurostilefurniture.com</t>
+          <t>513437660@qq.com</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>+86 182 5727 1590</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>www.zjseating.com</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
-        </is>
-      </c>
+          <t>+8618901960431</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5703,7 +5859,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>13.25$</t>
         </is>
       </c>
     </row>
@@ -5713,42 +5869,38 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Chaozhou Lefu Sanitary Ware Technology Co., Ltd.</t>
+          <t>中材(邯郸)新材料有限公司 (China National Building Materials (Handan) New Materials Co.,Ltd.)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Wangfeng</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>lucy@lefucz.com</t>
+          <t>2523911877@qq.com</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>+0086 18098114370</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>www.lefucz.com</t>
-        </is>
-      </c>
+          <t>13233648687</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lefu Sanitary Ware, Sheweikeng, Dengtang Town, Chaoan District, Chaozhou City, Guangdong Province, China</t>
+          <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>8.83$</t>
         </is>
       </c>
     </row>
@@ -5758,28 +5910,20 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co., Ltd.)</t>
+          <t>Zhejiang Tianyan Holding Ltd</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>胡沛能 / Oliver Hu</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>oliver@wireking.com</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>+86-13802465791</t>
-        </is>
-      </c>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
+          <t>Taizhou, Zhejiang</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5789,7 +5933,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>640 PCs, 3.72 RMB very good</t>
         </is>
       </c>
     </row>
@@ -5799,22 +5943,38 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>宜昌毛尖</t>
+          <t>Foshan Cofesu Sanitary Ware Co., Ltd.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>sales@cofesu.com</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>+86 181 2821 2128</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>www.cofesu.com</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Foshan, Guangdong, China</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Prices are go and packing and Verstaliy is more</t>
+          <t>30 PCs, 420 RMB, need check quality</t>
         </is>
       </c>
     </row>
@@ -5824,14 +5984,30 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>湖北龙王娅茶业有限公司</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
+          <t>中国广东柜邦精密金属制品有限公司 (China Guangdong Guibang Precision Metal Products Co.Ltd)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>唐一智 (JUNIOR)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>13621417@qq.com</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>+86-156-2562-1155</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
+        </is>
+      </c>
       <c r="H145" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5839,7 +6015,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>The taste anaroma is good of this product then anyother</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -5849,22 +6025,38 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>正山堂 (ZHENG SHAN TANG)</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
+          <t>Jieyang Yagegu Hardware Products Co., LTD</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Zoya</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2291828903@qq.com</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>+86 132 8810 6615</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
+        </is>
+      </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>the product prices are very good. looks attractive</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -5872,20 +6064,40 @@
       <c r="A147" t="n">
         <v>146</v>
       </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>广东启宏盛精密五金制品有限公司 (GUANGDONG QIHONGSHENG PRECISION HARDWARE PRODUCTS CO., LTD)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>邓美君 Jessica</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>bailide_hinge@163.com</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>+86 13823419116 / 0758-8565117</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>560 moq 200</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -5895,28 +6107,32 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>浙江雅柔装饰材料有限公司 (Zhejiang Yarou Decoration Material Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
+          <t>广东亚当斯金属精密制造有限公司 (Guangdong Adams Metal Precision Manufacturing Co.,Ltd)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Kelly Liang (梁凯莹)</t>
+        </is>
+      </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>sale01@yarouwallpaper.com.cn</t>
+          <t>kelly@adamsmetal.com.cn</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>+86-18069994326, +86-18069994377</t>
+          <t>+86-180-2935-2895 / +86-757-25331912</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.yarouwallpaper.com.cn/</t>
+          <t>www.adamsmetal.com.cn</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市福田街道涌金大道87号厂房二楼 (No. 1, Factory 2, Yongjin Avenue 87, Futian Subdistrict, Yiwu City, Jinhua City, Zhejiang Province)</t>
+          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -5926,7 +6142,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
+          <t>Depend on item</t>
         </is>
       </c>
     </row>
@@ -5936,26 +6152,18 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>淄博永顺装饰材料有限公司</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>戴艳辉</t>
-        </is>
-      </c>
+          <t>明德 (Mingde)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>18830173388</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>石家庄市正定县曙光路49号东标和聚居</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>www.mingde-china.com</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5963,7 +6171,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
+          <t>Depend of quantity</t>
         </is>
       </c>
     </row>
@@ -5973,42 +6181,42 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>宏宇集团 (HONGYU GROUP)</t>
+          <t>佛山市顺德区腾徽精密智造有限公司 (FoShan ShunDe TengHui Precision Intelligent Manufacturing Co., Ltd)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Melina 王玲</t>
+          <t>刘婉莹 Carol Liu</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>lina@hongyugroup.com</t>
+          <t>tenghuihardware@126.com</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>+86 13827702216</t>
+          <t>+86 133 1836 4599</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>en.hongyugroup.com</t>
+          <t>www.teehve.cn</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
+          <t>广东省佛山市顺德区勒流街道众涌村港口路以西8-9号之二 (No.8-9, West of GangKou Road, Zhongchong Village, Leliu Town, Shunde District, Foshan City, Guangdong, China)</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100/square meter</t>
         </is>
       </c>
     </row>
@@ -6016,12 +6224,36 @@
       <c r="A151" t="n">
         <v>150</v>
       </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>DUOCAI TENT (多彩帐蓬)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Jimmy 黄锦民</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>sales003@sdduocaizp.com</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>(86)133 2294 8506, +86-766-8298662</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>www.dc-tent.com, www.sdduocaizp.com</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>云浮市云安区佛山(云浮)产业转移工业园86号 (No.86 Foshan(Yunfu) Industrial transfer park, yunan, yunfu, Guangdong China)</t>
+        </is>
+      </c>
       <c r="H151" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -6029,7 +6261,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>RMB 15705 MOQ5; pleasant impression</t>
         </is>
       </c>
     </row>
@@ -6039,42 +6271,42 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Chongnuo(Shandong)NewMaterial Co.,Ltd.</t>
+          <t>佛山市路乐户外制品有限公司 (FOSHAN RULER OUTDOOR HARDWARES CO.,LTD)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Daisy</t>
+          <t>Marco Lau (刘嘉乐)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>sales06@chongnuo-floors.com</t>
+          <t>RULERAWNING07@163.COM</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>+86 19906379675</t>
+          <t>+86 13129016338</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>www.chongnuo-floors.com</t>
+          <t>WWW.RULER-AWNING.COM</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>QingyunCounty,DezhouCity,China</t>
+          <t>END OF ROAD SHATANXIAN, SHASHUI INDUSTRIAL ZONE, SONGGANG TOWN, SHISHAN DISTRICT, FOSHAN CITY, GUANGDONG PROVINCE, CHINA, 528200</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>9$</t>
+          <t>MOQ5 25799 RMB</t>
         </is>
       </c>
     </row>
@@ -6084,26 +6316,34 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>上海德翔木业有限公司 (Shanghai Dexiang Wood Industry Co., Ltd.)</t>
+          <t>Avant Sports Industrial Co., Ltd.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>崔强 (Cui Qiang)</t>
+          <t>Jay Zhou</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>513437660@qq.com</t>
+          <t>jay@avant.com.cn</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>+8618901960431</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
+          <t>+86-13128980150, +86-755-2968-8357</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>www.avantseating.com</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Avant Industrial Park, Zhoushi Road, Bao'an, Shenzhen, Guangdong Province, China</t>
+        </is>
+      </c>
       <c r="H153" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -6111,7 +6351,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>13.25$</t>
+          <t>RMB 19479; MOQ 1</t>
         </is>
       </c>
     </row>
@@ -6121,28 +6361,32 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>中材(邯郸)新材料有限公司 (China National Building Materials (Handan) New Materials Co.,Ltd.)</t>
+          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd.)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Wangfeng</t>
+          <t>孟少美 (Elite Meng)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2523911877@qq.com</t>
+          <t>ttf@hbtfjs.com</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>13233648687</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr"/>
+          <t>+86-13103196326</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>www.hbtfjs.com</t>
+        </is>
+      </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
+          <t>河北省隆尧县东谷子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6152,7 +6396,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8.83$</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -6162,30 +6406,42 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Zhejiang Tianyan Holding Ltd</t>
+          <t>揭阳市新骏业五金制品有限公司 (JIEYANG XINJUNYE HARDWARE PRODUCTS CO., LTD)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Nicole</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
+          <t>林树丹 (Lin Shudan)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>linshdong@qq.com</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>13751676456</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>www.xinjunye.com</t>
+        </is>
+      </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Taizhou, Zhejiang</t>
+          <t>广东省揭阳市揭东区锡场工业区 (Xichang Industrial Zone, Jiedong District, Jieyang City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>640 PCs, 3.72 RMB very good</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -6195,28 +6451,32 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Foshan Cofesu Sanitary Ware Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr"/>
+          <t>广州蒙娜丽莎控股集团有限公司 / 广州蒙娜丽莎卫浴股份有限公司</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>伍乐彤</t>
+        </is>
+      </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>sales@cofesu.com</t>
+          <t>monalisa702@monalisa.cn</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>+86 181 2821 2128</t>
+          <t>86 13711117863, 400 020 1818, 86 20-28607722, 86 20-28607788</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>www.cofesu.com</t>
+          <t>www.monalisa.cn</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Foshan, Guangdong, China</t>
+          <t>广州市花都区花东镇港头工业区4号</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6226,7 +6486,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>30 PCs, 420 RMB, need check quality</t>
+          <t>2000$, can be customized, very convenient</t>
         </is>
       </c>
     </row>
@@ -6234,12 +6494,36 @@
       <c r="A157" t="n">
         <v>156</v>
       </c>
-      <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>中山藝進不銹鋼裝飾制品有限公司 (ZHONGSHAN YIJIN STAINLESS STEEL DECORATION CO., LTD.)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Anson Yuen</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>info@hugemount.com</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>150 1954 6322 / 86-760-88702663</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>www.yijin.com</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>中国广东省中山市港口镇石特社区穗安工业区迎富2路1号 (NO.1, Ying Fu 2 Road, Sui An Gong Ye Qu, Gang Kou Zhen Shi Te She Qu, Zhongshan City, Guangdong Province, P.R.China)</t>
+        </is>
+      </c>
       <c r="H157" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -6247,7 +6531,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>10 PCs, 1150 RMB, very good</t>
+          <t>38$, very unique</t>
         </is>
       </c>
     </row>
@@ -6257,38 +6541,42 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>中国广东柜邦精密金属制品有限公司 (China Guangdong Guibang Precision Metal Products Co.Ltd)</t>
+          <t>宣城市宠爱卫浴有限公司 (CHONGAI SANITARY WARE CO., LTD.)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>唐一智 (JUNIOR)</t>
+          <t>Lucy (卢美珍)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>13621417@qq.com</t>
+          <t>export@vnsmilo.com</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>+86-156-2562-1155</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr"/>
+          <t>+86-13757322119</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>www.vnsmilo.com</t>
+        </is>
+      </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
+          <t>Xuancheng City Anhui, CHINA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>2050 rmb, very interesting, convenient to use for pets</t>
         </is>
       </c>
     </row>
@@ -6298,38 +6586,30 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Jieyang Yagegu Hardware Products Co., LTD</t>
+          <t>广西中晨木业有限公司 (Guangxi Zhongchen Wood Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Zoya</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2291828903@qq.com</t>
-        </is>
-      </c>
+          <t>张爱彬 (Zhang Aibin)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>+86 132 8810 6615</t>
+          <t>+86 18178085851</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
-        </is>
-      </c>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>25 rmb, 1 box, like this product</t>
         </is>
       </c>
     </row>
@@ -6339,38 +6619,42 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>广东启宏盛精密五金制品有限公司 (GUANGDONG QIHONGSHENG PRECISION HARDWARE PRODUCTS CO., LTD)</t>
+          <t>NINGBO YUSHENG HOME TECH CO., LTD. (宁波裕盛家居科技有限公司)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>邓美君 Jessica</t>
+          <t>Tequila Xu (徐孟杰)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>bailide_hinge@163.com</t>
+          <t>marketing@cxyushun.com, tequila8xu@gmail.com</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>+86 13823419116 / 0758-8565117</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr"/>
+          <t>0086-13819449988, +86 574 63190388</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>www.cxys8.com</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
+          <t>中国浙江慈溪市杨梅大道南路1518号 (NO.1518, YANGMEI AVENUE SOUTH ROAD, CIXI CITY, ZHEJIANG, CHINA)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>34 rmb, 1000, normal</t>
         </is>
       </c>
     </row>
@@ -6380,42 +6664,42 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>广东亚当斯金属精密制造有限公司 (Guangdong Adams Metal Precision Manufacturing Co.,Ltd)</t>
+          <t>河北建华锁业有限公司 (Hebei Jianhua Lock Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Kelly Liang (梁凯莹)</t>
+          <t>刘芳 (Jane Liu)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>kelly@adamsmetal.com.cn</t>
+          <t>jane@dirock.cn</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>+86-180-2935-2895 / +86-757-25331912</t>
+          <t>187 1377 2087</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>www.adamsmetal.com.cn</t>
+          <t>http://www.dirock.cn</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
+          <t>河北省泊头市寺门村镇后牛屯</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Depend on item</t>
+          <t>40 rmb, 2000, very good</t>
         </is>
       </c>
     </row>
@@ -6425,18 +6709,34 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>明德 (Mingde)</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
+          <t>浙江安吉双虎竹木业有限公司 / 安吉诺迪新材料有限公司</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>周瑶琳</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>lisa.nordi@nuodibm.com</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>+86-137 3822 8209</t>
+        </is>
+      </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>www.mingde-china.com</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr"/>
+          <t>www.tigerbamboo.com / www.nuodibm.com</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
+        </is>
+      </c>
       <c r="H162" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -6444,7 +6744,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Depend of quantity</t>
+          <t>1 container 250 rmb</t>
         </is>
       </c>
     </row>
@@ -6454,42 +6754,42 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>佛山市顺德区腾徽精密智造有限公司 (FoShan ShunDe TengHui Precision Intelligent Manufacturing Co., Ltd)</t>
+          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd)</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>刘婉莹 Carol Liu</t>
+          <t>马世晓 (Amelia Ma)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>tenghuihardware@126.com</t>
+          <t>tf@hbtfjs.com, mashixiaomsx@163.com</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>+86 133 1836 4599</t>
+          <t>15097968589, 0319-6581195</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>www.teehve.cn</t>
+          <t>www.hbtfjs.com</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区勒流街道众涌村港口路以西8-9号之二 (No.8-9, West of GangKou Road, Zhongchong Village, Leliu Town, Shunde District, Foshan City, Guangdong, China)</t>
+          <t>河北省隆尧县公子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>100/square meter</t>
+          <t>1 container 700 rmb</t>
         </is>
       </c>
     </row>
@@ -6499,648 +6799,24 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DUOCAI TENT (多彩帐蓬)</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Jimmy 黄锦民</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>sales003@sdduocaizp.com</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>(86)133 2294 8506, +86-766-8298662</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>www.dc-tent.com, www.sdduocaizp.com</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>云浮市云安区佛山(云浮)产业转移工业园86号 (No.86 Foshan(Yunfu) Industrial transfer park, yunan, yunfu, Guangdong China)</t>
-        </is>
-      </c>
+          <t>BANRUGE / KING LIYE</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>RMB 15705 MOQ5; pleasant impression</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>164</v>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>佛山市路乐户外制品有限公司 (FOSHAN RULER OUTDOOR HARDWARES CO.,LTD)</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Marco Lau (刘嘉乐)</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>RULERAWNING07@163.COM</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>+86 13129016338</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>WWW.RULER-AWNING.COM</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>END OF ROAD SHATANXIAN, SHASHUI INDUSTRIAL ZONE, SONGGANG TOWN, SHISHAN DISTRICT, FOSHAN CITY, GUANGDONG PROVINCE, CHINA, 528200</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Doors &amp; Windows</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>MOQ5 25799 RMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>165</v>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Avant Sports Industrial Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Jay Zhou</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>jay@avant.com.cn</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>+86-13128980150, +86-755-2968-8357</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>www.avantseating.com</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Avant Industrial Park, Zhoushi Road, Bao'an, Shenzhen, Guangdong Province, China</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>RMB 19479; MOQ 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>166</v>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>孟少美 (Elite Meng)</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>ttf@hbtfjs.com</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>+86-13103196326</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>www.hbtfjs.com</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>河北省隆尧县东谷子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>167</v>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>揭阳市新骏业五金制品有限公司 (JIEYANG XINJUNYE HARDWARE PRODUCTS CO., LTD)</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>林树丹 (Lin Shudan)</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>linshdong@qq.com</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>13751676456</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>www.xinjunye.com</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>广东省揭阳市揭东区锡场工业区 (Xichang Industrial Zone, Jiedong District, Jieyang City, Guangdong Province)</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>168</v>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>广州蒙娜丽莎控股集团有限公司 / 广州蒙娜丽莎卫浴股份有限公司</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>伍乐彤</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>monalisa702@monalisa.cn</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>86 13711117863, 400 020 1818, 86 20-28607722, 86 20-28607788</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>www.monalisa.cn</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>广州市花都区花东镇港头工业区4号</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Bath &amp; Sanitary</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>2000$, can be customized, very convenient</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>169</v>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>中山藝進不銹鋼裝飾制品有限公司 (ZHONGSHAN YIJIN STAINLESS STEEL DECORATION CO., LTD.)</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Anson Yuen</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>info@hugemount.com</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>150 1954 6322 / 86-760-88702663</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>www.yijin.com</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>中国广东省中山市港口镇石特社区穗安工业区迎富2路1号 (NO.1, Ying Fu 2 Road, Sui An Gong Ye Qu, Gang Kou Zhen Shi Te She Qu, Zhongshan City, Guangdong Province, P.R.China)</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Coatings &amp; Paints</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>38$, very unique</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>170</v>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>宣城市宠爱卫浴有限公司 (CHONGAI SANITARY WARE CO., LTD.)</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Lucy (卢美珍)</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>export@vnsmilo.com</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>+86-13757322119</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>www.vnsmilo.com</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Xuancheng City Anhui, CHINA</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Bath &amp; Sanitary</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>2050 rmb, very interesting, convenient to use for pets</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>171</v>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>广西中晨木业有限公司 (Guangxi Zhongchen Wood Industry Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>张爱彬 (Zhang Aibin)</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>+86 18178085851</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>25 rmb, 1 box, like this product</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>172</v>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>NINGBO YUSHENG HOME TECH CO., LTD. (宁波裕盛家居科技有限公司)</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Tequila Xu (徐孟杰)</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>marketing@cxyushun.com, tequila8xu@gmail.com</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>0086-13819449988, +86 574 63190388</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>www.cxys8.com</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>中国浙江慈溪市杨梅大道南路1518号 (NO.1518, YANGMEI AVENUE SOUTH ROAD, CIXI CITY, ZHEJIANG, CHINA)</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>34 rmb, 1000, normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>173</v>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>河北建华锁业有限公司 (Hebei Jianhua Lock Industry Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>刘芳 (Jane Liu)</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>jane@dirock.cn</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>187 1377 2087</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>http://www.dirock.cn</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>河北省泊头市寺门村镇后牛屯</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>40 rmb, 2000, very good</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>174</v>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>浙江安吉双虎竹木业有限公司 / 安吉诺迪新材料有限公司</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>周瑶琳</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>lisa.nordi@nuodibm.com</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>+86-137 3822 8209</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>www.tigerbamboo.com / www.nuodibm.com</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1 container 250 rmb</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>175</v>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd)</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>马世晓 (Amelia Ma)</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>tf@hbtfjs.com, mashixiaomsx@163.com</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>15097968589, 0319-6581195</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>www.hbtfjs.com</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>河北省隆尧县公子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>1 container 700 rmb</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>176</v>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>BANRUGE / KING LIYE</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Home Furnishing</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
           <t>Прайс отправят, от 100ед, хорошая компания</t>
         </is>
       </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>177</v>
-      </c>
-      <c r="B178" t="inlineStr"/>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>178</v>
-      </c>
-      <c r="B179" t="inlineStr"/>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>179</v>
-      </c>
-      <c r="B180" t="inlineStr"/>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I164"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,26 +682,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>旭博卫浴</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>榜威电子科技（上海）有限公司 (Bweetech Electronics Technology (Shanghai) Co., Ltd)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>骆剑 (Kim Lok)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>kim.lok@bweetech.com</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>186-5759-0678</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>www.bweetech.com</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>福建省南安市</t>
+          <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70$</t>
+          <t>500pcs / $100USD for pcs</t>
         </is>
       </c>
     </row>
@@ -711,22 +727,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>旭博恒温</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>DEIOUX WINDOWS &amp; DOORS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CANDICE CHOU</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>sales5@deiouxwindows.com</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>+86-13392246940</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>300 yuan</t>
+          <t>Custom order</t>
         </is>
       </c>
     </row>
@@ -736,42 +768,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>榜威电子科技（上海）有限公司 (Bweetech Electronics Technology (Shanghai) Co., Ltd)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>骆剑 (Kim Lok)</t>
-        </is>
-      </c>
+          <t>China Warren Windows and Doors Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>kim.lok@bweetech.com</t>
+          <t>info@warrenwindows.com</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>186-5759-0678</t>
+          <t>+86-400-811-0300</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>www.bweetech.com</t>
+          <t>www.warrenwindows.com</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
+          <t>Room 1007, Block B, Wangjing SOHO, Chaoyang District, Beijing, China</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>500pcs / $100USD for pcs</t>
+          <t>Custom order</t>
         </is>
       </c>
     </row>
@@ -781,14 +809,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>深圳市塞恩斯电子有限公司 (Sands Evermore Electronic)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Zhongshan Smartek Security Technology Co.,LTD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tim Pan</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>market@smarteklock.com</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>+86-15889896019</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>www.smarteklock.com</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City Guangdong, China 528415</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Smart Home &amp; Lighting</t>
@@ -796,7 +844,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50pcs / $50USD for pcs</t>
+          <t>170 to 335 usd</t>
         </is>
       </c>
     </row>
@@ -806,13 +854,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HDL</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>HDL Automation Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Krystal Wei</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>krystal@hdlautomation.com</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+86 19512956186</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>www.hdlautomation.com</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
@@ -821,7 +885,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20pcs / $100USD for pcs</t>
+          <t>100 to up</t>
         </is>
       </c>
     </row>
@@ -831,38 +895,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DEIOUX WINDOWS &amp; DOORS</t>
+          <t>Ningbo AIFEIBAO Intelligent Security Co., Ltd</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CANDICE CHOU</t>
+          <t>Sean Xiao</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sales5@deiouxwindows.com</t>
+          <t>sales@aifeibao.com</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+86-13392246940</t>
+          <t>0086 198 1730 8681</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>www.afbsafe.com</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No.1 Donghu Rd., Daxie Development Zone, Ningbo, China (315812)</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Custom order</t>
+          <t>100 to up usd</t>
         </is>
       </c>
     </row>
@@ -872,38 +940,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>China Warren Windows and Doors Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>info@warrenwindows.com</t>
-        </is>
-      </c>
+          <t>佛山市普辉亚科技有限公司 (Foshan Pu Huiya Technology Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>邹隆鹏</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+86-400-811-0300</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>www.warrenwindows.com</t>
-        </is>
-      </c>
+          <t>15818099349</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Room 1007, Block B, Wangjing SOHO, Chaoyang District, Beijing, China</t>
+          <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Custom order</t>
+          <t>Super</t>
         </is>
       </c>
     </row>
@@ -913,30 +977,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Matthew window&amp;door</t>
+          <t>广东招材建材科技有限公司</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>张小洪 (Matthew / Kevin)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>黎桃桃</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>toto.liblun@gmail.com</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>+8618934320539</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>www.liblun.com</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Foshan, Guangdong</t>
+          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Custom order</t>
+          <t>Super</t>
         </is>
       </c>
     </row>
@@ -946,42 +1022,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zhongshan Smartek Security Technology Co.,LTD</t>
+          <t>浙江鑫东洁具有限公司 (ZHEJIANG XINDONG SANITARY WARE CO., LTD.)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tim Pan</t>
+          <t>曾燕燕 Elyn</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>market@smarteklock.com</t>
+          <t>sales03@cn-xindong.com</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+86-15889896019</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>www.smarteklock.com</t>
-        </is>
-      </c>
+          <t>0086-182 5765 3405, 0086-576-87493988</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City Guangdong, China 528415</t>
+          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>170 to 335 usd</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -991,30 +1063,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HDL Automation Co., Ltd.</t>
+          <t>杭州南博装饰材料有限公司</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Krystal Wei</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>krystal@hdlautomation.com</t>
-        </is>
-      </c>
+          <t>王小忠</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+86 19512956186</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>www.hdlautomation.com</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>浙江省杭州市临平区运河街道育士路53-1号</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1022,7 +1090,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100 to up</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -1032,42 +1100,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ningbo AIFEIBAO Intelligent Security Co., Ltd</t>
+          <t>台州旭升卫浴股份有限公司</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sean Xiao</t>
+          <t>应杨军</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>sales@aifeibao.com</t>
+          <t>3572780651@qq.com</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0086 198 1730 8681</t>
+          <t>13511470999</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>www.afbsafe.com</t>
+          <t>www.xs88.cn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No.1 Donghu Rd., Daxie Development Zone, Ningbo, China (315812)</t>
+          <t>浙江省台州市台州湾新区海虹大道228#</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100 to up usd</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -1077,24 +1145,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>佛山市普辉亚科技有限公司 (Foshan Pu Huiya Technology Co., Ltd.)</t>
+          <t>NIFO 耐孚</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>邹隆鹏</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>顾鹏</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>962460053@qq.com</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15818099349</t>
+          <t>13326792105</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
+          <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1104,7 +1176,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>Wall sheet , 200 rmb per meter , 2000 mtr,</t>
         </is>
       </c>
     </row>
@@ -1114,42 +1186,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>广东招材建材科技有限公司</t>
+          <t>Zhejiang Oushe Home Improvement And New Materials Co., Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>黎桃桃</t>
+          <t>Davis Dong 董伟杰</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>toto.liblun@gmail.com</t>
+          <t>sales05@authoe.com</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>+8618934320539</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>www.liblun.com</t>
-        </is>
-      </c>
+          <t>+86-18906831082</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
+          <t>Jiaxing/Hongkong</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>Handles , 500 moq , 100 rmb per handle</t>
         </is>
       </c>
     </row>
@@ -1159,38 +1227,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>浙江鑫东洁具有限公司 (ZHEJIANG XINDONG SANITARY WARE CO., LTD.)</t>
+          <t>JIN OGMEI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>曾燕燕 Elyn</t>
+          <t>Alex Xing</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>sales03@cn-xindong.com</t>
+          <t>kindeli1771@gmail.com</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0086-182 5765 3405, 0086-576-87493988</t>
+          <t>+86-18302200384</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
+          <t>Shijiazhuang City, Hebei Province</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
         </is>
       </c>
     </row>
@@ -1200,34 +1268,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>杭州南博装饰材料有限公司</t>
+          <t>温州金锏智能锁具有限公司</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>王小忠</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>张丽</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>jinjian19@jinjianlock.com</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>15067804393</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>www.jinjianlock.com</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区运河街道育士路53-1号</t>
+          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for</t>
         </is>
       </c>
     </row>
@@ -1237,42 +1313,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台州旭升卫浴股份有限公司</t>
+          <t>上海世灿国际贸易有限公司</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>应杨军</t>
+          <t>杨苗</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3572780651@qq.com</t>
+          <t>yangm618@163.com</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13511470999</t>
+          <t>138 1618 4706</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>www.xs88.cn</t>
+          <t>http://www.shicanchina.com</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>浙江省台州市台州湾新区海虹大道228#</t>
+          <t>上海市浦东新区商城路889号C3-B06</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models an</t>
         </is>
       </c>
     </row>
@@ -1282,38 +1358,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NIFO 耐孚</t>
+          <t>COLOMAC DECOR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>顾鹏</t>
+          <t>Aaron Liu</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>962460053@qq.com</t>
+          <t>aaron@ccolomac.com</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13326792105</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>+86-0371-66350801, +86 15936292861</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>www.ccolomac.com</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
+          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Wall sheet , 200 rmb per meter , 2000 mtr,</t>
+          <t>Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 10</t>
         </is>
       </c>
     </row>
@@ -1323,38 +1403,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zhejiang Oushe Home Improvement And New Materials Co., Ltd.</t>
+          <t>佛山市同路匠人家具有限公司</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Davis Dong 董伟杰</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>sales05@authoe.com</t>
-        </is>
-      </c>
+          <t>赖华芳</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>+86-18906831082</t>
+          <t>13727479513, 400-8339513</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Jiaxing/Hongkong</t>
+          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Handles , 500 moq , 100 rmb per handle</t>
+          <t>Хорошее, 400rmb</t>
         </is>
       </c>
     </row>
@@ -1364,30 +1440,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JIN OGMEI</t>
+          <t>固豪木业 | SUNDIN尚鼎</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alex Xing</t>
+          <t>Clément / 付雄豪</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>kindeli1771@gmail.com</t>
+          <t>clement.fu@cqsdmy.com</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>+86-18302200384</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Shijiazhuang City, Hebei Province</t>
-        </is>
-      </c>
+          <t>+(86) 19112691557</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>www.guhaogroup.com / www.cqsdmy.com</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1395,7 +1471,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
+          <t>Хорошее , 1500rmb</t>
         </is>
       </c>
     </row>
@@ -1405,42 +1481,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>温州金锏智能锁具有限公司</t>
+          <t>佛山市嘉豪飞度家具有限公司 (FOSHAN KAHO FIT FURNITURE CO., LTD.)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>张丽</t>
+          <t>周灿灿</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jinjian19@jinjianlock.com</t>
+          <t>15986196312@163.com</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>15067804393</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>www.jinjianlock.com</t>
-        </is>
-      </c>
+          <t>159 1909 0393, +86-757-2339 1505</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号</t>
+          <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for</t>
+          <t>Нормальное</t>
         </is>
       </c>
     </row>
@@ -1450,42 +1522,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>上海世灿国际贸易有限公司</t>
+          <t>Suzhou Acousound New Material Technology Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杨苗</t>
+          <t>Yolanda He</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>yangm618@163.com</t>
+          <t>acousound07@polyacoustic.com</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>138 1618 4706</t>
+          <t>+86-18068038050</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>http://www.shicanchina.com</t>
+          <t>www.polyacoustic.com</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>上海市浦东新区商城路889号C3-B06</t>
+          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models an</t>
+          <t>$55, MOQ100pcs, good</t>
         </is>
       </c>
     </row>
@@ -1495,42 +1567,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>COLOMAC DECOR</t>
+          <t>CGCH</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Aaron Liu</t>
+          <t>陈洁玲 Rowling</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>aaron@ccolomac.com</t>
+          <t>014@cgchcontainer.com</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>+86-0371-66350801, +86 15936292861</t>
+          <t>+86 189 2997 1329</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>www.ccolomac.com</t>
+          <t>www.cgchcontainer.com</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
+          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 10</t>
+          <t>1000 yuan 1 square</t>
         </is>
       </c>
     </row>
@@ -1540,34 +1612,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>佛山市同路匠人家具有限公司</t>
+          <t>广东省中山名谷屋木门厂</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>赖华芳</t>
+          <t>罗美玲</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13727479513, 400-8339513</t>
+          <t>180 0760 4399</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
+          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Хорошее, 400rmb</t>
+          <t>150 rmb</t>
         </is>
       </c>
     </row>
@@ -1577,30 +1649,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>固豪木业 | SUNDIN尚鼎</t>
+          <t>multishades</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Clément / 付雄豪</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>clement.fu@cqsdmy.com</t>
+          <t>sophia@multishades.com.cn</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>+(86) 19112691557</t>
+          <t>0086-15918713187, 0086-757-86780865</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>www.guhaogroup.com / www.cqsdmy.com</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>www.multishades.com.cn</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Office: Room 1501, CITIC Plaza, No.233, Tianhebei Road, Guangzhou City, Guangdong Province, China; Factory: 1 Shengshi Road, Shibei Industrial Park, Shishan Town, Foshan City, Guangdong Province, China</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1608,7 +1684,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Хорошее , 1500rmb</t>
+          <t>570 rmb</t>
         </is>
       </c>
     </row>
@@ -1618,38 +1694,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>佛山市嘉豪飞度家具有限公司 (FOSHAN KAHO FIT FURNITURE CO., LTD.)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>周灿灿</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>15986196312@163.com</t>
-        </is>
-      </c>
+          <t>超友皮革家居</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>159 1909 0393, +86-757-2339 1505</t>
+          <t>1561767</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Нормальное</t>
+          <t>130 super</t>
         </is>
       </c>
     </row>
@@ -1659,22 +1723,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中山市福乐门智能科技有限公司 / 中山市乐帝智能科技有限公司</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co.,Ltd)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>欧阳玉滢 (Sonia Ouyang)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>sonia.ouyang@wireking.com</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>+86-13392758223</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>$176, MOQ 50, very good!</t>
+          <t>$32, MOQ 300, good</t>
         </is>
       </c>
     </row>
@@ -1684,42 +1764,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Suzhou Acousound New Material Technology Inc.</t>
+          <t>PTA DOOR Automation (Hunan Tianan Door Technology Co., Ltd.)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yolanda He</t>
+          <t>Eva Leng</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>acousound07@polyacoustic.com</t>
+          <t>eva@ptadoor.com</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>+86-18068038050</t>
+          <t>+86 19848080478, +44 7704 561086</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>www.polyacoustic.com</t>
+          <t>global.ptadoor.com</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+          <t>Xincheng technology park, Yuelu Avenue, Changsha Hunan China</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>$55, MOQ100pcs, good</t>
+          <t>¥3000, MoQ 1pcs, very good</t>
         </is>
       </c>
     </row>
@@ -1729,14 +1809,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>特斯豹工具</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+          <t>丰顺县泰雅达实业有限公司</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>徐小俊</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>281431686@qq.com</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>13802731123</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://taiyada1688.1688.com/</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>广东省丰顺县汤坑镇太平北路</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1744,7 +1844,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>$30, MOQ 10pcs, nice</t>
+          <t>¥17, Moq 50, good</t>
         </is>
       </c>
     </row>
@@ -1754,32 +1854,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CGCH</t>
+          <t>佛山市悠派家居科技有限公司</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>陈洁玲 Rowling</t>
+          <t>黄伟业</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>014@cgchcontainer.com</t>
+          <t>Yea@LGPKB.com</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>+86 189 2997 1329</t>
+          <t>13825596371</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>www.cgchcontainer.com</t>
+          <t>www.LGPKB.com</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1789,7 +1889,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1000 yuan 1 square</t>
+          <t>600 RMB Great, very cheap</t>
         </is>
       </c>
     </row>
@@ -1799,34 +1899,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>广东省中山名谷屋木门厂</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>罗美玲</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>常州市永春保温材料有限公司 (Changzhou Yongchun Thermal Insulation Materials Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>yc@ycbycl.com</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>180 0760 4399</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>0519-88931168</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>www.ycbycl.com</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
+          <t>江苏省常州市天宁区郑陆镇工业集中区</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>150 rmb</t>
+          <t>10$</t>
         </is>
       </c>
     </row>
@@ -1836,32 +1940,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>multishades</t>
+          <t>诺奥(福建)环保家居用品有限公司</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>曾令贵</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>sophia@multishades.com.cn</t>
+          <t>513573190@qq.com</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0086-15918713187, 0086-757-86780865</t>
+          <t>86-13585642723 / 0596-8273388-8083</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>www.multishades.com.cn</t>
+          <t>www.fjnuoao.cn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Office: Room 1501, CITIC Plaza, No.233, Tianhebei Road, Guangzhou City, Guangdong Province, China; Factory: 1 Shengshi Road, Shibei Industrial Park, Shishan Town, Foshan City, Guangdong Province, China</t>
+          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1871,7 +1975,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>570 rmb</t>
+          <t>69$</t>
         </is>
       </c>
     </row>
@@ -1881,18 +1985,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>超友皮革家居</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>大音声学 (DAYIN ACOUSTICS)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>唐佳豪 (Vance)</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1561767</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+          <t>+86 18925924350</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>www.dayinacoustics.com</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>佛山市南海区里水镇赤山大道32号 (No.32 Chishan Avenue, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1900,7 +2016,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>130 super</t>
+          <t>50-85$</t>
         </is>
       </c>
     </row>
@@ -1910,30 +2026,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co.,Ltd)</t>
+          <t>杭州班昇</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>欧阳玉滢 (Sonia Ouyang)</t>
+          <t>陈卓敏 Ruby</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>sonia.ouyang@wireking.com</t>
+          <t>295608376@qq.com</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>+86-13392758223</t>
+          <t>+86 13556688832</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1941,7 +2053,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>$32, MOQ 300, good</t>
+          <t>￥1000 good</t>
         </is>
       </c>
     </row>
@@ -1951,42 +2063,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PTA DOOR Automation (Hunan Tianan Door Technology Co., Ltd.)</t>
+          <t>FOSHAN SINCERE BUILDING MATERIALS CO., LTD.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eva Leng</t>
+          <t>Crystal 刘晓艺</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>eva@ptadoor.com</t>
+          <t>crystal@sincerechina.net</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>+86 19848080478, +44 7704 561086</t>
+          <t>86-15815992213</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>global.ptadoor.com</t>
+          <t>www.sincerechina.net</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Xincheng technology park, Yuelu Avenue, Changsha Hunan China</t>
+          <t>佛山市禅城区南庄镇季华西路中国陶瓷产业总部基地西区C07-C08栋 (China Ceramics Industry Headquaters Block No.C07-08, West Area, West Jihua Road, Nanzhuang, Foshan, China)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>¥3000, MoQ 1pcs, very good</t>
+          <t>¥ 500 good</t>
         </is>
       </c>
     </row>
@@ -1996,32 +2108,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>丰顺县泰雅达实业有限公司</t>
+          <t>Xiamen Golden Ricky Industry &amp; Trade Co.,Ltd</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>徐小俊</t>
+          <t>Joan Liu</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>281431686@qq.com</t>
+          <t>joan@goldenrickyhpl.com</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13802731123</t>
+          <t>+86 13599525074</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://taiyada1688.1688.com/</t>
+          <t>Https://goldenrickyhpl.com</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>广东省丰顺县汤坑镇太平北路</t>
+          <t>Xiamen City, Fujian, China</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2031,7 +2143,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥17, Moq 50, good</t>
+          <t>￥ 300 good</t>
         </is>
       </c>
     </row>
@@ -2041,42 +2153,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>佛山市悠派家居科技有限公司</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>黄伟业</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Yea@LGPKB.com</t>
-        </is>
-      </c>
+          <t>江门市新阳刚智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13825596371</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>www.LGPKB.com</t>
-        </is>
-      </c>
+          <t>135 3666 7789, 400-9090-518</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
+          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>600 RMB Great, very cheap</t>
+          <t>300 rmb and more. Good quality and good price. Small quantity</t>
         </is>
       </c>
     </row>
@@ -2086,18 +2186,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>艾锐特</t>
+          <t>河南蓝健陶瓷有限公司</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>冯蕾</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+          <t>王闻浠</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>lanjanweiyu@163.com</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>+86-13569915996</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>www.lanjan.com</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>河南省长葛市石固镇梁庄工业园区</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2105,7 +2221,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3400, Good price</t>
+          <t>33$ for 1 pcs. Good quality and quantity</t>
         </is>
       </c>
     </row>
@@ -2115,30 +2231,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>常州市永春保温材料有限公司 (Changzhou Yongchun Thermal Insulation Materials Co., Ltd.)</t>
+          <t>三强地毯</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>yc@ycbycl.com</t>
+          <t>hengsheng_carpet@163.com</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0519-88931168</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>www.ycbycl.com</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>江苏省常州市天宁区郑陆镇工业集中区</t>
-        </is>
-      </c>
+          <t>0769-89807692</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2146,7 +2254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10$</t>
+          <t>Good 👍</t>
         </is>
       </c>
     </row>
@@ -2156,32 +2264,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>诺奥(福建)环保家居用品有限公司</t>
+          <t>Higold Group Co., Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>曾令贵</t>
+          <t>Willer Zhou</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>513573190@qq.com</t>
+          <t>sale31@higold.com.cn</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>86-13585642723 / 0596-8273388-8083</t>
+          <t>+86 158 2865 5891</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>www.fjnuoao.cn</t>
+          <t>www.higoldhardware.com</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
+          <t>No.36 Shunye East Rd, Xingtan, Shunde, Foshan 528325, Guangdong, China</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2191,7 +2299,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>69$</t>
+          <t>5800</t>
         </is>
       </c>
     </row>
@@ -2201,38 +2309,42 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>大音声学 (DAYIN ACOUSTICS)</t>
+          <t>Zhejiang Kehon Intelligent Science &amp; Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>唐佳豪 (Vance)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Sammi Shi</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>sales01@kehon.cn</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>+86 18925924350</t>
+          <t>+86 156 8948 5097, 0578-3271096</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>www.dayinacoustics.com</t>
+          <t>www.kehon.cn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>佛山市南海区里水镇赤山大道32号 (No.32 Chishan Avenue, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>50-85$</t>
+          <t>130 yuan</t>
         </is>
       </c>
     </row>
@@ -2242,26 +2354,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>杭州班昇</t>
+          <t>Guangdong Wanbang Modular Building Co., Ltd</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>陈卓敏 Ruby</t>
+          <t>Richie Wang</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>295608376@qq.com</t>
+          <t>richie.wang@wbhouse.com</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>+86 13556688832</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+          <t>+86 137 1002 1675</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>www.gdwbprefabhouse.com</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Guangdong Factory: No.5, No. 161 Ganghe Avenue, Gaoming District, Foshan city, Guangdong, CHINA; Fujian Factory: Provincial Highway 308, Yunrong Township, Minqing County, Fuzhou City, Fujian Province, CHINA.</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2269,7 +2389,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>￥1000 good</t>
+          <t>20000usd</t>
         </is>
       </c>
     </row>
@@ -2279,32 +2399,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FOSHAN SINCERE BUILDING MATERIALS CO., LTD.</t>
+          <t>Guhao Group | SEAJOIN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Crystal 刘晓艺</t>
+          <t>Owen Li</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>crystal@sincerechina.net</t>
+          <t>owen.li@seajoinhouse.com</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>86-15815992213</t>
+          <t>(86) 133 9501 1076</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>www.sincerechina.net</t>
+          <t>www.seajoinhouse.com</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇季华西路中国陶瓷产业总部基地西区C07-C08栋 (China Ceramics Industry Headquaters Block No.C07-08, West Area, West Jihua Road, Nanzhuang, Foshan, China)</t>
+          <t>Chongqing, China / Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2314,7 +2434,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>¥ 500 good</t>
+          <t>500yuan</t>
         </is>
       </c>
     </row>
@@ -2324,42 +2444,42 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Xiamen Golden Ricky Industry &amp; Trade Co.,Ltd</t>
+          <t>CAE SANITARY FITTINGS INDUSTRY CO., LTD. GUANGDONG</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Joan Liu</t>
+          <t>Josie Guan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>joan@goldenrickyhpl.com</t>
+          <t>cae@china-cae.com</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>+86 13599525074</t>
+          <t>+86-13702279135</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Https://goldenrickyhpl.com</t>
+          <t>www.china-cae.com</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Xiamen City, Fujian, China</t>
+          <t>No.62-64, Xingda Rd., Shagang Dist., Shuikou Town, Kaiping, Guangdong, P.R.Of China.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>￥ 300 good</t>
+          <t>MOQ 100, 47 rnb per piece</t>
         </is>
       </c>
     </row>
@@ -2369,30 +2489,38 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>江门市新阳刚智能科技有限公司</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+          <t>盐城格子匠家居有限公司</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>董华</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>418897056@qq.com</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>135 3666 7789, 400-9090-518</t>
+          <t>13914649982, 18951488133</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
+          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>300 rmb and more. Good quality and good price. Small quantity</t>
+          <t>MOQ 50, 200 rnb per</t>
         </is>
       </c>
     </row>
@@ -2402,32 +2530,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>河南蓝健陶瓷有限公司</t>
+          <t>SUOFEIYA HOME COLLECTION CO., LTD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>王闻浠</t>
+          <t>Jasmine Guan 管敏秀</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>lanjanweiyu@163.com</t>
+          <t>jasmine@suofeiyahome.com</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>+86-13569915996</t>
+          <t>+86 147 7520 2759</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>www.lanjan.com</t>
+          <t>https://www.sofeyiahome.com</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>河南省长葛市石固镇梁庄工业园区</t>
+          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2437,7 +2565,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>33$ for 1 pcs. Good quality and quantity</t>
+          <t>MOQ 10, 845 per piece</t>
         </is>
       </c>
     </row>
@@ -2447,20 +2575,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>沃澜 (WOTUA)</t>
+          <t>利亚德光电股份有限公司 Leyard Optoelectronic Co., Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dion Sun</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+          <t>金厚强 Jin Houqiang</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>jinhouqiang@leyard.com</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>13510009569, 18829341125, 400-8592-666</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>www.leyard.com</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3座104号</t>
+          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2470,7 +2610,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Good quality and quantity. 140 rmb 1 pcs.</t>
+          <t>1pcs. Start from 60rmb. Novative technology</t>
         </is>
       </c>
     </row>
@@ -2480,30 +2620,38 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>三强地毯</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>JNOD 基诺德</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>周信朋 Joe Zhou</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>hengsheng_carpet@163.com</t>
+          <t>sales02@jnodwater.com</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0769-89807692</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>+86 199 2825 2201, +86-757-2361 7920</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>www.jnodwater.com</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Good 👍</t>
+          <t>1410</t>
         </is>
       </c>
     </row>
@@ -2513,42 +2661,42 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Higold Group Co., Ltd.</t>
+          <t>广州传祺时代智能科技有限公司</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Willer Zhou</t>
+          <t>洪美兰</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>sale31@higold.com.cn</t>
+          <t>jiang@chuangqitimes.com</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>+86 158 2865 5891</t>
+          <t>13450298606, 020-82511901</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>www.higoldhardware.com</t>
+          <t>www.chuangqitimes.com</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>No.36 Shunye East Rd, Xingtan, Shunde, Foshan 528325, Guangdong, China</t>
+          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>329</t>
         </is>
       </c>
     </row>
@@ -2558,42 +2706,38 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Zhejiang Kehon Intelligent Science &amp; Technology Co., Ltd.</t>
+          <t>RUIKANG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sammi Shi</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>sales01@kehon.cn</t>
+          <t>sales08@ruikang-cn.com</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>+86 156 8948 5097, 0578-3271096</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>www.kehon.cn</t>
-        </is>
-      </c>
+          <t>+86 18028330648, +86 18022073939</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
+          <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>130 yuan</t>
+          <t>229</t>
         </is>
       </c>
     </row>
@@ -2603,32 +2747,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Guangdong Wanbang Modular Building Co., Ltd</t>
+          <t>松下电器设备(中国)有限公司</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richie Wang</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>richie.wang@wbhouse.com</t>
-        </is>
-      </c>
+          <t>潘禹</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>+86 137 1002 1675</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>www.gdwbprefabhouse.com</t>
-        </is>
-      </c>
+          <t>13691864691</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Guangdong Factory: No.5, No. 161 Ganghe Avenue, Gaoming District, Foshan city, Guangdong, CHINA; Fujian Factory: Provincial Highway 308, Yunrong Township, Minqing County, Fuzhou City, Fujian Province, CHINA.</t>
+          <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2638,7 +2774,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20000usd</t>
+          <t>680</t>
         </is>
       </c>
     </row>
@@ -2648,32 +2784,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Guhao Group | SEAJOIN</t>
+          <t>CAE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Owen Li</t>
+          <t>Jack Guan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>owen.li@seajoinhouse.com</t>
+          <t>jack@cae.cn</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(86) 133 9501 1076</t>
+          <t>+86-750-8119338</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>www.seajoinhouse.com</t>
+          <t>www.cae.cn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chongqing, China / Ho Chi Minh City, Vietnam</t>
+          <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2683,7 +2819,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>500yuan</t>
+          <t>150 yuan, 100, good range of products</t>
         </is>
       </c>
     </row>
@@ -2693,42 +2829,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CAE SANITARY FITTINGS INDUSTRY CO., LTD. GUANGDONG</t>
+          <t>广东富矿智能家居有限公司 (Guangdong Fukuang Intelligent Home Co., Ltd.)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Josie Guan</t>
+          <t>余赛银 (Yu Saiyin)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>cae@china-cae.com</t>
+          <t>109786129@qq.com</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>+86-13702279135</t>
+          <t>+86 13660529010</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>www.china-cae.com</t>
+          <t>kingliye.com</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>No.62-64, Xingda Rd., Shagang Dist., Shuikou Town, Kaiping, Guangdong, P.R.Of China.</t>
+          <t>佛山市南海区里广路二号碧桂园金沙国际广场1201室 (Room 1201, Building 10, Jinsha International Plaza No.2 Liguang Road, Nanhai District, Foshan City)</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>MOQ 100, 47 rnb per piece</t>
+          <t>Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
         </is>
       </c>
     </row>
@@ -2738,38 +2874,38 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>盐城格子匠家居有限公司</t>
+          <t>肇庆合生雅居智能家居有限公司 (Zhaoqing Hesheng Yaju Intelligent Home Co., Ltd.)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>董华</t>
+          <t>Winni 何玲玲</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>418897056@qq.com</t>
+          <t>helingling@gdhsyj.com</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>13914649982, 18951488133</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
-        </is>
-      </c>
+          <t>+86 18924564942</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>WWW.HOPSOONER.COM</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>MOQ 50, 200 rnb per</t>
+          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
         </is>
       </c>
     </row>
@@ -2779,32 +2915,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SUOFEIYA HOME COLLECTION CO., LTD</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Jasmine Guan 管敏秀</t>
-        </is>
-      </c>
+          <t>视威电子科技（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jasmine@suofeiyahome.com</t>
+          <t>service@3weitech.com</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>+86 147 7520 2759</t>
+          <t>021-57715805</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.sofeyiahome.com</t>
+          <t>www.3weitech.com</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
+          <t>上海市闵行区新骏环路188号11号楼A座518室</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2814,7 +2946,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>MOQ 10, 845 per piece</t>
+          <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет пр</t>
         </is>
       </c>
     </row>
@@ -2824,42 +2956,38 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>利亚德光电股份有限公司 Leyard Optoelectronic Co., Ltd.</t>
+          <t>爱舒床垫集团有限公司</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>金厚强 Jin Houqiang</t>
+          <t>王鹏</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jinhouqiang@leyard.com</t>
+          <t>1319129904@qq.com</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>13510009569, 18829341125, 400-8592-666</t>
+          <t>189-2324-7677</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>www.leyard.com</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋</t>
-        </is>
-      </c>
+          <t>www.asnug.com</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1pcs. Start from 60rmb. Novative technology</t>
+          <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
         </is>
       </c>
     </row>
@@ -2869,12 +2997,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>林商学社</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+          <t>soundbox</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>劉奕紫 Cathy</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>sales19@soundbox.hk</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>+86 137 6339 3059</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
@@ -2884,7 +3024,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>From 1pc. Natural materials.</t>
+          <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккура</t>
         </is>
       </c>
     </row>
@@ -2894,22 +3034,42 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>佛山市威尔信保险柜有限公司 (Foshan Weierxin Safe Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+          <t>Shenzhen Kingston Sanitary Ware Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Felicity</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>sales09@spakingston.com</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>+86-18025851458</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>www.spakingston.com</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Kingston Company, JiangJun Road, Qiuchang, Huiyang, Huizhou, China</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1250rmb. MOQ 1 pc</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -2919,22 +3079,42 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SAKURA 樱花智能锁</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+          <t>Guangzhou Sunrans Sanitary Ware Co., Ltd / Guangzhou Sunrans New Energy Technology Co., Ltd</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>william@sunrans.com</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>+86 134 1613 9887, +86-20-26231998</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>http://www.sunrans.com</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very go</t>
         </is>
       </c>
     </row>
@@ -2942,31 +3122,15 @@
       <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>JNOD 基诺德</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>周信朋 Joe Zhou</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>sales02@jnodwater.com</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>+86 199 2825 2201, +86-757-2361 7920</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>www.jnodwater.com</t>
-        </is>
-      </c>
+          <t>15916159866</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
@@ -2975,7 +3139,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
         </is>
       </c>
     </row>
@@ -2985,42 +3149,42 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>广州传祺时代智能科技有限公司</t>
+          <t>IFUN PARK &amp; TIPTOPFUN AMUSEMENT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>洪美兰</t>
+          <t>Ivy Zhou</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jiang@chuangqitimes.com</t>
+          <t>ivy@ifunpark.com</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13450298606, 020-82511901</t>
+          <t>+86 133 0238 5758</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>www.chuangqitimes.com</t>
+          <t>www.ifunpark.com / www.ifunamusement.com</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
+          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>600</t>
         </is>
       </c>
     </row>
@@ -3030,28 +3194,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RUIKANG</t>
+          <t>RENQIU TUOXIN BUILDING MATERIALS CO., LTD</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jacky</t>
+          <t>Emily Li</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>sales08@ruikang-cn.com</t>
+          <t>tuoxinlqm@outlook.com</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>+86 18028330648, +86 18022073939</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>+86 19831737599</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.tuoxinfiberglassmesh.com/</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
+          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3061,7 +3229,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>0.6 usd/m2</t>
         </is>
       </c>
     </row>
@@ -3071,34 +3239,42 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>松下电器设备(中国)有限公司</t>
+          <t>河南威兰得建筑科技有限公司</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>潘禹</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>王虎旗</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>hectorwang1982@gmail.com</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>13691864691</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
+          <t>86 18638546565</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>www.weilandeglobal.com</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
+          <t>河南省郑州市曲梁工业园188号</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>Under negotiation, great opportunities</t>
         </is>
       </c>
     </row>
@@ -3108,42 +3284,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CAE</t>
+          <t>江门市新会区致恒科技材料有限公司</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jack Guan</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>jack@cae.cn</t>
-        </is>
-      </c>
+          <t>曹双林 (Edith Cao)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>+86-750-8119338</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>www.cae.cn</t>
-        </is>
-      </c>
+          <t>13286132534, 400-0750-889</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
+          <t>广东省江门市蓬江区迎宾大道西23号之129</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>150 yuan, 100, good range of products</t>
+          <t>1-5 usd/l</t>
         </is>
       </c>
     </row>
@@ -3153,42 +3321,38 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>广东富矿智能家居有限公司 (Guangdong Fukuang Intelligent Home Co., Ltd.)</t>
+          <t>优品声学 (YP ACOUSTICS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>余赛银 (Yu Saiyin)</t>
+          <t>李尚声 (Shangsheng Li)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>109786129@qq.com</t>
+          <t>15915975597@163.com</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>+86 13660529010</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>kingliye.com</t>
-        </is>
-      </c>
+          <t>15915974406</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>佛山市南海区里广路二号碧桂园金沙国际广场1201室 (Room 1201, Building 10, Jinsha International Plaza No.2 Liguang Road, Nanhai District, Foshan City)</t>
+          <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
+          <t>6000RMB</t>
         </is>
       </c>
     </row>
@@ -3198,14 +3362,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>THOR 索而</t>
+          <t>双龙智科</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3213,7 +3385,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+          <t>2000RMB&amp;gt;</t>
         </is>
       </c>
     </row>
@@ -3223,30 +3395,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>肇庆合生雅居智能家居有限公司 (Zhaoqing Hesheng Yaju Intelligent Home Co., Ltd.)</t>
+          <t>GUANGDONG TUOXUN INTELLIGENT TECHNOLOGY CO., LTD</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Winni 何玲玲</t>
+          <t>Wing</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>helingling@gdhsyj.com</t>
+          <t>wuyunying08@gmail.com</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>+86 18924564942</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>WWW.HOPSOONER.COM</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>189-2984-9818, 0758-8578545</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Smart Home &amp; Lighting</t>
@@ -3254,7 +3426,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+          <t>MOQ - 5000 and price - 7000 dollars</t>
         </is>
       </c>
     </row>
@@ -3264,38 +3436,38 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>视威电子科技（上海）有限公司</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>佛山市方泓五金建材有限公司 (Foshan Fangheng Hardware Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>陈施志凯 (CHEN SHI ZHI KAI)</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>service@3weitech.com</t>
+          <t>108455453@qq.com</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>021-57715805</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>www.3weitech.com</t>
-        </is>
-      </c>
+          <t>+86 134 3318 1558, 0757-8560 9159</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>上海市闵行区新骏环路188号11号楼A座518室</t>
+          <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет пр</t>
+          <t>The price cheap, merchant very friendly</t>
         </is>
       </c>
     </row>
@@ -3305,30 +3477,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>爱舒床垫集团有限公司</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>王鹏</t>
-        </is>
-      </c>
+          <t>Countermast Technology (Dalian) Company Limited</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1319129904@qq.com</t>
+          <t>sales.countermast.china@countermast.com</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>189-2324-7677</t>
+          <t>400-100-2228</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>www.asnug.com</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>www.countermast.cn</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Building No.7, Zhongqing Industrial Park, Dalian free trade zone, Liaoning, China</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3336,7 +3508,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
+          <t>The price more cheaper, good quality</t>
         </is>
       </c>
     </row>
@@ -3346,34 +3518,42 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>soundbox</t>
+          <t>广州蒙娜丽莎控股集团有限公司, 广州蒙娜丽莎卫浴股份有限公司</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>劉奕紫 Cathy</t>
+          <t>严金霞</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>sales19@soundbox.hk</t>
+          <t>monalisa38@monalisa.cn</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>+86 137 6339 3059</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+          <t>+86 13711113746, 400 020 1818, +86 20-28607711</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>www.monalisa.cn</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>广州市花都区花东镇港头工业区4号</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккура</t>
+          <t>Good merchant, perfect products</t>
         </is>
       </c>
     </row>
@@ -3383,14 +3563,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>顶固集团</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+          <t>高成 (Gaocheng)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>叶小龙/Dustin Ye</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>yedustin@gmail.com</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>+86-188 5861 0008</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>www.cngaocheng.cn</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>浙江省三门县浦坝港镇沿海工业城 (COASTAL INDUSTRIAL CITY, PUBAGANG TOWN, SANMEN, TAIZHOU CITY, ZHEJIANG PRO., CHINA)</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3398,7 +3598,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккуратно. Хорошее решение для сушки белья и </t>
+          <t>160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
         </is>
       </c>
     </row>
@@ -3408,42 +3608,42 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Shenzhen Kingston Sanitary Ware Co., Ltd.</t>
+          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD. / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Felicity</t>
+          <t>Pacao Yin</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>sales09@spakingston.com</t>
+          <t>pin@pingaolao.com</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>+86-18025851458</t>
+          <t>(0086)13903035682, (0086)0769-86378283, (0086)0769-86377522</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>www.spakingston.com</t>
+          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Kingston Company, JiangJun Road, Qiuchang, Huiyang, Huizhou, China</t>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15 RMB the product is interesting</t>
         </is>
       </c>
     </row>
@@ -3453,42 +3653,42 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Guangzhou Sunrans Sanitary Ware Co., Ltd / Guangzhou Sunrans New Energy Technology Co., Ltd</t>
+          <t>浙江瑞鑫环保设备有限公司</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>吴仁余</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>william@sunrans.com</t>
+          <t>294217488@qq.com</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>+86 134 1613 9887, +86-20-26231998</t>
+          <t>13967444542, 0579-82889122</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>http://www.sunrans.com</t>
+          <t>www.jhrxhb.com</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
+          <t>浙江省金华市婺城区罗店镇北山路精工工业园</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very go</t>
+          <t>nearly $15,000 for this production line</t>
         </is>
       </c>
     </row>
@@ -3496,16 +3696,36 @@
       <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ZHEJIANG DOUBLE-LIN VALVES CO., LTD.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Dream Lin</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>sale15@double-lin.com</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>15916159866</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
+          <t>86-020-66837727, 86-13710718529</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>www.double-lin.com</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3513,7 +3733,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -3523,32 +3743,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IFUN PARK &amp; TIPTOPFUN AMUSEMENT</t>
+          <t>苏州市富尔达科技股份有限公司</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ivy Zhou</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>ivy@ifunpark.com</t>
-        </is>
-      </c>
+          <t>袁佳磊</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>+86 133 0238 5758</t>
+          <t>18652449601</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>www.ifunpark.com / www.ifunamusement.com</t>
+          <t>www.cnfrd.cn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
+          <t>江苏省太仓市港区临江路1号</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3558,7 +3774,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>749</t>
         </is>
       </c>
     </row>
@@ -3568,14 +3784,34 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Weyth 惠特</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Eric Huang</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>464565801@qq.com</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>13813551160 / 0519-88784050</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>www.ycpanel.com</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>No.28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3583,7 +3819,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>5000 USD</t>
         </is>
       </c>
     </row>
@@ -3593,22 +3829,30 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>D.DELI 德利智能门锁</t>
+          <t>双龙中科</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
         </is>
       </c>
     </row>
@@ -3618,42 +3862,30 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RENQIU TUOXIN BUILDING MATERIALS CO., LTD</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Emily Li</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>tuoxinlqm@outlook.com</t>
-        </is>
-      </c>
+          <t>深圳市家为安智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>+86 19831737599</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>https://www.tuoxinfiberglassmesh.com/</t>
-        </is>
-      </c>
+          <t>186-0205-8898 / 400-608-0098</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
+          <t>广东省佛山市南海区里水镇</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0.6 usd/m2</t>
+          <t>249 RMB. They have fully described their products.</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3895,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>河南威兰得建筑科技有限公司</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>王虎旗</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>hectorwang1982@gmail.com</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>86 18638546565</t>
-        </is>
-      </c>
+          <t>广州市优品声学科技有限公司</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>www.weilandeglobal.com</t>
+          <t>www.gzypsx.com</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>河南省郑州市曲梁工业园188号</t>
+          <t>广东省广州市番禺区南村镇南村西路138号德意创意园二层</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3698,7 +3918,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Under negotiation, great opportunities</t>
+          <t>6000RMB，积极，详细地告诉了一切</t>
         </is>
       </c>
     </row>
@@ -3708,34 +3928,38 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>江门市新会区致恒科技材料有限公司</t>
+          <t>贵州佑远木业有限公司</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>曹双林 (Edith Cao)</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>颜加伟</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1164199388@qq.com</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>13286132534, 400-0750-889</t>
+          <t>133 9983 5678</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>广东省江门市蓬江区迎宾大道西23号之129</t>
+          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1-5 usd/l</t>
+          <t>400rmb /m2 good meeting</t>
         </is>
       </c>
     </row>
@@ -3745,30 +3969,34 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>安居福智能门 (ANJUFU INTELLIGENT GATE)</t>
+          <t>广西豪庭家具有限公司 (Guangxi Haoting Furniture Co., Ltd.)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>罗如玲</t>
+          <t>高学梅</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>17687627315</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>广东省中山市东凤镇</t>
+          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>350 rmb/m2</t>
         </is>
       </c>
     </row>
@@ -3778,22 +4006,42 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>欧派</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+          <t>Moershu (摩尔舒卫浴)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Thea</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>moershu3@moershu.com</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>13957622087</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>www.moershu.com</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>679 rmb</t>
+          <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
         </is>
       </c>
     </row>
@@ -3803,26 +4051,38 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>永康市鸿钰门业有限公司</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+          <t>Hangzhou Sciener Smart Technology Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Zoey Zhang</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>zoey@sciener.com</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>+86 178-5768-8782</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>浙江省永康市长城工业区</t>
+          <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>59 rmb</t>
+          <t>20 / MOQ 100 Nice worker answered all questions</t>
         </is>
       </c>
     </row>
@@ -3832,17 +4092,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>东方喜卡</t>
+          <t>江西荣科新型材料有限公司 / JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>果果</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+          <t>Lucy Zeng (曾露)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>lucy@rongkedecor.com</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>+86-13134020034</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://www.amerdecor.com/</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
@@ -3851,7 +4123,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>249RMB</t>
+          <t>80 rmb for 230 meter</t>
         </is>
       </c>
     </row>
@@ -3861,28 +4133,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>优品声学 (YP ACOUSTICS)</t>
+          <t>SANNORA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>李尚声 (Shangsheng Li)</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>15915975597@163.com</t>
-        </is>
-      </c>
+          <t>王冠</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>15915974406</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
+          <t>+86 13229297183</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>WWW.SANNORA.COM; WWW.SANNORA-BATH.COM</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
+          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3892,7 +4164,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>6000RMB</t>
+          <t>1560 rmb for whole item</t>
         </is>
       </c>
     </row>
@@ -3902,30 +4174,42 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>双龙智科</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
+          <t>Kaiping Gold Medal Sanitary Ware Co.,Ltd. / Guangdong Aosman Sanitary Ware Co.,Ltd</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Sophia Deng (邓小艳)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>sophiadeng@china-gold.cn</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
+          <t>+181 3838 6948</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>http://www.china-gold.cn, http://www.aosman.cn</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>江苏省太仓市双凤镇陆江路1号</t>
+          <t>198 Siqian Xi Road, Shuikou, Kaiping 529300, Guangdong PR.China</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2000RMB&amp;gt;</t>
+          <t>4600 rmb</t>
         </is>
       </c>
     </row>
@@ -3935,38 +4219,38 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GUANGDONG TUOXUN INTELLIGENT TECHNOLOGY CO., LTD</t>
+          <t>江西瑞京鸿兴实业有限公司</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wing</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>wuyunying08@gmail.com</t>
-        </is>
-      </c>
+          <t>朱支群</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>189-2984-9818, 0758-8578545</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
+          <t>13763963598</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>www.jx-wpc.com</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
+          <t>江西省瑞金市经济开发区创业一路东侧</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>MOQ - 5000 and price - 7000 dollars</t>
+          <t>250¥/м3</t>
         </is>
       </c>
     </row>
@@ -3976,38 +4260,42 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>佛山市方泓五金建材有限公司 (Foshan Fangheng Hardware Co., Ltd.)</t>
+          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>陈施志凯 (CHEN SHI ZHI KAI)</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>108455453@qq.com</t>
+          <t>victor@ck-bath.com</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>+86 134 3318 1558, 0757-8560 9159</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
+          <t>18656330093</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://ck-bath.com/</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>The price cheap, merchant very friendly</t>
+          <t>4500¥</t>
         </is>
       </c>
     </row>
@@ -4017,28 +4305,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Countermast Technology (Dalian) Company Limited</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>ciarra</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>sales.countermast.china@countermast.com</t>
+          <t>linda.lu@ciarrahome.com</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>400-100-2228</t>
+          <t>+86 1882 9964 960, +86 1343 2639 580</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>www.countermast.cn</t>
+          <t>www.ciarrahome.com</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Building No.7, Zhongqing Industrial Park, Dalian free trade zone, Liaoning, China</t>
+          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4048,7 +4340,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>The price more cheaper, good quality</t>
+          <t>300¥ 300pcs</t>
         </is>
       </c>
     </row>
@@ -4058,42 +4350,38 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>广州蒙娜丽莎控股集团有限公司, 广州蒙娜丽莎卫浴股份有限公司</t>
+          <t>Yekalon Mills</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>严金霞</t>
+          <t>Viola Liu</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>monalisa38@monalisa.cn</t>
+          <t>wood6@sennorwell.com</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>+86 13711113746, 400 020 1818, +86 20-28607711</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>www.monalisa.cn</t>
-        </is>
-      </c>
+          <t>(86) 158 8931 1832</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>广州市花都区花东镇港头工业区4号</t>
+          <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Good merchant, perfect products</t>
+          <t>50¥ 1000pcs</t>
         </is>
       </c>
     </row>
@@ -4103,42 +4391,42 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>高成 (Gaocheng)</t>
+          <t>Ideal Sanitary Ware Co., Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>叶小龙/Dustin Ye</t>
+          <t>Amy Liu 刘建美</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>yedustin@gmail.com</t>
+          <t>export@ideal-china.net</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>+86-188 5861 0008</t>
+          <t>+86 (0) 757 8558 9299</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>www.cngaocheng.cn</t>
+          <t>www.ideal-sanitary.com</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>浙江省三门县浦坝港镇沿海工业城 (COASTAL INDUSTRIAL CITY, PUBAGANG TOWN, SANMEN, TAIZHOU CITY, ZHEJIANG PRO., CHINA)</t>
+          <t>No.3 Hexi Road of Shashui, Yanghe Town, Gaoming District, Foshan City, Guangdong Province, 528515 - P.R.China.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
+          <t>500$ 100psc</t>
         </is>
       </c>
     </row>
@@ -4148,42 +4436,38 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD. / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
+          <t>佛山市旌晨铝门窗有限公司</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pacao Yin</t>
+          <t>胡光辉</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>pin@pingaolao.com</t>
+          <t>1525423805@qq.com</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(0086)13903035682, (0086)0769-86378283, (0086)0769-86377522</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
-        </is>
-      </c>
+          <t>18128752879</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+          <t>佛山狮山镇谭边工业区崩岗头路四号之一</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>15 RMB the product is interesting</t>
+          <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
         </is>
       </c>
     </row>
@@ -4193,42 +4477,42 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>浙江瑞鑫环保设备有限公司</t>
+          <t>佛山市乾泽科技有限公司</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>吴仁余</t>
+          <t>陈可樑</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>294217488@qq.com</t>
+          <t>hw-hardware@qian-ze.com</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>13967444542, 0579-82889122</t>
+          <t>180 3863 7238</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>www.jhrxhb.com</t>
+          <t>www.honeywell-hardware.com</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>浙江省金华市婺城区罗店镇北山路精工工业园</t>
+          <t>广东省佛山市三水区云东海街道宝盛路2号1座三层（合和建筑五金园区北门）</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>nearly $15,000 for this production line</t>
+          <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
         </is>
       </c>
     </row>
@@ -4238,32 +4522,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZHEJIANG DOUBLE-LIN VALVES CO., LTD.</t>
+          <t>景德镇窑珍陶瓷</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dream Lin</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>sale15@double-lin.com</t>
-        </is>
-      </c>
+          <t>徐云霞</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>86-020-66837727, 86-13710718529</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>www.double-lin.com</t>
-        </is>
-      </c>
+          <t>13697981203</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
+          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4273,7 +4549,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>100 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -4283,28 +4559,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>苏州市富尔达科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>袁佳磊</t>
-        </is>
-      </c>
+          <t>苏州东山茶厂 (Suzhou Dongshan Biluochun Tea Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>18652449601</t>
+          <t>0512-66281146</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>www.cnfrd.cn</t>
+          <t>www.dsteaf.com</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>江苏省太仓市港区临江路1号</t>
+          <t>江苏省苏州市吴中区东山镇 (Dongshan Town, Wuzhong District, Suzhou City)</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4314,7 +4586,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>150 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -4324,32 +4596,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Eric Huang</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>464565801@qq.com</t>
-        </is>
-      </c>
+          <t>知和香馆</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>13813551160 / 0519-88784050</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>www.ycpanel.com</t>
-        </is>
-      </c>
+          <t>15926183211</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>No.28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+          <t>福建永春达埔</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4359,7 +4619,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>5000 USD</t>
+          <t>They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
         </is>
       </c>
     </row>
@@ -4369,18 +4629,34 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>优品声学</t>
+          <t>San Nora (聖羅蘭·衛浴)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>杨伟杰</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+          <t>ALLEN XU (许熙平)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>sales@sannora.com</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>+86 137 0263 0244, +86-757-86438259</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>WWW.SANNORA.COM, WWW.SANNORA-BATH.COM</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>TANBIAN IND. ZONE, SHISHAN TOWN, NANHAI DIST., FOSHAN, GUANGDONG, CHINA</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -4388,7 +4664,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>6000 RMB. I like the way they explain everything about their product.</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -4398,30 +4674,38 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>双龙中科</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
+          <t>PTAT | 帕兰蒂诺</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Joy Yang</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>joy@rans.group</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>江苏省太仓市双凤镇陆江路1号</t>
-        </is>
-      </c>
+          <t>+86-13757430301</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>www.ptat.cn</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -4431,30 +4715,38 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>深圳市家为安智能科技有限公司</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>万磊建筑涂料有限公司</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>万磊市场部</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>186-0205-8898 / 400-608-0098</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
+          <t>186-8825-1404, 4000-147-187</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>http://www.fswanlei.com</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区里水镇</t>
+          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>249 RMB. They have fully described their products.</t>
+          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -4464,20 +4756,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>广州市优品声学科技有限公司</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+          <t>ZHEJIANG SEATING TECHNOLOGY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>May Zhang</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>sales5@anjeurostilefurniture.com</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>+86 182 5727 1590</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>www.gzypsx.com</t>
+          <t>www.zjseating.com</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区南村镇南村西路138号德意创意园二层</t>
+          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4487,7 +4791,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>6000RMB，积极，详细地告诉了一切</t>
+          <t>1100</t>
         </is>
       </c>
     </row>
@@ -4497,26 +4801,42 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>科维尔 (VIR)</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+          <t>Chaozhou Lefu Sanitary Ware Technology Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>lucy@lefucz.com</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>+0086 18098114370</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>www.lefucz.com</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>市长城工业区</t>
+          <t>Lefu Sanitary Ware, Sheweikeng, Dengtang Town, Chaoan District, Chaozhou City, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2000 RMB</t>
+          <t>1050</t>
         </is>
       </c>
     </row>
@@ -4526,28 +4846,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>贵州佑远木业有限公司</t>
+          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co., Ltd.)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>颜加伟</t>
+          <t>胡沛能 / Oliver Hu</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1164199388@qq.com</t>
+          <t>oliver@wireking.com</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>133 9983 5678</t>
+          <t>+86-13802465791</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
+          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4557,7 +4877,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>400rmb /m2 good meeting</t>
+          <t>550</t>
         </is>
       </c>
     </row>
@@ -4567,34 +4887,38 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>广西豪庭家具有限公司 (Guangxi Haoting Furniture Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>高学梅</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>浙江雅柔装饰材料有限公司 (Zhejiang Yarou Decoration Material Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>sale01@yarouwallpaper.com.cn</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>17687627315</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
+          <t>+86-18069994326, +86-18069994377</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://www.yarouwallpaper.com.cn/</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
+          <t>浙江省金华市义乌市福田街道涌金大道87号厂房二楼 (No. 1, Factory 2, Yongjin Avenue 87, Futian Subdistrict, Yiwu City, Jinhua City, Zhejiang Province)</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>350 rmb/m2</t>
+          <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
         </is>
       </c>
     </row>
@@ -4604,42 +4928,34 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Moershu (摩尔舒卫浴)</t>
+          <t>淄博永顺装饰材料有限公司</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Thea</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>moershu3@moershu.com</t>
-        </is>
-      </c>
+          <t>戴艳辉</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>13957622087</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>www.moershu.com</t>
-        </is>
-      </c>
+          <t>18830173388</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
+          <t>石家庄市正定县曙光路49号东标和聚居</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
+          <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
         </is>
       </c>
     </row>
@@ -4649,38 +4965,42 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Hangzhou Sciener Smart Technology Co.,Ltd.</t>
+          <t>宏宇集团 (HONGYU GROUP)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Zoey Zhang</t>
+          <t>Melina 王玲</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>zoey@sciener.com</t>
+          <t>lina@hongyugroup.com</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>+86 178-5768-8782</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
+          <t>+86 13827702216</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>en.hongyugroup.com</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
+          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>20 / MOQ 100 Nice worker answered all questions</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -4690,30 +5010,34 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>江西荣科新型材料有限公司 / JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.</t>
+          <t>Chongnuo(Shandong)NewMaterial Co.,Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lucy Zeng (曾露)</t>
+          <t>Daisy</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>lucy@rongkedecor.com</t>
+          <t>sales06@chongnuo-floors.com</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>+86-13134020034</t>
+          <t>+86 19906379675</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.amerdecor.com/</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr"/>
+          <t>www.chongnuo-floors.com</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>QingyunCounty,DezhouCity,China</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -4721,7 +5045,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>80 rmb for 230 meter</t>
+          <t>9$</t>
         </is>
       </c>
     </row>
@@ -4731,30 +5055,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SANNORA</t>
+          <t>上海德翔木业有限公司 (Shanghai Dexiang Wood Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>王冠</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>崔强 (Cui Qiang)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>513437660@qq.com</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>+86 13229297183</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>WWW.SANNORA.COM; WWW.SANNORA-BATH.COM</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区</t>
-        </is>
-      </c>
+          <t>+8618901960431</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -4762,7 +5082,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>1560 rmb for whole item</t>
+          <t>13.25$</t>
         </is>
       </c>
     </row>
@@ -4772,42 +5092,38 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Kaiping Gold Medal Sanitary Ware Co.,Ltd. / Guangdong Aosman Sanitary Ware Co.,Ltd</t>
+          <t>中材(邯郸)新材料有限公司 (China National Building Materials (Handan) New Materials Co.,Ltd.)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sophia Deng (邓小艳)</t>
+          <t>Wangfeng</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>sophiadeng@china-gold.cn</t>
+          <t>2523911877@qq.com</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>+181 3838 6948</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>http://www.china-gold.cn, http://www.aosman.cn</t>
-        </is>
-      </c>
+          <t>13233648687</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>198 Siqian Xi Road, Shuikou, Kaiping 529300, Guangdong PR.China</t>
+          <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>4600 rmb</t>
+          <t>8.83$</t>
         </is>
       </c>
     </row>
@@ -4817,22 +5133,38 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>东风汽车</t>
+          <t>Foshan Cofesu Sanitary Ware Co., Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>sales@cofesu.com</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>+86 181 2821 2128</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>www.cofesu.com</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Foshan, Guangdong, China</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>50 Yuan 50g (The taste is authentic and aroma is really good</t>
+          <t>30 PCs, 420 RMB, need check quality</t>
         </is>
       </c>
     </row>
@@ -4842,28 +5174,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>江西瑞京鸿兴实业有限公司</t>
+          <t>中国广东柜邦精密金属制品有限公司 (China Guangdong Guibang Precision Metal Products Co.Ltd)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>朱支群</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>唐一智 (JUNIOR)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>13621417@qq.com</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>13763963598</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>www.jx-wpc.com</t>
-        </is>
-      </c>
+          <t>+86-156-2562-1155</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>江西省瑞金市经济开发区创业一路东侧</t>
+          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4873,7 +5205,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>250¥/м3</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -4883,42 +5215,38 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd</t>
+          <t>Jieyang Yagegu Hardware Products Co., LTD</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Zoya</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>victor@ck-bath.com</t>
+          <t>2291828903@qq.com</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>18656330093</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>https://ck-bath.com/</t>
-        </is>
-      </c>
+          <t>+86 132 8810 6615</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
+          <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>4500¥</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -4928,42 +5256,38 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ciarra</t>
+          <t>广东启宏盛精密五金制品有限公司 (GUANGDONG QIHONGSHENG PRECISION HARDWARE PRODUCTS CO., LTD)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>邓美君 Jessica</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>linda.lu@ciarrahome.com</t>
+          <t>bailide_hinge@163.com</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>+86 1882 9964 960, +86 1343 2639 580</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>www.ciarrahome.com</t>
-        </is>
-      </c>
+          <t>+86 13823419116 / 0758-8565117</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
+          <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>300¥ 300pcs</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -4973,28 +5297,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Yekalon Mills</t>
+          <t>广东亚当斯金属精密制造有限公司 (Guangdong Adams Metal Precision Manufacturing Co.,Ltd)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Viola Liu</t>
+          <t>Kelly Liang (梁凯莹)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>wood6@sennorwell.com</t>
+          <t>kelly@adamsmetal.com.cn</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(86) 158 8931 1832</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
+          <t>+86-180-2935-2895 / +86-757-25331912</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>www.adamsmetal.com.cn</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
+          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5004,7 +5332,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>50¥ 1000pcs</t>
+          <t>Depend on item</t>
         </is>
       </c>
     </row>
@@ -5014,42 +5342,26 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ideal Sanitary Ware Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Amy Liu 刘建美</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>export@ideal-china.net</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>+86 (0) 757 8558 9299</t>
-        </is>
-      </c>
+          <t>明德 (Mingde)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>www.ideal-sanitary.com</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>No.3 Hexi Road of Shashui, Yanghe Town, Gaoming District, Foshan City, Guangdong Province, 528515 - P.R.China.</t>
-        </is>
-      </c>
+          <t>www.mingde-china.com</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>500$ 100psc</t>
+          <t>Depend of quantity</t>
         </is>
       </c>
     </row>
@@ -5059,38 +5371,42 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>佛山市旌晨铝门窗有限公司</t>
+          <t>佛山市顺德区腾徽精密智造有限公司 (FoShan ShunDe TengHui Precision Intelligent Manufacturing Co., Ltd)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>胡光辉</t>
+          <t>刘婉莹 Carol Liu</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1525423805@qq.com</t>
+          <t>tenghuihardware@126.com</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>18128752879</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
+          <t>+86 133 1836 4599</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>www.teehve.cn</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>佛山狮山镇谭边工业区崩岗头路四号之一</t>
+          <t>广东省佛山市顺德区勒流街道众涌村港口路以西8-9号之二 (No.8-9, West of GangKou Road, Zhongchong Village, Leliu Town, Shunde District, Foshan City, Guangdong, China)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
+          <t>100/square meter</t>
         </is>
       </c>
     </row>
@@ -5100,42 +5416,42 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>佛山市乾泽科技有限公司</t>
+          <t>DUOCAI TENT (多彩帐蓬)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>陈可樑</t>
+          <t>Jimmy 黄锦民</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>hw-hardware@qian-ze.com</t>
+          <t>sales003@sdduocaizp.com</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>180 3863 7238</t>
+          <t>(86)133 2294 8506, +86-766-8298662</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>www.honeywell-hardware.com</t>
+          <t>www.dc-tent.com, www.sdduocaizp.com</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>广东省佛山市三水区云东海街道宝盛路2号1座三层（合和建筑五金园区北门）</t>
+          <t>云浮市云安区佛山(云浮)产业转移工业园86号 (No.86 Foshan(Yunfu) Industrial transfer park, yunan, yunfu, Guangdong China)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
+          <t>RMB 15705 MOQ5; pleasant impression</t>
         </is>
       </c>
     </row>
@@ -5145,26 +5461,42 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ARTY 艺和</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+          <t>佛山市路乐户外制品有限公司 (FOSHAN RULER OUTDOOR HARDWARES CO.,LTD)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Marco Lau (刘嘉乐)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>RULERAWNING07@163.COM</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>+86 13129016338</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>WWW.RULER-AWNING.COM</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>广东 · 开平</t>
+          <t>END OF ROAD SHATANXIAN, SHASHUI INDUSTRIAL ZONE, SONGGANG TOWN, SHISHAN DISTRICT, FOSHAN CITY, GUANGDONG PROVINCE, CHINA, 528200</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
+          <t>MOQ5 25799 RMB</t>
         </is>
       </c>
     </row>
@@ -5174,24 +5506,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>景德镇窑珍陶瓷</t>
+          <t>Avant Sports Industrial Co., Ltd.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>徐云霞</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
+          <t>Jay Zhou</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>jay@avant.com.cn</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>13697981203</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
+          <t>+86-13128980150, +86-755-2968-8357</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>www.avantseating.com</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
+          <t>Avant Industrial Park, Zhoushi Road, Bao'an, Shenzhen, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5201,7 +5541,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>100 RMB per sample. The taste is very good</t>
+          <t>RMB 19479; MOQ 1</t>
         </is>
       </c>
     </row>
@@ -5211,24 +5551,32 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>苏州东山茶厂 (Suzhou Dongshan Biluochun Tea Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
+          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>孟少美 (Elite Meng)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ttf@hbtfjs.com</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>0512-66281146</t>
+          <t>+86-13103196326</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>www.dsteaf.com</t>
+          <t>www.hbtfjs.com</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区东山镇 (Dongshan Town, Wuzhong District, Suzhou City)</t>
+          <t>河北省隆尧县东谷子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5238,7 +5586,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>150 RMB per sample. The taste is very good</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -5248,22 +5596,42 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>武夷星</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+          <t>揭阳市新骏业五金制品有限公司 (JIEYANG XINJUNYE HARDWARE PRODUCTS CO., LTD)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>林树丹 (Lin Shudan)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>linshdong@qq.com</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>13751676456</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>www.xinjunye.com</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>广东省揭阳市揭东区锡场工业区 (Xichang Industrial Zone, Jiedong District, Jieyang City, Guangdong Province)</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>250 RMB per sample. The taste is very good</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -5273,22 +5641,42 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>湖北龙王垭茶业有限公司</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+          <t>广州蒙娜丽莎控股集团有限公司 / 广州蒙娜丽莎卫浴股份有限公司</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>伍乐彤</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>monalisa702@monalisa.cn</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>86 13711117863, 400 020 1818, 86 20-28607722, 86 20-28607788</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>www.monalisa.cn</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>广州市花都区花东镇港头工业区4号</t>
+        </is>
+      </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>498rmb/unit. I like the green tea in white color. First time to see colorless tea and it was amazing, i will recommend i</t>
+          <t>2000$, can be customized, very convenient</t>
         </is>
       </c>
     </row>
@@ -5298,20 +5686,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>知和香馆</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
+          <t>中山藝進不銹鋼裝飾制品有限公司 (ZHONGSHAN YIJIN STAINLESS STEEL DECORATION CO., LTD.)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Anson Yuen</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>info@hugemount.com</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>15926183211</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
+          <t>150 1954 6322 / 86-760-88702663</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>www.yijin.com</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>福建永春达埔</t>
+          <t>中国广东省中山市港口镇石特社区穗安工业区迎富2路1号 (NO.1, Ying Fu 2 Road, Sui An Gong Ye Qu, Gang Kou Zhen Shi Te She Qu, Zhongshan City, Guangdong Province, P.R.China)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5321,7 +5721,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
+          <t>38$, very unique</t>
         </is>
       </c>
     </row>
@@ -5331,42 +5731,42 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>San Nora (聖羅蘭·衛浴)</t>
+          <t>宣城市宠爱卫浴有限公司 (CHONGAI SANITARY WARE CO., LTD.)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ALLEN XU (许熙平)</t>
+          <t>Lucy (卢美珍)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>sales@sannora.com</t>
+          <t>export@vnsmilo.com</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>+86 137 0263 0244, +86-757-86438259</t>
+          <t>+86-13757322119</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>WWW.SANNORA.COM, WWW.SANNORA-BATH.COM</t>
+          <t>www.vnsmilo.com</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>TANBIAN IND. ZONE, SHISHAN TOWN, NANHAI DIST., FOSHAN, GUANGDONG, CHINA</t>
+          <t>Xuancheng City Anhui, CHINA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>2050 rmb, very interesting, convenient to use for pets</t>
         </is>
       </c>
     </row>
@@ -5376,29 +5776,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PTAT | 帕兰蒂诺</t>
+          <t>广西中晨木业有限公司 (Guangxi Zhongchen Wood Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Joy Yang</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>joy@rans.group</t>
-        </is>
-      </c>
+          <t>张爱彬 (Zhang Aibin)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>+86-13757430301</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>www.ptat.cn</t>
-        </is>
-      </c>
+          <t>+86 18178085851</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
@@ -5407,7 +5799,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>25 rmb, 1 box, like this product</t>
         </is>
       </c>
     </row>
@@ -5417,38 +5809,42 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>万磊建筑涂料有限公司</t>
+          <t>NINGBO YUSHENG HOME TECH CO., LTD. (宁波裕盛家居科技有限公司)</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>万磊市场部</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>Tequila Xu (徐孟杰)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>marketing@cxyushun.com, tequila8xu@gmail.com</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>186-8825-1404, 4000-147-187</t>
+          <t>0086-13819449988, +86 574 63190388</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>http://www.fswanlei.com</t>
+          <t>www.cxys8.com</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区</t>
+          <t>中国浙江慈溪市杨梅大道南路1518号 (NO.1518, YANGMEI AVENUE SOUTH ROAD, CIXI CITY, ZHEJIANG, CHINA)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Coatings &amp; Paints</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>34 rmb, 1000, normal</t>
         </is>
       </c>
     </row>
@@ -5458,42 +5854,42 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ZHEJIANG SEATING TECHNOLOGY CO., LTD.</t>
+          <t>河北建华锁业有限公司 (Hebei Jianhua Lock Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>May Zhang</t>
+          <t>刘芳 (Jane Liu)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>sales5@anjeurostilefurniture.com</t>
+          <t>jane@dirock.cn</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>+86 182 5727 1590</t>
+          <t>187 1377 2087</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>www.zjseating.com</t>
+          <t>http://www.dirock.cn</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
+          <t>河北省泊头市寺门村镇后牛屯</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>40 rmb, 2000, very good</t>
         </is>
       </c>
     </row>
@@ -5503,42 +5899,42 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Chaozhou Lefu Sanitary Ware Technology Co., Ltd.</t>
+          <t>浙江安吉双虎竹木业有限公司 / 安吉诺迪新材料有限公司</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>周瑶琳</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>lucy@lefucz.com</t>
+          <t>lisa.nordi@nuodibm.com</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>+0086 18098114370</t>
+          <t>+86-137 3822 8209</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>www.lefucz.com</t>
+          <t>www.tigerbamboo.com / www.nuodibm.com</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lefu Sanitary Ware, Sheweikeng, Dengtang Town, Chaoan District, Chaozhou City, Guangdong Province, China</t>
+          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1 container 250 rmb</t>
         </is>
       </c>
     </row>
@@ -5548,28 +5944,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co., Ltd.)</t>
+          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>胡沛能 / Oliver Hu</t>
+          <t>马世晓 (Amelia Ma)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>oliver@wireking.com</t>
+          <t>tf@hbtfjs.com, mashixiaomsx@163.com</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>+86-13802465791</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
+          <t>15097968589, 0319-6581195</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>www.hbtfjs.com</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
+          <t>河北省隆尧县公子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5579,7 +5979,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>1 container 700 rmb</t>
         </is>
       </c>
     </row>
@@ -5589,14 +5989,34 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>宜昌毛尖</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
+          <t>ZHEJIANG TIANYAN HOLDING CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ty11@cntianyan.com</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>+86-15867028552</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>www.cntianyan.com</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Chengjiang industrial zone,huangyan district taizhou,zhejiang,china</t>
+        </is>
+      </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5604,1217 +6024,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Prices are go and packing and Verstaliy is more</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>湖北龙王娅茶业有限公司</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>The taste anaroma is good of this product then anyother</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>正山堂 (ZHENG SHAN TANG)</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>the product prices are very good. looks attractive</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>浙江雅柔装饰材料有限公司 (Zhejiang Yarou Decoration Material Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>sale01@yarouwallpaper.com.cn</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>+86-18069994326, +86-18069994377</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>https://www.yarouwallpaper.com.cn/</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>浙江省金华市义乌市福田街道涌金大道87号厂房二楼 (No. 1, Factory 2, Yongjin Avenue 87, Futian Subdistrict, Yiwu City, Jinhua City, Zhejiang Province)</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>淄博永顺装饰材料有限公司</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>戴艳辉</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>18830173388</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>石家庄市正定县曙光路49号东标和聚居</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>宏宇集团 (HONGYU GROUP)</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Melina 王玲</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>lina@hongyugroup.com</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>+86 13827702216</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>en.hongyugroup.com</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Chongnuo(Shandong)NewMaterial Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Daisy</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>sales06@chongnuo-floors.com</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>+86 19906379675</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>www.chongnuo-floors.com</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>QingyunCounty,DezhouCity,China</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>9$</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>上海德翔木业有限公司 (Shanghai Dexiang Wood Industry Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>崔强 (Cui Qiang)</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>513437660@qq.com</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>+8618901960431</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>13.25$</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>中材(邯郸)新材料有限公司 (China National Building Materials (Handan) New Materials Co.,Ltd.)</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Wangfeng</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2523911877@qq.com</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>13233648687</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>8.83$</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Zhejiang Tianyan Holding Ltd</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Nicole</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Taizhou, Zhejiang</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>640 PCs, 3.72 RMB very good</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Foshan Cofesu Sanitary Ware Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>sales@cofesu.com</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>+86 181 2821 2128</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>www.cofesu.com</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Foshan, Guangdong, China</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Bath &amp; Sanitary</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>30 PCs, 420 RMB, need check quality</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>中国广东柜邦精密金属制品有限公司 (China Guangdong Guibang Precision Metal Products Co.Ltd)</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>唐一智 (JUNIOR)</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>13621417@qq.com</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>+86-156-2562-1155</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Jieyang Yagegu Hardware Products Co., LTD</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Zoya</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2291828903@qq.com</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>+86 132 8810 6615</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>广东启宏盛精密五金制品有限公司 (GUANGDONG QIHONGSHENG PRECISION HARDWARE PRODUCTS CO., LTD)</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>邓美君 Jessica</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>bailide_hinge@163.com</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>+86 13823419116 / 0758-8565117</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>广东亚当斯金属精密制造有限公司 (Guangdong Adams Metal Precision Manufacturing Co.,Ltd)</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Kelly Liang (梁凯莹)</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>kelly@adamsmetal.com.cn</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>+86-180-2935-2895 / +86-757-25331912</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>www.adamsmetal.com.cn</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Depend on item</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>明德 (Mingde)</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>www.mingde-china.com</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Depend of quantity</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>佛山市顺德区腾徽精密智造有限公司 (FoShan ShunDe TengHui Precision Intelligent Manufacturing Co., Ltd)</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>刘婉莹 Carol Liu</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>tenghuihardware@126.com</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>+86 133 1836 4599</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>www.teehve.cn</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区勒流街道众涌村港口路以西8-9号之二 (No.8-9, West of GangKou Road, Zhongchong Village, Leliu Town, Shunde District, Foshan City, Guangdong, China)</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Smart Home &amp; Lighting</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>100/square meter</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>DUOCAI TENT (多彩帐蓬)</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Jimmy 黄锦民</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>sales003@sdduocaizp.com</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>(86)133 2294 8506, +86-766-8298662</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>www.dc-tent.com, www.sdduocaizp.com</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>云浮市云安区佛山(云浮)产业转移工业园86号 (No.86 Foshan(Yunfu) Industrial transfer park, yunan, yunfu, Guangdong China)</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>RMB 15705 MOQ5; pleasant impression</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>151</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>佛山市路乐户外制品有限公司 (FOSHAN RULER OUTDOOR HARDWARES CO.,LTD)</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Marco Lau (刘嘉乐)</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>RULERAWNING07@163.COM</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>+86 13129016338</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>WWW.RULER-AWNING.COM</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>END OF ROAD SHATANXIAN, SHASHUI INDUSTRIAL ZONE, SONGGANG TOWN, SHISHAN DISTRICT, FOSHAN CITY, GUANGDONG PROVINCE, CHINA, 528200</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Doors &amp; Windows</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>MOQ5 25799 RMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>152</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Avant Sports Industrial Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Jay Zhou</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>jay@avant.com.cn</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>+86-13128980150, +86-755-2968-8357</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>www.avantseating.com</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Avant Industrial Park, Zhoushi Road, Bao'an, Shenzhen, Guangdong Province, China</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>RMB 19479; MOQ 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>孟少美 (Elite Meng)</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>ttf@hbtfjs.com</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>+86-13103196326</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>www.hbtfjs.com</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>河北省隆尧县东谷子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>揭阳市新骏业五金制品有限公司 (JIEYANG XINJUNYE HARDWARE PRODUCTS CO., LTD)</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>林树丹 (Lin Shudan)</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>linshdong@qq.com</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>13751676456</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>www.xinjunye.com</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>广东省揭阳市揭东区锡场工业区 (Xichang Industrial Zone, Jiedong District, Jieyang City, Guangdong Province)</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>155</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>广州蒙娜丽莎控股集团有限公司 / 广州蒙娜丽莎卫浴股份有限公司</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>伍乐彤</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>monalisa702@monalisa.cn</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>86 13711117863, 400 020 1818, 86 20-28607722, 86 20-28607788</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>www.monalisa.cn</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>广州市花都区花东镇港头工业区4号</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Bath &amp; Sanitary</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>2000$, can be customized, very convenient</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>中山藝進不銹鋼裝飾制品有限公司 (ZHONGSHAN YIJIN STAINLESS STEEL DECORATION CO., LTD.)</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Anson Yuen</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>info@hugemount.com</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>150 1954 6322 / 86-760-88702663</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>www.yijin.com</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>中国广东省中山市港口镇石特社区穗安工业区迎富2路1号 (NO.1, Ying Fu 2 Road, Sui An Gong Ye Qu, Gang Kou Zhen Shi Te She Qu, Zhongshan City, Guangdong Province, P.R.China)</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>38$, very unique</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>宣城市宠爱卫浴有限公司 (CHONGAI SANITARY WARE CO., LTD.)</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Lucy (卢美珍)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>export@vnsmilo.com</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>+86-13757322119</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>www.vnsmilo.com</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Xuancheng City Anhui, CHINA</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Bath &amp; Sanitary</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>2050 rmb, very interesting, convenient to use for pets</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>广西中晨木业有限公司 (Guangxi Zhongchen Wood Industry Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>张爱彬 (Zhang Aibin)</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>+86 18178085851</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>25 rmb, 1 box, like this product</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>NINGBO YUSHENG HOME TECH CO., LTD. (宁波裕盛家居科技有限公司)</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Tequila Xu (徐孟杰)</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>marketing@cxyushun.com, tequila8xu@gmail.com</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>0086-13819449988, +86 574 63190388</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>www.cxys8.com</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>中国浙江慈溪市杨梅大道南路1518号 (NO.1518, YANGMEI AVENUE SOUTH ROAD, CIXI CITY, ZHEJIANG, CHINA)</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>34 rmb, 1000, normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>河北建华锁业有限公司 (Hebei Jianhua Lock Industry Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>刘芳 (Jane Liu)</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>jane@dirock.cn</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>187 1377 2087</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>http://www.dirock.cn</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>河北省泊头市寺门村镇后牛屯</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>40 rmb, 2000, very good</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>161</v>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>浙江安吉双虎竹木业有限公司 / 安吉诺迪新材料有限公司</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>周瑶琳</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>lisa.nordi@nuodibm.com</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>+86-137 3822 8209</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>www.tigerbamboo.com / www.nuodibm.com</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>1 container 250 rmb</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>162</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd)</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>马世晓 (Amelia Ma)</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>tf@hbtfjs.com, mashixiaomsx@163.com</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>15097968589, 0319-6581195</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>www.hbtfjs.com</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>河北省隆尧县公子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>1 container 700 rmb</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>163</v>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>BANRUGE / KING LIYE</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Home Furnishing</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Прайс отправят, от 100ед, хорошая компания</t>
+          <t>Цена зависит от обьема, от 3 юаней, расходники</t>
         </is>
       </c>
     </row>

--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -567,14 +567,11 @@
           <t>张硕怡 (Stoney)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>134 1416 0636</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
@@ -750,7 +747,6 @@
           <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
@@ -771,7 +767,6 @@
           <t>China Warren Windows and Doors Co., Ltd.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>info@warrenwindows.com</t>
@@ -839,7 +834,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -877,7 +872,6 @@
           <t>www.hdlautomation.com</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -948,13 +942,11 @@
           <t>邹隆鹏</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>15818099349</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
@@ -1040,7 +1032,6 @@
           <t>0086-182 5765 3405, 0086-576-87493988</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
@@ -1071,13 +1062,11 @@
           <t>王小忠</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>浙江省杭州市临平区运河街道育士路53-1号</t>
@@ -1163,7 +1152,6 @@
           <t>13326792105</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
@@ -1171,7 +1159,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1204,7 +1192,6 @@
           <t>+86-18906831082</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Jiaxing/Hongkong</t>
@@ -1245,7 +1232,6 @@
           <t>+86-18302200384</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Shijiazhuang City, Hebei Province</t>
@@ -1343,7 +1329,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1388,7 +1374,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1411,13 +1397,11 @@
           <t>赖华芳</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>13727479513, 400-8339513</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
@@ -1463,7 +1447,6 @@
           <t>www.guhaogroup.com / www.cqsdmy.com</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1499,7 +1482,6 @@
           <t>159 1909 0393, +86-757-2339 1505</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
@@ -1552,7 +1534,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1597,7 +1579,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1620,13 +1602,11 @@
           <t>罗美玲</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>180 0760 4399</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>广东省中山市小榄镇东升门业生产基地F5B</t>
@@ -1634,7 +1614,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1697,15 +1677,11 @@
           <t>超友皮革家居</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>1561767</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1741,7 +1717,6 @@
           <t>+86-13392758223</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
@@ -1749,7 +1724,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1794,7 +1769,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1839,7 +1814,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1902,7 +1877,6 @@
           <t>常州市永春保温材料有限公司 (Changzhou Yongchun Thermal Insulation Materials Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>yc@ycbycl.com</t>
@@ -1993,7 +1967,6 @@
           <t>唐佳豪 (Vance)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>+86 18925924350</t>
@@ -2044,8 +2017,6 @@
           <t>+86 13556688832</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2156,14 +2127,11 @@
           <t>江门市新阳刚智能科技有限公司</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>135 3666 7789, 400-9090-518</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
@@ -2234,7 +2202,6 @@
           <t>三强地毯</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>hengsheng_carpet@163.com</t>
@@ -2245,8 +2212,6 @@
           <t>0769-89807692</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2339,7 +2304,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2429,7 +2394,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2474,7 +2439,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2507,7 +2472,6 @@
           <t>13914649982, 18951488133</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
@@ -2643,10 +2607,9 @@
           <t>www.jnodwater.com</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2691,7 +2654,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2724,7 +2687,6 @@
           <t>+86 18028330648, +86 18022073939</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
@@ -2732,7 +2694,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2755,13 +2717,11 @@
           <t>潘禹</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>13691864691</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
@@ -2814,7 +2774,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2897,10 +2857,9 @@
           <t>WWW.HOPSOONER.COM</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2918,7 +2877,6 @@
           <t>视威电子科技（上海）有限公司</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>service@3weitech.com</t>
@@ -2979,7 +2937,6 @@
           <t>www.asnug.com</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3015,8 +2972,6 @@
           <t>+86 137 6339 3059</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3122,19 +3077,14 @@
       <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>15916159866</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3224,7 +3174,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3292,13 +3242,11 @@
           <t>曹双林 (Edith Cao)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>13286132534, 400-0750-889</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>广东省江门市蓬江区迎宾大道西23号之129</t>
@@ -3339,7 +3287,6 @@
           <t>15915974406</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
@@ -3347,7 +3294,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3365,14 +3312,11 @@
           <t>双龙智科</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>江苏省太仓市双凤镇陆江路1号</t>
@@ -3413,7 +3357,6 @@
           <t>189-2984-9818, 0758-8578545</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
@@ -3421,7 +3364,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3454,7 +3397,6 @@
           <t>+86 134 3318 1558, 0757-8560 9159</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
@@ -3480,7 +3422,6 @@
           <t>Countermast Technology (Dalian) Company Limited</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>sales.countermast.china@countermast.com</t>
@@ -3683,7 +3624,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3728,7 +3669,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3751,7 +3692,6 @@
           <t>袁佳磊</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>18652449601</t>
@@ -3769,7 +3709,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3832,14 +3772,11 @@
           <t>双龙中科</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>江苏省太仓市双凤镇陆江路1号</t>
@@ -3865,14 +3802,11 @@
           <t>深圳市家为安智能科技有限公司</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>186-0205-8898 / 400-608-0098</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>广东省佛山市南海区里水镇</t>
@@ -3880,7 +3814,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3898,9 +3832,6 @@
           <t>广州市优品声学科技有限公司</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>www.gzypsx.com</t>
@@ -3913,7 +3844,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3946,7 +3877,6 @@
           <t>133 9983 5678</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
@@ -3977,13 +3907,11 @@
           <t>高学梅</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>17687627315</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
@@ -4069,7 +3997,6 @@
           <t>+86 178-5768-8782</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
@@ -4077,7 +4004,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4115,7 +4042,6 @@
           <t>https://www.amerdecor.com/</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -4141,7 +4067,6 @@
           <t>王冠</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>+86 13229297183</t>
@@ -4204,7 +4129,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4227,7 +4152,6 @@
           <t>朱支群</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>13763963598</t>
@@ -4368,7 +4292,6 @@
           <t>(86) 158 8931 1832</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
@@ -4454,7 +4377,6 @@
           <t>18128752879</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>佛山狮山镇谭边工业区崩岗头路四号之一</t>
@@ -4507,7 +4429,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4530,13 +4452,11 @@
           <t>徐云霞</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>13697981203</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
@@ -4562,8 +4482,6 @@
           <t>苏州东山茶厂 (Suzhou Dongshan Biluochun Tea Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>0512-66281146</t>
@@ -4599,14 +4517,11 @@
           <t>知和香馆</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>15926183211</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>福建永春达埔</t>
@@ -4697,7 +4612,6 @@
           <t>www.ptat.cn</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -4723,7 +4637,6 @@
           <t>万磊市场部</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>186-8825-1404, 4000-147-187</t>
@@ -4864,7 +4777,6 @@
           <t>+86-13802465791</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
@@ -4872,7 +4784,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -4890,7 +4802,6 @@
           <t>浙江雅柔装饰材料有限公司 (Zhejiang Yarou Decoration Material Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>sale01@yarouwallpaper.com.cn</t>
@@ -4936,13 +4847,11 @@
           <t>戴艳辉</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>18830173388</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>石家庄市正定县曙光路49号东标和聚居</t>
@@ -4950,7 +4859,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5073,8 +4982,6 @@
           <t>+8618901960431</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5110,7 +5017,6 @@
           <t>13233648687</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
@@ -5136,7 +5042,6 @@
           <t>Foshan Cofesu Sanitary Ware Co., Ltd.</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>sales@cofesu.com</t>
@@ -5192,7 +5097,6 @@
           <t>+86-156-2562-1155</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
@@ -5200,7 +5104,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5233,7 +5137,6 @@
           <t>+86 132 8810 6615</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
@@ -5274,7 +5177,6 @@
           <t>+86 13823419116 / 0758-8565117</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
@@ -5327,7 +5229,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5345,18 +5247,14 @@
           <t>明德 (Mingde)</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>www.mingde-china.com</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5536,7 +5434,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5784,14 +5682,11 @@
           <t>张爱彬 (Zhang Aibin)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>+86 18178085851</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -6019,7 +5914,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">

--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$I$134</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +27,38 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Inter"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000071E3"/>
+        <bgColor rgb="000071E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F7"/>
+        <bgColor rgb="00F5F5F7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +66,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E8E8ED"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E8E8ED"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E8E8ED"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E8E8ED"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,5515 +462,5632 @@
   </sheetPr>
   <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Company Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Contact Person</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Sunhohi</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Crystal Wong</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>crystal@sunhohiglobal.com</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>+86-137 0262 5097</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>www.sunhohiwindow.com</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Marketing Center: 20th Floor, Building A1, Full International Financial Center, No. 28, Haiwu Road, Guicheng Street, Nanhai District, Foshan City, Guangdong Province, China; Factory: Zhenxing 3rd Road, Xincheng Town, Xinxing County, Yunfu City, Guangdong Province, China</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>50.000¥. Moq-1</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Guangdong Fuson Windoor Industry Co., Ltd</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Eileen Yip (叶颖怡)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>export09@fusonwindoor.com</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+86 18028156982</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>www.fusonwindoor.com</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Fuxuan Office Building, 2nd Longhu Rd, High Tech District, Zhaoqing City, Guangdong Province</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>50.000¥. Moq-1</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>开平艺和门业有限公司</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>开平艺和门业有限公司 (Kaiping Yihe Door Industry Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>张硕怡 (Stoney)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>134 1416 0636</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>50.000¥. Moq-1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>河南贝迪塑业有限公司 (Henan Beidi Plastic Industry Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Jane Li (李蓉娟)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Jane@hncrown.com</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>+86 187 3917 6242 / 86-0372-6270170</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>www.baydeegroup.com / www.hnbeidi.com</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>中国·河南省鹤壁市 (Hebi City, Henan Province, China)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>1000 pcs price 38 USD</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Guangzhou NewHoo Technology Co. Ltd</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Tony</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>export01@gznewhoo.com</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>+86-198-7837-3626</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>www.gznewhoo.com</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Building 7, Hongyu Smart Industrial Park, No. 333 Juhuashi Avenue, Huadu District, Guangzhou</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>80$</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>榜威电子科技（上海）有限公司 (Bweetech Electronics Technology (Shanghai) Co., Ltd)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>骆剑 (Kim Lok)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>kim.lok@bweetech.com</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>186-5759-0678</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>www.bweetech.com</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>500pcs / $100USD for pcs</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>DEIOUX WINDOWS &amp; DOORS</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>CANDICE CHOU</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>sales5@deiouxwindows.com</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>+86-13392246940</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Custom order</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>China Warren Windows and Doors Co., Ltd.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>info@warrenwindows.com</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>+86-400-811-0300</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>www.warrenwindows.com</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Room 1007, Block B, Wangjing SOHO, Chaoyang District, Beijing, China</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Custom order</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Zhongshan Smartek Security Technology Co.,LTD</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Tim Pan</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>market@smarteklock.com</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>+86-15889896019</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>www.smarteklock.com</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City Guangdong, China 528415</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>170 to 335 usd</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>HDL Automation Co., Ltd.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Krystal Wei</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>krystal@hdlautomation.com</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>+86 19512956186</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>www.hdlautomation.com</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>100 to up</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Ningbo AIFEIBAO Intelligent Security Co., Ltd</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Sean Xiao</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>sales@aifeibao.com</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>0086 198 1730 8681</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>www.afbsafe.com</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>No.1 Donghu Rd., Daxie Development Zone, Ningbo, China (315812)</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>100 to up usd</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>佛山市普辉亚科技有限公司 (Foshan Pu Huiya Technology Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>邹隆鹏</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>15818099349</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Super</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>广东招材建材科技有限公司</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>广东招材建材科技有限公司 (Guangdong Zhaocai Building Materials Technology Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>黎桃桃</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>toto.liblun@gmail.com</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>+8618934320539</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>www.liblun.com</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>广东省佛山市南海区罗行社区新下村5号厂房 (Workshop No. 5, Xinxia Village, Luoxing Community, Nanhai District, Foshan City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Super</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>浙江鑫东洁具有限公司 (ZHEJIANG XINDONG SANITARY WARE CO., LTD.)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>曾燕燕 Elyn</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>sales03@cn-xindong.com</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>0086-182 5765 3405, 0086-576-87493988</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Bath &amp; Sanitary</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>杭州南博装饰材料有限公司</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>杭州南博装饰材料有限公司 (Hangzhou Nanbo Decorative Materials Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>王小忠</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>浙江省杭州市临平区运河街道育士路53-1号</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市临平区运河街道育士路53-1号 (No. 53-1, Yushi Road, Yunhe Sub-district, Linping District, Hangzhou City, Zhejiang Province)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>台州旭升卫浴股份有限公司</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>台州旭升卫浴股份有限公司 (Taizhou Xusheng Sanitary Ware Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>应杨军</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>3572780651@qq.com</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>13511470999</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>www.xs88.cn</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>浙江省台州市台州湾新区海虹大道228#</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>浙江省台州市台州湾新区海虹大道228# (No. 228, Haihong Avenue, Taizhou Bay New Area, Taizhou City, Zhejiang Province)</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Bath &amp; Sanitary</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NIFO 耐孚</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>NIFO 耐孚 (NIFO Naifu)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>顾鹏</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>962460053@qq.com</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>13326792105</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Wall sheet , 200 rmb per meter , 2000 mtr,</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Zhejiang Oushe Home Improvement And New Materials Co., Ltd.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Davis Dong 董伟杰</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>sales05@authoe.com</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>+86-18906831082</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Jiaxing/Hongkong</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Handles , 500 moq , 100 rmb per handle</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>JIN OGMEI</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Alex Xing</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>kindeli1771@gmail.com</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>+86-18302200384</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Shijiazhuang City, Hebei Province</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>温州金锏智能锁具有限公司</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>温州金锏智能锁具有限公司 (Wenzhou Jinjian Intelligent Lock Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>张丽</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>jinjian19@jinjianlock.com</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>15067804393</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>www.jinjianlock.com</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号 (No. 1, Huameng Special Light Industry Park, Louqiao Sub-district, Ouhai District, Wenzhou City)</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>上海世灿国际贸易有限公司</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>上海世灿国际贸易有限公司 (Shanghai Shican International Trade Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>杨苗</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>yangm618@163.com</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>138 1618 4706</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>http://www.shicanchina.com</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>上海市浦东新区商城路889号C3-B06</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>上海市浦东新区商城路889号C3-B06 (C3-B06, No. 889 Shangcheng Road, Pudong New Area, Shanghai)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models an</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>COLOMAC DECOR</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Aaron Liu</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>aaron@ccolomac.com</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>+86-0371-66350801, +86 15936292861</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>www.ccolomac.com</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 10</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>佛山市同路匠人家具有限公司</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>佛山市同路匠人家具有限公司 (Foshan Tonglu Jiangren Furniture Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>赖华芳</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>13727479513, 400-8339513</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部 (9513 Furniture Headquarters, No. 3 Liansu Jiayuan 3rd Road, Longjiang Town, Shunde District, Foshan City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Home Furnishing</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Хорошее, 400rmb</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>固豪木业 | SUNDIN尚鼎</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>固豪木业 | SUNDIN尚鼎 (Guhao Wood Industry | SUNDIN Shangding)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Clément / 付雄豪</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>clement.fu@cqsdmy.com</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>+(86) 19112691557</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>www.guhaogroup.com / www.cqsdmy.com</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>Хорошее , 1500rmb</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>佛山市嘉豪飞度家具有限公司 (FOSHAN KAHO FIT FURNITURE CO., LTD.)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>周灿灿</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>15986196312@163.com</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>159 1909 0393, +86-757-2339 1505</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区乐从镇黎湖工业区 (Lihu Industrial Zone, Lecong Town, Shunde District, Foshan City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Home Furnishing</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Нормальное</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Suzhou Acousound New Material Technology Inc.</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Yolanda He</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>acousound07@polyacoustic.com</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>+86-18068038050</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>www.polyacoustic.com</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>$55, MOQ100pcs, good</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>CGCH</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>陈洁玲 Rowling</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>014@cgchcontainer.com</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>+86 189 2997 1329</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>www.cgchcontainer.com</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>1000 yuan 1 square</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>广东省中山名谷屋木门厂</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>广东省中山名谷屋木门厂 (Guangdong Zhongshan Mingguyu Wooden Door Factory)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>罗美玲</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>180 0760 4399</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>广东省中山市小榄镇东升门业生产基地F5B (F5B, Dongsheng Door Industry Production Base, Xiaolan Town, Zhongshan City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>150 rmb</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>multishades</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Sophia</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>sophia@multishades.com.cn</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>0086-15918713187, 0086-757-86780865</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>www.multishades.com.cn</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Office: Room 1501, CITIC Plaza, No.233, Tianhebei Road, Guangzhou City, Guangdong Province, China; Factory: 1 Shengshi Road, Shibei Industrial Park, Shishan Town, Foshan City, Guangdong Province, China</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>570 rmb</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>超友皮革家居</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>超友皮革家居 (Chaoyou Leather Home Furnishings)</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>1561767</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>130 super</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co.,Ltd)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>欧阳玉滢 (Sonia Ouyang)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>sonia.ouyang@wireking.com</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>+86-13392758223</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>$32, MOQ 300, good</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>PTA DOOR Automation (Hunan Tianan Door Technology Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Eva Leng</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>eva@ptadoor.com</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>+86 19848080478, +44 7704 561086</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>global.ptadoor.com</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Xincheng technology park, Yuelu Avenue, Changsha Hunan China</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>¥3000, MoQ 1pcs, very good</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>丰顺县泰雅达实业有限公司</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>丰顺县泰雅达实业有限公司 (Fengshun County Taiyada Industrial Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>徐小俊</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>281431686@qq.com</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>13802731123</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>https://taiyada1688.1688.com/</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>广东省丰顺县汤坑镇太平北路</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>广东省丰顺县汤坑镇太平北路 (Taiping North Road, Tangkeng Town, Fengshun County, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>¥17, Moq 50, good</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>佛山市悠派家居科技有限公司</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>佛山市悠派家居科技有限公司 (Foshan Youpai Home Technology Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>黄伟业</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Yea@LGPKB.com</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>13825596371</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>www.LGPKB.com</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区大良街道古鉴成展路3号 (No. 3, Chengzhan Road, Gujian, Daliang Subdistrict, Shunde District, Foshan City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>600 RMB Great, very cheap</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>常州市永春保温材料有限公司 (Changzhou Yongchun Thermal Insulation Materials Co., Ltd.)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>yc@ycbycl.com</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>0519-88931168</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>www.ycbycl.com</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>江苏省常州市天宁区郑陆镇工业集中区</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>江苏省常州市天宁区郑陆镇工业集中区 (Industrial Concentration Zone, Zhenglu Town, Tianning District, Changzhou City, Jiangsu Province)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>10$</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>诺奥(福建)环保家居用品有限公司</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>曾令贵</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>513573190@qq.com</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>86-13585642723 / 0596-8273388-8083</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>www.fjnuoao.cn</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号 (No. 191 Jindu Road, Taiwan Industrial Park, Xingtai Industrial Zone, Changtai District, Zhangzhou City, Fujian Province)</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>69$</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>大音声学 (DAYIN ACOUSTICS)</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>唐佳豪 (Vance)</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>+86 18925924350</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>www.dayinacoustics.com</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>佛山市南海区里水镇赤山大道32号 (No.32 Chishan Avenue, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>50-85$</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>杭州班昇</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>杭州班昇 (Hangzhou Bansheng)</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>陈卓敏 Ruby</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>295608376@qq.com</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>+86 13556688832</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>￥1000 good</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>FOSHAN SINCERE BUILDING MATERIALS CO., LTD.</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Crystal 刘晓艺</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>crystal@sincerechina.net</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>86-15815992213</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>www.sincerechina.net</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>佛山市禅城区南庄镇季华西路中国陶瓷产业总部基地西区C07-C08栋 (China Ceramics Industry Headquaters Block No.C07-08, West Area, West Jihua Road, Nanzhuang, Foshan, China)</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>¥ 500 good</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Xiamen Golden Ricky Industry &amp; Trade Co.,Ltd</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Joan Liu</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>joan@goldenrickyhpl.com</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>+86 13599525074</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Https://goldenrickyhpl.com</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Xiamen City, Fujian, China</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>￥ 300 good</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>江门市新阳刚智能科技有限公司</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>江门市新阳刚智能科技有限公司 (Jiangmen Xinyanggang Intelligent Technology Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>135 3666 7789, 400-9090-518</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>广东省江门市新会区大泽镇万洋众创城38-1号 (No. 38-1, Wanyang Zhongchuang City, Daze Town, Xinhui District, Jiangmen City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>300 rmb and more. Good quality and good price. Small quantity</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>河南蓝健陶瓷有限公司</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>河南蓝健陶瓷有限公司 (Henan Lanjian Ceramics Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>王闻浠</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>lanjanweiyu@163.com</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>+86-13569915996</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>www.lanjan.com</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>河南省长葛市石固镇梁庄工业园区</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>河南省长葛市石固镇梁庄工业园区 (Liangzhuang Industrial Park, Shigu Town, Changge City, Henan Province)</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>33$ for 1 pcs. Good quality and quantity</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>三强地毯</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>三强地毯 (Sanqiang Carpet)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>hengsheng_carpet@163.com</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>0769-89807692</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>Good 👍</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Higold Group Co., Ltd.</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Willer Zhou</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>sale31@higold.com.cn</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>+86 158 2865 5891</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>www.higoldhardware.com</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>No.36 Shunye East Rd, Xingtan, Shunde, Foshan 528325, Guangdong, China</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>5800</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Zhejiang Kehon Intelligent Science &amp; Technology Co., Ltd.</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Sammi Shi</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>sales01@kehon.cn</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>+86 156 8948 5097, 0578-3271096</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>www.kehon.cn</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>130 yuan</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Guangdong Wanbang Modular Building Co., Ltd</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Richie Wang</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>richie.wang@wbhouse.com</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>+86 137 1002 1675</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>www.gdwbprefabhouse.com</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Guangdong Factory: No.5, No. 161 Ganghe Avenue, Gaoming District, Foshan city, Guangdong, CHINA; Fujian Factory: Provincial Highway 308, Yunrong Township, Minqing County, Fuzhou City, Fujian Province, CHINA.</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>20000usd</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Guhao Group | SEAJOIN</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Owen Li</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>owen.li@seajoinhouse.com</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>(86) 133 9501 1076</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>www.seajoinhouse.com</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Chongqing, China / Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>500yuan</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>CAE SANITARY FITTINGS INDUSTRY CO., LTD. GUANGDONG</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Josie Guan</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>cae@china-cae.com</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>+86-13702279135</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>www.china-cae.com</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>No.62-64, Xingda Rd., Shagang Dist., Shuikou Town, Kaiping, Guangdong, P.R.Of China.</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>MOQ 100, 47 rnb per piece</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>盐城格子匠家居有限公司</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>盐城格子匠家居有限公司 (Yancheng Gezijiang Home Furnishing Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>董华</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>418897056@qq.com</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>13914649982, 18951488133</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号 (No. 10 Quanchuang Road, Qingdun Touzao Industrial Park, Tinghu District, Yancheng City, Jiangsu Province)</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>MOQ 50, 200 rnb per</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>SUOFEIYA HOME COLLECTION CO., LTD</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Jasmine Guan 管敏秀</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>jasmine@suofeiyahome.com</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>+86 147 7520 2759</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>https://www.sofeyiahome.com</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>MOQ 10, 845 per piece</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>利亚德光电股份有限公司 Leyard Optoelectronic Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>利亚德光电股份有限公司 Leyard Optoelectronic Co., Ltd. (Leyard Optoelectronic Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>金厚强 Jin Houqiang</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>jinhouqiang@leyard.com</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>13510009569, 18829341125, 400-8592-666</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>www.leyard.com</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋 (No. 9 Zhenghongqi West Street, Yiheyuan North (North of Summer Palace), Haidian District, Beijing / Building A, Shenzhen Leyard Micro-LED Southern Industrial Park, No. 6 Guanhe Road, Junzibu Community, Guanlan Sub-district, Longhua District, Shenzhen)</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>1pcs. Start from 60rmb. Novative technology</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>JNOD 基诺德</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>JNOD 基诺德 (JNOD)</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>周信朋 Joe Zhou</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>sales02@jnodwater.com</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>+86 199 2825 2201, +86-757-2361 7920</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>www.jnodwater.com</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>1410</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>广州传祺时代智能科技有限公司</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>广州传祺时代智能科技有限公司 (Guangzhou Chuanqi Era Intelligent Technology Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>洪美兰</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>jiang@chuangqitimes.com</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>13450298606, 020-82511901</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>www.chuangqitimes.com</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>广州市黄埔区云埔工业区观达路20号密博科技园 (Mibo Science Park, No. 20 Guanda Road, Yunpu Industrial Zone, Huangpu District, Guangzhou City)</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>RUIKANG</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>sales08@ruikang-cn.com</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>+86 18028330648, +86 18022073939</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>229</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>松下电器设备(中国)有限公司</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>潘禹</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>13691864691</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>广东省惠州市惠城区演达大道19号国安居6楼 (6th Floor, Guoanju, No. 19 Yanda Avenue, Huicheng District, Huizhou City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>680</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>CAE</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Jack Guan</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>jack@cae.cn</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>+86-750-8119338</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>www.cae.cn</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>150 yuan, 100, good range of products</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>广东富矿智能家居有限公司 (Guangdong Fukuang Intelligent Home Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>余赛银 (Yu Saiyin)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>109786129@qq.com</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>+86 13660529010</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>kingliye.com</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>佛山市南海区里广路二号碧桂园金沙国际广场1201室 (Room 1201, Building 10, Jinsha International Plaza No.2 Liguang Road, Nanhai District, Foshan City)</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Home Furnishing</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>肇庆合生雅居智能家居有限公司 (Zhaoqing Hesheng Yaju Intelligent Home Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Winni 何玲玲</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>helingling@gdhsyj.com</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>+86 18924564942</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>WWW.HOPSOONER.COM</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>视威电子科技（上海）有限公司</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>视威电子科技（上海）有限公司 (Shiwei Electronics Technology (Shanghai) Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>service@3weitech.com</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>021-57715805</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>www.3weitech.com</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>上海市闵行区新骏环路188号11号楼A座518室</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>上海市闵行区新骏环路188号11号楼A座518室 (Room 518, Block A, Building 11, No. 188 Xinjun Ring Road, Minhang District, Shanghai)</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет пр</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>爱舒床垫集团有限公司</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>爱舒床垫集团有限公司 (Aishu Mattress Group Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>王鹏</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>1319129904@qq.com</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>189-2324-7677</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>www.asnug.com</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>soundbox</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>劉奕紫 Cathy</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>sales19@soundbox.hk</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>+86 137 6339 3059</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккура</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>Shenzhen Kingston Sanitary Ware Co., Ltd.</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>Felicity</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>sales09@spakingston.com</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>+86-18025851458</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>www.spakingston.com</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>Kingston Company, JiangJun Road, Qiuchang, Huiyang, Huizhou, China</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>Bath &amp; Sanitary</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Guangzhou Sunrans Sanitary Ware Co., Ltd / Guangzhou Sunrans New Energy Technology Co., Ltd</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>William</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>william@sunrans.com</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>+86 134 1613 9887, +86-20-26231998</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>http://www.sunrans.com</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Bath &amp; Sanitary</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very go</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>15916159866</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>IFUN PARK &amp; TIPTOPFUN AMUSEMENT</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Ivy Zhou</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>ivy@ifunpark.com</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>+86 133 0238 5758</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>www.ifunpark.com / www.ifunamusement.com</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>RENQIU TUOXIN BUILDING MATERIALS CO., LTD</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>Emily Li</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>tuoxinlqm@outlook.com</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>+86 19831737599</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>https://www.tuoxinfiberglassmesh.com/</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>0.6 usd/m2</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>河南威兰得建筑科技有限公司</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>河南威兰得建筑科技有限公司 (Henan Weilande Building Technology Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>王虎旗</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>hectorwang1982@gmail.com</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>86 18638546565</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>www.weilandeglobal.com</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>河南省郑州市曲梁工业园188号</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>河南省郑州市曲梁工业园188号 (No. 188, Quliang Industrial Park, Zhengzhou City, Henan Province)</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>Under negotiation, great opportunities</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>江门市新会区致恒科技材料有限公司</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>江门市新会区致恒科技材料有限公司 (Jiangmen City Xinhui District Zhiheng Technology Materials Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>曹双林 (Edith Cao)</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>13286132534, 400-0750-889</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>广东省江门市蓬江区迎宾大道西23号之129</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>广东省江门市蓬江区迎宾大道西23号之129 (No. 23-129, West Yingbin Avenue, Pengjiang District, Jiangmen City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>1-5 usd/l</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>优品声学 (YP ACOUSTICS)</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>李尚声 (Shangsheng Li)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>15915975597@163.com</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>15915974406</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>6000RMB</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>双龙智科</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>双龙智科 (Shuanglong Intelligent Technology)</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>江苏省太仓市双凤镇陆江路1号</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>江苏省太仓市双凤镇陆江路1号 (No. 1 Lujiang Road, Shuangfeng Town, Taicang City, Jiangsu Province)</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>2000RMB&amp;gt;</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>GUANGDONG TUOXUN INTELLIGENT TECHNOLOGY CO., LTD</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Wing</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>wuyunying08@gmail.com</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>189-2984-9818, 0758-8578545</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>MOQ - 5000 and price - 7000 dollars</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>佛山市方泓五金建材有限公司 (Foshan Fangheng Hardware Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>陈施志凯 (CHEN SHI ZHI KAI)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>108455453@qq.com</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>+86 134 3318 1558, 0757-8560 9159</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>中国广东省佛山市南海区里水镇 (Lishui Town, Nanhai District, Foshan City, Guangdong Province)大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" s="3" t="inlineStr">
         <is>
           <t>The price cheap, merchant very friendly</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Countermast Technology (Dalian) Company Limited</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>sales.countermast.china@countermast.com</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>400-100-2228</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>www.countermast.cn</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>Building No.7, Zhongqing Industrial Park, Dalian free trade zone, Liaoning, China</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr">
         <is>
           <t>The price more cheaper, good quality</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>广州蒙娜丽莎控股集团有限公司, 广州蒙娜丽莎卫浴股份有限公司</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>广州蒙娜丽莎控股集团有限公司, 广州蒙娜丽莎卫浴股份有限公司 (Guangzhou Monalisa Holding Group Co., Ltd., Guangzhou Monalisa Bath Ware Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>严金霞</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>monalisa38@monalisa.cn</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>+86 13711113746, 400 020 1818, +86 20-28607711</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>www.monalisa.cn</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>广州市花都区花东镇港头工业区4号</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>广州市花都区花东镇港头工业区4号 (No. 4, Gangtou Industrial Zone, Huadong Town, Huadu District, Guangzhou City)</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>Bath &amp; Sanitary</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
         <is>
           <t>Good merchant, perfect products</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>高成 (Gaocheng)</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>叶小龙/Dustin Ye</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>yedustin@gmail.com</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>+86-188 5861 0008</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>www.cngaocheng.cn</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>浙江省三门县浦坝港镇沿海工业城 (COASTAL INDUSTRIAL CITY, PUBAGANG TOWN, SANMEN, TAIZHOU CITY, ZHEJIANG PRO., CHINA)</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr">
         <is>
           <t>160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>HONGKONG PINGAO INDUSTRIAL CO., LTD. / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>Pacao Yin</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>pin@pingaolao.com</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>(0086)13903035682, (0086)0769-86378283, (0086)0769-86377522</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>www.pingaolao.com, https://dgpingao.1688.com</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I77" s="3" t="inlineStr">
         <is>
           <t>15 RMB the product is interesting</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
+      <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>浙江瑞鑫环保设备有限公司</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>浙江瑞鑫环保设备有限公司 (Zhejiang Ruixin Environmental Protection Equipment Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>吴仁余</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>294217488@qq.com</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>13967444542, 0579-82889122</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>www.jhrxhb.com</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>浙江省金华市婺城区罗店镇北山路精工工业园</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>浙江省金华市婺城区罗店镇北山路精工工业园 (Jinggong Industrial Park, Beishan Road, Luodian Town, Wucheng District, Jinhua City, Zhejiang Province)</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>nearly $15,000 for this production line</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>ZHEJIANG DOUBLE-LIN VALVES CO., LTD.</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>Dream Lin</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>sale15@double-lin.com</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>86-020-66837727, 86-13710718529</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>www.double-lin.com</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I79" s="3" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>苏州市富尔达科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>苏州市富尔达科技股份有限公司 (Suzhou Fuerda Technology Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>袁佳磊</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>18652449601</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>www.cnfrd.cn</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>江苏省太仓市港区临江路1号</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>江苏省太仓市港区临江路1号 (No. 1 Linjiang Road, Port Area, Taicang City, Jiangsu Province)</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>749</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.,LTD.</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>Eric Huang</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>464565801@qq.com</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>13813551160 / 0519-88784050</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>www.ycpanel.com</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G81" s="3" t="inlineStr">
         <is>
           <t>No.28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I81" s="3" t="inlineStr">
         <is>
           <t>5000 USD</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
+      <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>双龙中科</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>双龙中科 (Shuanglong Zhongke)</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>江苏省太仓市双凤镇陆江路1号</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>江苏省太仓市双凤镇陆江路1号 (No. 1 Lujiang Road, Shuangfeng Town, Taicang City, Jiangsu Province)</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>深圳市家为安智能科技有限公司</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>深圳市家为安智能科技有限公司 (Shenzhen Jiaweian Intelligent Technology Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n"/>
+      <c r="D83" s="3" t="n"/>
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>186-0205-8898 / 400-608-0098</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>广东省佛山市南海区里水镇</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
+      <c r="F83" s="3" t="n"/>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市南海区里水镇 (Lishui Town, Nanhai District, Foshan City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I83" s="3" t="inlineStr">
         <is>
           <t>249 RMB. They have fully described their products.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>广州市优品声学科技有限公司</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>广州市优品声学科技有限公司 (Guangzhou Youpin Acoustics Technology Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>www.gzypsx.com</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>广东省广州市番禺区南村镇南村西路138号德意创意园二层</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>广东省广州市番禺区南村镇南村西路138号德意创意园二层 (2nd Floor, Deyi Creative Park, No. 138 Nancun West Road, Nancun Town, Panyu District, Guangzhou City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>6000RMB，积极，详细地告诉了一切</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
+      <c r="A85" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>贵州佑远木业有限公司</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>贵州佑远木业有限公司 (Guizhou Youyuan Wood Industry Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>颜加伟</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>1164199388@qq.com</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>133 9983 5678</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="F85" s="3" t="n"/>
+      <c r="G85" s="3" t="inlineStr">
         <is>
           <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H85" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I85" s="3" t="inlineStr">
         <is>
           <t>400rmb /m2 good meeting</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
+      <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>广西豪庭家具有限公司 (Guangxi Haoting Furniture Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>高学梅</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>17687627315</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Home Furnishing</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr">
         <is>
           <t>350 rmb/m2</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>Moershu (摩尔舒卫浴)</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>Thea</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>moershu3@moershu.com</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>13957622087</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>www.moershu.com</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>Bath &amp; Sanitary</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I87" s="3" t="inlineStr">
         <is>
           <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
+      <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Hangzhou Sciener Smart Technology Co.,Ltd.</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Zoey Zhang</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>zoey@sciener.com</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>+86 178-5768-8782</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr">
         <is>
           <t>20 / MOQ 100 Nice worker answered all questions</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
+      <c r="A89" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>江西荣科新型材料有限公司 / JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>江西荣科新型材料有限公司 / JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD. (Jiangxi Rongke New Materials Co., Ltd. / JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.)</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>Lucy Zeng (曾露)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>lucy@rongkedecor.com</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>+86-13134020034</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>https://www.amerdecor.com/</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I89" s="3" t="inlineStr">
         <is>
           <t>80 rmb for 230 meter</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
+      <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>SANNORA</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>王冠</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>+86 13229297183</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>WWW.SANNORA.COM; WWW.SANNORA-BATH.COM</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区 (Showroom: Block C03, East Area, China Ceramics Industry Headquarters Base, No. 68 Jihua West Road, Chancheng District, Foshan City; Factory: Tanbian Industrial Zone 2, Shishan Town, Nanhai District, Foshan City)</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr">
         <is>
           <t>1560 rmb for whole item</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
+      <c r="A91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>Kaiping Gold Medal Sanitary Ware Co.,Ltd. / Guangdong Aosman Sanitary Ware Co.,Ltd</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>Sophia Deng (邓小艳)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>sophiadeng@china-gold.cn</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>+181 3838 6948</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>http://www.china-gold.cn, http://www.aosman.cn</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G91" s="3" t="inlineStr">
         <is>
           <t>198 Siqian Xi Road, Shuikou, Kaiping 529300, Guangdong PR.China</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H91" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I91" s="3" t="inlineStr">
         <is>
           <t>4600 rmb</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
+      <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>江西瑞京鸿兴实业有限公司</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>江西瑞京鸿兴实业有限公司 (Jiangxi Ruijing Hongxing Industrial Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>朱支群</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>13763963598</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>www.jx-wpc.com</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>江西省瑞金市经济开发区创业一路东侧</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>江西省瑞金市经济开发区创业一路东侧 (East Side of Chuangye 1st Road, Economic Development Zone, Ruijin City, Jiangxi Province)</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr">
         <is>
           <t>250¥/м3</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
+      <c r="A93" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>Xuancheng Hengxin Sanitary Ware Co., Ltd</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>Anne</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>victor@ck-bath.com</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>18656330093</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>https://ck-bath.com/</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G93" s="3" t="inlineStr">
         <is>
           <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H93" s="3" t="inlineStr">
         <is>
           <t>Bath &amp; Sanitary</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I93" s="3" t="inlineStr">
         <is>
           <t>4500¥</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
+      <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>ciarra</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Linda</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>linda.lu@ciarrahome.com</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>+86 1882 9964 960, +86 1343 2639 580</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>www.ciarrahome.com</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr">
         <is>
           <t>300¥ 300pcs</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
+      <c r="A95" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>Yekalon Mills</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>Viola Liu</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>wood6@sennorwell.com</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>(86) 158 8931 1832</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="F95" s="3" t="n"/>
+      <c r="G95" s="3" t="inlineStr">
         <is>
           <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H95" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I95" s="3" t="inlineStr">
         <is>
           <t>50¥ 1000pcs</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
+      <c r="A96" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Ideal Sanitary Ware Co., Ltd.</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Amy Liu 刘建美</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>export@ideal-china.net</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>+86 (0) 757 8558 9299</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>www.ideal-sanitary.com</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>No.3 Hexi Road of Shashui, Yanghe Town, Gaoming District, Foshan City, Guangdong Province, 528515 - P.R.China.</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Bath &amp; Sanitary</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr">
         <is>
           <t>500$ 100psc</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>佛山市旌晨铝门窗有限公司</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>佛山市旌晨铝门窗有限公司 (Foshan Jingchen Aluminum Doors and Windows Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>胡光辉</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>1525423805@qq.com</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>18128752879</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>佛山狮山镇谭边工业区崩岗头路四号之一</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
+      <c r="F97" s="3" t="n"/>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>佛山狮山镇谭边工业区崩岗头路四号之一 (No. 4-1, Benggangtou Road, Tanbian Industrial Zone, Shishan Town, Foshan City)</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I97" s="3" t="inlineStr">
         <is>
           <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
+      <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>佛山市乾泽科技有限公司</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>佛山市乾泽科技有限公司 (Foshan Qianze Technology Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>陈可樑</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>hw-hardware@qian-ze.com</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>180 3863 7238</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>www.honeywell-hardware.com</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>广东省佛山市三水区云东海街道宝盛路2号1座三层（合和建筑五金园区北门）</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>广东省佛山市三水区云东海街道宝盛路2号1座三层（合和建筑五金园区北门） (3rd Floor, Block 1, No. 2 Baosheng Road, Yundonghai Sub-district, Sanshui District, Foshan City, Guangdong Province (North Gate of Hehe Building Hardware Park))</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
         <is>
           <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
+      <c r="A99" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>景德镇窑珍陶瓷</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>景德镇窑珍陶瓷 (Jingdezhen Yaozhen Ceramics)</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>徐云霞</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="D99" s="3" t="n"/>
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>13697981203</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
+      <c r="F99" s="3" t="n"/>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号 (Store Address: No. 1 Guomao Street, Guomao Plaza, Jingdezhen City, Jiangxi Province; Factory Address: No. 008 Goushang, Lvmeng High-tech Industrial Park)</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I99" s="3" t="inlineStr">
         <is>
           <t>100 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
+      <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>苏州东山茶厂 (Suzhou Dongshan Biluochun Tea Co., Ltd.)</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>0512-66281146</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>www.dsteaf.com</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>江苏省苏州市吴中区东山镇 (Dongshan Town, Wuzhong District, Suzhou City)</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>150 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
+      <c r="A101" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>知和香馆</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>知和香馆 (Zhihe Incense Pavilion)</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n"/>
+      <c r="D101" s="3" t="n"/>
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>15926183211</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>福建永春达埔</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
+      <c r="F101" s="3" t="n"/>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>福建永春达埔 (Dapu, Yongchun, Fujian)</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I101" s="3" t="inlineStr">
         <is>
           <t>They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
+      <c r="A102" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>San Nora (聖羅蘭·衛浴)</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>ALLEN XU (许熙平)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>sales@sannora.com</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>+86 137 0263 0244, +86-757-86438259</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>WWW.SANNORA.COM, WWW.SANNORA-BATH.COM</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>TANBIAN IND. ZONE, SHISHAN TOWN, NANHAI DIST., FOSHAN, GUANGDONG, CHINA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
+      <c r="A103" s="3" t="n">
         <v>102</v>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>PTAT | 帕兰蒂诺</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>PTAT | 帕兰蒂诺 (PTAT | Palantino)</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>Joy Yang</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>joy@rans.group</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>+86-13757430301</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>www.ptat.cn</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="G103" s="3" t="n"/>
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I103" s="3" t="inlineStr">
         <is>
           <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
+      <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>万磊建筑涂料有限公司</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>万磊建筑涂料有限公司 (Wanlei Architectural Coatings Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>万磊市场部</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>186-8825-1404, 4000-147-187</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>http://www.fswanlei.com</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区 (Headquarters: Songgang Wanshi Industrial Zone, Nanhai District, Foshan City, Guangdong Province; Branch Factory: Ganhua Park, Industrial Park, Qintang District, Guigang City, Guangxi Province)</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
+      <c r="A105" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>ZHEJIANG SEATING TECHNOLOGY CO., LTD.</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>May Zhang</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>sales5@anjeurostilefurniture.com</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>+86 182 5727 1590</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" s="3" t="inlineStr">
         <is>
           <t>www.zjseating.com</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G105" s="3" t="inlineStr">
         <is>
           <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H105" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I105" s="3" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
+      <c r="A106" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Chaozhou Lefu Sanitary Ware Technology Co., Ltd.</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Ethan</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>lucy@lefucz.com</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>+0086 18098114370</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>www.lefucz.com</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>Lefu Sanitary Ware, Sheweikeng, Dengtang Town, Chaoan District, Chaozhou City, Guangdong Province, China</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Bath &amp; Sanitary</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>1050</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
+      <c r="A107" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>胡沛能 / Oliver Hu</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>oliver@wireking.com</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>+86-13802465791</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="F107" s="3" t="n"/>
+      <c r="G107" s="3" t="inlineStr">
         <is>
           <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="H107" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I107" s="3" t="inlineStr">
         <is>
           <t>550</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
+      <c r="A108" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>浙江雅柔装饰材料有限公司 (Zhejiang Yarou Decoration Material Co., Ltd.)</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>sale01@yarouwallpaper.com.cn</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>+86-18069994326, +86-18069994377</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>https://www.yarouwallpaper.com.cn/</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>浙江省金华市义乌市福田街道涌金大道87号厂房二楼 (No. 1, Factory 2, Yongjin Avenue 87, Futian Subdistrict, Yiwu City, Jinhua City, Zhejiang Province)</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
+      <c r="A109" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>淄博永顺装饰材料有限公司</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>淄博永顺装饰材料有限公司 (Zibo Yongshun Decorative Materials Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>戴艳辉</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="D109" s="3" t="n"/>
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>18830173388</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>石家庄市正定县曙光路49号东标和聚居</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
+      <c r="F109" s="3" t="n"/>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>石家庄市正定县曙光路49号东标和聚居 (Dongbiaohejuju, No. 49 Shuguang Road, Zhengding County, Shijiazhuang City)</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I109" s="3" t="inlineStr">
         <is>
           <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
+      <c r="A110" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>宏宇集团 (HONGYU GROUP)</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Melina 王玲</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>lina@hongyugroup.com</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>+86 13827702216</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>en.hongyugroup.com</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="n">
+      <c r="A111" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>Chongnuo(Shandong)NewMaterial Co.,Ltd.</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>Daisy</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>sales06@chongnuo-floors.com</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>+86 19906379675</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>www.chongnuo-floors.com</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G111" s="3" t="inlineStr">
         <is>
           <t>QingyunCounty,DezhouCity,China</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="H111" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I111" s="3" t="inlineStr">
         <is>
           <t>9$</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
+      <c r="A112" s="2" t="n">
         <v>111</v>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>上海德翔木业有限公司 (Shanghai Dexiang Wood Industry Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>崔强 (Cui Qiang)</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>513437660@qq.com</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>+8618901960431</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>13.25$</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
+      <c r="A113" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>中材(邯郸)新材料有限公司 (China National Building Materials (Handan) New Materials Co.,Ltd.)</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>Wangfeng</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>2523911877@qq.com</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>13233648687</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="F113" s="3" t="n"/>
+      <c r="G113" s="3" t="inlineStr">
         <is>
           <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="H113" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I113" s="3" t="inlineStr">
         <is>
           <t>8.83$</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="n">
+      <c r="A114" s="2" t="n">
         <v>113</v>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Foshan Cofesu Sanitary Ware Co., Ltd.</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>sales@cofesu.com</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>+86 181 2821 2128</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>www.cofesu.com</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>Foshan, Guangdong, China</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Bath &amp; Sanitary</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr">
         <is>
           <t>30 PCs, 420 RMB, need check quality</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="n">
+      <c r="A115" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t>中国广东柜邦精密金属制品有限公司 (China Guangdong Guibang Precision Metal Products Co.Ltd)</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="3" t="inlineStr">
         <is>
           <t>唐一智 (JUNIOR)</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>13621417@qq.com</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>+86-156-2562-1155</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="F115" s="3" t="n"/>
+      <c r="G115" s="3" t="inlineStr">
         <is>
           <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="H115" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="I115" s="3" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="n">
+      <c r="A116" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Jieyang Yagegu Hardware Products Co., LTD</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>Zoya</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>2291828903@qq.com</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>+86 132 8810 6615</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="F116" s="2" t="n"/>
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
+      <c r="A117" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t>广东启宏盛精密五金制品有限公司 (GUANGDONG QIHONGSHENG PRECISION HARDWARE PRODUCTS CO., LTD)</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>邓美君 Jessica</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>bailide_hinge@163.com</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>+86 13823419116 / 0758-8565117</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="F117" s="3" t="n"/>
+      <c r="G117" s="3" t="inlineStr">
         <is>
           <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H117" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I117" s="3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
+      <c r="A118" s="2" t="n">
         <v>117</v>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>广东亚当斯金属精密制造有限公司 (Guangdong Adams Metal Precision Manufacturing Co.,Ltd)</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>Kelly Liang (梁凯莹)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>kelly@adamsmetal.com.cn</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>+86-180-2935-2895 / +86-757-25331912</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>www.adamsmetal.com.cn</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr">
         <is>
           <t>Depend on item</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
+      <c r="A119" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>明德 (Mingde)</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="C119" s="3" t="n"/>
+      <c r="D119" s="3" t="n"/>
+      <c r="E119" s="3" t="n"/>
+      <c r="F119" s="3" t="inlineStr">
         <is>
           <t>www.mingde-china.com</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="G119" s="3" t="n"/>
+      <c r="H119" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I119" s="3" t="inlineStr">
         <is>
           <t>Depend of quantity</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
+      <c r="A120" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>佛山市顺德区腾徽精密智造有限公司 (FoShan ShunDe TengHui Precision Intelligent Manufacturing Co., Ltd)</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>刘婉莹 Carol Liu</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>tenghuihardware@126.com</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>+86 133 1836 4599</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>www.teehve.cn</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>广东省佛山市顺德区勒流街道众涌村港口路以西8-9号之二 (No.8-9, West of GangKou Road, Zhongchong Village, Leliu Town, Shunde District, Foshan City, Guangdong, China)</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr">
         <is>
           <t>100/square meter</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
+      <c r="A121" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>DUOCAI TENT (多彩帐蓬)</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>Jimmy 黄锦民</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>sales003@sdduocaizp.com</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>(86)133 2294 8506, +86-766-8298662</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>www.dc-tent.com, www.sdduocaizp.com</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>云浮市云安区佛山(云浮)产业转移工业园86号 (No.86 Foshan(Yunfu) Industrial transfer park, yunan, yunfu, Guangdong China)</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="H121" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="I121" s="3" t="inlineStr">
         <is>
           <t>RMB 15705 MOQ5; pleasant impression</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
+      <c r="A122" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>佛山市路乐户外制品有限公司 (FOSHAN RULER OUTDOOR HARDWARES CO.,LTD)</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>Marco Lau (刘嘉乐)</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>RULERAWNING07@163.COM</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>+86 13129016338</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>WWW.RULER-AWNING.COM</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>END OF ROAD SHATANXIAN, SHASHUI INDUSTRIAL ZONE, SONGGANG TOWN, SHISHAN DISTRICT, FOSHAN CITY, GUANGDONG PROVINCE, CHINA, 528200</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr">
         <is>
           <t>MOQ5 25799 RMB</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
+      <c r="A123" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>Avant Sports Industrial Co., Ltd.</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>Jay Zhou</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>jay@avant.com.cn</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>+86-13128980150, +86-755-2968-8357</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>www.avantseating.com</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G123" s="3" t="inlineStr">
         <is>
           <t>Avant Industrial Park, Zhoushi Road, Bao'an, Shenzhen, Guangdong Province, China</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H123" s="3" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="I123" s="3" t="inlineStr">
         <is>
           <t>RMB 19479; MOQ 1</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="n">
+      <c r="A124" s="2" t="n">
         <v>123</v>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>孟少美 (Elite Meng)</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>ttf@hbtfjs.com</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>+86-13103196326</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>www.hbtfjs.com</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>河北省隆尧县东谷子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="n">
+      <c r="A125" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>揭阳市新骏业五金制品有限公司 (JIEYANG XINJUNYE HARDWARE PRODUCTS CO., LTD)</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>林树丹 (Lin Shudan)</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>linshdong@qq.com</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>13751676456</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr">
         <is>
           <t>www.xinjunye.com</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G125" s="3" t="inlineStr">
         <is>
           <t>广东省揭阳市揭东区锡场工业区 (Xichang Industrial Zone, Jiedong District, Jieyang City, Guangdong Province)</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H125" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="I125" s="3" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="n">
+      <c r="A126" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>广州蒙娜丽莎控股集团有限公司 / 广州蒙娜丽莎卫浴股份有限公司</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>广州蒙娜丽莎控股集团有限公司 / 广州蒙娜丽莎卫浴股份有限公司 (Guangzhou Monalisa Holding Group Co., Ltd. / Guangzhou Monalisa Sanitary Ware Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>伍乐彤</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>monalisa702@monalisa.cn</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>86 13711117863, 400 020 1818, 86 20-28607722, 86 20-28607788</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>www.monalisa.cn</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>广州市花都区花东镇港头工业区4号</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>广州市花都区花东镇港头工业区4号 (No. 4, Gangtou Industrial Zone, Huadong Town, Huadu District, Guangzhou City)</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Bath &amp; Sanitary</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr">
         <is>
           <t>2000$, can be customized, very convenient</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="n">
+      <c r="A127" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>中山藝進不銹鋼裝飾制品有限公司 (ZHONGSHAN YIJIN STAINLESS STEEL DECORATION CO., LTD.)</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
         <is>
           <t>Anson Yuen</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>info@hugemount.com</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>150 1954 6322 / 86-760-88702663</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr">
         <is>
           <t>www.yijin.com</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G127" s="3" t="inlineStr">
         <is>
           <t>中国广东省中山市港口镇石特社区穗安工业区迎富2路1号 (NO.1, Ying Fu 2 Road, Sui An Gong Ye Qu, Gang Kou Zhen Shi Te She Qu, Zhongshan City, Guangdong Province, P.R.China)</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="H127" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I127" s="3" t="inlineStr">
         <is>
           <t>38$, very unique</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
+      <c r="A128" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>宣城市宠爱卫浴有限公司 (CHONGAI SANITARY WARE CO., LTD.)</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>Lucy (卢美珍)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>export@vnsmilo.com</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>+86-13757322119</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>www.vnsmilo.com</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>Xuancheng City Anhui, CHINA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Bath &amp; Sanitary</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr">
         <is>
           <t>2050 rmb, very interesting, convenient to use for pets</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="n">
+      <c r="A129" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t>广西中晨木业有限公司 (Guangxi Zhongchen Wood Industry Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="3" t="inlineStr">
         <is>
           <t>张爱彬 (Zhang Aibin)</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="D129" s="3" t="n"/>
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>+86 18178085851</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="F129" s="3" t="n"/>
+      <c r="G129" s="3" t="n"/>
+      <c r="H129" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="I129" s="3" t="inlineStr">
         <is>
           <t>25 rmb, 1 box, like this product</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="n">
+      <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>NINGBO YUSHENG HOME TECH CO., LTD. (宁波裕盛家居科技有限公司)</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>Tequila Xu (徐孟杰)</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>marketing@cxyushun.com, tequila8xu@gmail.com</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>0086-13819449988, +86 574 63190388</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>www.cxys8.com</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>中国浙江慈溪市杨梅大道南路1518号 (NO.1518, YANGMEI AVENUE SOUTH ROAD, CIXI CITY, ZHEJIANG, CHINA)</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr">
         <is>
           <t>34 rmb, 1000, normal</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="n">
+      <c r="A131" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
         <is>
           <t>河北建华锁业有限公司 (Hebei Jianhua Lock Industry Co., Ltd.)</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>刘芳 (Jane Liu)</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>jane@dirock.cn</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>187 1377 2087</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr">
         <is>
           <t>http://www.dirock.cn</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>河北省泊头市寺门村镇后牛屯</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>河北省泊头市寺门村镇后牛屯 (Houniutun, Simencun Town, Botou City, Hebei Province)</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="I131" s="3" t="inlineStr">
         <is>
           <t>40 rmb, 2000, very good</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
+      <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>浙江安吉双虎竹木业有限公司 / 安吉诺迪新材料有限公司</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>浙江安吉双虎竹木业有限公司 / 安吉诺迪新材料有限公司 (Zhejiang Anji Shuanghu Bamboo and Wood Industry Co., Ltd. / Anji Nuodi New Materials Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>周瑶琳</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>lisa.nordi@nuodibm.com</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>+86-137 3822 8209</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>www.tigerbamboo.com / www.nuodibm.com</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>浙江省湖州市安吉县孝丰镇大竹村 (Dazhu Village, Xiaofeng Town, Anji County, Huzhou City, Zhejiang Province)</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr">
         <is>
           <t>1 container 250 rmb</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="n">
+      <c r="A133" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd)</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>马世晓 (Amelia Ma)</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>tf@hbtfjs.com, mashixiaomsx@163.com</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>15097968589, 0319-6581195</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>www.hbtfjs.com</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G133" s="3" t="inlineStr">
         <is>
           <t>河北省隆尧县公子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H133" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I133" s="3" t="inlineStr">
         <is>
           <t>1 container 700 rmb</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
+      <c r="A134" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>ZHEJIANG TIANYAN HOLDING CO.,LTD.</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>Nicole</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>ty11@cntianyan.com</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>+86-15867028552</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>www.cntianyan.com</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>Chengjiang industrial zone,huangyan district taizhou,zhejiang,china</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr">
         <is>
           <t>Цена зависит от обьема, от 3 юаней, расходники</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>50.000¥. Moq-1</t>
+          <t>Buyer: 50.000¥. Moq-1</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>50.000¥. Moq-1</t>
+          <t>Buyer: 50.000¥. Moq-1</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50.000¥. Moq-1</t>
+          <t>Buyer: 50.000¥. Moq-1</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>1000 pcs price 38 USD</t>
+          <t>Buyer: 1000 pcs price 38 USD</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80$</t>
+          <t>Buyer: 80$</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>500pcs / $100USD for pcs</t>
+          <t>Buyer: 500pcs / $100USD for pcs</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Custom order</t>
+          <t>Buyer: Custom order</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Custom order</t>
+          <t>Buyer: Custom order</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>170 to 335 usd</t>
+          <t>Buyer: 170 to 335 usd</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>100 to up</t>
+          <t>Buyer: 100 to up</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>100 to up usd</t>
+          <t>Buyer: 100 to up usd</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>邹隆鹏</t>
+          <t>邹隆鹏 (Zou Longpeng)</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>Buyer: Super</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>黎桃桃</t>
+          <t>黎桃桃 (Li Taotao)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>Buyer: Super</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>曾燕燕 Elyn</t>
+          <t>曾燕燕 Elyn (Zeng Yanyan Elyn)</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Buyer: 50</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>王小忠</t>
+          <t>王小忠 (Wang Xiaozhong)</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>应杨军</t>
+          <t>应杨军 (Ying Yangjun)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>顾鹏</t>
+          <t>顾鹏 (Gu Peng)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Wall sheet , 200 rmb per meter , 2000 mtr,</t>
+          <t>Buyer: Wall sheet , 200 rmb per meter , 2000 mtr,</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Handles , 500 moq , 100 rmb per handle</t>
+          <t>Buyer: Handles , 500 moq , 100 rmb per handle</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
+          <t>Buyer: Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>张丽</t>
+          <t>张丽 (Zhang Li)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for</t>
+          <t>Buyer: Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>杨苗</t>
+          <t>杨苗 (Yang Miao)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models an</t>
+          <t>Buyer: Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models an</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 10</t>
+          <t>Buyer: Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 10</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>赖华芳</t>
+          <t>赖华芳 (Lai Huafang)</t>
         </is>
       </c>
       <c r="D24" s="2" t="n"/>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Хорошее, 400rmb</t>
+          <t>Buyer: Хорошее, 400rmb</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Clément / 付雄豪</t>
+          <t>Clément / 付雄豪 (Clément / Fu Xionghao)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Хорошее , 1500rmb</t>
+          <t>Buyer: Хорошее , 1500rmb</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>周灿灿</t>
+          <t>周灿灿 (Zhou Cancan)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Нормальное</t>
+          <t>Buyer: Нормальное</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>$55, MOQ100pcs, good</t>
+          <t>Buyer: $55, MOQ100pcs, good</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>陈洁玲 Rowling</t>
+          <t>陈洁玲 Rowling (Rowling Chen Jieling (or Chen Jieling Rowling))</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1000 yuan 1 square</t>
+          <t>Buyer: 1000 yuan 1 square</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>罗美玲</t>
+          <t>罗美玲 (Luo Meiling)</t>
         </is>
       </c>
       <c r="D29" s="3" t="n"/>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>150 rmb</t>
+          <t>Buyer: 150 rmb</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>570 rmb</t>
+          <t>Buyer: 570 rmb</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>130 super</t>
+          <t>Buyer: 130 super</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>$32, MOQ 300, good</t>
+          <t>Buyer: $32, MOQ 300, good</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>¥3000, MoQ 1pcs, very good</t>
+          <t>Buyer: ¥3000, MoQ 1pcs, very good</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>徐小俊</t>
+          <t>徐小俊 (Xu Xiaojun)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>¥17, Moq 50, good</t>
+          <t>Buyer: ¥17, Moq 50, good</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>黄伟业</t>
+          <t>黄伟业 (Huang Weiye)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>600 RMB Great, very cheap</t>
+          <t>Buyer: 600 RMB Great, very cheap</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10$</t>
+          <t>Buyer: 10$</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>曾令贵</t>
+          <t>曾令贵 (Zeng Linggui)</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>69$</t>
+          <t>Buyer: 69$</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>50-85$</t>
+          <t>Buyer: 50-85$</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>陈卓敏 Ruby</t>
+          <t>陈卓敏 Ruby (Ruby Chen Zhuomin)</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>￥1000 good</t>
+          <t>Buyer: ￥1000 good</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Crystal 刘晓艺</t>
+          <t>Crystal 刘晓艺 (Crystal Liu Xiaoyi)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>¥ 500 good</t>
+          <t>Buyer: ¥ 500 good</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>￥ 300 good</t>
+          <t>Buyer: ￥ 300 good</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>300 rmb and more. Good quality and good price. Small quantity</t>
+          <t>Buyer: 300 rmb and more. Good quality and good price. Small quantity</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>王闻浠</t>
+          <t>王闻浠 (Wang Wenxi)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>33$ for 1 pcs. Good quality and quantity</t>
+          <t>Buyer: 33$ for 1 pcs. Good quality and quantity</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Good 👍</t>
+          <t>Buyer: Good 👍</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>Buyer: 5800</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>130 yuan</t>
+          <t>Buyer: 130 yuan</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>20000usd</t>
+          <t>Buyer: 20000usd</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>500yuan</t>
+          <t>Buyer: 500yuan</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>MOQ 100, 47 rnb per piece</t>
+          <t>Buyer: MOQ 100, 47 rnb per piece</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>董华</t>
+          <t>董华 (Dong Hua)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MOQ 50, 200 rnb per</t>
+          <t>Buyer: MOQ 50, 200 rnb per</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>MOQ 10, 845 per piece</t>
+          <t>Buyer: MOQ 10, 845 per piece</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1pcs. Start from 60rmb. Novative technology</t>
+          <t>Buyer: 1pcs. Start from 60rmb. Novative technology</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>Buyer: 1410</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>洪美兰</t>
+          <t>洪美兰 (Hong Meilan)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>Buyer: 329</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>Buyer: 229</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>潘禹</t>
+          <t>潘禹 (Pan Yu)</t>
         </is>
       </c>
       <c r="D56" s="2" t="n"/>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>Buyer: 680</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>150 yuan, 100, good range of products</t>
+          <t>Buyer: 150 yuan, 100, good range of products</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
+          <t>Buyer: Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Winni 何玲玲</t>
+          <t>Winni 何玲玲 (Winni He Lingling)</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+          <t>Buyer: The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет пр</t>
+          <t>Buyer: 167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет пр</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>王鹏</t>
+          <t>王鹏 (Wang Peng)</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
+          <t>Buyer: 20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>劉奕紫 Cathy</t>
+          <t>劉奕紫 Cathy (Cathy Liu Yizi)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккура</t>
+          <t>Buyer: От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккура</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very go</t>
+          <t>Buyer: MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very go</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
+          <t>Buyer: MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>Buyer: 600</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>0.6 usd/m2</t>
+          <t>Buyer: 0.6 usd/m2</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>王虎旗</t>
+          <t>王虎旗 (Wang Huqi)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Under negotiation, great opportunities</t>
+          <t>Buyer: Under negotiation, great opportunities</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>1-5 usd/l</t>
+          <t>Buyer: 1-5 usd/l</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>6000RMB</t>
+          <t>Buyer: 6000RMB</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>2000RMB&amp;gt;</t>
+          <t>Buyer: 2000RMB&amp;gt;</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MOQ - 5000 and price - 7000 dollars</t>
+          <t>Buyer: MOQ - 5000 and price - 7000 dollars</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>The price cheap, merchant very friendly</t>
+          <t>Buyer: The price cheap, merchant very friendly</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>The price more cheaper, good quality</t>
+          <t>Buyer: The price more cheaper, good quality</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>严金霞</t>
+          <t>严金霞 (Yan Jinxia)</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Good merchant, perfect products</t>
+          <t>Buyer: Good merchant, perfect products</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>叶小龙/Dustin Ye</t>
+          <t>叶小龙/Dustin Ye (Ye Xiaolong/Dustin Ye)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
+          <t>Buyer: 160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>15 RMB the product is interesting</t>
+          <t>Buyer: 15 RMB the product is interesting</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>吴仁余</t>
+          <t>吴仁余 (Wu Renyu)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>nearly $15,000 for this production line</t>
+          <t>Buyer: nearly $15,000 for this production line</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>Buyer: 149</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>袁佳磊</t>
+          <t>袁佳磊 (Yuan Jialei)</t>
         </is>
       </c>
       <c r="D80" s="2" t="n"/>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>Buyer: 749</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>5000 USD</t>
+          <t>Buyer: 5000 USD</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
+          <t>Buyer: Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>249 RMB. They have fully described their products.</t>
+          <t>Buyer: 249 RMB. They have fully described their products.</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>6000RMB，积极，详细地告诉了一切</t>
+          <t>Buyer: 6000RMB，积极，详细地告诉了一切</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>颜加伟</t>
+          <t>颜加伟 (Yan Jiawei)</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>400rmb /m2 good meeting</t>
+          <t>Buyer: 400rmb /m2 good meeting</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>高学梅</t>
+          <t>高学梅 (Gao Xuemei)</t>
         </is>
       </c>
       <c r="D86" s="2" t="n"/>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>350 rmb/m2</t>
+          <t>Buyer: 350 rmb/m2</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
+          <t>Buyer: 194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>20 / MOQ 100 Nice worker answered all questions</t>
+          <t>Buyer: 20 / MOQ 100 Nice worker answered all questions</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>80 rmb for 230 meter</t>
+          <t>Buyer: 80 rmb for 230 meter</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>王冠</t>
+          <t>王冠 (Wang Guan)</t>
         </is>
       </c>
       <c r="D90" s="2" t="n"/>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>1560 rmb for whole item</t>
+          <t>Buyer: 1560 rmb for whole item</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>4600 rmb</t>
+          <t>Buyer: 4600 rmb</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>朱支群</t>
+          <t>朱支群 (Zhu Zhiqun)</t>
         </is>
       </c>
       <c r="D92" s="2" t="n"/>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>250¥/м3</t>
+          <t>Buyer: 250¥/м3</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>4500¥</t>
+          <t>Buyer: 4500¥</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>300¥ 300pcs</t>
+          <t>Buyer: 300¥ 300pcs</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>50¥ 1000pcs</t>
+          <t>Buyer: 50¥ 1000pcs</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Amy Liu 刘建美</t>
+          <t>Amy Liu 刘建美 (Amy Liu / Liu Jianmei)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>500$ 100psc</t>
+          <t>Buyer: 500$ 100psc</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>胡光辉</t>
+          <t>胡光辉 (Hu Guanghui)</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>980y/m2, moq 1000p, like doors with Mosquito netting</t>
+          <t>Buyer: 980y/m2, moq 1000p, like doors with Mosquito netting</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>陈可樑</t>
+          <t>陈可樑 (Chen Keliang)</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>1000-2000p, 1.7-7$, good beautiful doors handless</t>
+          <t>Buyer: 1000-2000p, 1.7-7$, good beautiful doors handless</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>徐云霞</t>
+          <t>徐云霞 (Xu Yunxia)</t>
         </is>
       </c>
       <c r="D99" s="3" t="n"/>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>100 RMB per sample. The taste is very good</t>
+          <t>Buyer: 100 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>150 RMB per sample. The taste is very good</t>
+          <t>Buyer: 150 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
+          <t>Buyer: They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>万磊市场部</t>
+          <t>万磊市场部 (Wan Lei - Marketing Department)</t>
         </is>
       </c>
       <c r="D104" s="2" t="n"/>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>Buyer: 1100</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>Buyer: 1050</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>胡沛能 / Oliver Hu</t>
+          <t>胡沛能 / Oliver Hu (Hu Peineng / Oliver Hu)</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>Buyer: 550</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
+          <t>Buyer: 14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>戴艳辉</t>
+          <t>戴艳辉 (Dai Yanhui)</t>
         </is>
       </c>
       <c r="D109" s="3" t="n"/>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
+          <t>Buyer: 0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Melina 王玲</t>
+          <t>Melina 王玲 (Melina Wang Ling)</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Buyer: 20</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>9$</t>
+          <t>Buyer: 9$</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>13.25$</t>
+          <t>Buyer: 13.25$</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>8.83$</t>
+          <t>Buyer: 8.83$</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>30 PCs, 420 RMB, need check quality</t>
+          <t>Buyer: 30 PCs, 420 RMB, need check quality</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>Buyer: 10000</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>Buyer: 10000</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>邓美君 Jessica</t>
+          <t>邓美君 Jessica (Jessica Deng Meijun)</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Depend on item</t>
+          <t>Buyer: Depend on item</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>Depend of quantity</t>
+          <t>Buyer: Depend of quantity</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>刘婉莹 Carol Liu</t>
+          <t>刘婉莹 Carol Liu (Carol Liu Wanying)</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>100/square meter</t>
+          <t>Buyer: 100/square meter</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Jimmy 黄锦民</t>
+          <t>Jimmy 黄锦民 (Jimmy Huang Jinmin)</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>RMB 15705 MOQ5; pleasant impression</t>
+          <t>Buyer: RMB 15705 MOQ5; pleasant impression</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>MOQ5 25799 RMB</t>
+          <t>Buyer: MOQ5 25799 RMB</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>RMB 19479; MOQ 1</t>
+          <t>Buyer: RMB 19479; MOQ 1</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>Buyer: 1000</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>Buyer: 1000</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>伍乐彤</t>
+          <t>伍乐彤 (Wu Letong (or Ng Lok Tung in Cantonese))</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2000$, can be customized, very convenient</t>
+          <t>Buyer: 2000$, can be customized, very convenient</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>38$, very unique</t>
+          <t>Buyer: 38$, very unique</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2050 rmb, very interesting, convenient to use for pets</t>
+          <t>Buyer: 2050 rmb, very interesting, convenient to use for pets</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>25 rmb, 1 box, like this product</t>
+          <t>Buyer: 25 rmb, 1 box, like this product</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>34 rmb, 1000, normal</t>
+          <t>Buyer: 34 rmb, 1000, normal</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>40 rmb, 2000, very good</t>
+          <t>Buyer: 40 rmb, 2000, very good</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>周瑶琳</t>
+          <t>周瑶琳 (Zhou Yaolin)</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>1 container 250 rmb</t>
+          <t>Buyer: 1 container 250 rmb</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>1 container 700 rmb</t>
+          <t>Buyer: 1 container 700 rmb</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Цена зависит от обьема, от 3 юаней, расходники</t>
+          <t>Buyer: Цена зависит от обьема, от 3 юаней, расходники</t>
         </is>
       </c>
     </row>

--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CBD Suppliers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CBD Suppliers'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CBD Suppliers'!$A$1:$I$177</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -457,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -550,7 +553,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -559,8 +562,6675 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Eileen Yip (叶颖怡)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>export09@fusonwindoor.com</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>+86 18028156982</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>www.fusonwindoor.com</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Fuxuan Office Building, 2nd Longhu Rd, High Tech District, Zhaoqing City, Guangdong Province</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 50.000¥. Moq-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>张硕怡 (Stoney)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>134 1416 0636</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 50.000¥. Moq-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Crystal Wong 黄健秋</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>info@sunhohiglobal.com, crystalwindowsanddoors0908@gmail.com</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>0086-137 0262 5097, 0086-138 2396 7979</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>www.sunhohiwindow.com</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>R&amp;F International Financial Center, Nanhai District, Foshan City, Guangdong Province, China</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1000 pcs price 120 usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Jane Li (李蓉娟)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Jane@hncrown.com</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>+86 187 3917 6242 / 86-0372-6270170</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>www.baydeegroup.com / www.hnbeidi.com</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>中国·河南省鹤壁市 (Hebi City, Henan Province, China)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 1000 pcs price 38 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Tony</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>export01@gznewhoo.com</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>+86-198-7837-3626</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>www.gznewhoo.com</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Building 7, Hongyu Smart Industrial Park, No. 333 Juhuashi Avenue, Huadu District, Guangzhou</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 80$</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>骆剑 (Kim Lok)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>kim.lok@bweetech.com</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>186-5759-0678</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>www.bweetech.com</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 500pcs / $100USD for pcs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>CANDICE CHOU</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>sales5@deiouxwindows.com</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>+86-13392246940</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Custom order</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>info@warrenwindows.com</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>+86-400-811-0300</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>www.warrenwindows.com</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Room 1007, Block B, Wangjing SOHO, Chaoyang District, Beijing, China</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: Custom order</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Tim Pan</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>market@smarteklock.com</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>+86-15889896019</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>www.smarteklock.com</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City Guangdong, China 528415</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 170 to 335 usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Krystal Wei</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>krystal@hdlautomation.com</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>+86 19512956186</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>www.hdlautomation.com</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 100 to up</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Sean Xiao</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>sales@aifeibao.com</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>0086 198 1730 8681</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>www.afbsafe.com</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>No.1 Donghu Rd., Daxie Development Zone, Ningbo, China (315812)</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 100 to up usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>邹隆鹏</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15818099349</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: Super</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>黎桃桃</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>toto.liblun@gmail.com</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>+8618934320539</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>www.liblun.com</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Super</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>曾燕燕 Elyn</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>sales03@cn-xindong.com</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0086-182 5765 3405, 0086-576-87493988</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>王小忠</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>浙江省杭州市临平区运河街道育士路53-1号</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>应杨军</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3572780651@qq.com</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13511470999</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>www.xs88.cn</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>浙江省台州市台州湾新区海虹大道228#</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>顾鹏</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>962460053@qq.com</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>13326792105</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Wall sheet , 200 rmb per meter , 2000 mtr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Davis Dong 董伟杰</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>sales05@authoe.com</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>+86-18906831082</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Jiaxing/Hongkong</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: Handles , 500 moq , 100 rmb per handle</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Alex Xing</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>kindeli1771@gmail.com</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>+86-18302200384</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Shijiazhuang City, Hebei Province</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>张丽</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>jinjian19@jinjianlock.com</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15067804393</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>www.jinjianlock.com</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for customized branding. Feedback: The company has a professional production line and solid hardware quality. Their prices are very competitive for the mass market, although their software ecosystem is less advanced than Innovation's current solutions. They are a reliable choice for high-volume, cost-effective projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>杨苗</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>yangm618@163.com</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>138 1618 4706</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>http://www.shicanchina.com</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>上海市浦东新区商城路889号C3-B06</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models and 150 units for custom OEM branding. Feedback: Yang Miao Miao demonstrates excellent mechanical build quality and focuses heavily on the structural integrity of the doors. Their pricing is mid-range, offering a good balance between durability and cost. They are highly flexible with custom design requests, making them a strong potential partner for Innovation’s specialized architectural projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Aaron Liu</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>aaron@ccolomac.com</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>+86-0371-66350801, +86 15936292861</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>www.ccolomac.com</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 100 units for customized decorative panels. Feedback: Colomac Decor stands out for its superior aesthetic design and premium finishing materials. Their products align well with luxury interiors, showing high attention to detail in surface textures. They are an ideal partner for Innovation when the goal is to merge smart technology with high-end interior aesthetics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>赖华芳</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>13727479513, 400-8339513</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Хорошее, 400rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Clément / 付雄豪</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>clement.fu@cqsdmy.com</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>+(86) 19112691557</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>www.guhaogroup.com / www.cqsdmy.com</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: Хорошее , 1500rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>周灿灿</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>15986196312@163.com</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>159 1909 0393, +86-757-2339 1505</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Нормальное</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Yolanda He</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>acousound07@polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>+86-18068038050</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: $55, MOQ100pcs, good</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>陈洁玲 Rowling</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>014@cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>+86 189 2997 1329</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>www.cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1000 yuan 1 square</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>罗美玲</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>180 0760 4399</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 150 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Sophia</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>sophia@multishades.com.cn</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>0086-15918713187, 0086-757-86780865</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>www.multishades.com.cn</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Office: Room 1501, CITIC Plaza, No.233, Tianhebei Road, Guangzhou City, Guangdong Province, China; Factory: 1 Shengshi Road, Shibei Industrial Park, Shishan Town, Foshan City, Guangdong Province, China</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 570 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>黎桃桃</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>toto.liblun@gmail.com</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>+8618934320539</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>www.liblun.com</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 620 super</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>黄上梅</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>13434829660, 400-8339513</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区龙江镇联登碧园三路3号9513家具总部</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1500 super</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1561767</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 130 super</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>欧阳玉滢 (Sonia Ouyang)</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>sonia.ouyang@wireking.com</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>+86-13392758223</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: $32, MOQ 300, good</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Eva Leng</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>eva@ptadoor.com</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>+86 19848080478, +44 7704 561086</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>global.ptadoor.com</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Xincheng technology park, Yuelu Avenue, Changsha Hunan China</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: ¥3000, MoQ 1pcs, very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>徐小俊</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>281431686@qq.com</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>13802731123</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>https://taiyada1688.1688.com/</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>广东省丰顺县汤坑镇太平北路</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: ¥17, Moq 50, good</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>黄伟业</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Yea@LGPKB.com</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>13825596371</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>www.LGPKB.com</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 600 RMB Great, very cheap</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>yc@ycbycl.com</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>0519-88931168</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>www.ycbycl.com</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>江苏省常州市天宁区郑陆镇工业集中区</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 10$</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>曾令贵</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>513573190@qq.com</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>86-13585642723 / 0596-8273388-8083</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>www.fjnuoao.cn</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 69$</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>唐佳豪 (Vance)</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>+86 18925924350</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>www.dayinacoustics.com</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>佛山市南海区里水镇赤山大道32号 (No.32 Chishan Avenue, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 50-85$</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>陈卓敏 Ruby</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>295608376@qq.com</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>+86 13556688832</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: ￥1000 good</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Crystal 刘晓艺</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>crystal@sincerechina.net</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>86-15815992213</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>www.sincerechina.net</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>佛山市禅城区南庄镇季华西路中国陶瓷产业总部基地西区C07-C08栋 (China Ceramics Industry Headquaters Block No.C07-08, West Area, West Jihua Road, Nanzhuang, Foshan, China)</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: ¥ 500 good</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Joan Liu</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>joan@goldenrickyhpl.com</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>+86 13599525074</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Https://goldenrickyhpl.com</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Xiamen City, Fujian, China</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: ￥ 300 good</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>135 3666 7789, 400-9090-518</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 300 rmb and more. Good quality and good price. Small quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>王闻浠</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>lanjanweiyu@163.com</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>+86-13569915996</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>www.lanjan.com</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>河南省长葛市石固镇梁庄工业园区</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 33$ for 1 pcs. Good quality and quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>hengsheng_carpet@163.com</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>0769-89807692</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Good 👍</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Willer Zhou</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>sale31@higold.com.cn</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>+86 158 2865 5891</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>www.higoldhardware.com</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>No.36 Shunye East Rd, Xingtan, Shunde, Foshan 528325, Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 5800</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr"/>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Sammi Shi</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>sales01@kehon.cn</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>+86 156 8948 5097, 0578-3271096</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>www.kehon.cn</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 130 yuan</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Richie Wang</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>richie.wang@wbhouse.com</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>+86 137 1002 1675</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>www.gdwbprefabhouse.com</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Guangdong Factory: No.5, No. 161 Ganghe Avenue, Gaoming District, Foshan city, Guangdong, CHINA; Fujian Factory: Provincial Highway 308, Yunrong Township, Minqing County, Fuzhou City, Fujian Province, CHINA.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 20000usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr"/>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Owen Li</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>owen.li@seajoinhouse.com</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>(86) 133 9501 1076</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>www.seajoinhouse.com</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Chongqing, China / Ho Chi Minh City, Vietnam</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 500yuan</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Josie Guan</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>cae@china-cae.com</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>+86-13702279135</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>www.china-cae.com</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>No.62-64, Xingda Rd., Shagang Dist., Shuikou Town, Kaiping, Guangdong, P.R.Of China.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: MOQ 100, 47 rnb per piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr"/>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>董华</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>418897056@qq.com</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>13914649982, 18951488133</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: MOQ 50, 200 rnb per</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Jasmine Guan 管敏秀</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>jasmine@suofeiyahome.com</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>+86 147 7520 2759</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofeyiahome.com</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: MOQ 10, 845 per piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr"/>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>金厚强 Jin Houqiang</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>jinhouqiang@leyard.com</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>13510009569, 18829341125, 400-8592-666</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>www.leyard.com</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1pcs. Start from 60rmb. Novative technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>sales02@kehon.cn</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>+86 157 5573 4990</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>www.kehon.cn</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 399</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr"/>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>周信朋 Joe Zhou</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>sales02@jnodwater.com</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>+86 199 2825 2201, +86-757-2361 7920</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>www.jnodwater.com</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1410</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>洪美兰</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>jiang@chuangqitimes.com</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>13450298606, 020-82511901</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>www.chuangqitimes.com</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 329</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr"/>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>sales08@ruikang-cn.com</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>+86 18028330648, +86 18022073939</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 229</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>潘禹</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>13691864691</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 680</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr"/>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Jack Guan</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>jack@cae.cn</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>+86-750-8119338</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>www.cae.cn</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 150 yuan, 100, good range of products</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Jasmine Guan 管敏秀</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>jasmine@suofeiyahome.com</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>+86 147 7520 2759</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofeyiahome.com</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 800usd, very nice, good quality product</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr"/>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>余赛银 (Yu Saiyin)</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>109786129@qq.com</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>+86 13660529010</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>kingliye.com</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>佛山市南海区里广路二号碧桂园金沙国际广场1201室 (Room 1201, Building 10, Jinsha International Plaza No.2 Liguang Road, Nanhai District, Foshan City)</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Winni 何玲玲</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>helingling@gdhsyj.com</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>+86 18924564942</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>WWW.HOPSOONER.COM</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr"/>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>周信朋 (Joe Zhou)</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>sales02@jnodwater.com</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>+86 199 2825 2201, +86-757-2361 7920</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>www.jnodwater.com</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 199</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>sales02@kehon.cn</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>+86 157 5573 4990 / 0578-3271096</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>www.kehon.cn</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 1410</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr"/>
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>service@3weitech.com</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>021-57715805</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>www.3weitech.com</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>上海市闵行区新骏环路188号11号楼A座518室</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет проблема синхронизации . Есть свой искусственный интеллект . Нужно тестировать . Купили ленту у него лед, на телевизор как образец</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>王鹏</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>1319129904@qq.com</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>189-2324-7677</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>www.asnug.com</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr"/>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Yolanda He</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>ecosound02@polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>+86-18018130150</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>No.10 Jinxi Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного метра 150 юаней сказала примерно. Не до конца поняла точность минимальной партии, но говорили часто 100 кВ метром</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>劉奕紫 Cathy</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>sales19@soundbox.hk</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>+86 137 6339 3059</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккуратная комната, достаточно комфортная. Цена немного завышена, встречали на других выставках пониже стоимостью.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr"/>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>蔡缘缘</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>wendyyian@163.com</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>0086-13599917696</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>www.fjnuoao.cn</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 2900 usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Felicity</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>sales09@spakingston.com</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>+86-18025851458</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>www.spakingston.com</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Kingston Company, JiangJun Road, Qiuchang, Huiyang, Huizhou, China</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr"/>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>蔡缘缘</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>wendyyian@163.com</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>0086-13599917696, 0592-7081636</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>www.fjnuoao.cn</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>william@sunrans.com</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>+86 134 1613 9887, +86-20-26231998</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>http://www.sunrans.com</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very good and good products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr"/>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>梁莹慧 Fiona</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>003@cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>+86 183 4456 5547</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>www.cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: MOQ 1, they got samples. 8000usd. Very well made product, trendy and popular. This capsules houses very affordable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>15916159866</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr"/>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Ivy Zhou</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>ivy@ifunpark.com</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>+86 133 0238 5758</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>www.ifunpark.com / www.ifunamusement.com</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 600</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Emily Li</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>tuoxinlqm@outlook.com</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>+86 19831737599</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tuoxinfiberglassmesh.com/</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 0.6 usd/m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr"/>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>王虎旗</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>hectorwang1982@gmail.com</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>86 18638546565</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>www.weilandeglobal.com</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>河南省郑州市曲梁工业园188号</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Under negotiation, great opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>曹双林 (Edith Cao)</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>13286132534, 400-0750-889</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>广东省江门市蓬江区迎宾大道西23号之129</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 1-5 usd/l</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr"/>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>李尚声 (Shangsheng Li)</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>15915975597@163.com</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>15915974406</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 6000RMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 2000RMB&amp;gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr"/>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Wing</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>wuyunying08@gmail.com</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>189-2984-9818, 0758-8578545</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: MOQ - 5000 and price - 7000 dollars</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Susan Xia</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>acousound16@polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>+86-15512435605</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu 215152</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 4000$</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="3" t="inlineStr"/>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>黄斌</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>464565801@qq.com</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>13813551160</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>www.ycpanel.com</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>常州市武进区横林镇长虹东路28号</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 3000 dollars</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>陈施志凯 (CHEN SHI ZHI KAI)</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>108455453@qq.com</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>+86 134 3318 1558, 0757-8560 9159</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: The price cheap, merchant very friendly</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr"/>
+      <c r="C87" s="3" t="inlineStr"/>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>sales.countermast.china@countermast.com</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>400-100-2228</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>www.countermast.cn</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>Building No.7, Zhongqing Industrial Park, Dalian free trade zone, Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: The price more cheaper, good quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>严金霞</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>monalisa38@monalisa.cn</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>+86 13711113746, 400 020 1818, +86 20-28607711</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>www.monalisa.cn</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>广州市花都区花东镇港头工业区4号</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: Good merchant, perfect products</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr"/>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>叶小龙/Dustin Ye</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>yedustin@gmail.com</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>+86-188 5861 0008</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>www.cngaocheng.cn</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>浙江省三门县浦坝港镇沿海工业城 (COASTAL INDUSTRIAL CITY, PUBAGANG TOWN, SANMEN, TAIZHOU CITY, ZHEJIANG PRO., CHINA)</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Pacao Yin</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>pin@pingaolao.com</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>(0086)13903035682, (0086)0769-86378283, (0086)0769-86377522</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 15 RMB the product is interesting</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="3" t="inlineStr"/>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>吴仁余</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>294217488@qq.com</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>13967444542, 0579-82889122</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>www.jhrxhb.com</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>浙江省金华市婺城区罗店镇北山路精工工业园</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: nearly $15,000 for this production line</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Dream Lin</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>sale15@double-lin.com</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>86-020-66837727, 86-13710718529</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>www.double-lin.com</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 149</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr"/>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Aaron Liu</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>aaron@ccolomac.com</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>+86-0371-66350801, +86 15936292861</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>www.ccolomac.com</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 249</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>袁佳磊</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>18652449601</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>www.cnfrd.cn</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>江苏省太仓市港区临江路1号</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 749</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr"/>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Eric Huang</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>464565801@qq.com</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>13813551160 / 0519-88784050</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>www.ycpanel.com</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>No.28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 5000 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Wing</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>wuyunying08@gmail.com</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>189-2984-9818, 0758-8578545</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 3000 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="3" t="inlineStr"/>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Susan Xia</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>acousound16@polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>+86-15512435605</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu 215152</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 3000 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="3" t="inlineStr"/>
+      <c r="C99" s="3" t="inlineStr"/>
+      <c r="D99" s="3" t="inlineStr"/>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>186-0205-8898 / 400-608-0098</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr"/>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市南海区里水镇</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 249 RMB. They have fully described their products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>186-0205-8898, 400-608-0098</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>广东省中山市小榄镇四沙盛和路5号</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 249RMB , 价格很便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="3" t="inlineStr"/>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>颜加伟</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>1164199388@qq.com</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>133 9983 5678</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr"/>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 400rmb /m2 good meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>高学梅</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>17687627315</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 350 rmb/m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="3" t="inlineStr"/>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Pacao Yin</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>pin@pingaolao.com</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>Mobile: (0086)13903035682, Tel: (0086)0769-86378283</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: MOQ 5000 pieces</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>颜加伟</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>1164199388@qq.com</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>133 9983 5678</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 400rmb/m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="3" t="inlineStr"/>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>高学梅</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr"/>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>17687627315</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr"/>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 350rmb/m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr"/>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Pacao Yin</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>pin@pingaolao.com</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Tel: (0086)0769-86378283, (0086)0769-86377522; Mobile: (0086)13903035682</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: MOQ 5000 pieces</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="3" t="inlineStr"/>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Thea</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>moershu3@moershu.com</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>13957622087</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>www.moershu.com</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr"/>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>杨苗</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>yangm618@163.com</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>13816184706</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>http://www.shicanchina.com</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>上海市浦东新区商城路889号C3-B06</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 3000 / MOQ 1 Inside view is luxury, i love it</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="3" t="inlineStr"/>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Zoey Zhang</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>zoey@sciener.com</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>+86 178-5768-8782</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr"/>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 20 / MOQ 100 Nice worker answered all questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr"/>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Lucy Zeng (曾露)</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>lucy@rongkedecor.com</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>+86-13134020034</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amerdecor.com/</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 80 rmb for 230 meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="3" t="inlineStr"/>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>王冠</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr"/>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>+86 13229297183</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>WWW.SANNORA.COM; WWW.SANNORA-BATH.COM</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1560 rmb for whole item</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr"/>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Sophia Deng (邓小艳)</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>sophiadeng@china-gold.cn</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>+181 3838 6948</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>http://www.china-gold.cn, http://www.aosman.cn</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>198 Siqian Xi Road, Shuikou, Kaiping 529300, Guangdong PR.China</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 4600 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="3" t="inlineStr"/>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Eric Huang</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>464565801@qq.com</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>13813551160, 0519-88784050</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>www.ycpanel.com</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>#28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 2085</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr"/>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Wing</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>wuyunying08@gmail.com</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>189-2984-9818, 0758-8578545</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 2147</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="3" t="inlineStr"/>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Eric Huang</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>464565801@qq.com</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>13813551160, 0519-88784050</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>www.ycpanel.com</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>#28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 2223</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr"/>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>朱支群</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>13763963598</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>www.jx-wpc.com</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>江西省瑞金市经济开发区创业一路东侧</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 250¥/м3</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="3" t="inlineStr"/>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Anne</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>victor@ck-bath.com</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>18656330093</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>https://ck-bath.com/</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 4500¥</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr"/>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>刘朔雅 Gigi</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>004@cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>+86 189 2997 1101</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>www.cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 8790$</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="3" t="inlineStr"/>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>linda.lu@ciarrahome.com</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>+86 1882 9964 960, +86 1343 2639 580</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>www.ciarrahome.com</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 300¥ 300pcs</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr"/>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Viola Liu</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>wood6@sennorwell.com</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>(86) 158 8931 1832</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 50¥ 1000pcs</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="3" t="inlineStr"/>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Amy Liu 刘建美</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>export@ideal-china.net</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>+86 (0) 757 8558 9299</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>www.ideal-sanitary.com</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>No.3 Hexi Road of Shashui, Yanghe Town, Gaoming District, Foshan City, Guangdong Province, 528515 - P.R.China.</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 500$ 100psc</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr"/>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Anne</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>victor@ck-bath.com</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>18656330093</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>https://ck-bath.com/</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 4500¥</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="3" t="inlineStr"/>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>刘朔雅 Gigi</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>004@cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>+86 189 2997 1101</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>www.cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 8790$</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr"/>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>朱友群</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr"/>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>13763963598</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>www.hx-wpc.com</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>江西省瑞金市经济开发区创业一路东侧</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 250¥/m3</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="3" t="inlineStr"/>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>胡光辉</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>1525423805@qq.com</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>18128752879</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr"/>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>佛山狮山镇谭边工业区崩岗头路四号之一</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 980y/m2, moq 1000p, like doors with Mosquito netting</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr"/>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>陈可樑</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>hw-hardware@qian-ze.com</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>180 3863 7238</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>www.honeywell-hardware.com</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>广东省佛山市三水区云东海街道宝盛路2号1座三层（合和建筑五金园区北门）</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 1000-2000p, 1.7-7$, good beautiful doors handless</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="3" t="inlineStr"/>
+      <c r="C127" s="3" t="inlineStr"/>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>info@sunhohiglobal.com</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>+86-137 0262 5097, +86-139 2779 1971</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sunhohiglobal.com/</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>Marketing Center: R&amp;F International Financial Center, Nanhai District, Foshan City, Guangdong Province, China; Factory: Zhenxing 3rd Road, Xincheng Town, Xinxing County, Yunfu City, Guangdong Province, China</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1p, 10000$m2, very beautiful big red door</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr"/>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Cathy Dai (代桂菊)</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>cathy@hnbeidi.com</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>+86 151 3737 2072</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>www.baydeegroup.com, www.hnbeidi.com</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>中国 河南省鹤壁市 (Hebi City, Henan Province, China)</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 1 container (400 square meters), 60 dollars for 1 square meters</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="3" t="inlineStr"/>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>叶韵怡</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr"/>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>13726080225</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr"/>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Moq is 1 door, 530 RMB for 1 door</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr"/>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>李旭文 Nigel</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>006@cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>+86 138 2231 8296</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>www.cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 14400 dollars, moq - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="3" t="inlineStr"/>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>张广帅</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>1525423805@qq.com</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>13726358587</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr"/>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>佛山市狮山镇谭边工业区顺岗头路四号之一</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr"/>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>徐云霞</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>13697981203</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 100 RMB per sample. The taste is very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="3" t="inlineStr"/>
+      <c r="C133" s="3" t="inlineStr"/>
+      <c r="D133" s="3" t="inlineStr"/>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>0512-66281146</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>www.dsteaf.com</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>江苏省苏州市吴中区东山镇 (Dongshan Town, Wuzhong District, Suzhou City)</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 150 RMB per sample. The taste is very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr"/>
+      <c r="C134" s="2" t="inlineStr"/>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>15926183211</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>福建永春达埔</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="3" t="inlineStr"/>
+      <c r="C135" s="3" t="inlineStr"/>
+      <c r="D135" s="3" t="inlineStr"/>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>15926183211</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr"/>
+      <c r="G135" s="3" t="inlineStr"/>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: The 中国好水 brand water was really good. They are using deep water instead of shallow water (used by nongfu), and trace minerals are also added which makes its pH 7.5 which is good salty water. Overall i am impressed by their health committed approach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr"/>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>ALLEN XU (许熙平)</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>sales@sannora.com</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>+86 137 0263 0244, +86-757-86438259</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>WWW.SANNORA.COM, WWW.SANNORA-BATH.COM</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>TANBIAN IND. ZONE, SHISHAN TOWN, NANHAI DIST., FOSHAN, GUANGDONG, CHINA</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="3" t="inlineStr"/>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Joy Yang</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>joy@rans.group</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>+86-13757430301</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>www.ptat.cn</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr"/>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr"/>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>万磊市场部</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>186-8825-1404, 4000-147-187</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>http://www.fswanlei.com</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="3" t="inlineStr"/>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>May Zhang</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>sales5@anjeurostilefurniture.com</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>+86 182 5727 1590</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>www.zjseating.com</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr"/>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>lucy@lefucz.com</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>+0086 18098114370</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>www.lefucz.com</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Lefu Sanitary Ware, Sheweikeng, Dengtang Town, Chaoan District, Chaozhou City, Guangdong Province, China</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="3" t="inlineStr"/>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>胡沛能 / Oliver Hu</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>oliver@wireking.com</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>+86-13802465791</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr"/>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 550</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr"/>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>蒙玉婷</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>13160953218 / 400-8339513</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区龙江镇联塑工业园三路3号9513家具总部</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 820 rmb moq 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="3" t="inlineStr"/>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Lucy Zeng (曾露)</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>lucy@rongkedecor.com</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>+86-13134020034</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>https://www.amerdecor.com/</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr"/>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 650 moq 300</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr"/>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Pacao Yin</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>pin@pingaolao.com</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>(0086)0769-86378283, (0086)13903035682</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 2.5 RMB per unit, MOQ is 500 pieces. The plastic material was high quality and company was willing to provide samples on need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="3" t="inlineStr"/>
+      <c r="C145" s="3" t="inlineStr"/>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>sale01@yarouwallpaper.com.cn</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>+86-18069994326, +86-18069994377</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yarouwallpaper.com.cn/</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>浙江省金华市义乌市福田街道涌金大道87号厂房二楼 (No. 1, Factory 2, Yongjin Avenue 87, Futian Subdistrict, Yiwu City, Jinhua City, Zhejiang Province)</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr"/>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>戴艳辉</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>18830173388</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>石家庄市正定县曙光路49号东标和聚居</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="3" t="inlineStr"/>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>肖汶兰</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr"/>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>18675197017, 400-8339513</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr"/>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1299, MOQ 200. I like the company and people there . Very friendly and know their products very good . I would be happy to cooperate with them in the future ,to buy their products</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr"/>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Abby Li</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>abbyli@sofeyiahome.com</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>+ 86 18029769660</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofeyiahome.com</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 5000rmb MOQ 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="3" t="inlineStr"/>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Karl Lai</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>laisheng_352m@163.com</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>15073995010</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr"/>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>Showroom&amp;Office: Nanke Village Section, Expo Boulevard Avenue, Houjie Town, Dongguan City, Guangdong Province; Factory add: Building #25, Wanyang Zhongchuang Centre, Xinghong Town, Qingyuan City, Guangdong Province</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1500 rmb MOQ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr"/>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>冯晶晶 Joanna</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>sales06@cn-xindong.com</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>0086-159 9067 6107 / 0086-576-87499008</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: Black matt tap water $20</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="3" t="inlineStr"/>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Melina 王玲</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>lina@hongyugroup.com</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>+86 13827702216</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>en.hongyugroup.com</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr"/>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Daisy</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>sales06@chongnuo-floors.com</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>+86 19906379675</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>www.chongnuo-floors.com</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>QingyunCounty,DezhouCity,China</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 9$</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="3" t="inlineStr"/>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>崔强 (Cui Qiang)</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>513437660@qq.com</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>+8618901960431</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr"/>
+      <c r="G153" s="3" t="inlineStr"/>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 13.25$</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr"/>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Wangfeng</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>2523911877@qq.com</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>13233648687</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 8.83$</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="3" t="inlineStr"/>
+      <c r="C155" s="3" t="inlineStr"/>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>sales@cofesu.com</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>+86 181 2821 2128</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>www.cofesu.com</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>Foshan, Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 30 PCs, 420 RMB, need check quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr"/>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>唐一智 (JUNIOR)</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>13621417@qq.com</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>+86-156-2562-1155</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="3" t="inlineStr"/>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Zoya</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>2291828903@qq.com</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>+86 132 8810 6615</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr"/>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr"/>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>邓美君 Jessica</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>bailide_hinge@163.com</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>+86 13823419116 / 0758-8565117</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="3" t="inlineStr"/>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Kelly Liang (梁凯莹)</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>kelly@adamsmetal.com.cn</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>+86-180-2935-2895 / +86-757-25331912</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>www.adamsmetal.com.cn</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Depend on item</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr"/>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>刘婉莹 Carol Liu</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>tenghuihardware@126.com</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>+86 133 1836 4599</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>www.teehve.cn</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区勒流街道众涌村港口路以西8-9号之二 (No.8-9, West of GangKou Road, Zhongchong Village, Leliu Town, Shunde District, Foshan City, Guangdong, China)</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 100/square meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="3" t="inlineStr"/>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Jimmy 黄锦民</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>sales003@sdduocaizp.com</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>(86)133 2294 8506, +86-766-8298662</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>www.dc-tent.com, www.sdduocaizp.com</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>云浮市云安区佛山(云浮)产业转移工业园86号 (No.86 Foshan(Yunfu) Industrial transfer park, yunan, yunfu, Guangdong China)</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: RMB 15705 MOQ5; pleasant impression</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr"/>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Marco Lau (刘嘉乐)</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>RULERAWNING07@163.COM</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>+86 13129016338</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>WWW.RULER-AWNING.COM</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>END OF ROAD SHATANXIAN, SHASHUI INDUSTRIAL ZONE, SONGGANG TOWN, SHISHAN DISTRICT, FOSHAN CITY, GUANGDONG PROVINCE, CHINA, 528200</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: MOQ5 25799 RMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="3" t="inlineStr"/>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Jay Zhou</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>jay@avant.com.cn</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>+86-13128980150, +86-755-2968-8357</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>www.avantseating.com</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>Avant Industrial Park, Zhoushi Road, Bao'an, Shenzhen, Guangdong Province, China</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: RMB 19479; MOQ 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr"/>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>孟少美 (Elite Meng)</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>ttf@hbtfjs.com</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>+86-13103196326</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>www.hbtfjs.com</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>河北省隆尧县东谷子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="3" t="inlineStr"/>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>林树丹 (Lin Shudan)</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>linshdong@qq.com</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>13751676456</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>www.xinjunye.com</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>广东省揭阳市揭东区锡场工业区 (Xichang Industrial Zone, Jiedong District, Jieyang City, Guangdong Province)</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr"/>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Kelly Liang (梁凯莹)</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>kelly@adamsmetal.com.cn</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>+86-180-2935-2895, +86-757-25331912</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>www.adamsmetal.com.cn</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province (广东省佛山市顺德区勒流镇港口路10号)</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="3" t="inlineStr"/>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>伍乐彤</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>monalisa702@monalisa.cn</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>86 13711117863, 400 020 1818, 86 20-28607722, 86 20-28607788</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>www.monalisa.cn</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>广州市花都区花东镇港头工业区4号</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 2000$, can be customized, very convenient</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr"/>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Anson Yuen</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>info@hugemount.com</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>150 1954 6322 / 86-760-88702663</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>www.yijin.com</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>中国广东省中山市港口镇石特社区穗安工业区迎富2路1号 (NO.1, Ying Fu 2 Road, Sui An Gong Ye Qu, Gang Kou Zhen Shi Te She Qu, Zhongshan City, Guangdong Province, P.R.China)</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 38$, very unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="3" t="inlineStr"/>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Lucy (卢美珍)</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>export@vnsmilo.com</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>+86-13757322119</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>www.vnsmilo.com</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>Xuancheng City Anhui, CHINA</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 2050 rmb, very interesting, convenient to use for pets</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr"/>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>张爱彬 (Zhang Aibin)</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr"/>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>+86 18178085851</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 25 rmb, 1 box, like this product</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="3" t="inlineStr"/>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Tequila Xu (徐孟杰)</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>marketing@cxyushun.com, tequila8xu@gmail.com</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>0086-13819449988, +86 574 63190388</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>www.cxys8.com</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>中国浙江慈溪市杨梅大道南路1518号 (NO.1518, YANGMEI AVENUE SOUTH ROAD, CIXI CITY, ZHEJIANG, CHINA)</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I171" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 34 rmb, 1000, normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr"/>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>刘芳 (Jane Liu)</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>jane@dirock.cn</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>187 1377 2087</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>http://www.dirock.cn</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>河北省泊头市寺门村镇后牛屯</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 40 rmb, 2000, very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="3" t="inlineStr"/>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>周瑶琳</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>lisa.nordi@nuodibm.com</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>+86-137 3822 8209</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>www.tigerbamboo.com / www.nuodibm.com</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1 container 250 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr"/>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>张爱彬 (Zhang Aibin)</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr"/>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>+8618178085851</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: 1 container 500 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="3" t="inlineStr"/>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>马世晓 (Amelia Ma)</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>tf@hbtfjs.com, mashixiaomsx@163.com</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>15097968589, 0319-6581195</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>www.hbtfjs.com</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>河北省隆尧县公子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
+        </is>
+      </c>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I175" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: 1 container 700 rmb</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr"/>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Melina 王玲</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>lina@hongyugroup.com</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>+86 13827702216</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>en.hongyugroup.com</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Buyer: Жду коммерческое предложение. Компания понравилась</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="3" t="inlineStr"/>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>ty11@cntianyan.com</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>+86-15867028552</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>www.cntianyan.com</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t>Chengjiang industrial zone,huangyan district taizhou,zhejiang,china</t>
+        </is>
+      </c>
+      <c r="H177" s="3" t="inlineStr">
+        <is>
+          <t>Building Decoration</t>
+        </is>
+      </c>
+      <c r="I177" s="3" t="inlineStr">
+        <is>
+          <t>Buyer: Цена зависит от обьема, от 3 юаней, расходники</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CBD Suppliers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CBD Suppliers'!$A$1:$I$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CBD Suppliers'!$A$1:$I$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I177"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,11 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Sunhohi</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Crystal Wong</t>
@@ -566,7 +570,11 @@
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Guangdong Fuson Windoor Industry Co., Ltd</t>
+        </is>
+      </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Eileen Yip (叶颖怡)</t>
@@ -594,7 +602,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -607,7 +615,11 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>开平艺和门业有限公司</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>张硕怡 (Stoney)</t>
@@ -623,7 +635,7 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -636,7 +648,11 @@
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>SUNHOHI Smart Home Co., Ltd</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Crystal Wong 黄健秋</t>
@@ -677,7 +693,11 @@
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>河南贝迪塑业有限公司 (Henan Beidi Plastic Industry Co., Ltd.)</t>
+        </is>
+      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Jane Li (李蓉娟)</t>
@@ -718,7 +738,11 @@
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Guangzhou NewHoo Technology Co. Ltd</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Tony</t>
@@ -759,30 +783,18 @@
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>骆剑 (Kim Lok)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>kim.lok@bweetech.com</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>186-5759-0678</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>www.bweetech.com</t>
-        </is>
-      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>旭博卫浴</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
+          <t>福建省南安市</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -792,7 +804,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 500pcs / $100USD for pcs</t>
+          <t>Buyer: 70$</t>
         </is>
       </c>
     </row>
@@ -800,27 +812,15 @@
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>CANDICE CHOU</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>sales5@deiouxwindows.com</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>+86-13392246940</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
-        </is>
-      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>旭博恒温</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Custom order</t>
+          <t>Buyer: 300 yuan</t>
         </is>
       </c>
     </row>
@@ -837,26 +837,34 @@
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>榜威电子科技（上海）有限公司 (Bweetech Electronics Technology (Shanghai) Co., Ltd)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>骆剑 (Kim Lok)</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>info@warrenwindows.com</t>
+          <t>kim.lok@bweetech.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>+86-400-811-0300</t>
+          <t>186-5759-0678</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>www.warrenwindows.com</t>
+          <t>www.bweetech.com</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Room 1007, Block B, Wangjing SOHO, Chaoyang District, Beijing, China</t>
+          <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -866,7 +874,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Custom order</t>
+          <t>Buyer: 500pcs / $100USD for pcs</t>
         </is>
       </c>
     </row>
@@ -874,32 +882,16 @@
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Tim Pan</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>market@smarteklock.com</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>+86-15889896019</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>www.smarteklock.com</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City Guangdong, China 528415</t>
-        </is>
-      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>深圳市塞恩斯电子有限公司 (Sands Evermore Electronic)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -907,7 +899,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 170 to 335 usd</t>
+          <t>Buyer: 50pcs / $50USD for pcs</t>
         </is>
       </c>
     </row>
@@ -915,27 +907,15 @@
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Krystal Wei</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>krystal@hdlautomation.com</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>+86 19512956186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>www.hdlautomation.com</t>
-        </is>
-      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>HDL</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -944,7 +924,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 100 to up</t>
+          <t>Buyer: 20pcs / $100USD for pcs</t>
         </is>
       </c>
     </row>
@@ -952,40 +932,40 @@
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>DEIOUX WINDOWS &amp; DOORS</t>
+        </is>
+      </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Sean Xiao</t>
+          <t>CANDICE CHOU</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>sales@aifeibao.com</t>
+          <t>sales5@deiouxwindows.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>0086 198 1730 8681</t>
+          <t>+86-13392246940</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>www.afbsafe.com</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>No.1 Donghu Rd., Daxie Development Zone, Ningbo, China (315812)</t>
-        </is>
-      </c>
+          <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 100 to up usd</t>
+          <t>Buyer: Custom order</t>
         </is>
       </c>
     </row>
@@ -993,32 +973,40 @@
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>邹隆鹏</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>China Warren Windows and Doors Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>info@warrenwindows.com</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15818099349</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
+          <t>+86-400-811-0300</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>www.warrenwindows.com</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
+          <t>Room 1007, Block B, Wangjing SOHO, Chaoyang District, Beijing, China</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Super</t>
+          <t>Buyer: Custom order</t>
         </is>
       </c>
     </row>
@@ -1026,30 +1014,22 @@
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Matthew window&amp;door</t>
+        </is>
+      </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>黎桃桃</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>toto.liblun@gmail.com</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>+8618934320539</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>www.liblun.com</t>
-        </is>
-      </c>
+          <t>张小洪 (Matthew / Kevin)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
+          <t>Foshan, Guangdong</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1059,7 +1039,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Super</t>
+          <t>Buyer: Custom order</t>
         </is>
       </c>
     </row>
@@ -1067,36 +1047,44 @@
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Zhongshan Smartek Security Technology Co.,LTD</t>
+        </is>
+      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>曾燕燕 Elyn</t>
+          <t>Tim Pan</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>sales03@cn-xindong.com</t>
+          <t>market@smarteklock.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0086-182 5765 3405, 0086-576-87493988</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>+86-15889896019</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>www.smarteklock.com</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
+          <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City Guangdong, China 528415</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 50</t>
+          <t>Buyer: 170 to 335 usd</t>
         </is>
       </c>
     </row>
@@ -1104,24 +1092,32 @@
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>HDL Automation Co., Ltd.</t>
+        </is>
+      </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>王小忠</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr"/>
+          <t>Krystal Wei</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>krystal@hdlautomation.com</t>
+        </is>
+      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>浙江省杭州市临平区运河街道育士路53-1号</t>
-        </is>
-      </c>
+          <t>+86 19512956186</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>www.hdlautomation.com</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1129,7 +1125,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 100</t>
+          <t>Buyer: 100 to up</t>
         </is>
       </c>
     </row>
@@ -1137,40 +1133,44 @@
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Ningbo AIFEIBAO Intelligent Security Co., Ltd</t>
+        </is>
+      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>应杨军</t>
+          <t>Sean Xiao</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3572780651@qq.com</t>
+          <t>sales@aifeibao.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13511470999</t>
+          <t>0086 198 1730 8681</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>www.xs88.cn</t>
+          <t>www.afbsafe.com</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>浙江省台州市台州湾新区海虹大道228#</t>
+          <t>No.1 Donghu Rd., Daxie Development Zone, Ningbo, China (315812)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 100</t>
+          <t>Buyer: 100 to up usd</t>
         </is>
       </c>
     </row>
@@ -1178,26 +1178,26 @@
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>佛山市普辉亚科技有限公司 (Foshan Pu Huiya Technology Co., Ltd.)</t>
+        </is>
+      </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>顾鹏</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>962460053@qq.com</t>
-        </is>
-      </c>
+          <t>邹隆鹏</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>13326792105</t>
+          <t>15818099349</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
+          <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Wall sheet , 200 rmb per meter , 2000 mtr,</t>
+          <t>Buyer: Super</t>
         </is>
       </c>
     </row>
@@ -1215,26 +1215,34 @@
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>广东招材建材科技有限公司</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Davis Dong 董伟杰</t>
+          <t>黎桃桃</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>sales05@authoe.com</t>
+          <t>toto.liblun@gmail.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>+86-18906831082</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
+          <t>+8618934320539</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>www.liblun.com</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Jiaxing/Hongkong</t>
+          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1244,7 +1252,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Handles , 500 moq , 100 rmb per handle</t>
+          <t>Buyer: Super</t>
         </is>
       </c>
     </row>
@@ -1252,36 +1260,40 @@
       <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>浙江鑫东洁具有限公司 (ZHEJIANG XINDONG SANITARY WARE CO., LTD.)</t>
+        </is>
+      </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Alex Xing</t>
+          <t>曾燕燕 Elyn</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>kindeli1771@gmail.com</t>
+          <t>sales03@cn-xindong.com</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>+86-18302200384</t>
+          <t>0086-182 5765 3405, 0086-576-87493988</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Shijiazhuang City, Hebei Province</t>
+          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
+          <t>Buyer: 50</t>
         </is>
       </c>
     </row>
@@ -1289,30 +1301,26 @@
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>杭州南博装饰材料有限公司</t>
+        </is>
+      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>张丽</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>jinjian19@jinjianlock.com</t>
-        </is>
-      </c>
+          <t>王小忠</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15067804393</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>www.jinjianlock.com</t>
-        </is>
-      </c>
+          <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号</t>
+          <t>浙江省杭州市临平区运河街道育士路53-1号</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1322,7 +1330,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for customized branding. Feedback: The company has a professional production line and solid hardware quality. Their prices are very competitive for the mass market, although their software ecosystem is less advanced than Innovation's current solutions. They are a reliable choice for high-volume, cost-effective projects.</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -1330,40 +1338,44 @@
       <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>台州旭升卫浴股份有限公司</t>
+        </is>
+      </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>杨苗</t>
+          <t>应杨军</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>yangm618@163.com</t>
+          <t>3572780651@qq.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>138 1618 4706</t>
+          <t>13511470999</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>http://www.shicanchina.com</t>
+          <t>www.xs88.cn</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>上海市浦东新区商城路889号C3-B06</t>
+          <t>浙江省台州市台州湾新区海虹大道228#</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models and 150 units for custom OEM branding. Feedback: Yang Miao Miao demonstrates excellent mechanical build quality and focuses heavily on the structural integrity of the doors. Their pricing is mid-range, offering a good balance between durability and cost. They are highly flexible with custom design requests, making them a strong potential partner for Innovation’s specialized architectural projects.</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -1371,40 +1383,40 @@
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>NIFO 耐孚</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Aaron Liu</t>
+          <t>顾鹏</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>aaron@ccolomac.com</t>
+          <t>962460053@qq.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>+86-0371-66350801, +86 15936292861</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>www.ccolomac.com</t>
-        </is>
-      </c>
+          <t>13326792105</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
+          <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 100 units for customized decorative panels. Feedback: Colomac Decor stands out for its superior aesthetic design and premium finishing materials. Their products align well with luxury interiors, showing high attention to detail in surface textures. They are an ideal partner for Innovation when the goal is to merge smart technology with high-end interior aesthetics.</t>
+          <t>Buyer: Wall sheet , 200 rmb per meter , 2000 mtr,</t>
         </is>
       </c>
     </row>
@@ -1412,32 +1424,40 @@
       <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Zhejiang Oushe Home Improvement And New Materials Co., Ltd.</t>
+        </is>
+      </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>赖华芳</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr"/>
+          <t>Davis Dong 董伟杰</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>sales05@authoe.com</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>13727479513, 400-8339513</t>
+          <t>+86-18906831082</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
+          <t>Jiaxing/Hongkong</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Хорошее, 400rmb</t>
+          <t>Buyer: Handles , 500 moq , 100 rmb per handle</t>
         </is>
       </c>
     </row>
@@ -1445,28 +1465,32 @@
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>JIN OGMEI</t>
+        </is>
+      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Clément / 付雄豪</t>
+          <t>Alex Xing</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>clement.fu@cqsdmy.com</t>
+          <t>kindeli1771@gmail.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>+(86) 19112691557</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>www.guhaogroup.com / www.cqsdmy.com</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
+          <t>+86-18302200384</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Shijiazhuang City, Hebei Province</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1474,7 +1498,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Хорошее , 1500rmb</t>
+          <t>Buyer: Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
         </is>
       </c>
     </row>
@@ -1482,36 +1506,44 @@
       <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>温州金锏智能锁具有限公司</t>
+        </is>
+      </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>周灿灿</t>
+          <t>张丽</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>15986196312@163.com</t>
+          <t>jinjian19@jinjianlock.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>159 1909 0393, +86-757-2339 1505</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr"/>
+          <t>15067804393</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>www.jinjianlock.com</t>
+        </is>
+      </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
+          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Нормальное</t>
+          <t>Buyer: Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for customized branding. Feedback: The company has a professional production line and solid hardware quality. Their prices are very competitive for the mass market, although their software ecosystem is less advanced than Innovation's current solutions. They are a reliable choice for high-volume, cost-effective projects.</t>
         </is>
       </c>
     </row>
@@ -1519,40 +1551,44 @@
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>上海世灿国际贸易有限公司</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Yolanda He</t>
+          <t>杨苗</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>acousound07@polyacoustic.com</t>
+          <t>yangm618@163.com</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>+86-18068038050</t>
+          <t>138 1618 4706</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>www.polyacoustic.com</t>
+          <t>http://www.shicanchina.com</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+          <t>上海市浦东新区商城路889号C3-B06</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Buyer: $55, MOQ100pcs, good</t>
+          <t>Buyer: Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models and 150 units for custom OEM branding. Feedback: Yang Miao Miao demonstrates excellent mechanical build quality and focuses heavily on the structural integrity of the doors. Their pricing is mid-range, offering a good balance between durability and cost. They are highly flexible with custom design requests, making them a strong potential partner for Innovation’s specialized architectural projects.</t>
         </is>
       </c>
     </row>
@@ -1560,40 +1596,44 @@
       <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>COLOMAC DECOR</t>
+        </is>
+      </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>陈洁玲 Rowling</t>
+          <t>Aaron Liu</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>014@cgchcontainer.com</t>
+          <t>aaron@ccolomac.com</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>+86 189 2997 1329</t>
+          <t>+86-0371-66350801, +86 15936292861</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>www.cgchcontainer.com</t>
+          <t>www.ccolomac.com</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1000 yuan 1 square</t>
+          <t>Buyer: Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 100 units for customized decorative panels. Feedback: Colomac Decor stands out for its superior aesthetic design and premium finishing materials. Their products align well with luxury interiors, showing high attention to detail in surface textures. They are an ideal partner for Innovation when the goal is to merge smart technology with high-end interior aesthetics.</t>
         </is>
       </c>
     </row>
@@ -1601,32 +1641,36 @@
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>佛山市同路匠人家具有限公司</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>罗美玲</t>
+          <t>赖华芳</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>180 0760 4399</t>
+          <t>13727479513, 400-8339513</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
+          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 150 rmb</t>
+          <t>Buyer: Хорошее, 400rmb</t>
         </is>
       </c>
     </row>
@@ -1634,32 +1678,32 @@
       <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="inlineStr"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>固豪木业 | SUNDIN尚鼎</t>
+        </is>
+      </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>Clément / 付雄豪</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>sophia@multishades.com.cn</t>
+          <t>clement.fu@cqsdmy.com</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>0086-15918713187, 0086-757-86780865</t>
+          <t>+(86) 19112691557</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>www.multishades.com.cn</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Office: Room 1501, CITIC Plaza, No.233, Tianhebei Road, Guangzhou City, Guangdong Province, China; Factory: 1 Shengshi Road, Shibei Industrial Park, Shishan Town, Foshan City, Guangdong Province, China</t>
-        </is>
-      </c>
+          <t>www.guhaogroup.com / www.cqsdmy.com</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
       <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1667,7 +1711,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 570 rmb</t>
+          <t>Buyer: Хорошее , 1500rmb</t>
         </is>
       </c>
     </row>
@@ -1675,40 +1719,40 @@
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>佛山市嘉豪飞度家具有限公司 (FOSHAN KAHO FIT FURNITURE CO., LTD.)</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>黎桃桃</t>
+          <t>周灿灿</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>toto.liblun@gmail.com</t>
+          <t>15986196312@163.com</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>+8618934320539</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>www.liblun.com</t>
-        </is>
-      </c>
+          <t>159 1909 0393, +86-757-2339 1505</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
+          <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 620 super</t>
+          <t>Buyer: Нормальное</t>
         </is>
       </c>
     </row>
@@ -1716,24 +1760,16 @@
       <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="inlineStr"/>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>黄上梅</t>
-        </is>
-      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>中山市福乐门智能科技有限公司 / 中山市乐帝智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>13434829660, 400-8339513</t>
-        </is>
-      </c>
+      <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区龙江镇联登碧园三路3号9513家具总部</t>
-        </is>
-      </c>
+      <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1741,7 +1777,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1500 super</t>
+          <t>Buyer: $176, MOQ 50, very good!</t>
         </is>
       </c>
     </row>
@@ -1749,24 +1785,44 @@
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Suzhou Acousound New Material Technology Inc.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Yolanda He</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>acousound07@polyacoustic.com</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1561767</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+          <t>+86-18068038050</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 130 super</t>
+          <t>Buyer: $55, MOQ100pcs, good</t>
         </is>
       </c>
     </row>
@@ -1774,28 +1830,16 @@
       <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="inlineStr"/>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>欧阳玉滢 (Sonia Ouyang)</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>sonia.ouyang@wireking.com</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>+86-13392758223</t>
-        </is>
-      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>特斯豹工具</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
-        </is>
-      </c>
+      <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1803,7 +1847,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Buyer: $32, MOQ 300, good</t>
+          <t>Buyer: $30, MOQ 10pcs, nice</t>
         </is>
       </c>
     </row>
@@ -1811,40 +1855,44 @@
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>CGCH</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Eva Leng</t>
+          <t>陈洁玲 Rowling</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>eva@ptadoor.com</t>
+          <t>014@cgchcontainer.com</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>+86 19848080478, +44 7704 561086</t>
+          <t>+86 189 2997 1329</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>global.ptadoor.com</t>
+          <t>www.cgchcontainer.com</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Xincheng technology park, Yuelu Avenue, Changsha Hunan China</t>
+          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Buyer: ¥3000, MoQ 1pcs, very good</t>
+          <t>Buyer: 1000 yuan 1 square</t>
         </is>
       </c>
     </row>
@@ -1852,40 +1900,36 @@
       <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="inlineStr"/>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>广东省中山名谷屋木门厂</t>
+        </is>
+      </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>徐小俊</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>281431686@qq.com</t>
-        </is>
-      </c>
+          <t>罗美玲</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>13802731123</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>https://taiyada1688.1688.com/</t>
-        </is>
-      </c>
+          <t>180 0760 4399</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>广东省丰顺县汤坑镇太平北路</t>
+          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Buyer: ¥17, Moq 50, good</t>
+          <t>Buyer: 150 rmb</t>
         </is>
       </c>
     </row>
@@ -1893,30 +1937,34 @@
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>multishades</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>黄伟业</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Yea@LGPKB.com</t>
+          <t>sophia@multishades.com.cn</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>13825596371</t>
+          <t>0086-15918713187, 0086-757-86780865</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>www.LGPKB.com</t>
+          <t>www.multishades.com.cn</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
+          <t>Office: Room 1501, CITIC Plaza, No.233, Tianhebei Road, Guangzhou City, Guangdong Province, China; Factory: 1 Shengshi Road, Shibei Industrial Park, Shishan Town, Foshan City, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1926,7 +1974,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 600 RMB Great, very cheap</t>
+          <t>Buyer: 570 rmb</t>
         </is>
       </c>
     </row>
@@ -1934,28 +1982,20 @@
       <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="inlineStr"/>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>超友皮革家居</t>
+        </is>
+      </c>
       <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>yc@ycbycl.com</t>
-        </is>
-      </c>
+      <c r="D39" s="3" t="inlineStr"/>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>0519-88931168</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>www.ycbycl.com</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>江苏省常州市天宁区郑陆镇工业集中区</t>
-        </is>
-      </c>
+          <t>1561767</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1963,7 +2003,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 10$</t>
+          <t>Buyer: 130 super</t>
         </is>
       </c>
     </row>
@@ -1971,40 +2011,40 @@
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co.,Ltd)</t>
+        </is>
+      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>曾令贵</t>
+          <t>欧阳玉滢 (Sonia Ouyang)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>513573190@qq.com</t>
+          <t>sonia.ouyang@wireking.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>86-13585642723 / 0596-8273388-8083</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>www.fjnuoao.cn</t>
-        </is>
-      </c>
+          <t>+86-13392758223</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
+          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 69$</t>
+          <t>Buyer: $32, MOQ 300, good</t>
         </is>
       </c>
     </row>
@@ -2012,36 +2052,44 @@
       <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="inlineStr"/>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>PTA DOOR Automation (Hunan Tianan Door Technology Co., Ltd.)</t>
+        </is>
+      </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>唐佳豪 (Vance)</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr"/>
+          <t>Eva Leng</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>eva@ptadoor.com</t>
+        </is>
+      </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>+86 18925924350</t>
+          <t>+86 19848080478, +44 7704 561086</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>www.dayinacoustics.com</t>
+          <t>global.ptadoor.com</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>佛山市南海区里水镇赤山大道32号 (No.32 Chishan Avenue, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+          <t>Xincheng technology park, Yuelu Avenue, Changsha Hunan China</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 50-85$</t>
+          <t>Buyer: ¥3000, MoQ 1pcs, very good</t>
         </is>
       </c>
     </row>
@@ -2049,32 +2097,44 @@
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>丰顺县泰雅达实业有限公司</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>陈卓敏 Ruby</t>
+          <t>徐小俊</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>295608376@qq.com</t>
+          <t>281431686@qq.com</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>+86 13556688832</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+          <t>13802731123</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://taiyada1688.1688.com/</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>广东省丰顺县汤坑镇太平北路</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Buyer: ￥1000 good</t>
+          <t>Buyer: ¥17, Moq 50, good</t>
         </is>
       </c>
     </row>
@@ -2082,30 +2142,34 @@
       <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>佛山市悠派家居科技有限公司</t>
+        </is>
+      </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Crystal 刘晓艺</t>
+          <t>黄伟业</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>crystal@sincerechina.net</t>
+          <t>Yea@LGPKB.com</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>86-15815992213</t>
+          <t>13825596371</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>www.sincerechina.net</t>
+          <t>www.LGPKB.com</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇季华西路中国陶瓷产业总部基地西区C07-C08栋 (China Ceramics Industry Headquaters Block No.C07-08, West Area, West Jihua Road, Nanzhuang, Foshan, China)</t>
+          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -2115,7 +2179,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Buyer: ¥ 500 good</t>
+          <t>Buyer: 600 RMB Great, very cheap</t>
         </is>
       </c>
     </row>
@@ -2123,32 +2187,20 @@
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>艾锐特</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Joan Liu</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>joan@goldenrickyhpl.com</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>+86 13599525074</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Https://goldenrickyhpl.com</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Xiamen City, Fujian, China</t>
-        </is>
-      </c>
+          <t>冯蕾</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2156,7 +2208,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Buyer: ￥ 300 good</t>
+          <t>Buyer: 3400, Good price</t>
         </is>
       </c>
     </row>
@@ -2164,18 +2216,30 @@
       <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>常州市永春保温材料有限公司 (Changzhou Yongchun Thermal Insulation Materials Co., Ltd.)</t>
+        </is>
+      </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>yc@ycbycl.com</t>
+        </is>
+      </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>135 3666 7789, 400-9090-518</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr"/>
+          <t>0519-88931168</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>www.ycbycl.com</t>
+        </is>
+      </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
+          <t>江苏省常州市天宁区郑陆镇工业集中区</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -2185,7 +2249,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 300 rmb and more. Good quality and good price. Small quantity</t>
+          <t>Buyer: 10$</t>
         </is>
       </c>
     </row>
@@ -2193,30 +2257,34 @@
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>诺奥(福建)环保家居用品有限公司</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>王闻浠</t>
+          <t>曾令贵</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>lanjanweiyu@163.com</t>
+          <t>513573190@qq.com</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>+86-13569915996</t>
+          <t>86-13585642723 / 0596-8273388-8083</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>www.lanjan.com</t>
+          <t>www.fjnuoao.cn</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>河南省长葛市石固镇梁庄工业园区</t>
+          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2226,7 +2294,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 33$ for 1 pcs. Good quality and quantity</t>
+          <t>Buyer: 69$</t>
         </is>
       </c>
     </row>
@@ -2234,20 +2302,32 @@
       <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="inlineStr"/>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>hengsheng_carpet@163.com</t>
-        </is>
-      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>大音声学 (DAYIN ACOUSTICS)</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>唐佳豪 (Vance)</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>0769-89807692</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
+          <t>+86 18925924350</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>www.dayinacoustics.com</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>佛山市南海区里水镇赤山大道32号 (No.32 Chishan Avenue, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+        </is>
+      </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2255,7 +2335,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Good 👍</t>
+          <t>Buyer: 50-85$</t>
         </is>
       </c>
     </row>
@@ -2263,32 +2343,28 @@
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>杭州班昇</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Willer Zhou</t>
+          <t>陈卓敏 Ruby</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>sale31@higold.com.cn</t>
+          <t>295608376@qq.com</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>+86 158 2865 5891</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>www.higoldhardware.com</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>No.36 Shunye East Rd, Xingtan, Shunde, Foshan 528325, Guangdong, China</t>
-        </is>
-      </c>
+          <t>+86 13556688832</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2296,7 +2372,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 5800</t>
+          <t>Buyer: ￥1000 good</t>
         </is>
       </c>
     </row>
@@ -2304,30 +2380,34 @@
       <c r="A49" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>FOSHAN SINCERE BUILDING MATERIALS CO., LTD.</t>
+        </is>
+      </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Sammi Shi</t>
+          <t>Crystal 刘晓艺</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>sales01@kehon.cn</t>
+          <t>crystal@sincerechina.net</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>+86 156 8948 5097, 0578-3271096</t>
+          <t>86-15815992213</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>www.kehon.cn</t>
+          <t>www.sincerechina.net</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
+          <t>佛山市禅城区南庄镇季华西路中国陶瓷产业总部基地西区C07-C08栋 (China Ceramics Industry Headquaters Block No.C07-08, West Area, West Jihua Road, Nanzhuang, Foshan, China)</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -2337,7 +2417,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 130 yuan</t>
+          <t>Buyer: ¥ 500 good</t>
         </is>
       </c>
     </row>
@@ -2345,30 +2425,34 @@
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Xiamen Golden Ricky Industry &amp; Trade Co.,Ltd</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Richie Wang</t>
+          <t>Joan Liu</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>richie.wang@wbhouse.com</t>
+          <t>joan@goldenrickyhpl.com</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>+86 137 1002 1675</t>
+          <t>+86 13599525074</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>www.gdwbprefabhouse.com</t>
+          <t>Https://goldenrickyhpl.com</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Guangdong Factory: No.5, No. 161 Ganghe Avenue, Gaoming District, Foshan city, Guangdong, CHINA; Fujian Factory: Provincial Highway 308, Yunrong Township, Minqing County, Fuzhou City, Fujian Province, CHINA.</t>
+          <t>Xiamen City, Fujian, China</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2378,7 +2462,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 20000usd</t>
+          <t>Buyer: ￥ 300 good</t>
         </is>
       </c>
     </row>
@@ -2386,40 +2470,32 @@
       <c r="A51" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="inlineStr"/>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>Owen Li</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>owen.li@seajoinhouse.com</t>
-        </is>
-      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>江门市新阳刚智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>(86) 133 9501 1076</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>www.seajoinhouse.com</t>
-        </is>
-      </c>
+          <t>135 3666 7789, 400-9090-518</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Chongqing, China / Ho Chi Minh City, Vietnam</t>
+          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 500yuan</t>
+          <t>Buyer: 300 rmb and more. Good quality and good price. Small quantity</t>
         </is>
       </c>
     </row>
@@ -2427,30 +2503,34 @@
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>河南蓝健陶瓷有限公司</t>
+        </is>
+      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Josie Guan</t>
+          <t>王闻浠</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>cae@china-cae.com</t>
+          <t>lanjanweiyu@163.com</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>+86-13702279135</t>
+          <t>+86-13569915996</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>www.china-cae.com</t>
+          <t>www.lanjan.com</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>No.62-64, Xingda Rd., Shagang Dist., Shuikou Town, Kaiping, Guangdong, P.R.Of China.</t>
+          <t>河南省长葛市石固镇梁庄工业园区</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2460,7 +2540,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 100, 47 rnb per piece</t>
+          <t>Buyer: 33$ for 1 pcs. Good quality and quantity</t>
         </is>
       </c>
     </row>
@@ -2468,26 +2548,22 @@
       <c r="A53" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="3" t="inlineStr"/>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>沃澜 (WOTUA)</t>
+        </is>
+      </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>董华</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>418897056@qq.com</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>13914649982, 18951488133</t>
-        </is>
-      </c>
+          <t>Dion Sun</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
       <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
+          <t>3座104号</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -2497,7 +2573,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 50, 200 rnb per</t>
+          <t>Buyer: Good quality and quantity. 140 rmb 1 pcs.</t>
         </is>
       </c>
     </row>
@@ -2505,32 +2581,24 @@
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="inlineStr"/>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Jasmine Guan 管敏秀</t>
-        </is>
-      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>三强地毯</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>jasmine@suofeiyahome.com</t>
+          <t>hengsheng_carpet@163.com</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>+86 147 7520 2759</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofeyiahome.com</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
-        </is>
-      </c>
+          <t>0769-89807692</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2538,7 +2606,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 10, 845 per piece</t>
+          <t>Buyer: Good 👍</t>
         </is>
       </c>
     </row>
@@ -2546,30 +2614,34 @@
       <c r="A55" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="3" t="inlineStr"/>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Higold Group Co., Ltd.</t>
+        </is>
+      </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>金厚强 Jin Houqiang</t>
+          <t>Willer Zhou</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>jinhouqiang@leyard.com</t>
+          <t>sale31@higold.com.cn</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>13510009569, 18829341125, 400-8592-666</t>
+          <t>+86 158 2865 5891</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>www.leyard.com</t>
+          <t>www.higoldhardware.com</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋</t>
+          <t>No.36 Shunye East Rd, Xingtan, Shunde, Foshan 528325, Guangdong, China</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
@@ -2579,7 +2651,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1pcs. Start from 60rmb. Novative technology</t>
+          <t>Buyer: 5800</t>
         </is>
       </c>
     </row>
@@ -2587,20 +2659,24 @@
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Zhejiang Kehon Intelligent Science &amp; Technology Co., Ltd.</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Sammi Shi</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>sales02@kehon.cn</t>
+          <t>sales01@kehon.cn</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>+86 157 5573 4990</t>
+          <t>+86 156 8948 5097, 0578-3271096</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2615,12 +2691,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 399</t>
+          <t>Buyer: 130 yuan</t>
         </is>
       </c>
     </row>
@@ -2628,28 +2704,36 @@
       <c r="A57" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="3" t="inlineStr"/>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Guangdong Wanbang Modular Building Co., Ltd</t>
+        </is>
+      </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>周信朋 Joe Zhou</t>
+          <t>Richie Wang</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>sales02@jnodwater.com</t>
+          <t>richie.wang@wbhouse.com</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>+86 199 2825 2201, +86-757-2361 7920</t>
+          <t>+86 137 1002 1675</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>www.jnodwater.com</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr"/>
+          <t>www.gdwbprefabhouse.com</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Guangdong Factory: No.5, No. 161 Ganghe Avenue, Gaoming District, Foshan city, Guangdong, CHINA; Fujian Factory: Provincial Highway 308, Yunrong Township, Minqing County, Fuzhou City, Fujian Province, CHINA.</t>
+        </is>
+      </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2657,7 +2741,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1410</t>
+          <t>Buyer: 20000usd</t>
         </is>
       </c>
     </row>
@@ -2665,40 +2749,44 @@
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Guhao Group | SEAJOIN</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>洪美兰</t>
+          <t>Owen Li</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>jiang@chuangqitimes.com</t>
+          <t>owen.li@seajoinhouse.com</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>13450298606, 020-82511901</t>
+          <t>(86) 133 9501 1076</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>www.chuangqitimes.com</t>
+          <t>www.seajoinhouse.com</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
+          <t>Chongqing, China / Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 329</t>
+          <t>Buyer: 500yuan</t>
         </is>
       </c>
     </row>
@@ -2706,36 +2794,44 @@
       <c r="A59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="3" t="inlineStr"/>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>CAE SANITARY FITTINGS INDUSTRY CO., LTD. GUANGDONG</t>
+        </is>
+      </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Jacky</t>
+          <t>Josie Guan</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>sales08@ruikang-cn.com</t>
+          <t>cae@china-cae.com</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>+86 18028330648, +86 18022073939</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr"/>
+          <t>+86-13702279135</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>www.china-cae.com</t>
+        </is>
+      </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
+          <t>No.62-64, Xingda Rd., Shagang Dist., Shuikou Town, Kaiping, Guangdong, P.R.Of China.</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 229</t>
+          <t>Buyer: MOQ 100, 47 rnb per piece</t>
         </is>
       </c>
     </row>
@@ -2743,22 +2839,30 @@
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>盐城格子匠家居有限公司</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>潘禹</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
+          <t>董华</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>418897056@qq.com</t>
+        </is>
+      </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>13691864691</t>
+          <t>13914649982, 18951488133</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
+          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2768,7 +2872,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 680</t>
+          <t>Buyer: MOQ 50, 200 rnb per</t>
         </is>
       </c>
     </row>
@@ -2776,30 +2880,34 @@
       <c r="A61" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="3" t="inlineStr"/>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>SUOFEIYA HOME COLLECTION CO., LTD</t>
+        </is>
+      </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Jack Guan</t>
+          <t>Jasmine Guan 管敏秀</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>jack@cae.cn</t>
+          <t>jasmine@suofeiyahome.com</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>+86-750-8119338</t>
+          <t>+86 147 7520 2759</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>www.cae.cn</t>
+          <t>https://www.sofeyiahome.com</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
+          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
@@ -2809,7 +2917,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 150 yuan, 100, good range of products</t>
+          <t>Buyer: MOQ 10, 845 per piece</t>
         </is>
       </c>
     </row>
@@ -2817,30 +2925,34 @@
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>利亚德光电股份有限公司 Leyard Optoelectronic Co., Ltd.</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Jasmine Guan 管敏秀</t>
+          <t>金厚强 Jin Houqiang</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>jasmine@suofeiyahome.com</t>
+          <t>jinhouqiang@leyard.com</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>+86 147 7520 2759</t>
+          <t>13510009569, 18829341125, 400-8592-666</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://www.sofeyiahome.com</t>
+          <t>www.leyard.com</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
+          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -2850,7 +2962,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 800usd, very nice, good quality product</t>
+          <t>Buyer: 1pcs. Start from 60rmb. Novative technology</t>
         </is>
       </c>
     </row>
@@ -2858,32 +2970,16 @@
       <c r="A63" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="3" t="inlineStr"/>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>余赛银 (Yu Saiyin)</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>109786129@qq.com</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>+86 13660529010</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>kingliye.com</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>佛山市南海区里广路二号碧桂园金沙国际广场1201室 (Room 1201, Building 10, Jinsha International Plaza No.2 Liguang Road, Nanhai District, Foshan City)</t>
-        </is>
-      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>林商学社</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr"/>
+      <c r="G63" s="3" t="inlineStr"/>
       <c r="H63" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2891,7 +2987,7 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
+          <t>Buyer: From 1pc. Natural materials.</t>
         </is>
       </c>
     </row>
@@ -2899,27 +2995,15 @@
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="inlineStr"/>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Winni 何玲玲</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>helingling@gdhsyj.com</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>+86 18924564942</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>WWW.HOPSOONER.COM</t>
-        </is>
-      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>佛山市威尔信保险柜有限公司 (Foshan Weierxin Safe Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -2928,7 +3012,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Buyer: The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+          <t>Buyer: 1250rmb. MOQ 1 pc</t>
         </is>
       </c>
     </row>
@@ -2936,27 +3020,15 @@
       <c r="A65" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="3" t="inlineStr"/>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>周信朋 (Joe Zhou)</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>sales02@jnodwater.com</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>+86 199 2825 2201, +86-757-2361 7920</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>www.jnodwater.com</t>
-        </is>
-      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>SAKURA 樱花智能锁</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" s="3" t="inlineStr"/>
       <c r="H65" s="3" t="inlineStr">
         <is>
@@ -2973,35 +3045,35 @@
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>JNOD 基诺德</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>周信朋 Joe Zhou</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>sales02@kehon.cn</t>
+          <t>sales02@jnodwater.com</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>+86 157 5573 4990 / 0578-3271096</t>
+          <t>+86 199 2825 2201, +86-757-2361 7920</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>www.kehon.cn</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
-        </is>
-      </c>
+          <t>www.jnodwater.com</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3014,36 +3086,44 @@
       <c r="A67" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="3" t="inlineStr"/>
-      <c r="C67" s="3" t="inlineStr"/>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>广州传祺时代智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>洪美兰</t>
+        </is>
+      </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>service@3weitech.com</t>
+          <t>jiang@chuangqitimes.com</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>021-57715805</t>
+          <t>13450298606, 020-82511901</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>www.3weitech.com</t>
+          <t>www.chuangqitimes.com</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>上海市闵行区新骏环路188号11号楼A座518室</t>
+          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет проблема синхронизации . Есть свой искусственный интеллект . Нужно тестировать . Купили ленту у него лед, на телевизор как образец</t>
+          <t>Buyer: 329</t>
         </is>
       </c>
     </row>
@@ -3051,36 +3131,40 @@
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>RUIKANG</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>王鹏</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1319129904@qq.com</t>
+          <t>sales08@ruikang-cn.com</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>189-2324-7677</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>www.asnug.com</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
+          <t>+86 18028330648, +86 18022073939</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
+          <t>Buyer: 229</t>
         </is>
       </c>
     </row>
@@ -3088,30 +3172,26 @@
       <c r="A69" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="3" t="inlineStr"/>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>松下电器设备(中国)有限公司</t>
+        </is>
+      </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Yolanda He</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>ecosound02@polyacoustic.com</t>
-        </is>
-      </c>
+          <t>潘禹</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>+86-18018130150</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>www.polyacoustic.com</t>
-        </is>
-      </c>
+          <t>13691864691</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>No.10 Jinxi Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+          <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
@@ -3121,7 +3201,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного метра 150 юаней сказала примерно. Не до конца поняла точность минимальной партии, но говорили часто 100 кВ метром</t>
+          <t>Buyer: 680</t>
         </is>
       </c>
     </row>
@@ -3129,32 +3209,44 @@
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>CAE</t>
+        </is>
+      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>劉奕紫 Cathy</t>
+          <t>Jack Guan</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>sales19@soundbox.hk</t>
+          <t>jack@cae.cn</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>+86 137 6339 3059</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
+          <t>+86-750-8119338</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>www.cae.cn</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Buyer: От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккуратная комната, достаточно комфортная. Цена немного завышена, встречали на других выставках пониже стоимостью.</t>
+          <t>Buyer: 150 yuan, 100, good range of products</t>
         </is>
       </c>
     </row>
@@ -3162,40 +3254,44 @@
       <c r="A71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="3" t="inlineStr"/>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>广东富矿智能家居有限公司 (Guangdong Fukuang Intelligent Home Co., Ltd.)</t>
+        </is>
+      </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>蔡缘缘</t>
+          <t>余赛银 (Yu Saiyin)</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>wendyyian@163.com</t>
+          <t>109786129@qq.com</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>0086-13599917696</t>
+          <t>+86 13660529010</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>www.fjnuoao.cn</t>
+          <t>kingliye.com</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
+          <t>佛山市南海区里广路二号碧桂园金沙国际广场1201室 (Room 1201, Building 10, Jinsha International Plaza No.2 Liguang Road, Nanhai District, Foshan City)</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 2900 usd</t>
+          <t>Buyer: Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
         </is>
       </c>
     </row>
@@ -3203,32 +3299,16 @@
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="inlineStr"/>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Felicity</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>sales09@spakingston.com</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>+86-18025851458</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>www.spakingston.com</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Kingston Company, JiangJun Road, Qiuchang, Huiyang, Huizhou, China</t>
-        </is>
-      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>THOR 索而</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3236,7 +3316,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 100</t>
+          <t>Buyer: The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
         </is>
       </c>
     </row>
@@ -3244,40 +3324,40 @@
       <c r="A73" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="3" t="inlineStr"/>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>肇庆合生雅居智能家居有限公司 (Zhaoqing Hesheng Yaju Intelligent Home Co., Ltd.)</t>
+        </is>
+      </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>蔡缘缘</t>
+          <t>Winni 何玲玲</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>wendyyian@163.com</t>
+          <t>helingling@gdhsyj.com</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>0086-13599917696, 0592-7081636</t>
+          <t>+86 18924564942</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>www.fjnuoao.cn</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
-        </is>
-      </c>
+          <t>WWW.HOPSOONER.COM</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1</t>
+          <t>Buyer: The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
         </is>
       </c>
     </row>
@@ -3285,30 +3365,30 @@
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="2" t="inlineStr"/>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>William</t>
-        </is>
-      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>视威电子科技（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>william@sunrans.com</t>
+          <t>service@3weitech.com</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>+86 134 1613 9887, +86-20-26231998</t>
+          <t>021-57715805</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>http://www.sunrans.com</t>
+          <t>www.3weitech.com</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
+          <t>上海市闵行区新骏环路188号11号楼A座518室</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3318,7 +3398,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very good and good products.</t>
+          <t>Buyer: 167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет проблема синхронизации . Есть свой искусственный интеллект . Нужно тестировать . Купили ленту у него лед, на телевизор как образец</t>
         </is>
       </c>
     </row>
@@ -3326,32 +3406,32 @@
       <c r="A75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="3" t="inlineStr"/>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>爱舒床垫集团有限公司</t>
+        </is>
+      </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>梁莹慧 Fiona</t>
+          <t>王鹏</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>003@cgchcontainer.com</t>
+          <t>1319129904@qq.com</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>+86 183 4456 5547</t>
+          <t>189-2324-7677</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>www.cgchcontainer.com</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
-        </is>
-      </c>
+          <t>www.asnug.com</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
       <c r="H75" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3359,7 +3439,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 1, they got samples. 8000usd. Very well made product, trendy and popular. This capsules houses very affordable.</t>
+          <t>Buyer: 20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
         </is>
       </c>
     </row>
@@ -3367,16 +3447,36 @@
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="2" t="inlineStr"/>
-      <c r="C76" s="2" t="inlineStr"/>
-      <c r="D76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Suzhou Acesound New Material Technology Inc.</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Yolanda He</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>ecosound02@polyacoustic.com</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>15916159866</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
+          <t>+86-18018130150</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>No.10 Jinxi Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3384,7 +3484,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
+          <t>Buyer: Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного метра 150 юаней сказала примерно. Не до конца поняла точность минимальной партии, но говорили часто 100 кВ метром</t>
         </is>
       </c>
     </row>
@@ -3392,32 +3492,28 @@
       <c r="A77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="3" t="inlineStr"/>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>soundbox</t>
+        </is>
+      </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Ivy Zhou</t>
+          <t>劉奕紫 Cathy</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>ivy@ifunpark.com</t>
+          <t>sales19@soundbox.hk</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>+86 133 0238 5758</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>www.ifunpark.com / www.ifunamusement.com</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
-        </is>
-      </c>
+          <t>+86 137 6339 3059</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr"/>
       <c r="H77" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3425,7 +3521,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 600</t>
+          <t>Buyer: От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккуратная комната, достаточно комфортная. Цена немного завышена, встречали на других выставках пониже стоимостью.</t>
         </is>
       </c>
     </row>
@@ -3433,32 +3529,16 @@
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="2" t="inlineStr"/>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Emily Li</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>tuoxinlqm@outlook.com</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>+86 19831737599</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tuoxinfiberglassmesh.com/</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
-        </is>
-      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>顶固集团</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3466,7 +3546,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 0.6 usd/m2</t>
+          <t>Buyer: От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккуратно. Хорошее решение для сушки белья и экономии места. Стоимость чуть больше 200 юаней</t>
         </is>
       </c>
     </row>
@@ -3474,40 +3554,44 @@
       <c r="A79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="3" t="inlineStr"/>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Shenzhen Kingston Sanitary Ware Co., Ltd.</t>
+        </is>
+      </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>王虎旗</t>
+          <t>Felicity</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>hectorwang1982@gmail.com</t>
+          <t>sales09@spakingston.com</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>86 18638546565</t>
+          <t>+86-18025851458</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>www.weilandeglobal.com</t>
+          <t>www.spakingston.com</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>河南省郑州市曲梁工业园188号</t>
+          <t>Kingston Company, JiangJun Road, Qiuchang, Huiyang, Huizhou, China</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Under negotiation, great opportunities</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -3515,32 +3599,44 @@
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou Sunrans Sanitary Ware Co., Ltd / Guangzhou Sunrans New Energy Technology Co., Ltd</t>
+        </is>
+      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>曹双林 (Edith Cao)</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>william@sunrans.com</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>13286132534, 400-0750-889</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr"/>
+          <t>+86 134 1613 9887, +86-20-26231998</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>http://www.sunrans.com</t>
+        </is>
+      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>广东省江门市蓬江区迎宾大道西23号之129</t>
+          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1-5 usd/l</t>
+          <t>Buyer: MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very good and good products.</t>
         </is>
       </c>
     </row>
@@ -3549,27 +3645,15 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="inlineStr"/>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>李尚声 (Shangsheng Li)</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>15915975597@163.com</t>
-        </is>
-      </c>
+      <c r="C81" s="3" t="inlineStr"/>
+      <c r="D81" s="3" t="inlineStr"/>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>15915974406</t>
+          <t>15916159866</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr"/>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
-        </is>
-      </c>
+      <c r="G81" s="3" t="inlineStr"/>
       <c r="H81" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3577,7 +3661,7 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 6000RMB</t>
+          <t>Buyer: MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
         </is>
       </c>
     </row>
@@ -3585,18 +3669,34 @@
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="2" t="inlineStr"/>
-      <c r="C82" s="2" t="inlineStr"/>
-      <c r="D82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>IFUN PARK &amp; TIPTOPFUN AMUSEMENT</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Ivy Zhou</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>ivy@ifunpark.com</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr"/>
+          <t>+86 133 0238 5758</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>www.ifunpark.com / www.ifunamusement.com</t>
+        </is>
+      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>江苏省太仓市双凤镇陆江路1号</t>
+          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3606,7 +3706,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 2000RMB&amp;gt;</t>
+          <t>Buyer: 600</t>
         </is>
       </c>
     </row>
@@ -3614,28 +3714,16 @@
       <c r="A83" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="3" t="inlineStr"/>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>Wing</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>wuyunying08@gmail.com</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>189-2984-9818, 0758-8578545</t>
-        </is>
-      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Weyth 惠特</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr"/>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr"/>
       <c r="F83" s="3" t="inlineStr"/>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
-        </is>
-      </c>
+      <c r="G83" s="3" t="inlineStr"/>
       <c r="H83" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3643,7 +3731,7 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>Buyer: MOQ - 5000 and price - 7000 dollars</t>
+          <t>Buyer: 500</t>
         </is>
       </c>
     </row>
@@ -3651,32 +3739,16 @@
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="2" t="inlineStr"/>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Susan Xia</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>acousound16@polyacoustic.com</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>+86-15512435605</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>www.polyacoustic.com</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu 215152</t>
-        </is>
-      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>D.DELI 德利智能门锁</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3684,7 +3756,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 4000$</t>
+          <t>Buyer: 43</t>
         </is>
       </c>
     </row>
@@ -3692,40 +3764,44 @@
       <c r="A85" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="3" t="inlineStr"/>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>RENQIU TUOXIN BUILDING MATERIALS CO., LTD</t>
+        </is>
+      </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>黄斌</t>
+          <t>Emily Li</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>464565801@qq.com</t>
+          <t>tuoxinlqm@outlook.com</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>13813551160</t>
+          <t>+86 19831737599</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>www.ycpanel.com</t>
+          <t>https://www.tuoxinfiberglassmesh.com/</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>常州市武进区横林镇长虹东路28号</t>
+          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 3000 dollars</t>
+          <t>Buyer: 0.6 usd/m2</t>
         </is>
       </c>
     </row>
@@ -3733,26 +3809,34 @@
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>河南威兰得建筑科技有限公司</t>
+        </is>
+      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>陈施志凯 (CHEN SHI ZHI KAI)</t>
+          <t>王虎旗</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>108455453@qq.com</t>
+          <t>hectorwang1982@gmail.com</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>+86 134 3318 1558, 0757-8560 9159</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr"/>
+          <t>86 18638546565</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>www.weilandeglobal.com</t>
+        </is>
+      </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+          <t>河南省郑州市曲梁工业园188号</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -3762,7 +3846,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Buyer: The price cheap, merchant very friendly</t>
+          <t>Buyer: Under negotiation, great opportunities</t>
         </is>
       </c>
     </row>
@@ -3770,36 +3854,36 @@
       <c r="A87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="3" t="inlineStr"/>
-      <c r="C87" s="3" t="inlineStr"/>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>sales.countermast.china@countermast.com</t>
-        </is>
-      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>江门市新会区致恒科技材料有限公司</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>曹双林 (Edith Cao)</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr"/>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>400-100-2228</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>www.countermast.cn</t>
-        </is>
-      </c>
+          <t>13286132534, 400-0750-889</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr"/>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>Building No.7, Zhongqing Industrial Park, Dalian free trade zone, Liaoning, China</t>
+          <t>广东省江门市蓬江区迎宾大道西23号之129</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>Buyer: The price more cheaper, good quality</t>
+          <t>Buyer: 1-5 usd/l</t>
         </is>
       </c>
     </row>
@@ -3807,30 +3891,22 @@
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>安居福智能门 (ANJUFU INTELLIGENT GATE)</t>
+        </is>
+      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>严金霞</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>monalisa38@monalisa.cn</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>+86 13711113746, 400 020 1818, +86 20-28607711</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>www.monalisa.cn</t>
-        </is>
-      </c>
+          <t>罗如玲</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区花东镇港头工业区4号</t>
+          <t>广东省中山市东凤镇</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -3840,7 +3916,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Good merchant, perfect products</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -3848,32 +3924,16 @@
       <c r="A89" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="3" t="inlineStr"/>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>叶小龙/Dustin Ye</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>yedustin@gmail.com</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>+86-188 5861 0008</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>www.cngaocheng.cn</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>浙江省三门县浦坝港镇沿海工业城 (COASTAL INDUSTRIAL CITY, PUBAGANG TOWN, SANMEN, TAIZHOU CITY, ZHEJIANG PRO., CHINA)</t>
-        </is>
-      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>欧派</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr"/>
+      <c r="D89" s="3" t="inlineStr"/>
+      <c r="E89" s="3" t="inlineStr"/>
+      <c r="F89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr"/>
       <c r="H89" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3881,7 +3941,7 @@
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
+          <t>Buyer: 679 rmb</t>
         </is>
       </c>
     </row>
@@ -3889,30 +3949,18 @@
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="2" t="inlineStr"/>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Pacao Yin</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>pin@pingaolao.com</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>(0086)13903035682, (0086)0769-86378283, (0086)0769-86377522</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
-        </is>
-      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>永康市鸿钰门业有限公司</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+          <t>浙江省永康市长城工业区</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -3922,7 +3970,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 15 RMB the product is interesting</t>
+          <t>Buyer: 59 rmb</t>
         </is>
       </c>
     </row>
@@ -3930,32 +3978,20 @@
       <c r="A91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="3" t="inlineStr"/>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>东方喜卡</t>
+        </is>
+      </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>吴仁余</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>294217488@qq.com</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>13967444542, 0579-82889122</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="inlineStr">
-        <is>
-          <t>www.jhrxhb.com</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>浙江省金华市婺城区罗店镇北山路精工工业园</t>
-        </is>
-      </c>
+          <t>果果</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr"/>
+      <c r="E91" s="3" t="inlineStr"/>
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr"/>
       <c r="H91" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3963,7 +3999,7 @@
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>Buyer: nearly $15,000 for this production line</t>
+          <t>Buyer: 249RMB</t>
         </is>
       </c>
     </row>
@@ -3971,40 +4007,40 @@
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>优品声学 (YP ACOUSTICS)</t>
+        </is>
+      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Dream Lin</t>
+          <t>李尚声 (Shangsheng Li)</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>sale15@double-lin.com</t>
+          <t>15915975597@163.com</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>86-020-66837727, 86-13710718529</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>www.double-lin.com</t>
-        </is>
-      </c>
+          <t>15915974406</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
+          <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 149</t>
+          <t>Buyer: 6000RMB</t>
         </is>
       </c>
     </row>
@@ -4012,30 +4048,22 @@
       <c r="A93" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="3" t="inlineStr"/>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>Aaron Liu</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>aaron@ccolomac.com</t>
-        </is>
-      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>双龙智科</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr"/>
+      <c r="D93" s="3" t="inlineStr"/>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>+86-0371-66350801, +86 15936292861</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>www.ccolomac.com</t>
-        </is>
-      </c>
+          <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr"/>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
@@ -4045,7 +4073,7 @@
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 249</t>
+          <t>Buyer: 2000RMB&amp;gt;</t>
         </is>
       </c>
     </row>
@@ -4053,36 +4081,40 @@
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>GUANGDONG TUOXUN INTELLIGENT TECHNOLOGY CO., LTD</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>袁佳磊</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr"/>
+          <t>Wing</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>wuyunying08@gmail.com</t>
+        </is>
+      </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>18652449601</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>www.cnfrd.cn</t>
-        </is>
-      </c>
+          <t>189-2984-9818, 0758-8578545</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>江苏省太仓市港区临江路1号</t>
+          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 749</t>
+          <t>Buyer: MOQ - 5000 and price - 7000 dollars</t>
         </is>
       </c>
     </row>
@@ -4090,40 +4122,44 @@
       <c r="A95" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="3" t="inlineStr"/>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Suzhou Acousound New Material Technology Co., Ltd.</t>
+        </is>
+      </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Eric Huang</t>
+          <t>Susan Xia</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>464565801@qq.com</t>
+          <t>acousound16@polyacoustic.com</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>13813551160 / 0519-88784050</t>
+          <t>+86-15512435605</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>www.ycpanel.com</t>
+          <t>www.polyacoustic.com</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>No.28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu 215152</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 5000 USD</t>
+          <t>Buyer: 4000$</t>
         </is>
       </c>
     </row>
@@ -4131,36 +4167,40 @@
       <c r="A96" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>佛山市方泓五金建材有限公司 (Foshan Fangheng Hardware Co., Ltd.)</t>
+        </is>
+      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Wing</t>
+          <t>陈施志凯 (CHEN SHI ZHI KAI)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>wuyunying08@gmail.com</t>
+          <t>108455453@qq.com</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>189-2984-9818, 0758-8578545</t>
+          <t>+86 134 3318 1558, 0757-8560 9159</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
+          <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 3000 USD</t>
+          <t>Buyer: The price cheap, merchant very friendly</t>
         </is>
       </c>
     </row>
@@ -4168,30 +4208,30 @@
       <c r="A97" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="3" t="inlineStr"/>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>Susan Xia</t>
-        </is>
-      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Countermast Technology (Dalian) Company Limited</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr"/>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>acousound16@polyacoustic.com</t>
+          <t>sales.countermast.china@countermast.com</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>+86-15512435605</t>
+          <t>400-100-2228</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>www.polyacoustic.com</t>
+          <t>www.countermast.cn</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu 215152</t>
+          <t>Building No.7, Zhongqing Industrial Park, Dalian free trade zone, Liaoning, China</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
@@ -4201,7 +4241,7 @@
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 3000 USD</t>
+          <t>Buyer: The price more cheaper, good quality</t>
         </is>
       </c>
     </row>
@@ -4209,28 +4249,44 @@
       <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="2" t="inlineStr"/>
-      <c r="C98" s="2" t="inlineStr"/>
-      <c r="D98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>广州蒙娜丽莎控股集团有限公司, 广州蒙娜丽莎卫浴股份有限公司</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>严金霞</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>monalisa38@monalisa.cn</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr"/>
+          <t>+86 13711113746, 400 020 1818, +86 20-28607711</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>www.monalisa.cn</t>
+        </is>
+      </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>江苏省太仓市双凤镇陆江路1号</t>
+          <t>广州市花都区花东镇港头工业区4号</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
+          <t>Buyer: Good merchant, perfect products</t>
         </is>
       </c>
     </row>
@@ -4238,18 +4294,34 @@
       <c r="A99" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="3" t="inlineStr"/>
-      <c r="C99" s="3" t="inlineStr"/>
-      <c r="D99" s="3" t="inlineStr"/>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>高成 (Gaocheng)</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>叶小龙/Dustin Ye</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>yedustin@gmail.com</t>
+        </is>
+      </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>186-0205-8898 / 400-608-0098</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr"/>
+          <t>+86-188 5861 0008</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>www.cngaocheng.cn</t>
+        </is>
+      </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区里水镇</t>
+          <t>浙江省三门县浦坝港镇沿海工业城 (COASTAL INDUSTRIAL CITY, PUBAGANG TOWN, SANMEN, TAIZHOU CITY, ZHEJIANG PRO., CHINA)</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
@@ -4259,7 +4331,7 @@
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 249 RMB. They have fully described their products.</t>
+          <t>Buyer: 160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
         </is>
       </c>
     </row>
@@ -4267,28 +4339,44 @@
       <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="2" t="inlineStr"/>
-      <c r="C100" s="2" t="inlineStr"/>
-      <c r="D100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD. / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Pacao Yin</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>pin@pingaolao.com</t>
+        </is>
+      </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>186-0205-8898, 400-608-0098</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr"/>
+          <t>(0086)13903035682, (0086)0769-86378283, (0086)0769-86377522</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
+        </is>
+      </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>广东省中山市小榄镇四沙盛和路5号</t>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 249RMB , 价格很便宜</t>
+          <t>Buyer: 15 RMB the product is interesting</t>
         </is>
       </c>
     </row>
@@ -4296,36 +4384,44 @@
       <c r="A101" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="3" t="inlineStr"/>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>浙江瑞鑫环保设备有限公司</t>
+        </is>
+      </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>颜加伟</t>
+          <t>吴仁余</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>1164199388@qq.com</t>
+          <t>294217488@qq.com</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>133 9983 5678</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr"/>
+          <t>13967444542, 0579-82889122</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>www.jhrxhb.com</t>
+        </is>
+      </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
+          <t>浙江省金华市婺城区罗店镇北山路精工工业园</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 400rmb /m2 good meeting</t>
+          <t>Buyer: nearly $15,000 for this production line</t>
         </is>
       </c>
     </row>
@@ -4333,32 +4429,44 @@
       <c r="A102" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>ZHEJIANG DOUBLE-LIN VALVES CO., LTD.</t>
+        </is>
+      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>高学梅</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr"/>
+          <t>Dream Lin</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>sale15@double-lin.com</t>
+        </is>
+      </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>17687627315</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr"/>
+          <t>86-020-66837727, 86-13710718529</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>www.double-lin.com</t>
+        </is>
+      </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
+          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 350 rmb/m2</t>
+          <t>Buyer: 149</t>
         </is>
       </c>
     </row>
@@ -4366,40 +4474,40 @@
       <c r="A103" s="3" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="3" t="inlineStr"/>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>苏州市富尔达科技股份有限公司</t>
+        </is>
+      </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Pacao Yin</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>pin@pingaolao.com</t>
-        </is>
-      </c>
+          <t>袁佳磊</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr"/>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Mobile: (0086)13903035682, Tel: (0086)0769-86378283</t>
+          <t>18652449601</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
+          <t>www.cnfrd.cn</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+          <t>江苏省太仓市港区临江路1号</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 5000 pieces</t>
+          <t>Buyer: 749</t>
         </is>
       </c>
     </row>
@@ -4407,26 +4515,34 @@
       <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.,LTD.</t>
+        </is>
+      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>颜加伟</t>
+          <t>Eric Huang</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1164199388@qq.com</t>
+          <t>464565801@qq.com</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>133 9983 5678</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr"/>
+          <t>13813551160 / 0519-88784050</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>www.ycpanel.com</t>
+        </is>
+      </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
+          <t>No.28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -4436,7 +4552,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 400rmb/m2</t>
+          <t>Buyer: 5000 USD</t>
         </is>
       </c>
     </row>
@@ -4444,32 +4560,32 @@
       <c r="A105" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="3" t="inlineStr"/>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>高学梅</t>
-        </is>
-      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>双龙中科</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr"/>
       <c r="D105" s="3" t="inlineStr"/>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>17687627315</t>
+          <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr"/>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 350rmb/m2</t>
+          <t>Buyer: Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
         </is>
       </c>
     </row>
@@ -4477,40 +4593,32 @@
       <c r="A106" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="2" t="inlineStr"/>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Pacao Yin</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>pin@pingaolao.com</t>
-        </is>
-      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>深圳市家为安智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr"/>
+      <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Tel: (0086)0769-86378283, (0086)0769-86377522; Mobile: (0086)13903035682</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
-        </is>
-      </c>
+          <t>186-0205-8898 / 400-608-0098</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+          <t>广东省佛山市南海区里水镇</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 5000 pieces</t>
+          <t>Buyer: 249 RMB. They have fully described their products.</t>
         </is>
       </c>
     </row>
@@ -4518,40 +4626,32 @@
       <c r="A107" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="3" t="inlineStr"/>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>Thea</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>moershu3@moershu.com</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>13957622087</t>
-        </is>
-      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>广州市优品声学科技有限公司</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr"/>
+      <c r="D107" s="3" t="inlineStr"/>
+      <c r="E107" s="3" t="inlineStr"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>www.moershu.com</t>
+          <t>www.gzypsx.com</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
+          <t>广东省广州市番禺区南村镇南村西路138号德意创意园二层</t>
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
+          <t>Buyer: 6000RMB，积极，详细地告诉了一切</t>
         </is>
       </c>
     </row>
@@ -4559,30 +4659,18 @@
       <c r="A108" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="2" t="inlineStr"/>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>杨苗</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>yangm618@163.com</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>13816184706</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>http://www.shicanchina.com</t>
-        </is>
-      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>科维尔 (VIR)</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr"/>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区商城路889号C3-B06</t>
+          <t>市长城工业区</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -4592,7 +4680,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 3000 / MOQ 1 Inside view is luxury, i love it</t>
+          <t>Buyer: 2000 RMB</t>
         </is>
       </c>
     </row>
@@ -4600,26 +4688,30 @@
       <c r="A109" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="3" t="inlineStr"/>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>贵州佑远木业有限公司</t>
+        </is>
+      </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Zoey Zhang</t>
+          <t>颜加伟</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>zoey@sciener.com</t>
+          <t>1164199388@qq.com</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>+86 178-5768-8782</t>
+          <t>133 9983 5678</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr"/>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
+          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
@@ -4629,7 +4721,7 @@
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 20 / MOQ 100 Nice worker answered all questions</t>
+          <t>Buyer: 400rmb /m2 good meeting</t>
         </is>
       </c>
     </row>
@@ -4637,36 +4729,36 @@
       <c r="A110" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>广西豪庭家具有限公司 (Guangxi Haoting Furniture Co., Ltd.)</t>
+        </is>
+      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Lucy Zeng (曾露)</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>lucy@rongkedecor.com</t>
-        </is>
-      </c>
+          <t>高学梅</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>+86-13134020034</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amerdecor.com/</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr"/>
+          <t>17687627315</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 80 rmb for 230 meter</t>
+          <t>Buyer: 350 rmb/m2</t>
         </is>
       </c>
     </row>
@@ -4674,36 +4766,44 @@
       <c r="A111" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="3" t="inlineStr"/>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
+        </is>
+      </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>王冠</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr"/>
+          <t>Pacao Yin</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>pin@pingaolao.com</t>
+        </is>
+      </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>+86 13229297183</t>
+          <t>Mobile: (0086)13903035682, Tel: (0086)0769-86378283</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>WWW.SANNORA.COM; WWW.SANNORA-BATH.COM</t>
+          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区</t>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1560 rmb for whole item</t>
+          <t>Buyer: MOQ 5000 pieces</t>
         </is>
       </c>
     </row>
@@ -4711,40 +4811,44 @@
       <c r="A112" s="2" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="2" t="inlineStr"/>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Moershu (摩尔舒卫浴)</t>
+        </is>
+      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Sophia Deng (邓小艳)</t>
+          <t>Thea</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>sophiadeng@china-gold.cn</t>
+          <t>moershu3@moershu.com</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>+181 3838 6948</t>
+          <t>13957622087</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-gold.cn, http://www.aosman.cn</t>
+          <t>www.moershu.com</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>198 Siqian Xi Road, Shuikou, Kaiping 529300, Guangdong PR.China</t>
+          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 4600 rmb</t>
+          <t>Buyer: 194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
         </is>
       </c>
     </row>
@@ -4752,40 +4856,40 @@
       <c r="A113" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="3" t="inlineStr"/>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Hangzhou Sciener Smart Technology Co.,Ltd.</t>
+        </is>
+      </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Eric Huang</t>
+          <t>Zoey Zhang</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>464565801@qq.com</t>
+          <t>zoey@sciener.com</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>13813551160, 0519-88784050</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>www.ycpanel.com</t>
-        </is>
-      </c>
+          <t>+86 178-5768-8782</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr"/>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>#28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+          <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 2085</t>
+          <t>Buyer: 20 / MOQ 100 Nice worker answered all questions</t>
         </is>
       </c>
     </row>
@@ -4793,28 +4897,32 @@
       <c r="A114" s="2" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="2" t="inlineStr"/>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>江西荣科新型材料有限公司 / JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.</t>
+        </is>
+      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Wing</t>
+          <t>Lucy Zeng (曾露)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>wuyunying08@gmail.com</t>
+          <t>lucy@rongkedecor.com</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>189-2984-9818, 0758-8578545</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
-        </is>
-      </c>
+          <t>+86-13134020034</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amerdecor.com/</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -4822,7 +4930,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 2147</t>
+          <t>Buyer: 80 rmb for 230 meter</t>
         </is>
       </c>
     </row>
@@ -4830,30 +4938,30 @@
       <c r="A115" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="3" t="inlineStr"/>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>SANNORA</t>
+        </is>
+      </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Eric Huang</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>464565801@qq.com</t>
-        </is>
-      </c>
+          <t>王冠</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr"/>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>13813551160, 0519-88784050</t>
+          <t>+86 13229297183</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>www.ycpanel.com</t>
+          <t>WWW.SANNORA.COM; WWW.SANNORA-BATH.COM</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>#28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
@@ -4863,7 +4971,7 @@
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 2223</t>
+          <t>Buyer: 1560 rmb for whole item</t>
         </is>
       </c>
     </row>
@@ -4871,36 +4979,44 @@
       <c r="A116" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="2" t="inlineStr"/>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Kaiping Gold Medal Sanitary Ware Co.,Ltd. / Guangdong Aosman Sanitary Ware Co.,Ltd</t>
+        </is>
+      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>朱支群</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr"/>
+          <t>Sophia Deng (邓小艳)</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>sophiadeng@china-gold.cn</t>
+        </is>
+      </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>13763963598</t>
+          <t>+181 3838 6948</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>www.jx-wpc.com</t>
+          <t>http://www.china-gold.cn, http://www.aosman.cn</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>江西省瑞金市经济开发区创业一路东侧</t>
+          <t>198 Siqian Xi Road, Shuikou, Kaiping 529300, Guangdong PR.China</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 250¥/м3</t>
+          <t>Buyer: 4600 rmb</t>
         </is>
       </c>
     </row>
@@ -4908,32 +5024,16 @@
       <c r="A117" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="3" t="inlineStr"/>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>Anne</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>victor@ck-bath.com</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>18656330093</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>https://ck-bath.com/</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
-        </is>
-      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>东风汽车</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr"/>
+      <c r="D117" s="3" t="inlineStr"/>
+      <c r="E117" s="3" t="inlineStr"/>
+      <c r="F117" s="3" t="inlineStr"/>
+      <c r="G117" s="3" t="inlineStr"/>
       <c r="H117" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -4941,7 +5041,7 @@
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 4500¥</t>
+          <t>Buyer: 50 Yuan 50g (The taste is authentic and aroma is really good</t>
         </is>
       </c>
     </row>
@@ -4949,30 +5049,34 @@
       <c r="A118" s="2" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="2" t="inlineStr"/>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.LTD.</t>
+        </is>
+      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>刘朔雅 Gigi</t>
+          <t>Eric Huang</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>004@cgchcontainer.com</t>
+          <t>464565801@qq.com</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>+86 189 2997 1101</t>
+          <t>13813551160, 0519-88784050</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>www.cgchcontainer.com</t>
+          <t>www.ycpanel.com</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+          <t>#28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -4982,7 +5086,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 8790$</t>
+          <t>Buyer: 2085</t>
         </is>
       </c>
     </row>
@@ -4990,30 +5094,30 @@
       <c r="A119" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="3" t="inlineStr"/>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>江西瑞京鸿兴实业有限公司</t>
+        </is>
+      </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Linda</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>linda.lu@ciarrahome.com</t>
-        </is>
-      </c>
+          <t>朱支群</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr"/>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>+86 1882 9964 960, +86 1343 2639 580</t>
+          <t>13763963598</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>www.ciarrahome.com</t>
+          <t>www.jx-wpc.com</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
+          <t>江西省瑞金市经济开发区创业一路东侧</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
@@ -5023,7 +5127,7 @@
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 300¥ 300pcs</t>
+          <t>Buyer: 250¥/м3</t>
         </is>
       </c>
     </row>
@@ -5031,36 +5135,44 @@
       <c r="A120" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="2" t="inlineStr"/>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd</t>
+        </is>
+      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Viola Liu</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>wood6@sennorwell.com</t>
+          <t>victor@ck-bath.com</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>(86) 158 8931 1832</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr"/>
+          <t>18656330093</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>https://ck-bath.com/</t>
+        </is>
+      </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
+          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 50¥ 1000pcs</t>
+          <t>Buyer: 4500¥</t>
         </is>
       </c>
     </row>
@@ -5068,30 +5180,34 @@
       <c r="A121" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="3" t="inlineStr"/>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>ciarra</t>
+        </is>
+      </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Amy Liu 刘建美</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>export@ideal-china.net</t>
+          <t>linda.lu@ciarrahome.com</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>+86 (0) 757 8558 9299</t>
+          <t>+86 1882 9964 960, +86 1343 2639 580</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>www.ideal-sanitary.com</t>
+          <t>www.ciarrahome.com</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>No.3 Hexi Road of Shashui, Yanghe Town, Gaoming District, Foshan City, Guangdong Province, 528515 - P.R.China.</t>
+          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
@@ -5101,7 +5217,7 @@
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 500$ 100psc</t>
+          <t>Buyer: 300¥ 300pcs</t>
         </is>
       </c>
     </row>
@@ -5109,30 +5225,30 @@
       <c r="A122" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="2" t="inlineStr"/>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Yekalon Mills</t>
+        </is>
+      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Viola Liu</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>victor@ck-bath.com</t>
+          <t>wood6@sennorwell.com</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>18656330093</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>https://ck-bath.com/</t>
-        </is>
-      </c>
+          <t>(86) 158 8931 1832</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
+          <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -5142,7 +5258,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 4500¥</t>
+          <t>Buyer: 50¥ 1000pcs</t>
         </is>
       </c>
     </row>
@@ -5150,40 +5266,44 @@
       <c r="A123" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="3" t="inlineStr"/>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Ideal Sanitary Ware Co., Ltd.</t>
+        </is>
+      </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>刘朔雅 Gigi</t>
+          <t>Amy Liu 刘建美</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>004@cgchcontainer.com</t>
+          <t>export@ideal-china.net</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>+86 189 2997 1101</t>
+          <t>+86 (0) 757 8558 9299</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>www.cgchcontainer.com</t>
+          <t>www.ideal-sanitary.com</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+          <t>No.3 Hexi Road of Shashui, Yanghe Town, Gaoming District, Foshan City, Guangdong Province, 528515 - P.R.China.</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 8790$</t>
+          <t>Buyer: 500$ 100psc</t>
         </is>
       </c>
     </row>
@@ -5191,36 +5311,44 @@
       <c r="A124" s="2" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="2" t="inlineStr"/>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd.</t>
+        </is>
+      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>朱友群</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr"/>
+          <t>Anne</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>victor@ck-bath.com</t>
+        </is>
+      </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>13763963598</t>
+          <t>18656330093</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>www.hx-wpc.com</t>
+          <t>https://ck-bath.com/</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>江西省瑞金市经济开发区创业一路东侧</t>
+          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 250¥/m3</t>
+          <t>Buyer: 4500¥</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5356,11 @@
       <c r="A125" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="3" t="inlineStr"/>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>佛山市旌晨铝门窗有限公司</t>
+        </is>
+      </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
           <t>胡光辉</t>
@@ -5252,7 +5384,7 @@
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
@@ -5265,7 +5397,11 @@
       <c r="A126" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="2" t="inlineStr"/>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>佛山市乾泽科技有限公司</t>
+        </is>
+      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>陈可樑</t>
@@ -5293,7 +5429,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -5306,26 +5442,18 @@
       <c r="A127" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="3" t="inlineStr"/>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>ARTY 艺和</t>
+        </is>
+      </c>
       <c r="C127" s="3" t="inlineStr"/>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>info@sunhohiglobal.com</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>+86-137 0262 5097, +86-139 2779 1971</t>
-        </is>
-      </c>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sunhohiglobal.com/</t>
-        </is>
-      </c>
+      <c r="D127" s="3" t="inlineStr"/>
+      <c r="E127" s="3" t="inlineStr"/>
+      <c r="F127" s="3" t="inlineStr"/>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>Marketing Center: R&amp;F International Financial Center, Nanhai District, Foshan City, Guangdong Province, China; Factory: Zhenxing 3rd Road, Xincheng Town, Xinxing County, Yunfu City, Guangdong Province, China</t>
+          <t>广东 · 开平</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr">
@@ -5335,7 +5463,7 @@
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1p, 10000$m2, very beautiful big red door</t>
+          <t>Buyer: Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
         </is>
       </c>
     </row>
@@ -5343,32 +5471,16 @@
       <c r="A128" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="2" t="inlineStr"/>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Cathy Dai (代桂菊)</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>cathy@hnbeidi.com</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>+86 151 3737 2072</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>www.baydeegroup.com, www.hnbeidi.com</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>中国 河南省鹤壁市 (Hebi City, Henan Province, China)</t>
-        </is>
-      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>SUNHOHI 新豪轩门窗</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr"/>
+      <c r="D128" s="2" t="inlineStr"/>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5376,7 +5488,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1 container (400 square meters), 60 dollars for 1 square meters</t>
+          <t>Buyer: Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
         </is>
       </c>
     </row>
@@ -5384,22 +5496,26 @@
       <c r="A129" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="3" t="inlineStr"/>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>景德镇窑珍陶瓷</t>
+        </is>
+      </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>叶韵怡</t>
+          <t>徐云霞</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr"/>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>13726080225</t>
+          <t>13697981203</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr"/>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
+          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
@@ -5409,7 +5525,7 @@
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Moq is 1 door, 530 RMB for 1 door</t>
+          <t>Buyer: 100 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -5417,30 +5533,26 @@
       <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="2" t="inlineStr"/>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>李旭文 Nigel</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>006@cgchcontainer.com</t>
-        </is>
-      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>苏州东山茶厂 (Suzhou Dongshan Biluochun Tea Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr"/>
+      <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>+86 138 2231 8296</t>
+          <t>0512-66281146</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>www.cgchcontainer.com</t>
+          <t>www.dsteaf.com</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+          <t>江苏省苏州市吴中区东山镇 (Dongshan Town, Wuzhong District, Suzhou City)</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -5450,7 +5562,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 14400 dollars, moq - 1</t>
+          <t>Buyer: 150 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -5458,28 +5570,16 @@
       <c r="A131" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="3" t="inlineStr"/>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>张广帅</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>1525423805@qq.com</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>13726358587</t>
-        </is>
-      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>武夷星</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr"/>
+      <c r="D131" s="3" t="inlineStr"/>
+      <c r="E131" s="3" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr"/>
-      <c r="G131" s="3" t="inlineStr">
-        <is>
-          <t>佛山市狮山镇谭边工业区顺岗头路四号之一</t>
-        </is>
-      </c>
+      <c r="G131" s="3" t="inlineStr"/>
       <c r="H131" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5487,7 +5587,7 @@
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
+          <t>Buyer: 250 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -5495,24 +5595,16 @@
       <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="2" t="inlineStr"/>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>徐云霞</t>
-        </is>
-      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>湖北龙王垭茶业有限公司</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr"/>
       <c r="D132" s="2" t="inlineStr"/>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>13697981203</t>
-        </is>
-      </c>
+      <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
-        </is>
-      </c>
+      <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5520,7 +5612,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 100 RMB per sample. The taste is very good</t>
+          <t>Buyer: 498rmb/unit. I like the green tea in white color. First time to see colorless tea and it was amazing, i will recommend it to my country’s local market.</t>
         </is>
       </c>
     </row>
@@ -5528,22 +5620,22 @@
       <c r="A133" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="3" t="inlineStr"/>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>知和香馆</t>
+        </is>
+      </c>
       <c r="C133" s="3" t="inlineStr"/>
       <c r="D133" s="3" t="inlineStr"/>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>0512-66281146</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>www.dsteaf.com</t>
-        </is>
-      </c>
+          <t>15926183211</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr"/>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区东山镇 (Dongshan Town, Wuzhong District, Suzhou City)</t>
+          <t>福建永春达埔</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
@@ -5553,7 +5645,7 @@
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 150 RMB per sample. The taste is very good</t>
+          <t>Buyer: They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
         </is>
       </c>
     </row>
@@ -5561,18 +5653,34 @@
       <c r="A134" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="2" t="inlineStr"/>
-      <c r="C134" s="2" t="inlineStr"/>
-      <c r="D134" s="2" t="inlineStr"/>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>San Nora (聖羅蘭·衛浴)</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>ALLEN XU (许熙平)</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>sales@sannora.com</t>
+        </is>
+      </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>15926183211</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr"/>
+          <t>+86 137 0263 0244, +86-757-86438259</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>WWW.SANNORA.COM, WWW.SANNORA-BATH.COM</t>
+        </is>
+      </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>福建永春达埔</t>
+          <t>TANBIAN IND. ZONE, SHISHAN TOWN, NANHAI DIST., FOSHAN, GUANGDONG, CHINA</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -5582,7 +5690,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Buyer: They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
+          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -5590,15 +5698,31 @@
       <c r="A135" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="3" t="inlineStr"/>
-      <c r="C135" s="3" t="inlineStr"/>
-      <c r="D135" s="3" t="inlineStr"/>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>PTAT | 帕兰蒂诺</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Joy Yang</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>joy@rans.group</t>
+        </is>
+      </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>15926183211</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr"/>
+          <t>+86-13757430301</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>www.ptat.cn</t>
+        </is>
+      </c>
       <c r="G135" s="3" t="inlineStr"/>
       <c r="H135" s="3" t="inlineStr">
         <is>
@@ -5607,7 +5731,7 @@
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>Buyer: The 中国好水 brand water was really good. They are using deep water instead of shallow water (used by nongfu), and trace minerals are also added which makes its pH 7.5 which is good salty water. Overall i am impressed by their health committed approach.</t>
+          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -5615,30 +5739,30 @@
       <c r="A136" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="2" t="inlineStr"/>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>万磊建筑涂料有限公司</t>
+        </is>
+      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>ALLEN XU (许熙平)</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>sales@sannora.com</t>
-        </is>
-      </c>
+          <t>万磊市场部</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>+86 137 0263 0244, +86-757-86438259</t>
+          <t>186-8825-1404, 4000-147-187</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>WWW.SANNORA.COM, WWW.SANNORA-BATH.COM</t>
+          <t>http://www.fswanlei.com</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>TANBIAN IND. ZONE, SHISHAN TOWN, NANHAI DIST., FOSHAN, GUANGDONG, CHINA</t>
+          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -5656,28 +5780,36 @@
       <c r="A137" s="3" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="3" t="inlineStr"/>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>ZHEJIANG SEATING TECHNOLOGY CO., LTD.</t>
+        </is>
+      </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Joy Yang</t>
+          <t>May Zhang</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>joy@rans.group</t>
+          <t>sales5@anjeurostilefurniture.com</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>+86-13757430301</t>
+          <t>+86 182 5727 1590</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>www.ptat.cn</t>
-        </is>
-      </c>
-      <c r="G137" s="3" t="inlineStr"/>
+          <t>www.zjseating.com</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
+        </is>
+      </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5685,7 +5817,7 @@
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>Buyer: 1100</t>
         </is>
       </c>
     </row>
@@ -5693,36 +5825,44 @@
       <c r="A138" s="2" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="2" t="inlineStr"/>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Chaozhou Lefu Sanitary Ware Technology Co., Ltd.</t>
+        </is>
+      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>万磊市场部</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr"/>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>lucy@lefucz.com</t>
+        </is>
+      </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>186-8825-1404, 4000-147-187</t>
+          <t>+0086 18098114370</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>http://www.fswanlei.com</t>
+          <t>www.lefucz.com</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区</t>
+          <t>Lefu Sanitary Ware, Sheweikeng, Dengtang Town, Chaoan District, Chaozhou City, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>Buyer: 1050</t>
         </is>
       </c>
     </row>
@@ -5730,32 +5870,16 @@
       <c r="A139" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="3" t="inlineStr"/>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>May Zhang</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>sales5@anjeurostilefurniture.com</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>+86 182 5727 1590</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="inlineStr">
-        <is>
-          <t>www.zjseating.com</t>
-        </is>
-      </c>
-      <c r="G139" s="3" t="inlineStr">
-        <is>
-          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
-        </is>
-      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>宜昌毛尖</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr"/>
+      <c r="D139" s="3" t="inlineStr"/>
+      <c r="E139" s="3" t="inlineStr"/>
+      <c r="F139" s="3" t="inlineStr"/>
+      <c r="G139" s="3" t="inlineStr"/>
       <c r="H139" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5763,7 +5887,7 @@
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1100</t>
+          <t>Buyer: Prices are go and packing and Verstaliy is more</t>
         </is>
       </c>
     </row>
@@ -5771,32 +5895,16 @@
       <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="2" t="inlineStr"/>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>lucy@lefucz.com</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>+0086 18098114370</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>www.lefucz.com</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>Lefu Sanitary Ware, Sheweikeng, Dengtang Town, Chaoan District, Chaozhou City, Guangdong Province, China</t>
-        </is>
-      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>湖北龙王娅茶业有限公司</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr"/>
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5804,7 +5912,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1050</t>
+          <t>Buyer: The taste anaroma is good of this product then anyother</t>
         </is>
       </c>
     </row>
@@ -5812,28 +5920,16 @@
       <c r="A141" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="3" t="inlineStr"/>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>胡沛能 / Oliver Hu</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>oliver@wireking.com</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>+86-13802465791</t>
-        </is>
-      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>正山堂 (ZHENG SHAN TANG)</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr"/>
+      <c r="D141" s="3" t="inlineStr"/>
+      <c r="E141" s="3" t="inlineStr"/>
       <c r="F141" s="3" t="inlineStr"/>
-      <c r="G141" s="3" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
-        </is>
-      </c>
+      <c r="G141" s="3" t="inlineStr"/>
       <c r="H141" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5841,7 +5937,7 @@
       </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 550</t>
+          <t>Buyer: the product prices are very good. looks attractive</t>
         </is>
       </c>
     </row>
@@ -5849,24 +5945,32 @@
       <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="2" t="inlineStr"/>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>江西荣科新型建材有限公司 (JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.)</t>
+        </is>
+      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>蒙玉婷</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr"/>
+          <t>Lucy Zeng (曾露)</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>lucy@rongkedecor.com</t>
+        </is>
+      </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>13160953218 / 400-8339513</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区龙江镇联塑工业园三路3号9513家具总部</t>
-        </is>
-      </c>
+          <t>+86-13134020034</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amerdecor.com/</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5874,7 +5978,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 820 rmb moq 100</t>
+          <t>Buyer: 650 moq 300</t>
         </is>
       </c>
     </row>
@@ -5882,28 +5986,32 @@
       <c r="A143" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="3" t="inlineStr"/>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>Lucy Zeng (曾露)</t>
-        </is>
-      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>浙江雅柔装饰材料有限公司 (Zhejiang Yarou Decoration Material Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr"/>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>lucy@rongkedecor.com</t>
+          <t>sale01@yarouwallpaper.com.cn</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>+86-13134020034</t>
+          <t>+86-18069994326, +86-18069994377</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>https://www.amerdecor.com/</t>
-        </is>
-      </c>
-      <c r="G143" s="3" t="inlineStr"/>
+          <t>https://www.yarouwallpaper.com.cn/</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>浙江省金华市义乌市福田街道涌金大道87号厂房二楼 (No. 1, Factory 2, Yongjin Avenue 87, Futian Subdistrict, Yiwu City, Jinhua City, Zhejiang Province)</t>
+        </is>
+      </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5911,7 +6019,7 @@
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 650 moq 300</t>
+          <t>Buyer: 14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
         </is>
       </c>
     </row>
@@ -5919,40 +6027,36 @@
       <c r="A144" s="2" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="2" t="inlineStr"/>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>淄博永顺装饰材料有限公司</t>
+        </is>
+      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Pacao Yin</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>pin@pingaolao.com</t>
-        </is>
-      </c>
+          <t>戴艳辉</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr"/>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>(0086)0769-86378283, (0086)13903035682</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
-        </is>
-      </c>
+          <t>18830173388</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+          <t>石家庄市正定县曙光路49号东标和聚居</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 2.5 RMB per unit, MOQ is 500 pieces. The plastic material was high quality and company was willing to provide samples on need.</t>
+          <t>Buyer: 0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
         </is>
       </c>
     </row>
@@ -5960,26 +6064,34 @@
       <c r="A145" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="3" t="inlineStr"/>
-      <c r="C145" s="3" t="inlineStr"/>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>宏宇集团 (HONGYU GROUP)</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Melina 王玲</t>
+        </is>
+      </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>sale01@yarouwallpaper.com.cn</t>
+          <t>lina@hongyugroup.com</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>+86-18069994326, +86-18069994377</t>
+          <t>+86 13827702216</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>https://www.yarouwallpaper.com.cn/</t>
+          <t>en.hongyugroup.com</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市福田街道涌金大道87号厂房二楼 (No. 1, Factory 2, Yongjin Avenue 87, Futian Subdistrict, Yiwu City, Jinhua City, Zhejiang Province)</t>
+          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
@@ -5989,7 +6101,7 @@
       </c>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
+          <t>Buyer: 20</t>
         </is>
       </c>
     </row>
@@ -5997,22 +6109,34 @@
       <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="2" t="inlineStr"/>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Chongnuo(Shandong)NewMaterial Co.,Ltd.</t>
+        </is>
+      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>戴艳辉</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr"/>
+          <t>Daisy</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>sales06@chongnuo-floors.com</t>
+        </is>
+      </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>18830173388</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr"/>
+          <t>+86 19906379675</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>www.chongnuo-floors.com</t>
+        </is>
+      </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>石家庄市正定县曙光路49号东标和聚居</t>
+          <t>QingyunCounty,DezhouCity,China</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -6022,7 +6146,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
+          <t>Buyer: 9$</t>
         </is>
       </c>
     </row>
@@ -6030,24 +6154,28 @@
       <c r="A147" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="3" t="inlineStr"/>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>上海德翔木业有限公司 (Shanghai Dexiang Wood Industry Co., Ltd.)</t>
+        </is>
+      </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>肖汶兰</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr"/>
+          <t>崔强 (Cui Qiang)</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>513437660@qq.com</t>
+        </is>
+      </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>18675197017, 400-8339513</t>
+          <t>+8618901960431</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr"/>
-      <c r="G147" s="3" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
-        </is>
-      </c>
+      <c r="G147" s="3" t="inlineStr"/>
       <c r="H147" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -6055,7 +6183,7 @@
       </c>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1299, MOQ 200. I like the company and people there . Very friendly and know their products very good . I would be happy to cooperate with them in the future ,to buy their products</t>
+          <t>Buyer: 13.25$</t>
         </is>
       </c>
     </row>
@@ -6063,30 +6191,30 @@
       <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="2" t="inlineStr"/>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>中材(邯郸)新材料有限公司 (China National Building Materials (Handan) New Materials Co.,Ltd.)</t>
+        </is>
+      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Abby Li</t>
+          <t>Wangfeng</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>abbyli@sofeyiahome.com</t>
+          <t>2523911877@qq.com</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>+ 86 18029769660</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofeyiahome.com</t>
-        </is>
-      </c>
+          <t>13233648687</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
+          <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -6096,7 +6224,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 5000rmb MOQ 50</t>
+          <t>Buyer: 8.83$</t>
         </is>
       </c>
     </row>
@@ -6104,26 +6232,22 @@
       <c r="A149" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="3" t="inlineStr"/>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Zhejiang Tianyan Holding Ltd</t>
+        </is>
+      </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Karl Lai</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>laisheng_352m@163.com</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>15073995010</t>
-        </is>
-      </c>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr"/>
+      <c r="E149" s="3" t="inlineStr"/>
       <c r="F149" s="3" t="inlineStr"/>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>Showroom&amp;Office: Nanke Village Section, Expo Boulevard Avenue, Houjie Town, Dongguan City, Guangdong Province; Factory add: Building #25, Wanyang Zhongchuang Centre, Xinghong Town, Qingyuan City, Guangdong Province</t>
+          <t>Taizhou, Zhejiang</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
@@ -6133,7 +6257,7 @@
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1500 rmb MOQ 100</t>
+          <t>Buyer: 640 PCs, 3.72 RMB very good</t>
         </is>
       </c>
     </row>
@@ -6141,36 +6265,40 @@
       <c r="A150" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="2" t="inlineStr"/>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>冯晶晶 Joanna</t>
-        </is>
-      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Foshan Cofesu Sanitary Ware Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr"/>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>sales06@cn-xindong.com</t>
+          <t>sales@cofesu.com</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>0086-159 9067 6107 / 0086-576-87499008</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr"/>
+          <t>+86 181 2821 2128</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>www.cofesu.com</t>
+        </is>
+      </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
+          <t>Foshan, Guangdong, China</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Black matt tap water $20</t>
+          <t>Buyer: 30 PCs, 420 RMB, need check quality</t>
         </is>
       </c>
     </row>
@@ -6178,40 +6306,40 @@
       <c r="A151" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="3" t="inlineStr"/>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>中国广东柜邦精密金属制品有限公司 (China Guangdong Guibang Precision Metal Products Co.Ltd)</t>
+        </is>
+      </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Melina 王玲</t>
+          <t>唐一智 (JUNIOR)</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>lina@hongyugroup.com</t>
+          <t>13621417@qq.com</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>+86 13827702216</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t>en.hongyugroup.com</t>
-        </is>
-      </c>
+          <t>+86-156-2562-1155</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr"/>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
+          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 20</t>
+          <t>Buyer: 10000</t>
         </is>
       </c>
     </row>
@@ -6219,40 +6347,40 @@
       <c r="A152" s="2" t="n">
         <v>151</v>
       </c>
-      <c r="B152" s="2" t="inlineStr"/>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Jieyang Yagegu Hardware Products Co., LTD</t>
+        </is>
+      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Daisy</t>
+          <t>Zoya</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>sales06@chongnuo-floors.com</t>
+          <t>2291828903@qq.com</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>+86 19906379675</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>www.chongnuo-floors.com</t>
-        </is>
-      </c>
+          <t>+86 132 8810 6615</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>QingyunCounty,DezhouCity,China</t>
+          <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 9$</t>
+          <t>Buyer: 10000</t>
         </is>
       </c>
     </row>
@@ -6260,32 +6388,40 @@
       <c r="A153" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="3" t="inlineStr"/>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>广东启宏盛精密五金制品有限公司 (GUANGDONG QIHONGSHENG PRECISION HARDWARE PRODUCTS CO., LTD)</t>
+        </is>
+      </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>崔强 (Cui Qiang)</t>
+          <t>邓美君 Jessica</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>513437660@qq.com</t>
+          <t>bailide_hinge@163.com</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>+8618901960431</t>
+          <t>+86 13823419116 / 0758-8565117</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr"/>
-      <c r="G153" s="3" t="inlineStr"/>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
+        </is>
+      </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 13.25$</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -6293,36 +6429,44 @@
       <c r="A154" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="2" t="inlineStr"/>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>广东亚当斯金属精密制造有限公司 (Guangdong Adams Metal Precision Manufacturing Co.,Ltd)</t>
+        </is>
+      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Wangfeng</t>
+          <t>Kelly Liang (梁凯莹)</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>2523911877@qq.com</t>
+          <t>kelly@adamsmetal.com.cn</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>13233648687</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr"/>
+          <t>+86-180-2935-2895 / +86-757-25331912</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>www.adamsmetal.com.cn</t>
+        </is>
+      </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
+          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 8.83$</t>
+          <t>Buyer: Depend on item</t>
         </is>
       </c>
     </row>
@@ -6330,36 +6474,28 @@
       <c r="A155" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="3" t="inlineStr"/>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>明德 (Mingde)</t>
+        </is>
+      </c>
       <c r="C155" s="3" t="inlineStr"/>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>sales@cofesu.com</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>+86 181 2821 2128</t>
-        </is>
-      </c>
+      <c r="D155" s="3" t="inlineStr"/>
+      <c r="E155" s="3" t="inlineStr"/>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>www.cofesu.com</t>
-        </is>
-      </c>
-      <c r="G155" s="3" t="inlineStr">
-        <is>
-          <t>Foshan, Guangdong, China</t>
-        </is>
-      </c>
+          <t>www.mingde-china.com</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr"/>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 30 PCs, 420 RMB, need check quality</t>
+          <t>Buyer: Depend of quantity</t>
         </is>
       </c>
     </row>
@@ -6367,36 +6503,44 @@
       <c r="A156" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="2" t="inlineStr"/>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>佛山市顺德区腾徽精密智造有限公司 (FoShan ShunDe TengHui Precision Intelligent Manufacturing Co., Ltd)</t>
+        </is>
+      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>唐一智 (JUNIOR)</t>
+          <t>刘婉莹 Carol Liu</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>13621417@qq.com</t>
+          <t>tenghuihardware@126.com</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>+86-156-2562-1155</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr"/>
+          <t>+86 133 1836 4599</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>www.teehve.cn</t>
+        </is>
+      </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
+          <t>广东省佛山市顺德区勒流街道众涌村港口路以西8-9号之二 (No.8-9, West of GangKou Road, Zhongchong Village, Leliu Town, Shunde District, Foshan City, Guangdong, China)</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 10000</t>
+          <t>Buyer: 100/square meter</t>
         </is>
       </c>
     </row>
@@ -6404,26 +6548,34 @@
       <c r="A157" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="3" t="inlineStr"/>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>DUOCAI TENT (多彩帐蓬)</t>
+        </is>
+      </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Zoya</t>
+          <t>Jimmy 黄锦民</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>2291828903@qq.com</t>
+          <t>sales003@sdduocaizp.com</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>+86 132 8810 6615</t>
-        </is>
-      </c>
-      <c r="F157" s="3" t="inlineStr"/>
+          <t>(86)133 2294 8506, +86-766-8298662</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>www.dc-tent.com, www.sdduocaizp.com</t>
+        </is>
+      </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
+          <t>云浮市云安区佛山(云浮)产业转移工业园86号 (No.86 Foshan(Yunfu) Industrial transfer park, yunan, yunfu, Guangdong China)</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
@@ -6433,7 +6585,7 @@
       </c>
       <c r="I157" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 10000</t>
+          <t>Buyer: RMB 15705 MOQ5; pleasant impression</t>
         </is>
       </c>
     </row>
@@ -6441,36 +6593,44 @@
       <c r="A158" s="2" t="n">
         <v>157</v>
       </c>
-      <c r="B158" s="2" t="inlineStr"/>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>佛山市路乐户外制品有限公司 (FOSHAN RULER OUTDOOR HARDWARES CO.,LTD)</t>
+        </is>
+      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>邓美君 Jessica</t>
+          <t>Marco Lau (刘嘉乐)</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>bailide_hinge@163.com</t>
+          <t>RULERAWNING07@163.COM</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>+86 13823419116 / 0758-8565117</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr"/>
+          <t>+86 13129016338</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>WWW.RULER-AWNING.COM</t>
+        </is>
+      </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
+          <t>END OF ROAD SHATANXIAN, SHASHUI INDUSTRIAL ZONE, SONGGANG TOWN, SHISHAN DISTRICT, FOSHAN CITY, GUANGDONG PROVINCE, CHINA, 528200</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 100</t>
+          <t>Buyer: MOQ5 25799 RMB</t>
         </is>
       </c>
     </row>
@@ -6478,40 +6638,44 @@
       <c r="A159" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="B159" s="3" t="inlineStr"/>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>Avant Sports Industrial Co., Ltd.</t>
+        </is>
+      </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Kelly Liang (梁凯莹)</t>
+          <t>Jay Zhou</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>kelly@adamsmetal.com.cn</t>
+          <t>jay@avant.com.cn</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>+86-180-2935-2895 / +86-757-25331912</t>
+          <t>+86-13128980150, +86-755-2968-8357</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>www.adamsmetal.com.cn</t>
+          <t>www.avantseating.com</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
+          <t>Avant Industrial Park, Zhoushi Road, Bao'an, Shenzhen, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Depend on item</t>
+          <t>Buyer: RMB 19479; MOQ 1</t>
         </is>
       </c>
     </row>
@@ -6519,30 +6683,34 @@
       <c r="A160" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="B160" s="2" t="inlineStr"/>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd.)</t>
+        </is>
+      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>刘婉莹 Carol Liu</t>
+          <t>孟少美 (Elite Meng)</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>tenghuihardware@126.com</t>
+          <t>ttf@hbtfjs.com</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>+86 133 1836 4599</t>
+          <t>+86-13103196326</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>www.teehve.cn</t>
+          <t>www.hbtfjs.com</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区勒流街道众涌村港口路以西8-9号之二 (No.8-9, West of GangKou Road, Zhongchong Village, Leliu Town, Shunde District, Foshan City, Guangdong, China)</t>
+          <t>河北省隆尧县东谷子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -6552,7 +6720,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 100/square meter</t>
+          <t>Buyer: 1000</t>
         </is>
       </c>
     </row>
@@ -6560,40 +6728,44 @@
       <c r="A161" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="B161" s="3" t="inlineStr"/>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>揭阳市新骏业五金制品有限公司 (JIEYANG XINJUNYE HARDWARE PRODUCTS CO., LTD)</t>
+        </is>
+      </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Jimmy 黄锦民</t>
+          <t>林树丹 (Lin Shudan)</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>sales003@sdduocaizp.com</t>
+          <t>linshdong@qq.com</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>(86)133 2294 8506, +86-766-8298662</t>
+          <t>13751676456</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>www.dc-tent.com, www.sdduocaizp.com</t>
+          <t>www.xinjunye.com</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>云浮市云安区佛山(云浮)产业转移工业园86号 (No.86 Foshan(Yunfu) Industrial transfer park, yunan, yunfu, Guangdong China)</t>
+          <t>广东省揭阳市揭东区锡场工业区 (Xichang Industrial Zone, Jiedong District, Jieyang City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
         <is>
-          <t>Buyer: RMB 15705 MOQ5; pleasant impression</t>
+          <t>Buyer: 1000</t>
         </is>
       </c>
     </row>
@@ -6601,30 +6773,34 @@
       <c r="A162" s="2" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="2" t="inlineStr"/>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Guangdong Adams Metal Precision Manufacturing Co., Ltd (广东亚当斯金属精密制造有限公司)</t>
+        </is>
+      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Marco Lau (刘嘉乐)</t>
+          <t>Kelly Liang (梁凯莹)</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>RULERAWNING07@163.COM</t>
+          <t>kelly@adamsmetal.com.cn</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>+86 13129016338</t>
+          <t>+86-180-2935-2895, +86-757-25331912</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>WWW.RULER-AWNING.COM</t>
+          <t>www.adamsmetal.com.cn</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>END OF ROAD SHATANXIAN, SHASHUI INDUSTRIAL ZONE, SONGGANG TOWN, SHISHAN DISTRICT, FOSHAN CITY, GUANGDONG PROVINCE, CHINA, 528200</t>
+          <t>No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province (广东省佛山市顺德区勒流镇港口路10号)</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -6634,7 +6810,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ5 25799 RMB</t>
+          <t>Buyer: 1000</t>
         </is>
       </c>
     </row>
@@ -6642,40 +6818,44 @@
       <c r="A163" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="B163" s="3" t="inlineStr"/>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>广州蒙娜丽莎控股集团有限公司 / 广州蒙娜丽莎卫浴股份有限公司</t>
+        </is>
+      </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Jay Zhou</t>
+          <t>伍乐彤</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>jay@avant.com.cn</t>
+          <t>monalisa702@monalisa.cn</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>+86-13128980150, +86-755-2968-8357</t>
+          <t>86 13711117863, 400 020 1818, 86 20-28607722, 86 20-28607788</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>www.avantseating.com</t>
+          <t>www.monalisa.cn</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>Avant Industrial Park, Zhoushi Road, Bao'an, Shenzhen, Guangdong Province, China</t>
+          <t>广州市花都区花东镇港头工业区4号</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
         <is>
-          <t>Buyer: RMB 19479; MOQ 1</t>
+          <t>Buyer: 2000$, can be customized, very convenient</t>
         </is>
       </c>
     </row>
@@ -6683,30 +6863,34 @@
       <c r="A164" s="2" t="n">
         <v>163</v>
       </c>
-      <c r="B164" s="2" t="inlineStr"/>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>中山藝進不銹鋼裝飾制品有限公司 (ZHONGSHAN YIJIN STAINLESS STEEL DECORATION CO., LTD.)</t>
+        </is>
+      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>孟少美 (Elite Meng)</t>
+          <t>Anson Yuen</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>ttf@hbtfjs.com</t>
+          <t>info@hugemount.com</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>+86-13103196326</t>
+          <t>150 1954 6322 / 86-760-88702663</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>www.hbtfjs.com</t>
+          <t>www.yijin.com</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>河北省隆尧县东谷子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
+          <t>中国广东省中山市港口镇石特社区穗安工业区迎富2路1号 (NO.1, Ying Fu 2 Road, Sui An Gong Ye Qu, Gang Kou Zhen Shi Te She Qu, Zhongshan City, Guangdong Province, P.R.China)</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -6716,7 +6900,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1000</t>
+          <t>Buyer: 38$, very unique</t>
         </is>
       </c>
     </row>
@@ -6724,40 +6908,44 @@
       <c r="A165" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="3" t="inlineStr"/>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>宣城市宠爱卫浴有限公司 (CHONGAI SANITARY WARE CO., LTD.)</t>
+        </is>
+      </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>林树丹 (Lin Shudan)</t>
+          <t>Lucy (卢美珍)</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>linshdong@qq.com</t>
+          <t>export@vnsmilo.com</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>13751676456</t>
+          <t>+86-13757322119</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>www.xinjunye.com</t>
+          <t>www.vnsmilo.com</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>广东省揭阳市揭东区锡场工业区 (Xichang Industrial Zone, Jiedong District, Jieyang City, Guangdong Province)</t>
+          <t>Xuancheng City Anhui, CHINA</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1000</t>
+          <t>Buyer: 2050 rmb, very interesting, convenient to use for pets</t>
         </is>
       </c>
     </row>
@@ -6765,32 +6953,24 @@
       <c r="A166" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="2" t="inlineStr"/>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>广西中晨木业有限公司 (Guangxi Zhongchen Wood Industry Co., Ltd.)</t>
+        </is>
+      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Kelly Liang (梁凯莹)</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>kelly@adamsmetal.com.cn</t>
-        </is>
-      </c>
+          <t>张爱彬 (Zhang Aibin)</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr"/>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>+86-180-2935-2895, +86-757-25331912</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>www.adamsmetal.com.cn</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province (广东省佛山市顺德区勒流镇港口路10号)</t>
-        </is>
-      </c>
+          <t>+86 18178085851</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -6798,7 +6978,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1000</t>
+          <t>Buyer: 25 rmb, 1 box, like this product</t>
         </is>
       </c>
     </row>
@@ -6806,30 +6986,34 @@
       <c r="A167" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="3" t="inlineStr"/>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>NINGBO YUSHENG HOME TECH CO., LTD. (宁波裕盛家居科技有限公司)</t>
+        </is>
+      </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>伍乐彤</t>
+          <t>Tequila Xu (徐孟杰)</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>monalisa702@monalisa.cn</t>
+          <t>marketing@cxyushun.com, tequila8xu@gmail.com</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>86 13711117863, 400 020 1818, 86 20-28607722, 86 20-28607788</t>
+          <t>0086-13819449988, +86 574 63190388</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>www.monalisa.cn</t>
+          <t>www.cxys8.com</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>广州市花都区花东镇港头工业区4号</t>
+          <t>中国浙江慈溪市杨梅大道南路1518号 (NO.1518, YANGMEI AVENUE SOUTH ROAD, CIXI CITY, ZHEJIANG, CHINA)</t>
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr">
@@ -6839,7 +7023,7 @@
       </c>
       <c r="I167" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 2000$, can be customized, very convenient</t>
+          <t>Buyer: 34 rmb, 1000, normal</t>
         </is>
       </c>
     </row>
@@ -6847,40 +7031,44 @@
       <c r="A168" s="2" t="n">
         <v>167</v>
       </c>
-      <c r="B168" s="2" t="inlineStr"/>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>河北建华锁业有限公司 (Hebei Jianhua Lock Industry Co., Ltd.)</t>
+        </is>
+      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Anson Yuen</t>
+          <t>刘芳 (Jane Liu)</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>info@hugemount.com</t>
+          <t>jane@dirock.cn</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>150 1954 6322 / 86-760-88702663</t>
+          <t>187 1377 2087</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>www.yijin.com</t>
+          <t>http://www.dirock.cn</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>中国广东省中山市港口镇石特社区穗安工业区迎富2路1号 (NO.1, Ying Fu 2 Road, Sui An Gong Ye Qu, Gang Kou Zhen Shi Te She Qu, Zhongshan City, Guangdong Province, P.R.China)</t>
+          <t>河北省泊头市寺门村镇后牛屯</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 38$, very unique</t>
+          <t>Buyer: 40 rmb, 2000, very good</t>
         </is>
       </c>
     </row>
@@ -6888,30 +7076,34 @@
       <c r="A169" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="3" t="inlineStr"/>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>浙江安吉双虎竹木业有限公司 / 安吉诺迪新材料有限公司</t>
+        </is>
+      </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Lucy (卢美珍)</t>
+          <t>周瑶琳</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>export@vnsmilo.com</t>
+          <t>lisa.nordi@nuodibm.com</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>+86-13757322119</t>
+          <t>+86-137 3822 8209</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>www.vnsmilo.com</t>
+          <t>www.tigerbamboo.com / www.nuodibm.com</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>Xuancheng City Anhui, CHINA</t>
+          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
@@ -6921,7 +7113,7 @@
       </c>
       <c r="I169" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 2050 rmb, very interesting, convenient to use for pets</t>
+          <t>Buyer: 1 container 250 rmb</t>
         </is>
       </c>
     </row>
@@ -6929,20 +7121,36 @@
       <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
-      <c r="B170" s="2" t="inlineStr"/>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>宏宇集团 HONGYU GROUP</t>
+        </is>
+      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>张爱彬 (Zhang Aibin)</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr"/>
+          <t>Melina 王玲</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>lina@hongyugroup.com</t>
+        </is>
+      </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>+86 18178085851</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr"/>
-      <c r="G170" s="2" t="inlineStr"/>
+          <t>+86 13827702216</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>en.hongyugroup.com</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
+        </is>
+      </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -6950,7 +7158,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 25 rmb, 1 box, like this product</t>
+          <t>Buyer: Жду коммерческое предложение. Компания понравилась</t>
         </is>
       </c>
     </row>
@@ -6958,40 +7166,44 @@
       <c r="A171" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="B171" s="3" t="inlineStr"/>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>ZHEJIANG TIANYAN HOLDING CO.,LTD.</t>
+        </is>
+      </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Tequila Xu (徐孟杰)</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>marketing@cxyushun.com, tequila8xu@gmail.com</t>
+          <t>ty11@cntianyan.com</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>0086-13819449988, +86 574 63190388</t>
+          <t>+86-15867028552</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>www.cxys8.com</t>
+          <t>www.cntianyan.com</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>中国浙江慈溪市杨梅大道南路1518号 (NO.1518, YANGMEI AVENUE SOUTH ROAD, CIXI CITY, ZHEJIANG, CHINA)</t>
+          <t>Chengjiang industrial zone,huangyan district taizhou,zhejiang,china</t>
         </is>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 34 rmb, 1000, normal</t>
+          <t>Buyer: Цена зависит от обьема, от 3 юаней, расходники</t>
         </is>
       </c>
     </row>
@@ -6999,32 +7211,16 @@
       <c r="A172" s="2" t="n">
         <v>171</v>
       </c>
-      <c r="B172" s="2" t="inlineStr"/>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>刘芳 (Jane Liu)</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>jane@dirock.cn</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>187 1377 2087</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>http://www.dirock.cn</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>河北省泊头市寺门村镇后牛屯</t>
-        </is>
-      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>BANRUGE / KING LIYE</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr"/>
+      <c r="D172" s="2" t="inlineStr"/>
+      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -7032,205 +7228,12 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 40 rmb, 2000, very good</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="n">
-        <v>172</v>
-      </c>
-      <c r="B173" s="3" t="inlineStr"/>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>周瑶琳</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>lisa.nordi@nuodibm.com</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>+86-137 3822 8209</t>
-        </is>
-      </c>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t>www.tigerbamboo.com / www.nuodibm.com</t>
-        </is>
-      </c>
-      <c r="G173" s="3" t="inlineStr">
-        <is>
-          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
-        </is>
-      </c>
-      <c r="H173" s="3" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I173" s="3" t="inlineStr">
-        <is>
-          <t>Buyer: 1 container 250 rmb</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="n">
-        <v>173</v>
-      </c>
-      <c r="B174" s="2" t="inlineStr"/>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>张爱彬 (Zhang Aibin)</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr"/>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>+8618178085851</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr"/>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>Buyer: 1 container 500 rmb</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="B175" s="3" t="inlineStr"/>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>马世晓 (Amelia Ma)</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>tf@hbtfjs.com, mashixiaomsx@163.com</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>15097968589, 0319-6581195</t>
-        </is>
-      </c>
-      <c r="F175" s="3" t="inlineStr">
-        <is>
-          <t>www.hbtfjs.com</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="inlineStr">
-        <is>
-          <t>河北省隆尧县公子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
-        </is>
-      </c>
-      <c r="H175" s="3" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I175" s="3" t="inlineStr">
-        <is>
-          <t>Buyer: 1 container 700 rmb</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="n">
-        <v>175</v>
-      </c>
-      <c r="B176" s="2" t="inlineStr"/>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>Melina 王玲</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
-        <is>
-          <t>lina@hongyugroup.com</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>+86 13827702216</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>en.hongyugroup.com</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="inlineStr">
-        <is>
-          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
-        </is>
-      </c>
-      <c r="H176" s="2" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t>Buyer: Жду коммерческое предложение. Компания понравилась</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="B177" s="3" t="inlineStr"/>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>Nicole</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>ty11@cntianyan.com</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>+86-15867028552</t>
-        </is>
-      </c>
-      <c r="F177" s="3" t="inlineStr">
-        <is>
-          <t>www.cntianyan.com</t>
-        </is>
-      </c>
-      <c r="G177" s="3" t="inlineStr">
-        <is>
-          <t>Chengjiang industrial zone,huangyan district taizhou,zhejiang,china</t>
-        </is>
-      </c>
-      <c r="H177" s="3" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I177" s="3" t="inlineStr">
-        <is>
-          <t>Buyer: Цена зависит от обьема, от 3 юаней, расходники</t>
+          <t>Buyer: Прайс отправят, от 100ед, хорошая компания</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I177"/>
+  <autoFilter ref="A1:I172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CBD Suppliers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CBD Suppliers'!$A$1:$I$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CBD Suppliers'!$A$1:$I$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I172"/>
+  <dimension ref="A1:I171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -527,37 +527,37 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Sunhohi</t>
+          <t>Guangdong Fuson Windoor Industry Co., Ltd</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Crystal Wong</t>
+          <t>Eileen Yip (叶颖怡)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>crystal@sunhohiglobal.com</t>
+          <t>export09@fusonwindoor.com</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>+86-137 0262 5097</t>
+          <t>+86 18028156982</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>www.sunhohiwindow.com</t>
+          <t>www.fusonwindoor.com</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Marketing Center: 20th Floor, Building A1, Full International Financial Center, No. 28, Haiwu Road, Guicheng Street, Nanhai District, Foshan City, Guangdong Province, China; Factory: Zhenxing 3rd Road, Xincheng Town, Xinxing County, Yunfu City, Guangdong Province, China</t>
+          <t>Fuxuan Office Building, 2nd Longhu Rd, High Tech District, Zhaoqing City, Guangdong Province</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -572,34 +572,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Guangdong Fuson Windoor Industry Co., Ltd</t>
+          <t>开平艺和门业有限公司</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Eileen Yip (叶颖怡)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>export09@fusonwindoor.com</t>
-        </is>
-      </c>
+          <t>张硕怡 (Stoney)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>+86 18028156982</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>www.fusonwindoor.com</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Fuxuan Office Building, 2nd Longhu Rd, High Tech District, Zhaoqing City, Guangdong Province</t>
-        </is>
-      </c>
+          <t>134 1416 0636</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
@@ -617,30 +605,42 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>开平艺和门业有限公司</t>
+          <t>SUNHOHI Smart Home Co., Ltd</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>张硕怡 (Stoney)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>Crystal Wong 黄健秋</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>info@sunhohiglobal.com, crystalwindowsanddoors0908@gmail.com</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>134 1416 0636</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>0086-137 0262 5097, 0086-138 2396 7979</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>www.sunhohiwindow.com</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>R&amp;F International Financial Center, Nanhai District, Foshan City, Guangdong Province, China</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 50.000¥. Moq-1</t>
+          <t>Buyer: 1000 pcs price 120 usd</t>
         </is>
       </c>
     </row>
@@ -650,32 +650,32 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>SUNHOHI Smart Home Co., Ltd</t>
+          <t>河南贝迪塑业有限公司 (Henan Beidi Plastic Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Crystal Wong 黄健秋</t>
+          <t>Jane Li (李蓉娟)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>info@sunhohiglobal.com, crystalwindowsanddoors0908@gmail.com</t>
+          <t>Jane@hncrown.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0086-137 0262 5097, 0086-138 2396 7979</t>
+          <t>+86 187 3917 6242 / 86-0372-6270170</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>www.sunhohiwindow.com</t>
+          <t>www.baydeegroup.com / www.hnbeidi.com</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>R&amp;F International Financial Center, Nanhai District, Foshan City, Guangdong Province, China</t>
+          <t>中国·河南省鹤壁市 (Hebi City, Henan Province, China)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1000 pcs price 120 usd</t>
+          <t>Buyer: 1000 pcs price 38 USD</t>
         </is>
       </c>
     </row>
@@ -695,32 +695,32 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>河南贝迪塑业有限公司 (Henan Beidi Plastic Industry Co., Ltd.)</t>
+          <t>Guangzhou NewHoo Technology Co. Ltd</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Jane Li (李蓉娟)</t>
+          <t>Tony</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Jane@hncrown.com</t>
+          <t>export01@gznewhoo.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>+86 187 3917 6242 / 86-0372-6270170</t>
+          <t>+86-198-7837-3626</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>www.baydeegroup.com / www.hnbeidi.com</t>
+          <t>www.gznewhoo.com</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>中国·河南省鹤壁市 (Hebi City, Henan Province, China)</t>
+          <t>Building 7, Hongyu Smart Industrial Park, No. 333 Juhuashi Avenue, Huadu District, Guangzhou</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1000 pcs price 38 USD</t>
+          <t>Buyer: 80$</t>
         </is>
       </c>
     </row>
@@ -740,32 +740,16 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Guangzhou NewHoo Technology Co. Ltd</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Tony</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>export01@gznewhoo.com</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>+86-198-7837-3626</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>www.gznewhoo.com</t>
-        </is>
-      </c>
+          <t>旭博卫浴</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Building 7, Hongyu Smart Industrial Park, No. 333 Juhuashi Avenue, Huadu District, Guangzhou</t>
+          <t>福建省南安市</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -775,7 +759,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 80$</t>
+          <t>Buyer: 70$</t>
         </is>
       </c>
     </row>
@@ -785,18 +769,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>旭博卫浴</t>
+          <t>旭博恒温</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>福建省南安市</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -804,7 +784,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 70$</t>
+          <t>Buyer: 300 yuan</t>
         </is>
       </c>
     </row>
@@ -814,14 +794,34 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>旭博恒温</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+          <t>榜威电子科技（上海）有限公司 (Bweetech Electronics Technology (Shanghai) Co., Ltd)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>骆剑 (Kim Lok)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>kim.lok@bweetech.com</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>186-5759-0678</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>www.bweetech.com</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -829,7 +829,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 300 yuan</t>
+          <t>Buyer: 500pcs / $100USD for pcs</t>
         </is>
       </c>
     </row>
@@ -839,34 +839,14 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>榜威电子科技（上海）有限公司 (Bweetech Electronics Technology (Shanghai) Co., Ltd)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>骆剑 (Kim Lok)</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>kim.lok@bweetech.com</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>186-5759-0678</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>www.bweetech.com</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
-        </is>
-      </c>
+          <t>深圳市塞恩斯电子有限公司 (Sands Evermore Electronic)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -874,7 +854,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 500pcs / $100USD for pcs</t>
+          <t>Buyer: 50pcs / $50USD for pcs</t>
         </is>
       </c>
     </row>
@@ -884,7 +864,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>深圳市塞恩斯电子有限公司 (Sands Evermore Electronic)</t>
+          <t>HDL</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
@@ -899,7 +879,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 50pcs / $50USD for pcs</t>
+          <t>Buyer: 20pcs / $100USD for pcs</t>
         </is>
       </c>
     </row>
@@ -909,22 +889,38 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>HDL</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>DEIOUX WINDOWS &amp; DOORS</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>CANDICE CHOU</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>sales5@deiouxwindows.com</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>+86-13392246940</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 20pcs / $100USD for pcs</t>
+          <t>Buyer: Custom order</t>
         </is>
       </c>
     </row>
@@ -934,30 +930,30 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>DEIOUX WINDOWS &amp; DOORS</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>CANDICE CHOU</t>
-        </is>
-      </c>
+          <t>China Warren Windows and Doors Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>sales5@deiouxwindows.com</t>
+          <t>info@warrenwindows.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>+86-13392246940</t>
+          <t>+86-400-811-0300</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
+          <t>www.warrenwindows.com</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Room 1007, Block B, Wangjing SOHO, Chaoyang District, Beijing, China</t>
+        </is>
+      </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
@@ -975,33 +971,25 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>China Warren Windows and Doors Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>info@warrenwindows.com</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>+86-400-811-0300</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>www.warrenwindows.com</t>
-        </is>
-      </c>
+          <t>Matthew window&amp;door</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>张小洪 (Matthew / Kevin)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Room 1007, Block B, Wangjing SOHO, Chaoyang District, Beijing, China</t>
+          <t>Foshan, Guangdong</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1016,30 +1004,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Matthew window&amp;door</t>
+          <t>Zhongshan Smartek Security Technology Co.,LTD</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>张小洪 (Matthew / Kevin)</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
+          <t>Tim Pan</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>market@smarteklock.com</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>+86-15889896019</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>www.smarteklock.com</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Foshan, Guangdong</t>
+          <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City Guangdong, China 528415</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Custom order</t>
+          <t>Buyer: 170 to 335 usd</t>
         </is>
       </c>
     </row>
@@ -1049,42 +1049,38 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Zhongshan Smartek Security Technology Co.,LTD</t>
+          <t>HDL Automation Co., Ltd.</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Tim Pan</t>
+          <t>Krystal Wei</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>market@smarteklock.com</t>
+          <t>krystal@hdlautomation.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>+86-15889896019</t>
+          <t>+86 19512956186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>www.smarteklock.com</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City Guangdong, China 528415</t>
-        </is>
-      </c>
+          <t>www.hdlautomation.com</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 170 to 335 usd</t>
+          <t>Buyer: 100 to up</t>
         </is>
       </c>
     </row>
@@ -1094,38 +1090,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>HDL Automation Co., Ltd.</t>
+          <t>Ningbo AIFEIBAO Intelligent Security Co., Ltd</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Krystal Wei</t>
+          <t>Sean Xiao</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>krystal@hdlautomation.com</t>
+          <t>sales@aifeibao.com</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>+86 19512956186</t>
+          <t>0086 198 1730 8681</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>www.hdlautomation.com</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
+          <t>www.afbsafe.com</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>No.1 Donghu Rd., Daxie Development Zone, Ningbo, China (315812)</t>
+        </is>
+      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 100 to up</t>
+          <t>Buyer: 100 to up usd</t>
         </is>
       </c>
     </row>
@@ -1135,42 +1135,34 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Ningbo AIFEIBAO Intelligent Security Co., Ltd</t>
+          <t>佛山市普辉亚科技有限公司 (Foshan Pu Huiya Technology Co., Ltd.)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Sean Xiao</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>sales@aifeibao.com</t>
-        </is>
-      </c>
+          <t>邹隆鹏</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0086 198 1730 8681</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>www.afbsafe.com</t>
-        </is>
-      </c>
+          <t>15818099349</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>No.1 Donghu Rd., Daxie Development Zone, Ningbo, China (315812)</t>
+          <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 100 to up usd</t>
+          <t>Buyer: Super</t>
         </is>
       </c>
     </row>
@@ -1180,24 +1172,32 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>佛山市普辉亚科技有限公司 (Foshan Pu Huiya Technology Co., Ltd.)</t>
+          <t>广东招材建材科技有限公司</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>邹隆鹏</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr"/>
+          <t>黎桃桃</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>toto.liblun@gmail.com</t>
+        </is>
+      </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>15818099349</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr"/>
+          <t>+8618934320539</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>www.liblun.com</t>
+        </is>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
+          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1217,42 +1217,38 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>广东招材建材科技有限公司</t>
+          <t>浙江鑫东洁具有限公司 (ZHEJIANG XINDONG SANITARY WARE CO., LTD.)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>黎桃桃</t>
+          <t>曾燕燕 Elyn</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>toto.liblun@gmail.com</t>
+          <t>sales03@cn-xindong.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>+8618934320539</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>www.liblun.com</t>
-        </is>
-      </c>
+          <t>0086-182 5765 3405, 0086-576-87493988</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
+          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Super</t>
+          <t>Buyer: 50</t>
         </is>
       </c>
     </row>
@@ -1262,38 +1258,34 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>浙江鑫东洁具有限公司 (ZHEJIANG XINDONG SANITARY WARE CO., LTD.)</t>
+          <t>杭州南博装饰材料有限公司</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>曾燕燕 Elyn</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>sales03@cn-xindong.com</t>
-        </is>
-      </c>
+          <t>王小忠</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>0086-182 5765 3405, 0086-576-87493988</t>
+          <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
+          <t>浙江省杭州市临平区运河街道育士路53-1号</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 50</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -1303,29 +1295,37 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>杭州南博装饰材料有限公司</t>
+          <t>台州旭升卫浴股份有限公司</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>王小忠</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
+          <t>应杨军</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3572780651@qq.com</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
+          <t>13511470999</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>www.xs88.cn</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区运河街道育士路53-1号</t>
+          <t>浙江省台州市台州湾新区海虹大道228#</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1340,42 +1340,38 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>台州旭升卫浴股份有限公司</t>
+          <t>NIFO 耐孚</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>应杨军</t>
+          <t>顾鹏</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3572780651@qq.com</t>
+          <t>962460053@qq.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>13511470999</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>www.xs88.cn</t>
-        </is>
-      </c>
+          <t>13326792105</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>浙江省台州市台州湾新区海虹大道228#</t>
+          <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 100</t>
+          <t>Buyer: Wall sheet , 200 rmb per meter , 2000 mtr,</t>
         </is>
       </c>
     </row>
@@ -1385,28 +1381,28 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>NIFO 耐孚</t>
+          <t>Zhejiang Oushe Home Improvement And New Materials Co., Ltd.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>顾鹏</t>
+          <t>Davis Dong 董伟杰</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>962460053@qq.com</t>
+          <t>sales05@authoe.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13326792105</t>
+          <t>+86-18906831082</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
+          <t>Jiaxing/Hongkong</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1416,7 +1412,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Wall sheet , 200 rmb per meter , 2000 mtr,</t>
+          <t>Buyer: Handles , 500 moq , 100 rmb per handle</t>
         </is>
       </c>
     </row>
@@ -1426,38 +1422,38 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Zhejiang Oushe Home Improvement And New Materials Co., Ltd.</t>
+          <t>JIN OGMEI</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Davis Dong 董伟杰</t>
+          <t>Alex Xing</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>sales05@authoe.com</t>
+          <t>kindeli1771@gmail.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>+86-18906831082</t>
+          <t>+86-18302200384</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Jiaxing/Hongkong</t>
+          <t>Shijiazhuang City, Hebei Province</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Handles , 500 moq , 100 rmb per handle</t>
+          <t>Buyer: Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
         </is>
       </c>
     </row>
@@ -1467,38 +1463,42 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>JIN OGMEI</t>
+          <t>温州金锏智能锁具有限公司</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Alex Xing</t>
+          <t>张丽</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>kindeli1771@gmail.com</t>
+          <t>jinjian19@jinjianlock.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>+86-18302200384</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
+          <t>15067804393</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>www.jinjianlock.com</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Shijiazhuang City, Hebei Province</t>
+          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
+          <t>Buyer: Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for customized branding. Feedback: The company has a professional production line and solid hardware quality. Their prices are very competitive for the mass market, although their software ecosystem is less advanced than Innovation's current solutions. They are a reliable choice for high-volume, cost-effective projects.</t>
         </is>
       </c>
     </row>
@@ -1508,32 +1508,32 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>温州金锏智能锁具有限公司</t>
+          <t>上海世灿国际贸易有限公司</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>张丽</t>
+          <t>杨苗</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>jinjian19@jinjianlock.com</t>
+          <t>yangm618@163.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>15067804393</t>
+          <t>138 1618 4706</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>www.jinjianlock.com</t>
+          <t>http://www.shicanchina.com</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号</t>
+          <t>上海市浦东新区商城路889号C3-B06</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for customized branding. Feedback: The company has a professional production line and solid hardware quality. Their prices are very competitive for the mass market, although their software ecosystem is less advanced than Innovation's current solutions. They are a reliable choice for high-volume, cost-effective projects.</t>
+          <t>Buyer: Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models and 150 units for custom OEM branding. Feedback: Yang Miao Miao demonstrates excellent mechanical build quality and focuses heavily on the structural integrity of the doors. Their pricing is mid-range, offering a good balance between durability and cost. They are highly flexible with custom design requests, making them a strong potential partner for Innovation’s specialized architectural projects.</t>
         </is>
       </c>
     </row>
@@ -1553,32 +1553,32 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>上海世灿国际贸易有限公司</t>
+          <t>COLOMAC DECOR</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>杨苗</t>
+          <t>Aaron Liu</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>yangm618@163.com</t>
+          <t>aaron@ccolomac.com</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>138 1618 4706</t>
+          <t>+86-0371-66350801, +86 15936292861</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>http://www.shicanchina.com</t>
+          <t>www.ccolomac.com</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区商城路889号C3-B06</t>
+          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models and 150 units for custom OEM branding. Feedback: Yang Miao Miao demonstrates excellent mechanical build quality and focuses heavily on the structural integrity of the doors. Their pricing is mid-range, offering a good balance between durability and cost. They are highly flexible with custom design requests, making them a strong potential partner for Innovation’s specialized architectural projects.</t>
+          <t>Buyer: Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 100 units for customized decorative panels. Feedback: Colomac Decor stands out for its superior aesthetic design and premium finishing materials. Their products align well with luxury interiors, showing high attention to detail in surface textures. They are an ideal partner for Innovation when the goal is to merge smart technology with high-end interior aesthetics.</t>
         </is>
       </c>
     </row>
@@ -1598,42 +1598,34 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>COLOMAC DECOR</t>
+          <t>佛山市同路匠人家具有限公司</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Aaron Liu</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>aaron@ccolomac.com</t>
-        </is>
-      </c>
+          <t>赖华芳</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>+86-0371-66350801, +86 15936292861</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>www.ccolomac.com</t>
-        </is>
-      </c>
+          <t>13727479513, 400-8339513</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
+          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 100 units for customized decorative panels. Feedback: Colomac Decor stands out for its superior aesthetic design and premium finishing materials. Their products align well with luxury interiors, showing high attention to detail in surface textures. They are an ideal partner for Innovation when the goal is to merge smart technology with high-end interior aesthetics.</t>
+          <t>Buyer: Хорошее, 400rmb</t>
         </is>
       </c>
     </row>
@@ -1643,34 +1635,38 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>佛山市同路匠人家具有限公司</t>
+          <t>固豪木业 | SUNDIN尚鼎</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>赖华芳</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>Clément / 付雄豪</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>clement.fu@cqsdmy.com</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13727479513, 400-8339513</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
-        </is>
-      </c>
+          <t>+(86) 19112691557</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>www.guhaogroup.com / www.cqsdmy.com</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Хорошее, 400rmb</t>
+          <t>Buyer: Хорошее , 1500rmb</t>
         </is>
       </c>
     </row>
@@ -1680,38 +1676,38 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>固豪木业 | SUNDIN尚鼎</t>
+          <t>佛山市嘉豪飞度家具有限公司 (FOSHAN KAHO FIT FURNITURE CO., LTD.)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Clément / 付雄豪</t>
+          <t>周灿灿</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>clement.fu@cqsdmy.com</t>
+          <t>15986196312@163.com</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>+(86) 19112691557</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>www.guhaogroup.com / www.cqsdmy.com</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr"/>
+          <t>159 1909 0393, +86-757-2339 1505</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
+        </is>
+      </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Хорошее , 1500rmb</t>
+          <t>Buyer: Нормальное</t>
         </is>
       </c>
     </row>
@@ -1721,38 +1717,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>佛山市嘉豪飞度家具有限公司 (FOSHAN KAHO FIT FURNITURE CO., LTD.)</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>周灿灿</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>15986196312@163.com</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>159 1909 0393, +86-757-2339 1505</t>
-        </is>
-      </c>
+          <t>中山市福乐门智能科技有限公司 / 中山市乐帝智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Нормальное</t>
+          <t>Buyer: $176, MOQ 50, very good!</t>
         </is>
       </c>
     </row>
@@ -1762,22 +1742,42 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>中山市福乐门智能科技有限公司 / 中山市乐帝智能科技有限公司</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
+          <t>Suzhou Acousound New Material Technology Inc.</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Yolanda He</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>acousound07@polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>+86-18068038050</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+        </is>
+      </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Buyer: $176, MOQ 50, very good!</t>
+          <t>Buyer: $55, MOQ100pcs, good</t>
         </is>
       </c>
     </row>
@@ -1787,42 +1787,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Suzhou Acousound New Material Technology Inc.</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Yolanda He</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>acousound07@polyacoustic.com</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>+86-18068038050</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>www.polyacoustic.com</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
-        </is>
-      </c>
+          <t>特斯豹工具</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Buyer: $55, MOQ100pcs, good</t>
+          <t>Buyer: $30, MOQ 10pcs, nice</t>
         </is>
       </c>
     </row>
@@ -1832,22 +1812,42 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>特斯豹工具</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
+          <t>CGCH</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>陈洁玲 Rowling</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>014@cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>+86 189 2997 1329</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>www.cgchcontainer.com</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+        </is>
+      </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Buyer: $30, MOQ 10pcs, nice</t>
+          <t>Buyer: 1000 yuan 1 square</t>
         </is>
       </c>
     </row>
@@ -1857,42 +1857,34 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CGCH</t>
+          <t>广东省中山名谷屋木门厂</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>陈洁玲 Rowling</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>014@cgchcontainer.com</t>
-        </is>
-      </c>
+          <t>罗美玲</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>+86 189 2997 1329</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>www.cgchcontainer.com</t>
-        </is>
-      </c>
+          <t>180 0760 4399</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
+          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1000 yuan 1 square</t>
+          <t>Buyer: 150 rmb</t>
         </is>
       </c>
     </row>
@@ -1902,34 +1894,42 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>广东省中山名谷屋木门厂</t>
+          <t>multishades</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>罗美玲</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr"/>
+          <t>Sophia</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>sophia@multishades.com.cn</t>
+        </is>
+      </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>180 0760 4399</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr"/>
+          <t>0086-15918713187, 0086-757-86780865</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>www.multishades.com.cn</t>
+        </is>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
+          <t>Office: Room 1501, CITIC Plaza, No.233, Tianhebei Road, Guangzhou City, Guangdong Province, China; Factory: 1 Shengshi Road, Shibei Industrial Park, Shishan Town, Foshan City, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 150 rmb</t>
+          <t>Buyer: 570 rmb</t>
         </is>
       </c>
     </row>
@@ -1939,34 +1939,18 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>multishades</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Sophia</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>sophia@multishades.com.cn</t>
-        </is>
-      </c>
+          <t>超友皮革家居</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0086-15918713187, 0086-757-86780865</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>www.multishades.com.cn</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Office: Room 1501, CITIC Plaza, No.233, Tianhebei Road, Guangzhou City, Guangdong Province, China; Factory: 1 Shengshi Road, Shibei Industrial Park, Shishan Town, Foshan City, Guangdong Province, China</t>
-        </is>
-      </c>
+          <t>1561767</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1974,7 +1958,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 570 rmb</t>
+          <t>Buyer: 130 super</t>
         </is>
       </c>
     </row>
@@ -1984,26 +1968,38 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>超友皮革家居</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
+          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co.,Ltd)</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>欧阳玉滢 (Sonia Ouyang)</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>sonia.ouyang@wireking.com</t>
+        </is>
+      </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>1561767</t>
+          <t>+86-13392758223</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
+        </is>
+      </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 130 super</t>
+          <t>Buyer: $32, MOQ 300, good</t>
         </is>
       </c>
     </row>
@@ -2013,28 +2009,32 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co.,Ltd)</t>
+          <t>PTA DOOR Automation (Hunan Tianan Door Technology Co., Ltd.)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>欧阳玉滢 (Sonia Ouyang)</t>
+          <t>Eva Leng</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>sonia.ouyang@wireking.com</t>
+          <t>eva@ptadoor.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>+86-13392758223</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
+          <t>+86 19848080478, +44 7704 561086</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>global.ptadoor.com</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
+          <t>Xincheng technology park, Yuelu Avenue, Changsha Hunan China</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Buyer: $32, MOQ 300, good</t>
+          <t>Buyer: ¥3000, MoQ 1pcs, very good</t>
         </is>
       </c>
     </row>
@@ -2054,32 +2054,32 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>PTA DOOR Automation (Hunan Tianan Door Technology Co., Ltd.)</t>
+          <t>丰顺县泰雅达实业有限公司</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Eva Leng</t>
+          <t>徐小俊</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>eva@ptadoor.com</t>
+          <t>281431686@qq.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>+86 19848080478, +44 7704 561086</t>
+          <t>13802731123</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>global.ptadoor.com</t>
+          <t>https://taiyada1688.1688.com/</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Xincheng technology park, Yuelu Avenue, Changsha Hunan China</t>
+          <t>广东省丰顺县汤坑镇太平北路</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Buyer: ¥3000, MoQ 1pcs, very good</t>
+          <t>Buyer: ¥17, Moq 50, good</t>
         </is>
       </c>
     </row>
@@ -2099,42 +2099,42 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>丰顺县泰雅达实业有限公司</t>
+          <t>佛山市悠派家居科技有限公司</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>徐小俊</t>
+          <t>黄伟业</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>281431686@qq.com</t>
+          <t>Yea@LGPKB.com</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13802731123</t>
+          <t>13825596371</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://taiyada1688.1688.com/</t>
+          <t>www.LGPKB.com</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>广东省丰顺县汤坑镇太平北路</t>
+          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Buyer: ¥17, Moq 50, good</t>
+          <t>Buyer: 600 RMB Great, very cheap</t>
         </is>
       </c>
     </row>
@@ -2144,34 +2144,18 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>佛山市悠派家居科技有限公司</t>
+          <t>艾锐特</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>黄伟业</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Yea@LGPKB.com</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>13825596371</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>www.LGPKB.com</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
-        </is>
-      </c>
+          <t>冯蕾</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2179,7 +2163,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 600 RMB Great, very cheap</t>
+          <t>Buyer: 3400, Good price</t>
         </is>
       </c>
     </row>
@@ -2189,18 +2173,30 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>艾锐特</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>冯蕾</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+          <t>常州市永春保温材料有限公司 (Changzhou Yongchun Thermal Insulation Materials Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>yc@ycbycl.com</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>0519-88931168</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>www.ycbycl.com</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>江苏省常州市天宁区郑陆镇工业集中区</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2208,7 +2204,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 3400, Good price</t>
+          <t>Buyer: 10$</t>
         </is>
       </c>
     </row>
@@ -2218,28 +2214,32 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>常州市永春保温材料有限公司 (Changzhou Yongchun Thermal Insulation Materials Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr"/>
+          <t>诺奥(福建)环保家居用品有限公司</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>曾令贵</t>
+        </is>
+      </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>yc@ycbycl.com</t>
+          <t>513573190@qq.com</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>0519-88931168</t>
+          <t>86-13585642723 / 0596-8273388-8083</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>www.ycbycl.com</t>
+          <t>www.fjnuoao.cn</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>江苏省常州市天宁区郑陆镇工业集中区</t>
+          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 10$</t>
+          <t>Buyer: 69$</t>
         </is>
       </c>
     </row>
@@ -2259,32 +2259,28 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>诺奥(福建)环保家居用品有限公司</t>
+          <t>大音声学 (DAYIN ACOUSTICS)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>曾令贵</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>513573190@qq.com</t>
-        </is>
-      </c>
+          <t>唐佳豪 (Vance)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>86-13585642723 / 0596-8273388-8083</t>
+          <t>+86 18925924350</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>www.fjnuoao.cn</t>
+          <t>www.dayinacoustics.com</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
+          <t>佛山市南海区里水镇赤山大道32号 (No.32 Chishan Avenue, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2294,7 +2290,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 69$</t>
+          <t>Buyer: 50-85$</t>
         </is>
       </c>
     </row>
@@ -2304,30 +2300,26 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>大音声学 (DAYIN ACOUSTICS)</t>
+          <t>杭州班昇</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>唐佳豪 (Vance)</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr"/>
+          <t>陈卓敏 Ruby</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>295608376@qq.com</t>
+        </is>
+      </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>+86 18925924350</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>www.dayinacoustics.com</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>佛山市南海区里水镇赤山大道32号 (No.32 Chishan Avenue, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
-        </is>
-      </c>
+          <t>+86 13556688832</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
       <c r="H47" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2335,7 +2327,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 50-85$</t>
+          <t>Buyer: ￥1000 good</t>
         </is>
       </c>
     </row>
@@ -2345,26 +2337,34 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>杭州班昇</t>
+          <t>FOSHAN SINCERE BUILDING MATERIALS CO., LTD.</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>陈卓敏 Ruby</t>
+          <t>Crystal 刘晓艺</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>295608376@qq.com</t>
+          <t>crystal@sincerechina.net</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>+86 13556688832</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+          <t>86-15815992213</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>www.sincerechina.net</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>佛山市禅城区南庄镇季华西路中国陶瓷产业总部基地西区C07-C08栋 (China Ceramics Industry Headquaters Block No.C07-08, West Area, West Jihua Road, Nanzhuang, Foshan, China)</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Buyer: ￥1000 good</t>
+          <t>Buyer: ¥ 500 good</t>
         </is>
       </c>
     </row>
@@ -2382,32 +2382,32 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>FOSHAN SINCERE BUILDING MATERIALS CO., LTD.</t>
+          <t>Xiamen Golden Ricky Industry &amp; Trade Co.,Ltd</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Crystal 刘晓艺</t>
+          <t>Joan Liu</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>crystal@sincerechina.net</t>
+          <t>joan@goldenrickyhpl.com</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>86-15815992213</t>
+          <t>+86 13599525074</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>www.sincerechina.net</t>
+          <t>Https://goldenrickyhpl.com</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>佛山市禅城区南庄镇季华西路中国陶瓷产业总部基地西区C07-C08栋 (China Ceramics Industry Headquaters Block No.C07-08, West Area, West Jihua Road, Nanzhuang, Foshan, China)</t>
+          <t>Xiamen City, Fujian, China</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Buyer: ¥ 500 good</t>
+          <t>Buyer: ￥ 300 good</t>
         </is>
       </c>
     </row>
@@ -2427,42 +2427,30 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Xiamen Golden Ricky Industry &amp; Trade Co.,Ltd</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Joan Liu</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>joan@goldenrickyhpl.com</t>
-        </is>
-      </c>
+          <t>江门市新阳刚智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>+86 13599525074</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Https://goldenrickyhpl.com</t>
-        </is>
-      </c>
+          <t>135 3666 7789, 400-9090-518</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Xiamen City, Fujian, China</t>
+          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Buyer: ￥ 300 good</t>
+          <t>Buyer: 300 rmb and more. Good quality and good price. Small quantity</t>
         </is>
       </c>
     </row>
@@ -2472,30 +2460,42 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>江门市新阳刚智能科技有限公司</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
+          <t>河南蓝健陶瓷有限公司</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>王闻浠</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>lanjanweiyu@163.com</t>
+        </is>
+      </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>135 3666 7789, 400-9090-518</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr"/>
+          <t>+86-13569915996</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>www.lanjan.com</t>
+        </is>
+      </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
+          <t>河南省长葛市石固镇梁庄工业园区</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 300 rmb and more. Good quality and good price. Small quantity</t>
+          <t>Buyer: 33$ for 1 pcs. Good quality and quantity</t>
         </is>
       </c>
     </row>
@@ -2505,32 +2505,20 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>河南蓝健陶瓷有限公司</t>
+          <t>沃澜 (WOTUA)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>王闻浠</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>lanjanweiyu@163.com</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>+86-13569915996</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>www.lanjan.com</t>
-        </is>
-      </c>
+          <t>Dion Sun</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>河南省长葛市石固镇梁庄工业园区</t>
+          <t>3座104号</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2540,7 +2528,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 33$ for 1 pcs. Good quality and quantity</t>
+          <t>Buyer: Good quality and quantity. 140 rmb 1 pcs.</t>
         </is>
       </c>
     </row>
@@ -2550,22 +2538,22 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>沃澜 (WOTUA)</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Dion Sun</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
+          <t>三强地毯</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>hengsheng_carpet@163.com</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>0769-89807692</t>
+        </is>
+      </c>
       <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>3座104号</t>
-        </is>
-      </c>
+      <c r="G53" s="3" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2573,7 +2561,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Good quality and quantity. 140 rmb 1 pcs.</t>
+          <t>Buyer: Good 👍</t>
         </is>
       </c>
     </row>
@@ -2583,22 +2571,34 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>三强地毯</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr"/>
+          <t>Higold Group Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Willer Zhou</t>
+        </is>
+      </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>hengsheng_carpet@163.com</t>
+          <t>sale31@higold.com.cn</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>0769-89807692</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+          <t>+86 158 2865 5891</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>www.higoldhardware.com</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>No.36 Shunye East Rd, Xingtan, Shunde, Foshan 528325, Guangdong, China</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Good 👍</t>
+          <t>Buyer: 5800</t>
         </is>
       </c>
     </row>
@@ -2616,42 +2616,42 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Higold Group Co., Ltd.</t>
+          <t>Zhejiang Kehon Intelligent Science &amp; Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Willer Zhou</t>
+          <t>Sammi Shi</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>sale31@higold.com.cn</t>
+          <t>sales01@kehon.cn</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>+86 158 2865 5891</t>
+          <t>+86 156 8948 5097, 0578-3271096</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>www.higoldhardware.com</t>
+          <t>www.kehon.cn</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>No.36 Shunye East Rd, Xingtan, Shunde, Foshan 528325, Guangdong, China</t>
+          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 5800</t>
+          <t>Buyer: 130 yuan</t>
         </is>
       </c>
     </row>
@@ -2661,42 +2661,42 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Zhejiang Kehon Intelligent Science &amp; Technology Co., Ltd.</t>
+          <t>Guangdong Wanbang Modular Building Co., Ltd</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Sammi Shi</t>
+          <t>Richie Wang</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>sales01@kehon.cn</t>
+          <t>richie.wang@wbhouse.com</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>+86 156 8948 5097, 0578-3271096</t>
+          <t>+86 137 1002 1675</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>www.kehon.cn</t>
+          <t>www.gdwbprefabhouse.com</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
+          <t>Guangdong Factory: No.5, No. 161 Ganghe Avenue, Gaoming District, Foshan city, Guangdong, CHINA; Fujian Factory: Provincial Highway 308, Yunrong Township, Minqing County, Fuzhou City, Fujian Province, CHINA.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 130 yuan</t>
+          <t>Buyer: 20000usd</t>
         </is>
       </c>
     </row>
@@ -2706,42 +2706,42 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Guangdong Wanbang Modular Building Co., Ltd</t>
+          <t>Guhao Group | SEAJOIN</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Richie Wang</t>
+          <t>Owen Li</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>richie.wang@wbhouse.com</t>
+          <t>owen.li@seajoinhouse.com</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>+86 137 1002 1675</t>
+          <t>(86) 133 9501 1076</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>www.gdwbprefabhouse.com</t>
+          <t>www.seajoinhouse.com</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Guangdong Factory: No.5, No. 161 Ganghe Avenue, Gaoming District, Foshan city, Guangdong, CHINA; Fujian Factory: Provincial Highway 308, Yunrong Township, Minqing County, Fuzhou City, Fujian Province, CHINA.</t>
+          <t>Chongqing, China / Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 20000usd</t>
+          <t>Buyer: 500yuan</t>
         </is>
       </c>
     </row>
@@ -2751,42 +2751,42 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Guhao Group | SEAJOIN</t>
+          <t>CAE SANITARY FITTINGS INDUSTRY CO., LTD. GUANGDONG</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Owen Li</t>
+          <t>Josie Guan</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>owen.li@seajoinhouse.com</t>
+          <t>cae@china-cae.com</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>(86) 133 9501 1076</t>
+          <t>+86-13702279135</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>www.seajoinhouse.com</t>
+          <t>www.china-cae.com</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Chongqing, China / Ho Chi Minh City, Vietnam</t>
+          <t>No.62-64, Xingda Rd., Shagang Dist., Shuikou Town, Kaiping, Guangdong, P.R.Of China.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 500yuan</t>
+          <t>Buyer: MOQ 100, 47 rnb per piece</t>
         </is>
       </c>
     </row>
@@ -2796,42 +2796,38 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>CAE SANITARY FITTINGS INDUSTRY CO., LTD. GUANGDONG</t>
+          <t>盐城格子匠家居有限公司</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Josie Guan</t>
+          <t>董华</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>cae@china-cae.com</t>
+          <t>418897056@qq.com</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>+86-13702279135</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>www.china-cae.com</t>
-        </is>
-      </c>
+          <t>13914649982, 18951488133</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>No.62-64, Xingda Rd., Shagang Dist., Shuikou Town, Kaiping, Guangdong, P.R.Of China.</t>
+          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 100, 47 rnb per piece</t>
+          <t>Buyer: MOQ 50, 200 rnb per</t>
         </is>
       </c>
     </row>
@@ -2841,28 +2837,32 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>盐城格子匠家居有限公司</t>
+          <t>SUOFEIYA HOME COLLECTION CO., LTD</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>董华</t>
+          <t>Jasmine Guan 管敏秀</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>418897056@qq.com</t>
+          <t>jasmine@suofeiyahome.com</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>13914649982, 18951488133</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr"/>
+          <t>+86 147 7520 2759</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sofeyiahome.com</t>
+        </is>
+      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
+          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 50, 200 rnb per</t>
+          <t>Buyer: MOQ 10, 845 per piece</t>
         </is>
       </c>
     </row>
@@ -2882,32 +2882,32 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>SUOFEIYA HOME COLLECTION CO., LTD</t>
+          <t>利亚德光电股份有限公司 Leyard Optoelectronic Co., Ltd.</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Jasmine Guan 管敏秀</t>
+          <t>金厚强 Jin Houqiang</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>jasmine@suofeiyahome.com</t>
+          <t>jinhouqiang@leyard.com</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>+86 147 7520 2759</t>
+          <t>13510009569, 18829341125, 400-8592-666</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>https://www.sofeyiahome.com</t>
+          <t>www.leyard.com</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
+          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 10, 845 per piece</t>
+          <t>Buyer: 1pcs. Start from 60rmb. Novative technology</t>
         </is>
       </c>
     </row>
@@ -2927,34 +2927,14 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>利亚德光电股份有限公司 Leyard Optoelectronic Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>金厚强 Jin Houqiang</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>jinhouqiang@leyard.com</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>13510009569, 18829341125, 400-8592-666</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>www.leyard.com</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋</t>
-        </is>
-      </c>
+          <t>林商学社</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2962,7 +2942,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1pcs. Start from 60rmb. Novative technology</t>
+          <t>Buyer: From 1pc. Natural materials.</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2952,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>林商学社</t>
+          <t>佛山市威尔信保险柜有限公司 (Foshan Weierxin Safe Co., Ltd.)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr"/>
@@ -2987,7 +2967,7 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Buyer: From 1pc. Natural materials.</t>
+          <t>Buyer: 1250rmb. MOQ 1 pc</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2977,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>佛山市威尔信保险柜有限公司 (Foshan Weierxin Safe Co., Ltd.)</t>
+          <t>SAKURA 樱花智能锁</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr"/>
@@ -3012,7 +2992,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1250rmb. MOQ 1 pc</t>
+          <t>Buyer: 199</t>
         </is>
       </c>
     </row>
@@ -3022,22 +3002,38 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>SAKURA 樱花智能锁</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr"/>
-      <c r="D65" s="3" t="inlineStr"/>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="inlineStr"/>
+          <t>JNOD 基诺德</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>周信朋 Joe Zhou</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>sales02@jnodwater.com</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>+86 199 2825 2201, +86-757-2361 7920</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>www.jnodwater.com</t>
+        </is>
+      </c>
       <c r="G65" s="3" t="inlineStr"/>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 199</t>
+          <t>Buyer: 1410</t>
         </is>
       </c>
     </row>
@@ -3047,30 +3043,34 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>JNOD 基诺德</t>
+          <t>广州传祺时代智能科技有限公司</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>周信朋 Joe Zhou</t>
+          <t>洪美兰</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>sales02@jnodwater.com</t>
+          <t>jiang@chuangqitimes.com</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>+86 199 2825 2201, +86-757-2361 7920</t>
+          <t>13450298606, 020-82511901</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>www.jnodwater.com</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
+          <t>www.chuangqitimes.com</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1410</t>
+          <t>Buyer: 329</t>
         </is>
       </c>
     </row>
@@ -3088,32 +3088,28 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>广州传祺时代智能科技有限公司</t>
+          <t>RUIKANG</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>洪美兰</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>jiang@chuangqitimes.com</t>
+          <t>sales08@ruikang-cn.com</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>13450298606, 020-82511901</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>www.chuangqitimes.com</t>
-        </is>
-      </c>
+          <t>+86 18028330648, +86 18022073939</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
+          <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
@@ -3123,7 +3119,7 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 329</t>
+          <t>Buyer: 229</t>
         </is>
       </c>
     </row>
@@ -3133,38 +3129,34 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>RUIKANG</t>
+          <t>松下电器设备(中国)有限公司</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Jacky</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>sales08@ruikang-cn.com</t>
-        </is>
-      </c>
+          <t>潘禹</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>+86 18028330648, +86 18022073939</t>
+          <t>13691864691</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
+          <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 229</t>
+          <t>Buyer: 680</t>
         </is>
       </c>
     </row>
@@ -3174,34 +3166,42 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>松下电器设备(中国)有限公司</t>
+          <t>CAE</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>潘禹</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr"/>
+          <t>Jack Guan</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>jack@cae.cn</t>
+        </is>
+      </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>13691864691</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr"/>
+          <t>+86-750-8119338</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>www.cae.cn</t>
+        </is>
+      </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
+          <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 680</t>
+          <t>Buyer: 150 yuan, 100, good range of products</t>
         </is>
       </c>
     </row>
@@ -3211,42 +3211,42 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>CAE</t>
+          <t>广东富矿智能家居有限公司 (Guangdong Fukuang Intelligent Home Co., Ltd.)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Jack Guan</t>
+          <t>余赛银 (Yu Saiyin)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>jack@cae.cn</t>
+          <t>109786129@qq.com</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>+86-750-8119338</t>
+          <t>+86 13660529010</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>www.cae.cn</t>
+          <t>kingliye.com</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
+          <t>佛山市南海区里广路二号碧桂园金沙国际广场1201室 (Room 1201, Building 10, Jinsha International Plaza No.2 Liguang Road, Nanhai District, Foshan City)</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 150 yuan, 100, good range of products</t>
+          <t>Buyer: Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
         </is>
       </c>
     </row>
@@ -3256,42 +3256,22 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>广东富矿智能家居有限公司 (Guangdong Fukuang Intelligent Home Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>余赛银 (Yu Saiyin)</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>109786129@qq.com</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>+86 13660529010</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>kingliye.com</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>佛山市南海区里广路二号碧桂园金沙国际广场1201室 (Room 1201, Building 10, Jinsha International Plaza No.2 Liguang Road, Nanhai District, Foshan City)</t>
-        </is>
-      </c>
+          <t>THOR 索而</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr"/>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
+          <t>Buyer: The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
         </is>
       </c>
     </row>
@@ -3301,17 +3281,33 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>THOR 索而</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
+          <t>肇庆合生雅居智能家居有限公司 (Zhaoqing Hesheng Yaju Intelligent Home Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Winni 何玲玲</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>helingling@gdhsyj.com</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>+86 18924564942</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>WWW.HOPSOONER.COM</t>
+        </is>
+      </c>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3326,38 +3322,38 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>肇庆合生雅居智能家居有限公司 (Zhaoqing Hesheng Yaju Intelligent Home Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>Winni 何玲玲</t>
-        </is>
-      </c>
+          <t>视威电子科技（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr"/>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>helingling@gdhsyj.com</t>
+          <t>service@3weitech.com</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>+86 18924564942</t>
+          <t>021-57715805</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>WWW.HOPSOONER.COM</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr"/>
+          <t>www.3weitech.com</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>上海市闵行区新骏环路188号11号楼A座518室</t>
+        </is>
+      </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Buyer: The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+          <t>Buyer: 167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет проблема синхронизации . Есть свой искусственный интеллект . Нужно тестировать . Купили ленту у него лед, на телевизор как образец</t>
         </is>
       </c>
     </row>
@@ -3367,30 +3363,30 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>视威电子科技（上海）有限公司</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr"/>
+          <t>爱舒床垫集团有限公司</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>王鹏</t>
+        </is>
+      </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>service@3weitech.com</t>
+          <t>1319129904@qq.com</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>021-57715805</t>
+          <t>189-2324-7677</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>www.3weitech.com</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>上海市闵行区新骏环路188号11号楼A座518室</t>
-        </is>
-      </c>
+          <t>www.asnug.com</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3398,7 +3394,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет проблема синхронизации . Есть свой искусственный интеллект . Нужно тестировать . Купили ленту у него лед, на телевизор как образец</t>
+          <t>Buyer: 20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
         </is>
       </c>
     </row>
@@ -3408,30 +3404,34 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>爱舒床垫集团有限公司</t>
+          <t>Suzhou Acesound New Material Technology Inc.</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>王鹏</t>
+          <t>Yolanda He</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>1319129904@qq.com</t>
+          <t>ecosound02@polyacoustic.com</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>189-2324-7677</t>
+          <t>+86-18018130150</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>www.asnug.com</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr"/>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>No.10 Jinxi Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+        </is>
+      </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
+          <t>Buyer: Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного метра 150 юаней сказала примерно. Не до конца поняла точность минимальной партии, но говорили часто 100 кВ метром</t>
         </is>
       </c>
     </row>
@@ -3449,34 +3449,26 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Suzhou Acesound New Material Technology Inc.</t>
+          <t>soundbox</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Yolanda He</t>
+          <t>劉奕紫 Cathy</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>ecosound02@polyacoustic.com</t>
+          <t>sales19@soundbox.hk</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>+86-18018130150</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>www.polyacoustic.com</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>No.10 Jinxi Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
-        </is>
-      </c>
+          <t>+86 137 6339 3059</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3484,7 +3476,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного метра 150 юаней сказала примерно. Не до конца поняла точность минимальной партии, но говорили часто 100 кВ метром</t>
+          <t>Buyer: От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккуратная комната, достаточно комфортная. Цена немного завышена, встречали на других выставках пониже стоимостью.</t>
         </is>
       </c>
     </row>
@@ -3494,24 +3486,12 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>soundbox</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>劉奕紫 Cathy</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>sales19@soundbox.hk</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>+86 137 6339 3059</t>
-        </is>
-      </c>
+          <t>顶固集团</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr"/>
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr"/>
       <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" s="3" t="inlineStr"/>
       <c r="H77" s="3" t="inlineStr">
@@ -3521,7 +3501,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Buyer: От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккуратная комната, достаточно комфортная. Цена немного завышена, встречали на других выставках пониже стоимостью.</t>
+          <t>Buyer: От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккуратно. Хорошее решение для сушки белья и экономии места. Стоимость чуть больше 200 юаней</t>
         </is>
       </c>
     </row>
@@ -3531,22 +3511,42 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>顶固集团</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr"/>
-      <c r="D78" s="2" t="inlineStr"/>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
+          <t>Shenzhen Kingston Sanitary Ware Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Felicity</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>sales09@spakingston.com</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>+86-18025851458</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>www.spakingston.com</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Kingston Company, JiangJun Road, Qiuchang, Huiyang, Huizhou, China</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Buyer: От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккуратно. Хорошее решение для сушки белья и экономии места. Стоимость чуть больше 200 юаней</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -3556,32 +3556,32 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Shenzhen Kingston Sanitary Ware Co., Ltd.</t>
+          <t>Guangzhou Sunrans Sanitary Ware Co., Ltd / Guangzhou Sunrans New Energy Technology Co., Ltd</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Felicity</t>
+          <t>William</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>sales09@spakingston.com</t>
+          <t>william@sunrans.com</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>+86-18025851458</t>
+          <t>+86 134 1613 9887, +86-20-26231998</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>www.spakingston.com</t>
+          <t>http://www.sunrans.com</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Kingston Company, JiangJun Road, Qiuchang, Huiyang, Huizhou, China</t>
+          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 100</t>
+          <t>Buyer: MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very good and good products.</t>
         </is>
       </c>
     </row>
@@ -3599,44 +3599,24 @@
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Guangzhou Sunrans Sanitary Ware Co., Ltd / Guangzhou Sunrans New Energy Technology Co., Ltd</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>William</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>william@sunrans.com</t>
-        </is>
-      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>+86 134 1613 9887, +86-20-26231998</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>http://www.sunrans.com</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
-        </is>
-      </c>
+          <t>15916159866</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very good and good products.</t>
+          <t>Buyer: MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
         </is>
       </c>
     </row>
@@ -3644,16 +3624,36 @@
       <c r="A81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="3" t="inlineStr"/>
-      <c r="C81" s="3" t="inlineStr"/>
-      <c r="D81" s="3" t="inlineStr"/>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>IFUN PARK &amp; TIPTOPFUN AMUSEMENT</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Ivy Zhou</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>ivy@ifunpark.com</t>
+        </is>
+      </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>15916159866</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr"/>
-      <c r="G81" s="3" t="inlineStr"/>
+          <t>+86 133 0238 5758</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>www.ifunpark.com / www.ifunamusement.com</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
+        </is>
+      </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
+          <t>Buyer: 600</t>
         </is>
       </c>
     </row>
@@ -3671,34 +3671,14 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>IFUN PARK &amp; TIPTOPFUN AMUSEMENT</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Ivy Zhou</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>ivy@ifunpark.com</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>+86 133 0238 5758</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>www.ifunpark.com / www.ifunamusement.com</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
-        </is>
-      </c>
+          <t>Weyth 惠特</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3706,7 +3686,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 600</t>
+          <t>Buyer: 500</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3696,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Weyth 惠特</t>
+          <t>D.DELI 德利智能门锁</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr"/>
@@ -3731,7 +3711,7 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 500</t>
+          <t>Buyer: 43</t>
         </is>
       </c>
     </row>
@@ -3741,22 +3721,42 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>D.DELI 德利智能门锁</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr"/>
-      <c r="D84" s="2" t="inlineStr"/>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+          <t>RENQIU TUOXIN BUILDING MATERIALS CO., LTD</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Emily Li</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>tuoxinlqm@outlook.com</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>+86 19831737599</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tuoxinfiberglassmesh.com/</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 43</t>
+          <t>Buyer: 0.6 usd/m2</t>
         </is>
       </c>
     </row>
@@ -3766,42 +3766,42 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>RENQIU TUOXIN BUILDING MATERIALS CO., LTD</t>
+          <t>河南威兰得建筑科技有限公司</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Emily Li</t>
+          <t>王虎旗</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>tuoxinlqm@outlook.com</t>
+          <t>hectorwang1982@gmail.com</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>+86 19831737599</t>
+          <t>86 18638546565</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>https://www.tuoxinfiberglassmesh.com/</t>
+          <t>www.weilandeglobal.com</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
+          <t>河南省郑州市曲梁工业园188号</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 0.6 usd/m2</t>
+          <t>Buyer: Under negotiation, great opportunities</t>
         </is>
       </c>
     </row>
@@ -3811,42 +3811,34 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>河南威兰得建筑科技有限公司</t>
+          <t>江门市新会区致恒科技材料有限公司</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>王虎旗</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>hectorwang1982@gmail.com</t>
-        </is>
-      </c>
+          <t>曹双林 (Edith Cao)</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>86 18638546565</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>www.weilandeglobal.com</t>
-        </is>
-      </c>
+          <t>13286132534, 400-0750-889</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>河南省郑州市曲梁工业园188号</t>
+          <t>广东省江门市蓬江区迎宾大道西23号之129</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Under negotiation, great opportunities</t>
+          <t>Buyer: 1-5 usd/l</t>
         </is>
       </c>
     </row>
@@ -3856,34 +3848,30 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>江门市新会区致恒科技材料有限公司</t>
+          <t>安居福智能门 (ANJUFU INTELLIGENT GATE)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>曹双林 (Edith Cao)</t>
+          <t>罗如玲</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr"/>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>13286132534, 400-0750-889</t>
-        </is>
-      </c>
+      <c r="E87" s="3" t="inlineStr"/>
       <c r="F87" s="3" t="inlineStr"/>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市蓬江区迎宾大道西23号之129</t>
+          <t>广东省中山市东凤镇</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1-5 usd/l</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -3893,22 +3881,14 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>安居福智能门 (ANJUFU INTELLIGENT GATE)</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>罗如玲</t>
-        </is>
-      </c>
+          <t>欧派</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>广东省中山市东凤镇</t>
-        </is>
-      </c>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3916,7 +3896,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 100</t>
+          <t>Buyer: 679 rmb</t>
         </is>
       </c>
     </row>
@@ -3926,14 +3906,18 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>欧派</t>
+          <t>永康市鸿钰门业有限公司</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr"/>
       <c r="D89" s="3" t="inlineStr"/>
       <c r="E89" s="3" t="inlineStr"/>
       <c r="F89" s="3" t="inlineStr"/>
-      <c r="G89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>浙江省永康市长城工业区</t>
+        </is>
+      </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3941,7 +3925,7 @@
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 679 rmb</t>
+          <t>Buyer: 59 rmb</t>
         </is>
       </c>
     </row>
@@ -3951,18 +3935,18 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>永康市鸿钰门业有限公司</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr"/>
+          <t>东方喜卡</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>果果</t>
+        </is>
+      </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>浙江省永康市长城工业区</t>
-        </is>
-      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3970,7 +3954,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 59 rmb</t>
+          <t>Buyer: 249RMB</t>
         </is>
       </c>
     </row>
@@ -3980,26 +3964,38 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>东方喜卡</t>
+          <t>优品声学 (YP ACOUSTICS)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>果果</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr"/>
-      <c r="E91" s="3" t="inlineStr"/>
+          <t>李尚声 (Shangsheng Li)</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>15915975597@163.com</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>15915974406</t>
+        </is>
+      </c>
       <c r="F91" s="3" t="inlineStr"/>
-      <c r="G91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
+        </is>
+      </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 249RMB</t>
+          <t>Buyer: 6000RMB</t>
         </is>
       </c>
     </row>
@@ -4009,38 +4005,30 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>优品声学 (YP ACOUSTICS)</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>李尚声 (Shangsheng Li)</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>15915975597@163.com</t>
-        </is>
-      </c>
+          <t>双龙智科</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>15915974406</t>
+          <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 6000RMB</t>
+          <t>Buyer: 2000RMB&amp;gt;</t>
         </is>
       </c>
     </row>
@@ -4050,30 +4038,38 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>双龙智科</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr"/>
-      <c r="D93" s="3" t="inlineStr"/>
+          <t>GUANGDONG TUOXUN INTELLIGENT TECHNOLOGY CO., LTD</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Wing</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>wuyunying08@gmail.com</t>
+        </is>
+      </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
+          <t>189-2984-9818, 0758-8578545</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr"/>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>江苏省太仓市双凤镇陆江路1号</t>
+          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 2000RMB&amp;gt;</t>
+          <t>Buyer: MOQ - 5000 and price - 7000 dollars</t>
         </is>
       </c>
     </row>
@@ -4083,28 +4079,32 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>GUANGDONG TUOXUN INTELLIGENT TECHNOLOGY CO., LTD</t>
+          <t>Suzhou Acousound New Material Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Wing</t>
+          <t>Susan Xia</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>wuyunying08@gmail.com</t>
+          <t>acousound16@polyacoustic.com</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>189-2984-9818, 0758-8578545</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr"/>
+          <t>+86-15512435605</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
+          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu 215152</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ - 5000 and price - 7000 dollars</t>
+          <t>Buyer: 4000$</t>
         </is>
       </c>
     </row>
@@ -4124,32 +4124,28 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Suzhou Acousound New Material Technology Co., Ltd.</t>
+          <t>佛山市方泓五金建材有限公司 (Foshan Fangheng Hardware Co., Ltd.)</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Susan Xia</t>
+          <t>陈施志凯 (CHEN SHI ZHI KAI)</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>acousound16@polyacoustic.com</t>
+          <t>108455453@qq.com</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>+86-15512435605</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>www.polyacoustic.com</t>
-        </is>
-      </c>
+          <t>+86 134 3318 1558, 0757-8560 9159</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr"/>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu 215152</t>
+          <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
@@ -4159,7 +4155,7 @@
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 4000$</t>
+          <t>Buyer: The price cheap, merchant very friendly</t>
         </is>
       </c>
     </row>
@@ -4169,38 +4165,38 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>佛山市方泓五金建材有限公司 (Foshan Fangheng Hardware Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>陈施志凯 (CHEN SHI ZHI KAI)</t>
-        </is>
-      </c>
+          <t>Countermast Technology (Dalian) Company Limited</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>108455453@qq.com</t>
+          <t>sales.countermast.china@countermast.com</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>+86 134 3318 1558, 0757-8560 9159</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr"/>
+          <t>400-100-2228</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>www.countermast.cn</t>
+        </is>
+      </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+          <t>Building No.7, Zhongqing Industrial Park, Dalian free trade zone, Liaoning, China</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Buyer: The price cheap, merchant very friendly</t>
+          <t>Buyer: The price more cheaper, good quality</t>
         </is>
       </c>
     </row>
@@ -4210,38 +4206,42 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Countermast Technology (Dalian) Company Limited</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr"/>
+          <t>广州蒙娜丽莎控股集团有限公司, 广州蒙娜丽莎卫浴股份有限公司</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>严金霞</t>
+        </is>
+      </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>sales.countermast.china@countermast.com</t>
+          <t>monalisa38@monalisa.cn</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>400-100-2228</t>
+          <t>+86 13711113746, 400 020 1818, +86 20-28607711</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>www.countermast.cn</t>
+          <t>www.monalisa.cn</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>Building No.7, Zhongqing Industrial Park, Dalian free trade zone, Liaoning, China</t>
+          <t>广州市花都区花东镇港头工业区4号</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>Buyer: The price more cheaper, good quality</t>
+          <t>Buyer: Good merchant, perfect products</t>
         </is>
       </c>
     </row>
@@ -4251,42 +4251,42 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>广州蒙娜丽莎控股集团有限公司, 广州蒙娜丽莎卫浴股份有限公司</t>
+          <t>高成 (Gaocheng)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>严金霞</t>
+          <t>叶小龙/Dustin Ye</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>monalisa38@monalisa.cn</t>
+          <t>yedustin@gmail.com</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>+86 13711113746, 400 020 1818, +86 20-28607711</t>
+          <t>+86-188 5861 0008</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>www.monalisa.cn</t>
+          <t>www.cngaocheng.cn</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区花东镇港头工业区4号</t>
+          <t>浙江省三门县浦坝港镇沿海工业城 (COASTAL INDUSTRIAL CITY, PUBAGANG TOWN, SANMEN, TAIZHOU CITY, ZHEJIANG PRO., CHINA)</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Good merchant, perfect products</t>
+          <t>Buyer: 160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
         </is>
       </c>
     </row>
@@ -4296,42 +4296,42 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>高成 (Gaocheng)</t>
+          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD. / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>叶小龙/Dustin Ye</t>
+          <t>Pacao Yin</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>yedustin@gmail.com</t>
+          <t>pin@pingaolao.com</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>+86-188 5861 0008</t>
+          <t>(0086)13903035682, (0086)0769-86378283, (0086)0769-86377522</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>www.cngaocheng.cn</t>
+          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>浙江省三门县浦坝港镇沿海工业城 (COASTAL INDUSTRIAL CITY, PUBAGANG TOWN, SANMEN, TAIZHOU CITY, ZHEJIANG PRO., CHINA)</t>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
+          <t>Buyer: 15 RMB the product is interesting</t>
         </is>
       </c>
     </row>
@@ -4341,32 +4341,32 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD. / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
+          <t>浙江瑞鑫环保设备有限公司</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Pacao Yin</t>
+          <t>吴仁余</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>pin@pingaolao.com</t>
+          <t>294217488@qq.com</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>(0086)13903035682, (0086)0769-86378283, (0086)0769-86377522</t>
+          <t>13967444542, 0579-82889122</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
+          <t>www.jhrxhb.com</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+          <t>浙江省金华市婺城区罗店镇北山路精工工业园</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 15 RMB the product is interesting</t>
+          <t>Buyer: nearly $15,000 for this production line</t>
         </is>
       </c>
     </row>
@@ -4386,32 +4386,32 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>浙江瑞鑫环保设备有限公司</t>
+          <t>ZHEJIANG DOUBLE-LIN VALVES CO., LTD.</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>吴仁余</t>
+          <t>Dream Lin</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>294217488@qq.com</t>
+          <t>sale15@double-lin.com</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>13967444542, 0579-82889122</t>
+          <t>86-020-66837727, 86-13710718529</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>www.jhrxhb.com</t>
+          <t>www.double-lin.com</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>浙江省金华市婺城区罗店镇北山路精工工业园</t>
+          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>Buyer: nearly $15,000 for this production line</t>
+          <t>Buyer: 149</t>
         </is>
       </c>
     </row>
@@ -4431,32 +4431,28 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>ZHEJIANG DOUBLE-LIN VALVES CO., LTD.</t>
+          <t>苏州市富尔达科技股份有限公司</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Dream Lin</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>sale15@double-lin.com</t>
-        </is>
-      </c>
+          <t>袁佳磊</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>86-020-66837727, 86-13710718529</t>
+          <t>18652449601</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>www.double-lin.com</t>
+          <t>www.cnfrd.cn</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
+          <t>江苏省太仓市港区临江路1号</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -4466,7 +4462,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 149</t>
+          <t>Buyer: 749</t>
         </is>
       </c>
     </row>
@@ -4476,38 +4472,42 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>苏州市富尔达科技股份有限公司</t>
+          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.,LTD.</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>袁佳磊</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr"/>
+          <t>Eric Huang</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>464565801@qq.com</t>
+        </is>
+      </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>18652449601</t>
+          <t>13813551160 / 0519-88784050</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>www.cnfrd.cn</t>
+          <t>www.ycpanel.com</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>江苏省太仓市港区临江路1号</t>
+          <t>No.28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 749</t>
+          <t>Buyer: 5000 USD</t>
         </is>
       </c>
     </row>
@@ -4517,42 +4517,30 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Eric Huang</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>464565801@qq.com</t>
-        </is>
-      </c>
+          <t>双龙中科</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr"/>
+      <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>13813551160 / 0519-88784050</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>www.ycpanel.com</t>
-        </is>
-      </c>
+          <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>No.28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 5000 USD</t>
+          <t>Buyer: Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
         </is>
       </c>
     </row>
@@ -4562,30 +4550,30 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>双龙中科</t>
+          <t>深圳市家为安智能科技有限公司</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr"/>
       <c r="D105" s="3" t="inlineStr"/>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
+          <t>186-0205-8898 / 400-608-0098</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr"/>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>江苏省太仓市双凤镇陆江路1号</t>
+          <t>广东省佛山市南海区里水镇</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
+          <t>Buyer: 249 RMB. They have fully described their products.</t>
         </is>
       </c>
     </row>
@@ -4595,30 +4583,30 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>深圳市家为安智能科技有限公司</t>
+          <t>广州市优品声学科技有限公司</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr"/>
       <c r="D106" s="2" t="inlineStr"/>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>186-0205-8898 / 400-608-0098</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>www.gzypsx.com</t>
+        </is>
+      </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区里水镇</t>
+          <t>广东省广州市番禺区南村镇南村西路138号德意创意园二层</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 249 RMB. They have fully described their products.</t>
+          <t>Buyer: 6000RMB，积极，详细地告诉了一切</t>
         </is>
       </c>
     </row>
@@ -4628,30 +4616,26 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>广州市优品声学科技有限公司</t>
+          <t>科维尔 (VIR)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr"/>
       <c r="D107" s="3" t="inlineStr"/>
       <c r="E107" s="3" t="inlineStr"/>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>www.gzypsx.com</t>
-        </is>
-      </c>
+      <c r="F107" s="3" t="inlineStr"/>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区南村镇南村西路138号德意创意园二层</t>
+          <t>市长城工业区</t>
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 6000RMB，积极，详细地告诉了一切</t>
+          <t>Buyer: 2000 RMB</t>
         </is>
       </c>
     </row>
@@ -4661,16 +4645,28 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>科维尔 (VIR)</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr"/>
-      <c r="D108" s="2" t="inlineStr"/>
-      <c r="E108" s="2" t="inlineStr"/>
+          <t>贵州佑远木业有限公司</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>颜加伟</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>1164199388@qq.com</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>133 9983 5678</t>
+        </is>
+      </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>市长城工业区</t>
+          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -4680,7 +4676,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 2000 RMB</t>
+          <t>Buyer: 400rmb /m2 good meeting</t>
         </is>
       </c>
     </row>
@@ -4690,38 +4686,34 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>贵州佑远木业有限公司</t>
+          <t>广西豪庭家具有限公司 (Guangxi Haoting Furniture Co., Ltd.)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>颜加伟</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>1164199388@qq.com</t>
-        </is>
-      </c>
+          <t>高学梅</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr"/>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>133 9983 5678</t>
+          <t>17687627315</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr"/>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
+          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 400rmb /m2 good meeting</t>
+          <t>Buyer: 350 rmb/m2</t>
         </is>
       </c>
     </row>
@@ -4731,34 +4723,42 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>广西豪庭家具有限公司 (Guangxi Haoting Furniture Co., Ltd.)</t>
+          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>高学梅</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr"/>
+          <t>Pacao Yin</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>pin@pingaolao.com</t>
+        </is>
+      </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>17687627315</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr"/>
+          <t>Mobile: (0086)13903035682, Tel: (0086)0769-86378283</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
+        </is>
+      </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 350 rmb/m2</t>
+          <t>Buyer: MOQ 5000 pieces</t>
         </is>
       </c>
     </row>
@@ -4768,42 +4768,42 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
+          <t>Moershu (摩尔舒卫浴)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Pacao Yin</t>
+          <t>Thea</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>pin@pingaolao.com</t>
+          <t>moershu3@moershu.com</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Mobile: (0086)13903035682, Tel: (0086)0769-86378283</t>
+          <t>13957622087</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
+          <t>www.moershu.com</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 5000 pieces</t>
+          <t>Buyer: 194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
         </is>
       </c>
     </row>
@@ -4813,42 +4813,38 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Moershu (摩尔舒卫浴)</t>
+          <t>Hangzhou Sciener Smart Technology Co.,Ltd.</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Thea</t>
+          <t>Zoey Zhang</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>moershu3@moershu.com</t>
+          <t>zoey@sciener.com</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>13957622087</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>www.moershu.com</t>
-        </is>
-      </c>
+          <t>+86 178-5768-8782</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
+          <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
+          <t>Buyer: 20 / MOQ 100 Nice worker answered all questions</t>
         </is>
       </c>
     </row>
@@ -4858,38 +4854,38 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Hangzhou Sciener Smart Technology Co.,Ltd.</t>
+          <t>江西荣科新型材料有限公司 / JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Zoey Zhang</t>
+          <t>Lucy Zeng (曾露)</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>zoey@sciener.com</t>
+          <t>lucy@rongkedecor.com</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>+86 178-5768-8782</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr"/>
-      <c r="G113" s="3" t="inlineStr">
-        <is>
-          <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
-        </is>
-      </c>
+          <t>+86-13134020034</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.amerdecor.com/</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr"/>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 20 / MOQ 100 Nice worker answered all questions</t>
+          <t>Buyer: 80 rmb for 230 meter</t>
         </is>
       </c>
     </row>
@@ -4899,30 +4895,30 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>江西荣科新型材料有限公司 / JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.</t>
+          <t>SANNORA</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Lucy Zeng (曾露)</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>lucy@rongkedecor.com</t>
-        </is>
-      </c>
+          <t>王冠</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>+86-13134020034</t>
+          <t>+86 13229297183</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>https://www.amerdecor.com/</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr"/>
+          <t>WWW.SANNORA.COM; WWW.SANNORA-BATH.COM</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -4930,7 +4926,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 80 rmb for 230 meter</t>
+          <t>Buyer: 1560 rmb for whole item</t>
         </is>
       </c>
     </row>
@@ -4940,38 +4936,42 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>SANNORA</t>
+          <t>Kaiping Gold Medal Sanitary Ware Co.,Ltd. / Guangdong Aosman Sanitary Ware Co.,Ltd</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>王冠</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr"/>
+          <t>Sophia Deng (邓小艳)</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>sophiadeng@china-gold.cn</t>
+        </is>
+      </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>+86 13229297183</t>
+          <t>+181 3838 6948</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>WWW.SANNORA.COM; WWW.SANNORA-BATH.COM</t>
+          <t>http://www.china-gold.cn, http://www.aosman.cn</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区</t>
+          <t>198 Siqian Xi Road, Shuikou, Kaiping 529300, Guangdong PR.China</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1560 rmb for whole item</t>
+          <t>Buyer: 4600 rmb</t>
         </is>
       </c>
     </row>
@@ -4981,42 +4981,22 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Kaiping Gold Medal Sanitary Ware Co.,Ltd. / Guangdong Aosman Sanitary Ware Co.,Ltd</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Sophia Deng (邓小艳)</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>sophiadeng@china-gold.cn</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>+181 3838 6948</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>http://www.china-gold.cn, http://www.aosman.cn</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>198 Siqian Xi Road, Shuikou, Kaiping 529300, Guangdong PR.China</t>
-        </is>
-      </c>
+          <t>东风汽车</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr"/>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 4600 rmb</t>
+          <t>Buyer: 50 Yuan 50g (The taste is authentic and aroma is really good</t>
         </is>
       </c>
     </row>
@@ -5026,14 +5006,34 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>东风汽车</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr"/>
-      <c r="D117" s="3" t="inlineStr"/>
-      <c r="E117" s="3" t="inlineStr"/>
-      <c r="F117" s="3" t="inlineStr"/>
-      <c r="G117" s="3" t="inlineStr"/>
+          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.LTD.</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Eric Huang</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>464565801@qq.com</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>13813551160, 0519-88784050</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>www.ycpanel.com</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>#28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+        </is>
+      </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 50 Yuan 50g (The taste is authentic and aroma is really good</t>
+          <t>Buyer: 2085</t>
         </is>
       </c>
     </row>
@@ -5051,32 +5051,28 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.LTD.</t>
+          <t>江西瑞京鸿兴实业有限公司</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Eric Huang</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>464565801@qq.com</t>
-        </is>
-      </c>
+          <t>朱支群</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>13813551160, 0519-88784050</t>
+          <t>13763963598</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>www.ycpanel.com</t>
+          <t>www.jx-wpc.com</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>#28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+          <t>江西省瑞金市经济开发区创业一路东侧</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -5086,7 +5082,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 2085</t>
+          <t>Buyer: 250¥/м3</t>
         </is>
       </c>
     </row>
@@ -5096,38 +5092,42 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>江西瑞京鸿兴实业有限公司</t>
+          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>朱支群</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr"/>
+          <t>Anne</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>victor@ck-bath.com</t>
+        </is>
+      </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>13763963598</t>
+          <t>18656330093</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>www.jx-wpc.com</t>
+          <t>https://ck-bath.com/</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>江西省瑞金市经济开发区创业一路东侧</t>
+          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 250¥/м3</t>
+          <t>Buyer: 4500¥</t>
         </is>
       </c>
     </row>
@@ -5137,42 +5137,42 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd</t>
+          <t>ciarra</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>victor@ck-bath.com</t>
+          <t>linda.lu@ciarrahome.com</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>18656330093</t>
+          <t>+86 1882 9964 960, +86 1343 2639 580</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>https://ck-bath.com/</t>
+          <t>www.ciarrahome.com</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
+          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 4500¥</t>
+          <t>Buyer: 300¥ 300pcs</t>
         </is>
       </c>
     </row>
@@ -5182,32 +5182,28 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>ciarra</t>
+          <t>Yekalon Mills</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Viola Liu</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>linda.lu@ciarrahome.com</t>
+          <t>wood6@sennorwell.com</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>+86 1882 9964 960, +86 1343 2639 580</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>www.ciarrahome.com</t>
-        </is>
-      </c>
+          <t>(86) 158 8931 1832</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr"/>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
+          <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
@@ -5217,7 +5213,7 @@
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 300¥ 300pcs</t>
+          <t>Buyer: 50¥ 1000pcs</t>
         </is>
       </c>
     </row>
@@ -5227,38 +5223,42 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Yekalon Mills</t>
+          <t>Ideal Sanitary Ware Co., Ltd.</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Viola Liu</t>
+          <t>Amy Liu 刘建美</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>wood6@sennorwell.com</t>
+          <t>export@ideal-china.net</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>(86) 158 8931 1832</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr"/>
+          <t>+86 (0) 757 8558 9299</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>www.ideal-sanitary.com</t>
+        </is>
+      </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
+          <t>No.3 Hexi Road of Shashui, Yanghe Town, Gaoming District, Foshan City, Guangdong Province, 528515 - P.R.China.</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 50¥ 1000pcs</t>
+          <t>Buyer: 500$ 100psc</t>
         </is>
       </c>
     </row>
@@ -5268,32 +5268,32 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Ideal Sanitary Ware Co., Ltd.</t>
+          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd.</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Amy Liu 刘建美</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>export@ideal-china.net</t>
+          <t>victor@ck-bath.com</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>+86 (0) 757 8558 9299</t>
+          <t>18656330093</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>www.ideal-sanitary.com</t>
+          <t>https://ck-bath.com/</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>No.3 Hexi Road of Shashui, Yanghe Town, Gaoming District, Foshan City, Guangdong Province, 528515 - P.R.China.</t>
+          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 500$ 100psc</t>
+          <t>Buyer: 4500¥</t>
         </is>
       </c>
     </row>
@@ -5313,42 +5313,38 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd.</t>
+          <t>佛山市旌晨铝门窗有限公司</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>胡光辉</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>victor@ck-bath.com</t>
+          <t>1525423805@qq.com</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>18656330093</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>https://ck-bath.com/</t>
-        </is>
-      </c>
+          <t>18128752879</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
+          <t>佛山狮山镇谭边工业区崩岗头路四号之一</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 4500¥</t>
+          <t>Buyer: 980y/m2, moq 1000p, like doors with Mosquito netting</t>
         </is>
       </c>
     </row>
@@ -5358,38 +5354,42 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>佛山市旌晨铝门窗有限公司</t>
+          <t>佛山市乾泽科技有限公司</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>胡光辉</t>
+          <t>陈可樑</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>1525423805@qq.com</t>
+          <t>hw-hardware@qian-ze.com</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>18128752879</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr"/>
+          <t>180 3863 7238</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>www.honeywell-hardware.com</t>
+        </is>
+      </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>佛山狮山镇谭边工业区崩岗头路四号之一</t>
+          <t>广东省佛山市三水区云东海街道宝盛路2号1座三层（合和建筑五金园区北门）</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 980y/m2, moq 1000p, like doors with Mosquito netting</t>
+          <t>Buyer: 1000-2000p, 1.7-7$, good beautiful doors handless</t>
         </is>
       </c>
     </row>
@@ -5399,42 +5399,26 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>佛山市乾泽科技有限公司</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>陈可樑</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>hw-hardware@qian-ze.com</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>180 3863 7238</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>www.honeywell-hardware.com</t>
-        </is>
-      </c>
+          <t>ARTY 艺和</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr"/>
+      <c r="D126" s="2" t="inlineStr"/>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市三水区云东海街道宝盛路2号1座三层（合和建筑五金园区北门）</t>
+          <t>广东 · 开平</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1000-2000p, 1.7-7$, good beautiful doors handless</t>
+          <t>Buyer: Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
         </is>
       </c>
     </row>
@@ -5444,18 +5428,14 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>ARTY 艺和</t>
+          <t>SUNHOHI 新豪轩门窗</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr"/>
       <c r="D127" s="3" t="inlineStr"/>
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3" t="inlineStr"/>
-      <c r="G127" s="3" t="inlineStr">
-        <is>
-          <t>广东 · 开平</t>
-        </is>
-      </c>
+      <c r="G127" s="3" t="inlineStr"/>
       <c r="H127" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5473,14 +5453,26 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SUNHOHI 新豪轩门窗</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr"/>
+          <t>景德镇窑珍陶瓷</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>徐云霞</t>
+        </is>
+      </c>
       <c r="D128" s="2" t="inlineStr"/>
-      <c r="E128" s="2" t="inlineStr"/>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>13697981203</t>
+        </is>
+      </c>
       <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
+        </is>
+      </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5488,7 +5480,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
+          <t>Buyer: 100 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -5498,24 +5490,24 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>景德镇窑珍陶瓷</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>徐云霞</t>
-        </is>
-      </c>
+          <t>苏州东山茶厂 (Suzhou Dongshan Biluochun Tea Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr"/>
       <c r="D129" s="3" t="inlineStr"/>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>13697981203</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="inlineStr"/>
+          <t>0512-66281146</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>www.dsteaf.com</t>
+        </is>
+      </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
+          <t>江苏省苏州市吴中区东山镇 (Dongshan Town, Wuzhong District, Suzhou City)</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
@@ -5525,7 +5517,7 @@
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 100 RMB per sample. The taste is very good</t>
+          <t>Buyer: 150 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -5535,26 +5527,14 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>苏州东山茶厂 (Suzhou Dongshan Biluochun Tea Co., Ltd.)</t>
+          <t>武夷星</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr"/>
       <c r="D130" s="2" t="inlineStr"/>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>0512-66281146</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>www.dsteaf.com</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>江苏省苏州市吴中区东山镇 (Dongshan Town, Wuzhong District, Suzhou City)</t>
-        </is>
-      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5562,7 +5542,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 150 RMB per sample. The taste is very good</t>
+          <t>Buyer: 250 RMB per sample. The taste is very good</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5552,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>武夷星</t>
+          <t>湖北龙王垭茶业有限公司</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr"/>
@@ -5587,7 +5567,7 @@
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 250 RMB per sample. The taste is very good</t>
+          <t>Buyer: 498rmb/unit. I like the green tea in white color. First time to see colorless tea and it was amazing, i will recommend it to my country’s local market.</t>
         </is>
       </c>
     </row>
@@ -5597,14 +5577,22 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>湖北龙王垭茶业有限公司</t>
+          <t>知和香馆</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr"/>
       <c r="D132" s="2" t="inlineStr"/>
-      <c r="E132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>15926183211</t>
+        </is>
+      </c>
       <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>福建永春达埔</t>
+        </is>
+      </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5612,7 +5600,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 498rmb/unit. I like the green tea in white color. First time to see colorless tea and it was amazing, i will recommend it to my country’s local market.</t>
+          <t>Buyer: They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
         </is>
       </c>
     </row>
@@ -5622,20 +5610,32 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>知和香馆</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr"/>
-      <c r="D133" s="3" t="inlineStr"/>
+          <t>San Nora (聖羅蘭·衛浴)</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>ALLEN XU (许熙平)</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>sales@sannora.com</t>
+        </is>
+      </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>15926183211</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="inlineStr"/>
+          <t>+86 137 0263 0244, +86-757-86438259</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>WWW.SANNORA.COM, WWW.SANNORA-BATH.COM</t>
+        </is>
+      </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>福建永春达埔</t>
+          <t>TANBIAN IND. ZONE, SHISHAN TOWN, NANHAI DIST., FOSHAN, GUANGDONG, CHINA</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>Buyer: They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
+          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -5655,34 +5655,30 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>San Nora (聖羅蘭·衛浴)</t>
+          <t>PTAT | 帕兰蒂诺</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>ALLEN XU (许熙平)</t>
+          <t>Joy Yang</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>sales@sannora.com</t>
+          <t>joy@rans.group</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>+86 137 0263 0244, +86-757-86438259</t>
+          <t>+86-13757430301</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>WWW.SANNORA.COM, WWW.SANNORA-BATH.COM</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>TANBIAN IND. ZONE, SHISHAN TOWN, NANHAI DIST., FOSHAN, GUANGDONG, CHINA</t>
-        </is>
-      </c>
+          <t>www.ptat.cn</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5700,30 +5696,30 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>PTAT | 帕兰蒂诺</t>
+          <t>万磊建筑涂料有限公司</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Joy Yang</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>joy@rans.group</t>
-        </is>
-      </c>
+          <t>万磊市场部</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr"/>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>+86-13757430301</t>
+          <t>186-8825-1404, 4000-147-187</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>www.ptat.cn</t>
-        </is>
-      </c>
-      <c r="G135" s="3" t="inlineStr"/>
+          <t>http://www.fswanlei.com</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区</t>
+        </is>
+      </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5741,28 +5737,32 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>万磊建筑涂料有限公司</t>
+          <t>ZHEJIANG SEATING TECHNOLOGY CO., LTD.</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>万磊市场部</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr"/>
+          <t>May Zhang</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>sales5@anjeurostilefurniture.com</t>
+        </is>
+      </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>186-8825-1404, 4000-147-187</t>
+          <t>+86 182 5727 1590</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>http://www.fswanlei.com</t>
+          <t>www.zjseating.com</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区</t>
+          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>Buyer: 1100</t>
         </is>
       </c>
     </row>
@@ -5782,42 +5782,42 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>ZHEJIANG SEATING TECHNOLOGY CO., LTD.</t>
+          <t>Chaozhou Lefu Sanitary Ware Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>May Zhang</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>sales5@anjeurostilefurniture.com</t>
+          <t>lucy@lefucz.com</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>+86 182 5727 1590</t>
+          <t>+0086 18098114370</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>www.zjseating.com</t>
+          <t>www.lefucz.com</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
+          <t>Lefu Sanitary Ware, Sheweikeng, Dengtang Town, Chaoan District, Chaozhou City, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1100</t>
+          <t>Buyer: 1050</t>
         </is>
       </c>
     </row>
@@ -5827,42 +5827,22 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Chaozhou Lefu Sanitary Ware Technology Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>lucy@lefucz.com</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>+0086 18098114370</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>www.lefucz.com</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>Lefu Sanitary Ware, Sheweikeng, Dengtang Town, Chaoan District, Chaozhou City, Guangdong Province, China</t>
-        </is>
-      </c>
+          <t>宜昌毛尖</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr"/>
+      <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1050</t>
+          <t>Buyer: Prices are go and packing and Verstaliy is more</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5852,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>宜昌毛尖</t>
+          <t>湖北龙王娅茶业有限公司</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr"/>
@@ -5887,7 +5867,7 @@
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Prices are go and packing and Verstaliy is more</t>
+          <t>Buyer: The taste anaroma is good of this product then anyother</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5877,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>湖北龙王娅茶业有限公司</t>
+          <t>正山堂 (ZHENG SHAN TANG)</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr"/>
@@ -5912,7 +5892,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Buyer: The taste anaroma is good of this product then anyother</t>
+          <t>Buyer: the product prices are very good. looks attractive</t>
         </is>
       </c>
     </row>
@@ -5922,13 +5902,29 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>正山堂 (ZHENG SHAN TANG)</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr"/>
-      <c r="D141" s="3" t="inlineStr"/>
-      <c r="E141" s="3" t="inlineStr"/>
-      <c r="F141" s="3" t="inlineStr"/>
+          <t>江西荣科新型建材有限公司 (JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.)</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Lucy Zeng (曾露)</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>lucy@rongkedecor.com</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>+86-13134020034</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>https://www.amerdecor.com/</t>
+        </is>
+      </c>
       <c r="G141" s="3" t="inlineStr"/>
       <c r="H141" s="3" t="inlineStr">
         <is>
@@ -5937,7 +5933,7 @@
       </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>Buyer: the product prices are very good. looks attractive</t>
+          <t>Buyer: 650 moq 300</t>
         </is>
       </c>
     </row>
@@ -5947,30 +5943,30 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>江西荣科新型建材有限公司 (JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.)</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Lucy Zeng (曾露)</t>
-        </is>
-      </c>
+          <t>浙江雅柔装饰材料有限公司 (Zhejiang Yarou Decoration Material Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr"/>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>lucy@rongkedecor.com</t>
+          <t>sale01@yarouwallpaper.com.cn</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>+86-13134020034</t>
+          <t>+86-18069994326, +86-18069994377</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>https://www.amerdecor.com/</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr"/>
+          <t>https://www.yarouwallpaper.com.cn/</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>浙江省金华市义乌市福田街道涌金大道87号厂房二楼 (No. 1, Factory 2, Yongjin Avenue 87, Futian Subdistrict, Yiwu City, Jinhua City, Zhejiang Province)</t>
+        </is>
+      </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5978,7 +5974,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 650 moq 300</t>
+          <t>Buyer: 14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
         </is>
       </c>
     </row>
@@ -5988,38 +5984,34 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>浙江雅柔装饰材料有限公司 (Zhejiang Yarou Decoration Material Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr"/>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>sale01@yarouwallpaper.com.cn</t>
-        </is>
-      </c>
+          <t>淄博永顺装饰材料有限公司</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>戴艳辉</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr"/>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>+86-18069994326, +86-18069994377</t>
-        </is>
-      </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t>https://www.yarouwallpaper.com.cn/</t>
-        </is>
-      </c>
+          <t>18830173388</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr"/>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市福田街道涌金大道87号厂房二楼 (No. 1, Factory 2, Yongjin Avenue 87, Futian Subdistrict, Yiwu City, Jinhua City, Zhejiang Province)</t>
+          <t>石家庄市正定县曙光路49号东标和聚居</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
+          <t>Buyer: 0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
         </is>
       </c>
     </row>
@@ -6029,34 +6021,42 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>淄博永顺装饰材料有限公司</t>
+          <t>宏宇集团 (HONGYU GROUP)</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>戴艳辉</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr"/>
+          <t>Melina 王玲</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>lina@hongyugroup.com</t>
+        </is>
+      </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>18830173388</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr"/>
+          <t>+86 13827702216</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>en.hongyugroup.com</t>
+        </is>
+      </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>石家庄市正定县曙光路49号东标和聚居</t>
+          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
+          <t>Buyer: 20</t>
         </is>
       </c>
     </row>
@@ -6066,32 +6066,32 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>宏宇集团 (HONGYU GROUP)</t>
+          <t>Chongnuo(Shandong)NewMaterial Co.,Ltd.</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Melina 王玲</t>
+          <t>Daisy</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>lina@hongyugroup.com</t>
+          <t>sales06@chongnuo-floors.com</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>+86 13827702216</t>
+          <t>+86 19906379675</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>en.hongyugroup.com</t>
+          <t>www.chongnuo-floors.com</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
+          <t>QingyunCounty,DezhouCity,China</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 20</t>
+          <t>Buyer: 9$</t>
         </is>
       </c>
     </row>
@@ -6111,34 +6111,26 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Chongnuo(Shandong)NewMaterial Co.,Ltd.</t>
+          <t>上海德翔木业有限公司 (Shanghai Dexiang Wood Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Daisy</t>
+          <t>崔强 (Cui Qiang)</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>sales06@chongnuo-floors.com</t>
+          <t>513437660@qq.com</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>+86 19906379675</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>www.chongnuo-floors.com</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>QingyunCounty,DezhouCity,China</t>
-        </is>
-      </c>
+          <t>+8618901960431</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -6146,7 +6138,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 9$</t>
+          <t>Buyer: 13.25$</t>
         </is>
       </c>
     </row>
@@ -6156,26 +6148,30 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>上海德翔木业有限公司 (Shanghai Dexiang Wood Industry Co., Ltd.)</t>
+          <t>中材(邯郸)新材料有限公司 (China National Building Materials (Handan) New Materials Co.,Ltd.)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>崔强 (Cui Qiang)</t>
+          <t>Wangfeng</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>513437660@qq.com</t>
+          <t>2523911877@qq.com</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>+8618901960431</t>
+          <t>13233648687</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr"/>
-      <c r="G147" s="3" t="inlineStr"/>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
+        </is>
+      </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -6183,7 +6179,7 @@
       </c>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 13.25$</t>
+          <t>Buyer: 8.83$</t>
         </is>
       </c>
     </row>
@@ -6193,28 +6189,20 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>中材(邯郸)新材料有限公司 (China National Building Materials (Handan) New Materials Co.,Ltd.)</t>
+          <t>Zhejiang Tianyan Holding Ltd</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Wangfeng</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>2523911877@qq.com</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>13233648687</t>
-        </is>
-      </c>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
+          <t>Taizhou, Zhejiang</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -6224,7 +6212,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 8.83$</t>
+          <t>Buyer: 640 PCs, 3.72 RMB very good</t>
         </is>
       </c>
     </row>
@@ -6234,30 +6222,38 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Zhejiang Tianyan Holding Ltd</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>Nicole</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr"/>
-      <c r="E149" s="3" t="inlineStr"/>
-      <c r="F149" s="3" t="inlineStr"/>
+          <t>Foshan Cofesu Sanitary Ware Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr"/>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>sales@cofesu.com</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>+86 181 2821 2128</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>www.cofesu.com</t>
+        </is>
+      </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>Taizhou, Zhejiang</t>
+          <t>Foshan, Guangdong, China</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 640 PCs, 3.72 RMB very good</t>
+          <t>Buyer: 30 PCs, 420 RMB, need check quality</t>
         </is>
       </c>
     </row>
@@ -6267,38 +6263,38 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Foshan Cofesu Sanitary Ware Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr"/>
+          <t>中国广东柜邦精密金属制品有限公司 (China Guangdong Guibang Precision Metal Products Co.Ltd)</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>唐一智 (JUNIOR)</t>
+        </is>
+      </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>sales@cofesu.com</t>
+          <t>13621417@qq.com</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>+86 181 2821 2128</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>www.cofesu.com</t>
-        </is>
-      </c>
+          <t>+86-156-2562-1155</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Foshan, Guangdong, China</t>
+          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 30 PCs, 420 RMB, need check quality</t>
+          <t>Buyer: 10000</t>
         </is>
       </c>
     </row>
@@ -6308,28 +6304,28 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>中国广东柜邦精密金属制品有限公司 (China Guangdong Guibang Precision Metal Products Co.Ltd)</t>
+          <t>Jieyang Yagegu Hardware Products Co., LTD</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>唐一智 (JUNIOR)</t>
+          <t>Zoya</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>13621417@qq.com</t>
+          <t>2291828903@qq.com</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>+86-156-2562-1155</t>
+          <t>+86 132 8810 6615</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr"/>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
+          <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
@@ -6349,28 +6345,28 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Jieyang Yagegu Hardware Products Co., LTD</t>
+          <t>广东启宏盛精密五金制品有限公司 (GUANGDONG QIHONGSHENG PRECISION HARDWARE PRODUCTS CO., LTD)</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Zoya</t>
+          <t>邓美君 Jessica</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>2291828903@qq.com</t>
+          <t>bailide_hinge@163.com</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>+86 132 8810 6615</t>
+          <t>+86 13823419116 / 0758-8565117</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
+          <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -6380,7 +6376,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 10000</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -6390,28 +6386,32 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>广东启宏盛精密五金制品有限公司 (GUANGDONG QIHONGSHENG PRECISION HARDWARE PRODUCTS CO., LTD)</t>
+          <t>广东亚当斯金属精密制造有限公司 (Guangdong Adams Metal Precision Manufacturing Co.,Ltd)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>邓美君 Jessica</t>
+          <t>Kelly Liang (梁凯莹)</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>bailide_hinge@163.com</t>
+          <t>kelly@adamsmetal.com.cn</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>+86 13823419116 / 0758-8565117</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="inlineStr"/>
+          <t>+86-180-2935-2895 / +86-757-25331912</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>www.adamsmetal.com.cn</t>
+        </is>
+      </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
+          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 100</t>
+          <t>Buyer: Depend on item</t>
         </is>
       </c>
     </row>
@@ -6431,34 +6431,18 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>广东亚当斯金属精密制造有限公司 (Guangdong Adams Metal Precision Manufacturing Co.,Ltd)</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Kelly Liang (梁凯莹)</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>kelly@adamsmetal.com.cn</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>+86-180-2935-2895 / +86-757-25331912</t>
-        </is>
-      </c>
+          <t>明德 (Mingde)</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr"/>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>www.adamsmetal.com.cn</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
-        </is>
-      </c>
+          <t>www.mingde-china.com</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
@@ -6466,7 +6450,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Depend on item</t>
+          <t>Buyer: Depend of quantity</t>
         </is>
       </c>
     </row>
@@ -6476,26 +6460,42 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>明德 (Mingde)</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr"/>
-      <c r="D155" s="3" t="inlineStr"/>
-      <c r="E155" s="3" t="inlineStr"/>
+          <t>佛山市顺德区腾徽精密智造有限公司 (FoShan ShunDe TengHui Precision Intelligent Manufacturing Co., Ltd)</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>刘婉莹 Carol Liu</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>tenghuihardware@126.com</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>+86 133 1836 4599</t>
+        </is>
+      </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>www.mingde-china.com</t>
-        </is>
-      </c>
-      <c r="G155" s="3" t="inlineStr"/>
+          <t>www.teehve.cn</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区勒流街道众涌村港口路以西8-9号之二 (No.8-9, West of GangKou Road, Zhongchong Village, Leliu Town, Shunde District, Foshan City, Guangdong, China)</t>
+        </is>
+      </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Depend of quantity</t>
+          <t>Buyer: 100/square meter</t>
         </is>
       </c>
     </row>
@@ -6505,42 +6505,42 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>佛山市顺德区腾徽精密智造有限公司 (FoShan ShunDe TengHui Precision Intelligent Manufacturing Co., Ltd)</t>
+          <t>DUOCAI TENT (多彩帐蓬)</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>刘婉莹 Carol Liu</t>
+          <t>Jimmy 黄锦民</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>tenghuihardware@126.com</t>
+          <t>sales003@sdduocaizp.com</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>+86 133 1836 4599</t>
+          <t>(86)133 2294 8506, +86-766-8298662</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>www.teehve.cn</t>
+          <t>www.dc-tent.com, www.sdduocaizp.com</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区勒流街道众涌村港口路以西8-9号之二 (No.8-9, West of GangKou Road, Zhongchong Village, Leliu Town, Shunde District, Foshan City, Guangdong, China)</t>
+          <t>云浮市云安区佛山(云浮)产业转移工业园86号 (No.86 Foshan(Yunfu) Industrial transfer park, yunan, yunfu, Guangdong China)</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 100/square meter</t>
+          <t>Buyer: RMB 15705 MOQ5; pleasant impression</t>
         </is>
       </c>
     </row>
@@ -6550,42 +6550,42 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>DUOCAI TENT (多彩帐蓬)</t>
+          <t>佛山市路乐户外制品有限公司 (FOSHAN RULER OUTDOOR HARDWARES CO.,LTD)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Jimmy 黄锦民</t>
+          <t>Marco Lau (刘嘉乐)</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>sales003@sdduocaizp.com</t>
+          <t>RULERAWNING07@163.COM</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>(86)133 2294 8506, +86-766-8298662</t>
+          <t>+86 13129016338</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>www.dc-tent.com, www.sdduocaizp.com</t>
+          <t>WWW.RULER-AWNING.COM</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>云浮市云安区佛山(云浮)产业转移工业园86号 (No.86 Foshan(Yunfu) Industrial transfer park, yunan, yunfu, Guangdong China)</t>
+          <t>END OF ROAD SHATANXIAN, SHASHUI INDUSTRIAL ZONE, SONGGANG TOWN, SHISHAN DISTRICT, FOSHAN CITY, GUANGDONG PROVINCE, CHINA, 528200</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
         <is>
-          <t>Buyer: RMB 15705 MOQ5; pleasant impression</t>
+          <t>Buyer: MOQ5 25799 RMB</t>
         </is>
       </c>
     </row>
@@ -6595,32 +6595,32 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>佛山市路乐户外制品有限公司 (FOSHAN RULER OUTDOOR HARDWARES CO.,LTD)</t>
+          <t>Avant Sports Industrial Co., Ltd.</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Marco Lau (刘嘉乐)</t>
+          <t>Jay Zhou</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>RULERAWNING07@163.COM</t>
+          <t>jay@avant.com.cn</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>+86 13129016338</t>
+          <t>+86-13128980150, +86-755-2968-8357</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>WWW.RULER-AWNING.COM</t>
+          <t>www.avantseating.com</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>END OF ROAD SHATANXIAN, SHASHUI INDUSTRIAL ZONE, SONGGANG TOWN, SHISHAN DISTRICT, FOSHAN CITY, GUANGDONG PROVINCE, CHINA, 528200</t>
+          <t>Avant Industrial Park, Zhoushi Road, Bao'an, Shenzhen, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ5 25799 RMB</t>
+          <t>Buyer: RMB 19479; MOQ 1</t>
         </is>
       </c>
     </row>
@@ -6640,42 +6640,42 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Avant Sports Industrial Co., Ltd.</t>
+          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd.)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Jay Zhou</t>
+          <t>孟少美 (Elite Meng)</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>jay@avant.com.cn</t>
+          <t>ttf@hbtfjs.com</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>+86-13128980150, +86-755-2968-8357</t>
+          <t>+86-13103196326</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>www.avantseating.com</t>
+          <t>www.hbtfjs.com</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>Avant Industrial Park, Zhoushi Road, Bao'an, Shenzhen, Guangdong Province, China</t>
+          <t>河北省隆尧县东谷子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
         <is>
-          <t>Buyer: RMB 19479; MOQ 1</t>
+          <t>Buyer: 1000</t>
         </is>
       </c>
     </row>
@@ -6685,37 +6685,37 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd.)</t>
+          <t>揭阳市新骏业五金制品有限公司 (JIEYANG XINJUNYE HARDWARE PRODUCTS CO., LTD)</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>孟少美 (Elite Meng)</t>
+          <t>林树丹 (Lin Shudan)</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>ttf@hbtfjs.com</t>
+          <t>linshdong@qq.com</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>+86-13103196326</t>
+          <t>13751676456</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>www.hbtfjs.com</t>
+          <t>www.xinjunye.com</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>河北省隆尧县东谷子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
+          <t>广东省揭阳市揭东区锡场工业区 (Xichang Industrial Zone, Jiedong District, Jieyang City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>揭阳市新骏业五金制品有限公司 (JIEYANG XINJUNYE HARDWARE PRODUCTS CO., LTD)</t>
+          <t>Guangdong Adams Metal Precision Manufacturing Co., Ltd (广东亚当斯金属精密制造有限公司)</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>林树丹 (Lin Shudan)</t>
+          <t>Kelly Liang (梁凯莹)</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>linshdong@qq.com</t>
+          <t>kelly@adamsmetal.com.cn</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>13751676456</t>
+          <t>+86-180-2935-2895, +86-757-25331912</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>www.xinjunye.com</t>
+          <t>www.adamsmetal.com.cn</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>广东省揭阳市揭东区锡场工业区 (Xichang Industrial Zone, Jiedong District, Jieyang City, Guangdong Province)</t>
+          <t>No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province (广东省佛山市顺德区勒流镇港口路10号)</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
@@ -6775,42 +6775,42 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Guangdong Adams Metal Precision Manufacturing Co., Ltd (广东亚当斯金属精密制造有限公司)</t>
+          <t>广州蒙娜丽莎控股集团有限公司 / 广州蒙娜丽莎卫浴股份有限公司</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Kelly Liang (梁凯莹)</t>
+          <t>伍乐彤</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>kelly@adamsmetal.com.cn</t>
+          <t>monalisa702@monalisa.cn</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>+86-180-2935-2895, +86-757-25331912</t>
+          <t>86 13711117863, 400 020 1818, 86 20-28607722, 86 20-28607788</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>www.adamsmetal.com.cn</t>
+          <t>www.monalisa.cn</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province (广东省佛山市顺德区勒流镇港口路10号)</t>
+          <t>广州市花都区花东镇港头工业区4号</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1000</t>
+          <t>Buyer: 2000$, can be customized, very convenient</t>
         </is>
       </c>
     </row>
@@ -6820,42 +6820,42 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>广州蒙娜丽莎控股集团有限公司 / 广州蒙娜丽莎卫浴股份有限公司</t>
+          <t>中山藝進不銹鋼裝飾制品有限公司 (ZHONGSHAN YIJIN STAINLESS STEEL DECORATION CO., LTD.)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>伍乐彤</t>
+          <t>Anson Yuen</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>monalisa702@monalisa.cn</t>
+          <t>info@hugemount.com</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>86 13711117863, 400 020 1818, 86 20-28607722, 86 20-28607788</t>
+          <t>150 1954 6322 / 86-760-88702663</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>www.monalisa.cn</t>
+          <t>www.yijin.com</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>广州市花都区花东镇港头工业区4号</t>
+          <t>中国广东省中山市港口镇石特社区穗安工业区迎富2路1号 (NO.1, Ying Fu 2 Road, Sui An Gong Ye Qu, Gang Kou Zhen Shi Te She Qu, Zhongshan City, Guangdong Province, P.R.China)</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 2000$, can be customized, very convenient</t>
+          <t>Buyer: 38$, very unique</t>
         </is>
       </c>
     </row>
@@ -6865,42 +6865,42 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>中山藝進不銹鋼裝飾制品有限公司 (ZHONGSHAN YIJIN STAINLESS STEEL DECORATION CO., LTD.)</t>
+          <t>宣城市宠爱卫浴有限公司 (CHONGAI SANITARY WARE CO., LTD.)</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Anson Yuen</t>
+          <t>Lucy (卢美珍)</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>info@hugemount.com</t>
+          <t>export@vnsmilo.com</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>150 1954 6322 / 86-760-88702663</t>
+          <t>+86-13757322119</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>www.yijin.com</t>
+          <t>www.vnsmilo.com</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>中国广东省中山市港口镇石特社区穗安工业区迎富2路1号 (NO.1, Ying Fu 2 Road, Sui An Gong Ye Qu, Gang Kou Zhen Shi Te She Qu, Zhongshan City, Guangdong Province, P.R.China)</t>
+          <t>Xuancheng City Anhui, CHINA</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 38$, very unique</t>
+          <t>Buyer: 2050 rmb, very interesting, convenient to use for pets</t>
         </is>
       </c>
     </row>
@@ -6910,42 +6910,30 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>宣城市宠爱卫浴有限公司 (CHONGAI SANITARY WARE CO., LTD.)</t>
+          <t>广西中晨木业有限公司 (Guangxi Zhongchen Wood Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Lucy (卢美珍)</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>export@vnsmilo.com</t>
-        </is>
-      </c>
+          <t>张爱彬 (Zhang Aibin)</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr"/>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>+86-13757322119</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t>www.vnsmilo.com</t>
-        </is>
-      </c>
-      <c r="G165" s="3" t="inlineStr">
-        <is>
-          <t>Xuancheng City Anhui, CHINA</t>
-        </is>
-      </c>
+          <t>+86 18178085851</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr"/>
+      <c r="G165" s="3" t="inlineStr"/>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 2050 rmb, very interesting, convenient to use for pets</t>
+          <t>Buyer: 25 rmb, 1 box, like this product</t>
         </is>
       </c>
     </row>
@@ -6955,22 +6943,34 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>广西中晨木业有限公司 (Guangxi Zhongchen Wood Industry Co., Ltd.)</t>
+          <t>NINGBO YUSHENG HOME TECH CO., LTD. (宁波裕盛家居科技有限公司)</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>张爱彬 (Zhang Aibin)</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr"/>
+          <t>Tequila Xu (徐孟杰)</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>marketing@cxyushun.com, tequila8xu@gmail.com</t>
+        </is>
+      </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>+86 18178085851</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr"/>
-      <c r="G166" s="2" t="inlineStr"/>
+          <t>0086-13819449988, +86 574 63190388</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>www.cxys8.com</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>中国浙江慈溪市杨梅大道南路1518号 (NO.1518, YANGMEI AVENUE SOUTH ROAD, CIXI CITY, ZHEJIANG, CHINA)</t>
+        </is>
+      </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 25 rmb, 1 box, like this product</t>
+          <t>Buyer: 34 rmb, 1000, normal</t>
         </is>
       </c>
     </row>
@@ -6988,42 +6988,42 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>NINGBO YUSHENG HOME TECH CO., LTD. (宁波裕盛家居科技有限公司)</t>
+          <t>河北建华锁业有限公司 (Hebei Jianhua Lock Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Tequila Xu (徐孟杰)</t>
+          <t>刘芳 (Jane Liu)</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>marketing@cxyushun.com, tequila8xu@gmail.com</t>
+          <t>jane@dirock.cn</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>0086-13819449988, +86 574 63190388</t>
+          <t>187 1377 2087</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>www.cxys8.com</t>
+          <t>http://www.dirock.cn</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>中国浙江慈溪市杨梅大道南路1518号 (NO.1518, YANGMEI AVENUE SOUTH ROAD, CIXI CITY, ZHEJIANG, CHINA)</t>
+          <t>河北省泊头市寺门村镇后牛屯</t>
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 34 rmb, 1000, normal</t>
+          <t>Buyer: 40 rmb, 2000, very good</t>
         </is>
       </c>
     </row>
@@ -7033,42 +7033,42 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>河北建华锁业有限公司 (Hebei Jianhua Lock Industry Co., Ltd.)</t>
+          <t>浙江安吉双虎竹木业有限公司 / 安吉诺迪新材料有限公司</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>刘芳 (Jane Liu)</t>
+          <t>周瑶琳</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>jane@dirock.cn</t>
+          <t>lisa.nordi@nuodibm.com</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>187 1377 2087</t>
+          <t>+86-137 3822 8209</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>http://www.dirock.cn</t>
+          <t>www.tigerbamboo.com / www.nuodibm.com</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>河北省泊头市寺门村镇后牛屯</t>
+          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 40 rmb, 2000, very good</t>
+          <t>Buyer: 1 container 250 rmb</t>
         </is>
       </c>
     </row>
@@ -7078,32 +7078,32 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>浙江安吉双虎竹木业有限公司 / 安吉诺迪新材料有限公司</t>
+          <t>宏宇集团 HONGYU GROUP</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>周瑶琳</t>
+          <t>Melina 王玲</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>lisa.nordi@nuodibm.com</t>
+          <t>lina@hongyugroup.com</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>+86-137 3822 8209</t>
+          <t>+86 13827702216</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>www.tigerbamboo.com / www.nuodibm.com</t>
+          <t>en.hongyugroup.com</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
+          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="I169" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1 container 250 rmb</t>
+          <t>Buyer: Жду коммерческое предложение. Компания понравилась</t>
         </is>
       </c>
     </row>
@@ -7123,42 +7123,42 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>宏宇集团 HONGYU GROUP</t>
+          <t>ZHEJIANG TIANYAN HOLDING CO.,LTD.</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Melina 王玲</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>lina@hongyugroup.com</t>
+          <t>ty11@cntianyan.com</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>+86 13827702216</t>
+          <t>+86-15867028552</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>en.hongyugroup.com</t>
+          <t>www.cntianyan.com</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
+          <t>Chengjiang industrial zone,huangyan district taizhou,zhejiang,china</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Жду коммерческое предложение. Компания понравилась</t>
+          <t>Buyer: Цена зависит от обьема, от 3 юаней, расходники</t>
         </is>
       </c>
     </row>
@@ -7168,72 +7168,27 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>ZHEJIANG TIANYAN HOLDING CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>Nicole</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>ty11@cntianyan.com</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>+86-15867028552</t>
-        </is>
-      </c>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t>www.cntianyan.com</t>
-        </is>
-      </c>
-      <c r="G171" s="3" t="inlineStr">
-        <is>
-          <t>Chengjiang industrial zone,huangyan district taizhou,zhejiang,china</t>
-        </is>
-      </c>
+          <t>BANRUGE / KING LIYE</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr"/>
+      <c r="D171" s="3" t="inlineStr"/>
+      <c r="E171" s="3" t="inlineStr"/>
+      <c r="F171" s="3" t="inlineStr"/>
+      <c r="G171" s="3" t="inlineStr"/>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Цена зависит от обьема, от 3 юаней, расходники</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="n">
-        <v>171</v>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>BANRUGE / KING LIYE</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr"/>
-      <c r="D172" s="2" t="inlineStr"/>
-      <c r="E172" s="2" t="inlineStr"/>
-      <c r="F172" s="2" t="inlineStr"/>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>Building Decoration</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
           <t>Buyer: Прайс отправят, от 100ед, хорошая компания</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I172"/>
+  <autoFilter ref="A1:I171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cbd-catalog/cbd_suppliers.xlsx
+++ b/cbd-catalog/cbd_suppliers.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CBD Suppliers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CBD Suppliers'!$A$1:$I$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CBD Suppliers'!$A$1:$I$166</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I171"/>
+  <dimension ref="A1:I166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -527,37 +527,37 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Guangdong Fuson Windoor Industry Co., Ltd</t>
+          <t>Sunhohi</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Eileen Yip (叶颖怡)</t>
+          <t>Crystal Wong</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>export09@fusonwindoor.com</t>
+          <t>crystal@sunhohiglobal.com</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>+86 18028156982</t>
+          <t>+86-137 0262 5097</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>www.fusonwindoor.com</t>
+          <t>www.sunhohiwindow.com</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Fuxuan Office Building, 2nd Longhu Rd, High Tech District, Zhaoqing City, Guangdong Province</t>
+          <t>Marketing Center: 20th Floor, Building A1, Full International Financial Center, No. 28, Haiwu Road, Guicheng Street, Nanhai District, Foshan City, Guangdong Province, China; Factory: Zhenxing 3rd Road, Xincheng Town, Xinxing County, Yunfu City, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -572,22 +572,34 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>开平艺和门业有限公司</t>
+          <t>Guangdong Fuson Windoor Industry Co., Ltd</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>张硕怡 (Stoney)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
+          <t>Eileen Yip (叶颖怡)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>export09@fusonwindoor.com</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>134 1416 0636</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+          <t>+86 18028156982</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>www.fusonwindoor.com</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Fuxuan Office Building, 2nd Longhu Rd, High Tech District, Zhaoqing City, Guangdong Province</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
@@ -605,42 +617,30 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SUNHOHI Smart Home Co., Ltd</t>
+          <t>开平艺和门业有限公司</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Crystal Wong 黄健秋</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>info@sunhohiglobal.com, crystalwindowsanddoors0908@gmail.com</t>
-        </is>
-      </c>
+          <t>张硕怡 (Stoney)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0086-137 0262 5097, 0086-138 2396 7979</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>www.sunhohiwindow.com</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>R&amp;F International Financial Center, Nanhai District, Foshan City, Guangdong Province, China</t>
-        </is>
-      </c>
+          <t>134 1416 0636</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1000 pcs price 120 usd</t>
+          <t>Buyer: 50.000¥. Moq-1</t>
         </is>
       </c>
     </row>
@@ -650,32 +650,32 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>河南贝迪塑业有限公司 (Henan Beidi Plastic Industry Co., Ltd.)</t>
+          <t>SUNHOHI Smart Home Co., Ltd</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Jane Li (李蓉娟)</t>
+          <t>Crystal Wong 黄健秋</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Jane@hncrown.com</t>
+          <t>info@sunhohiglobal.com, crystalwindowsanddoors0908@gmail.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>+86 187 3917 6242 / 86-0372-6270170</t>
+          <t>0086-137 0262 5097, 0086-138 2396 7979</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>www.baydeegroup.com / www.hnbeidi.com</t>
+          <t>www.sunhohiwindow.com</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>中国·河南省鹤壁市 (Hebi City, Henan Province, China)</t>
+          <t>R&amp;F International Financial Center, Nanhai District, Foshan City, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1000 pcs price 38 USD</t>
+          <t>Buyer: 1000 pcs price 120 usd</t>
         </is>
       </c>
     </row>
@@ -695,32 +695,32 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Guangzhou NewHoo Technology Co. Ltd</t>
+          <t>河南贝迪塑业有限公司 (Henan Beidi Plastic Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Tony</t>
+          <t>Jane Li (李蓉娟)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>export01@gznewhoo.com</t>
+          <t>Jane@hncrown.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>+86-198-7837-3626</t>
+          <t>+86 187 3917 6242 / 86-0372-6270170</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>www.gznewhoo.com</t>
+          <t>www.baydeegroup.com / www.hnbeidi.com</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Building 7, Hongyu Smart Industrial Park, No. 333 Juhuashi Avenue, Huadu District, Guangzhou</t>
+          <t>中国·河南省鹤壁市 (Hebi City, Henan Province, China)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 80$</t>
+          <t>Buyer: 1000 pcs price 38 USD</t>
         </is>
       </c>
     </row>
@@ -740,16 +740,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>旭博卫浴</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
+          <t>Guangzhou NewHoo Technology Co. Ltd</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Tony</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>export01@gznewhoo.com</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>+86-198-7837-3626</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>www.gznewhoo.com</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>福建省南安市</t>
+          <t>Building 7, Hongyu Smart Industrial Park, No. 333 Juhuashi Avenue, Huadu District, Guangzhou</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -759,7 +775,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 70$</t>
+          <t>Buyer: 80$</t>
         </is>
       </c>
     </row>
@@ -769,14 +785,18 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>旭博恒温</t>
+          <t>旭博卫浴</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>福建省南安市</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -784,7 +804,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 300 yuan</t>
+          <t>Buyer: 70$</t>
         </is>
       </c>
     </row>
@@ -794,34 +814,14 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>榜威电子科技（上海）有限公司 (Bweetech Electronics Technology (Shanghai) Co., Ltd)</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>骆剑 (Kim Lok)</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>kim.lok@bweetech.com</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>186-5759-0678</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>www.bweetech.com</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
-        </is>
-      </c>
+          <t>旭博恒温</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -829,7 +829,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 500pcs / $100USD for pcs</t>
+          <t>Buyer: 300 yuan</t>
         </is>
       </c>
     </row>
@@ -839,14 +839,34 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>深圳市塞恩斯电子有限公司 (Sands Evermore Electronic)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>榜威电子科技（上海）有限公司 (Bweetech Electronics Technology (Shanghai) Co., Ltd)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>骆剑 (Kim Lok)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>kim.lok@bweetech.com</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>186-5759-0678</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>www.bweetech.com</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>上海市松江区沪亭北路99弄金地广场1号楼7层 (F7, #1, Plaza Jindi, Lane 99, North Huting Rd, Songjiang District, Shanghai)</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -854,7 +874,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 50pcs / $50USD for pcs</t>
+          <t>Buyer: 500pcs / $100USD for pcs</t>
         </is>
       </c>
     </row>
@@ -864,7 +884,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>HDL</t>
+          <t>深圳市塞恩斯电子有限公司 (Sands Evermore Electronic)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
@@ -879,7 +899,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 20pcs / $100USD for pcs</t>
+          <t>Buyer: 50pcs / $50USD for pcs</t>
         </is>
       </c>
     </row>
@@ -889,38 +909,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>DEIOUX WINDOWS &amp; DOORS</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>CANDICE CHOU</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>sales5@deiouxwindows.com</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>+86-13392246940</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
-        </is>
-      </c>
+          <t>HDL</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Custom order</t>
+          <t>Buyer: 20pcs / $100USD for pcs</t>
         </is>
       </c>
     </row>
@@ -930,30 +934,30 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>China Warren Windows and Doors Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr"/>
+          <t>DEIOUX WINDOWS &amp; DOORS</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>CANDICE CHOU</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>info@warrenwindows.com</t>
+          <t>sales5@deiouxwindows.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>+86-400-811-0300</t>
+          <t>+86-13392246940</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>www.warrenwindows.com</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Room 1007, Block B, Wangjing SOHO, Chaoyang District, Beijing, China</t>
-        </is>
-      </c>
+          <t>WWW.DEIOUXWINDOWS.COM / WWW.DEIOUX-WINDOW.COM</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Doors &amp; Windows</t>
@@ -971,25 +975,33 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Matthew window&amp;door</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>张小洪 (Matthew / Kevin)</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+          <t>China Warren Windows and Doors Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>info@warrenwindows.com</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>+86-400-811-0300</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>www.warrenwindows.com</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Foshan, Guangdong</t>
+          <t>Room 1007, Block B, Wangjing SOHO, Chaoyang District, Beijing, China</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1004,42 +1016,30 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Zhongshan Smartek Security Technology Co.,LTD</t>
+          <t>Matthew window&amp;door</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Tim Pan</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>market@smarteklock.com</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>+86-15889896019</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>www.smarteklock.com</t>
-        </is>
-      </c>
+          <t>张小洪 (Matthew / Kevin)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City Guangdong, China 528415</t>
+          <t>Foshan, Guangdong</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 170 to 335 usd</t>
+          <t>Buyer: Custom order</t>
         </is>
       </c>
     </row>
@@ -1049,38 +1049,42 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>HDL Automation Co., Ltd.</t>
+          <t>Zhongshan Smartek Security Technology Co.,LTD</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Krystal Wei</t>
+          <t>Tim Pan</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>krystal@hdlautomation.com</t>
+          <t>market@smarteklock.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>+86 19512956186</t>
+          <t>+86-15889896019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>www.hdlautomation.com</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>www.smarteklock.com</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6F, Bldg 10, No.1 Shengyu Rd.Jidonger, Xiaolan Town, Zhongshan City Guangdong, China 528415</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 100 to up</t>
+          <t>Buyer: 170 to 335 usd</t>
         </is>
       </c>
     </row>
@@ -1090,42 +1094,38 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Ningbo AIFEIBAO Intelligent Security Co., Ltd</t>
+          <t>HDL Automation Co., Ltd.</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Sean Xiao</t>
+          <t>Krystal Wei</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>sales@aifeibao.com</t>
+          <t>krystal@hdlautomation.com</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>0086 198 1730 8681</t>
+          <t>+86 19512956186</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>www.afbsafe.com</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>No.1 Donghu Rd., Daxie Development Zone, Ningbo, China (315812)</t>
-        </is>
-      </c>
+          <t>www.hdlautomation.com</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 100 to up usd</t>
+          <t>Buyer: 100 to up</t>
         </is>
       </c>
     </row>
@@ -1135,34 +1135,42 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>佛山市普辉亚科技有限公司 (Foshan Pu Huiya Technology Co., Ltd.)</t>
+          <t>Ningbo AIFEIBAO Intelligent Security Co., Ltd</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>邹隆鹏</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
+          <t>Sean Xiao</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>sales@aifeibao.com</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15818099349</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
+          <t>0086 198 1730 8681</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>www.afbsafe.com</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
+          <t>No.1 Donghu Rd., Daxie Development Zone, Ningbo, China (315812)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Super</t>
+          <t>Buyer: 100 to up usd</t>
         </is>
       </c>
     </row>
@@ -1172,32 +1180,24 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>广东招材建材科技有限公司</t>
+          <t>佛山市普辉亚科技有限公司 (Foshan Pu Huiya Technology Co., Ltd.)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>黎桃桃</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>toto.liblun@gmail.com</t>
-        </is>
-      </c>
+          <t>邹隆鹏</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>+8618934320539</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>www.liblun.com</t>
-        </is>
-      </c>
+          <t>15818099349</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
+          <t>佛山市顺德区北滘镇顺江社区兴业东路2号启德置业园5栋1楼 (1st Floor, Building 5, Qide Real Estate Park, No. 2 Xingye East Road, Shunjiang, Beijiao Town, Shunde District, Foshan City)</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1217,38 +1217,42 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>浙江鑫东洁具有限公司 (ZHEJIANG XINDONG SANITARY WARE CO., LTD.)</t>
+          <t>广东招材建材科技有限公司</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>曾燕燕 Elyn</t>
+          <t>黎桃桃</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>sales03@cn-xindong.com</t>
+          <t>toto.liblun@gmail.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0086-182 5765 3405, 0086-576-87493988</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
+          <t>+8618934320539</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>www.liblun.com</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
+          <t>广东省佛山市南海区罗行社区新下村5号厂房</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 50</t>
+          <t>Buyer: Super</t>
         </is>
       </c>
     </row>
@@ -1258,34 +1262,38 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>杭州南博装饰材料有限公司</t>
+          <t>浙江鑫东洁具有限公司 (ZHEJIANG XINDONG SANITARY WARE CO., LTD.)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>王小忠</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
+          <t>曾燕燕 Elyn</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>sales03@cn-xindong.com</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
+          <t>0086-182 5765 3405, 0086-576-87493988</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区运河街道育士路53-1号</t>
+          <t>Xuanmen Industrial Zone, Yuhuan, Zhejiang, China, 317608</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 100</t>
+          <t>Buyer: 50</t>
         </is>
       </c>
     </row>
@@ -1295,37 +1303,29 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>台州旭升卫浴股份有限公司</t>
+          <t>杭州南博装饰材料有限公司</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>应杨军</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>3572780651@qq.com</t>
-        </is>
-      </c>
+          <t>王小忠</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13511470999</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>www.xs88.cn</t>
-        </is>
-      </c>
+          <t>189 6909 8963, 0571-8936 7998, 89367999, 180 7280 6350, 300 755 1089</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>浙江省台州市台州湾新区海虹大道228#</t>
+          <t>浙江省杭州市临平区运河街道育士路53-1号</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1340,38 +1340,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>NIFO 耐孚</t>
+          <t>台州旭升卫浴股份有限公司</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>顾鹏</t>
+          <t>应杨军</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>962460053@qq.com</t>
+          <t>3572780651@qq.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>13326792105</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr"/>
+          <t>13511470999</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>www.xs88.cn</t>
+        </is>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
+          <t>浙江省台州市台州湾新区海虹大道228#</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Wall sheet , 200 rmb per meter , 2000 mtr,</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -1381,28 +1385,28 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Zhejiang Oushe Home Improvement And New Materials Co., Ltd.</t>
+          <t>NIFO 耐孚</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Davis Dong 董伟杰</t>
+          <t>顾鹏</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>sales05@authoe.com</t>
+          <t>962460053@qq.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>+86-18906831082</t>
+          <t>13326792105</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Jiaxing/Hongkong</t>
+          <t>广东省佛山市南海区狮山镇博爱东路博爱工业区横跨路一号(2号厂房)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1412,7 +1416,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Handles , 500 moq , 100 rmb per handle</t>
+          <t>Buyer: Wall sheet , 200 rmb per meter , 2000 mtr,</t>
         </is>
       </c>
     </row>
@@ -1422,38 +1426,38 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>JIN OGMEI</t>
+          <t>Zhejiang Oushe Home Improvement And New Materials Co., Ltd.</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Alex Xing</t>
+          <t>Davis Dong 董伟杰</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>kindeli1771@gmail.com</t>
+          <t>sales05@authoe.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>+86-18302200384</t>
+          <t>+86-18906831082</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Shijiazhuang City, Hebei Province</t>
+          <t>Jiaxing/Hongkong</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
+          <t>Buyer: Handles , 500 moq , 100 rmb per handle</t>
         </is>
       </c>
     </row>
@@ -1463,42 +1467,38 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>温州金锏智能锁具有限公司</t>
+          <t>JIN OGMEI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>张丽</t>
+          <t>Alex Xing</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>jinjian19@jinjianlock.com</t>
+          <t>kindeli1771@gmail.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15067804393</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>www.jinjianlock.com</t>
-        </is>
-      </c>
+          <t>+86-18302200384</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号</t>
+          <t>Shijiazhuang City, Hebei Province</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for customized branding. Feedback: The company has a professional production line and solid hardware quality. Their prices are very competitive for the mass market, although their software ecosystem is less advanced than Innovation's current solutions. They are a reliable choice for high-volume, cost-effective projects.</t>
+          <t>Buyer: Wall sheet and wooden wall sheet , 2000mtr , 150 rmb per mtr</t>
         </is>
       </c>
     </row>
@@ -1508,32 +1508,32 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>上海世灿国际贸易有限公司</t>
+          <t>温州金锏智能锁具有限公司</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>杨苗</t>
+          <t>张丽</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>yangm618@163.com</t>
+          <t>jinjian19@jinjianlock.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>138 1618 4706</t>
+          <t>15067804393</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>http://www.shicanchina.com</t>
+          <t>www.jinjianlock.com</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>上海市浦东新区商城路889号C3-B06</t>
+          <t>温州市瓯海区娄桥街道华盟特色轻工园区1号</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models and 150 units for custom OEM branding. Feedback: Yang Miao Miao demonstrates excellent mechanical build quality and focuses heavily on the structural integrity of the doors. Their pricing is mid-range, offering a good balance between durability and cost. They are highly flexible with custom design requests, making them a strong potential partner for Innovation’s specialized architectural projects.</t>
+          <t>Buyer: Price: 800 – 2600 CNY per unit depending on the model and features. MOQ: 100 units for standard orders and 300 units for customized branding. Feedback: The company has a professional production line and solid hardware quality. Their prices are very competitive for the mass market, although their software ecosystem is less advanced than Innovation's current solutions. They are a reliable choice for high-volume, cost-effective projects.</t>
         </is>
       </c>
     </row>
@@ -1553,32 +1553,32 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>COLOMAC DECOR</t>
+          <t>上海世灿国际贸易有限公司</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Aaron Liu</t>
+          <t>杨苗</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>aaron@ccolomac.com</t>
+          <t>yangm618@163.com</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>+86-0371-66350801, +86 15936292861</t>
+          <t>138 1618 4706</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>www.ccolomac.com</t>
+          <t>http://www.shicanchina.com</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
+          <t>上海市浦东新区商城路889号C3-B06</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 100 units for customized decorative panels. Feedback: Colomac Decor stands out for its superior aesthetic design and premium finishing materials. Their products align well with luxury interiors, showing high attention to detail in surface textures. They are an ideal partner for Innovation when the goal is to merge smart technology with high-end interior aesthetics.</t>
+          <t>Buyer: Price: 1200 – 3500 CNY per unit depending on materials and security specifications. MOQ: 50 units for standard models and 150 units for custom OEM branding. Feedback: Yang Miao Miao demonstrates excellent mechanical build quality and focuses heavily on the structural integrity of the doors. Their pricing is mid-range, offering a good balance between durability and cost. They are highly flexible with custom design requests, making them a strong potential partner for Innovation’s specialized architectural projects.</t>
         </is>
       </c>
     </row>
@@ -1598,34 +1598,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>佛山市同路匠人家具有限公司</t>
+          <t>COLOMAC DECOR</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>赖华芳</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr"/>
+          <t>Aaron Liu</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>aaron@ccolomac.com</t>
+        </is>
+      </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>13727479513, 400-8339513</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr"/>
+          <t>+86-0371-66350801, +86 15936292861</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>www.ccolomac.com</t>
+        </is>
+      </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
+          <t>No. 171 Zhongyuan Middle Road, Zhengzhou, Henan, China</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Хорошее, 400rmb</t>
+          <t>Buyer: Price: 1800 – 4500 CNY per unit based on the finish and decorative complexity. MOQ: 30 units for standard designs and 100 units for customized decorative panels. Feedback: Colomac Decor stands out for its superior aesthetic design and premium finishing materials. Their products align well with luxury interiors, showing high attention to detail in surface textures. They are an ideal partner for Innovation when the goal is to merge smart technology with high-end interior aesthetics.</t>
         </is>
       </c>
     </row>
@@ -1635,38 +1643,34 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>固豪木业 | SUNDIN尚鼎</t>
+          <t>佛山市同路匠人家具有限公司</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Clément / 付雄豪</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>clement.fu@cqsdmy.com</t>
-        </is>
-      </c>
+          <t>赖华芳</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>+(86) 19112691557</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>www.guhaogroup.com / www.cqsdmy.com</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
+          <t>13727479513, 400-8339513</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区龙江镇联塑嘉园三路3号9513家具总部</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Хорошее , 1500rmb</t>
+          <t>Buyer: Хорошее, 400rmb</t>
         </is>
       </c>
     </row>
@@ -1676,38 +1680,38 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>佛山市嘉豪飞度家具有限公司 (FOSHAN KAHO FIT FURNITURE CO., LTD.)</t>
+          <t>固豪木业 | SUNDIN尚鼎</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>周灿灿</t>
+          <t>Clément / 付雄豪</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>15986196312@163.com</t>
+          <t>clement.fu@cqsdmy.com</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>159 1909 0393, +86-757-2339 1505</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
-        </is>
-      </c>
+          <t>+(86) 19112691557</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>www.guhaogroup.com / www.cqsdmy.com</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Нормальное</t>
+          <t>Buyer: Хорошее , 1500rmb</t>
         </is>
       </c>
     </row>
@@ -1717,22 +1721,38 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>中山市福乐门智能科技有限公司 / 中山市乐帝智能科技有限公司</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
+          <t>佛山市嘉豪飞度家具有限公司 (FOSHAN KAHO FIT FURNITURE CO., LTD.)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>周灿灿</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>15986196312@163.com</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>159 1909 0393, +86-757-2339 1505</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区乐从镇黎湖工业区</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Buyer: $176, MOQ 50, very good!</t>
+          <t>Buyer: Нормальное</t>
         </is>
       </c>
     </row>
@@ -1742,42 +1762,22 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Suzhou Acousound New Material Technology Inc.</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Yolanda He</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>acousound07@polyacoustic.com</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>+86-18068038050</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>www.polyacoustic.com</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
-        </is>
-      </c>
+          <t>中山市福乐门智能科技有限公司 / 中山市乐帝智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Buyer: $55, MOQ100pcs, good</t>
+          <t>Buyer: $176, MOQ 50, very good!</t>
         </is>
       </c>
     </row>
@@ -1787,22 +1787,42 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>特斯豹工具</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+          <t>Suzhou Acousound New Material Technology Inc.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Yolanda He</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>acousound07@polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>+86-18068038050</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Buyer: $30, MOQ 10pcs, nice</t>
+          <t>Buyer: $55, MOQ100pcs, good</t>
         </is>
       </c>
     </row>
@@ -1812,42 +1832,22 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>CGCH</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>陈洁玲 Rowling</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>014@cgchcontainer.com</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>+86 189 2997 1329</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>www.cgchcontainer.com</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
-        </is>
-      </c>
+          <t>特斯豹工具</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1000 yuan 1 square</t>
+          <t>Buyer: $30, MOQ 10pcs, nice</t>
         </is>
       </c>
     </row>
@@ -1857,34 +1857,42 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>广东省中山名谷屋木门厂</t>
+          <t>CGCH</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>罗美玲</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>陈洁玲 Rowling</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>014@cgchcontainer.com</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>180 0760 4399</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
+          <t>+86 189 2997 1329</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>www.cgchcontainer.com</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
+          <t>Rm. 5710, 656 Huangpu Ave., Tianhe, Guangzhou</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 150 rmb</t>
+          <t>Buyer: 1000 yuan 1 square</t>
         </is>
       </c>
     </row>
@@ -1894,42 +1902,34 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>multishades</t>
+          <t>广东省中山名谷屋木门厂</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Sophia</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>sophia@multishades.com.cn</t>
-        </is>
-      </c>
+          <t>罗美玲</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>0086-15918713187, 0086-757-86780865</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>www.multishades.com.cn</t>
-        </is>
-      </c>
+          <t>180 0760 4399</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Office: Room 1501, CITIC Plaza, No.233, Tianhebei Road, Guangzhou City, Guangdong Province, China; Factory: 1 Shengshi Road, Shibei Industrial Park, Shishan Town, Foshan City, Guangdong Province, China</t>
+          <t>广东省中山市小榄镇东升门业生产基地F5B</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 570 rmb</t>
+          <t>Buyer: 150 rmb</t>
         </is>
       </c>
     </row>
@@ -1939,18 +1939,34 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>超友皮革家居</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>multishades</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Sophia</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>sophia@multishades.com.cn</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1561767</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+          <t>0086-15918713187, 0086-757-86780865</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>www.multishades.com.cn</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Office: Room 1501, CITIC Plaza, No.233, Tianhebei Road, Guangzhou City, Guangdong Province, China; Factory: 1 Shengshi Road, Shibei Industrial Park, Shishan Town, Foshan City, Guangdong Province, China</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -1958,7 +1974,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 130 super</t>
+          <t>Buyer: 570 rmb</t>
         </is>
       </c>
     </row>
@@ -1968,38 +1984,26 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co.,Ltd)</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>欧阳玉滢 (Sonia Ouyang)</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>sonia.ouyang@wireking.com</t>
-        </is>
-      </c>
+          <t>超友皮革家居</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>+86-13392758223</t>
+          <t>1561767</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
-        </is>
-      </c>
+      <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Buyer: $32, MOQ 300, good</t>
+          <t>Buyer: 130 super</t>
         </is>
       </c>
     </row>
@@ -2009,32 +2013,28 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PTA DOOR Automation (Hunan Tianan Door Technology Co., Ltd.)</t>
+          <t>广东伟经家居制品有限公司 (Guangdong Wireking Household Products Co.,Ltd)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Eva Leng</t>
+          <t>欧阳玉滢 (Sonia Ouyang)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>eva@ptadoor.com</t>
+          <t>sonia.ouyang@wireking.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>+86 19848080478, +44 7704 561086</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>global.ptadoor.com</t>
-        </is>
-      </c>
+          <t>+86-13392758223</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Xincheng technology park, Yuelu Avenue, Changsha Hunan China</t>
+          <t>广东省佛山市顺德区均安镇智安北路12号 (No.12 Zhi'an North Road, Jun'an, Shunde, Foshan, Guangdong, China)</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Buyer: ¥3000, MoQ 1pcs, very good</t>
+          <t>Buyer: $32, MOQ 300, good</t>
         </is>
       </c>
     </row>
@@ -2054,32 +2054,32 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>丰顺县泰雅达实业有限公司</t>
+          <t>PTA DOOR Automation (Hunan Tianan Door Technology Co., Ltd.)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>徐小俊</t>
+          <t>Eva Leng</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>281431686@qq.com</t>
+          <t>eva@ptadoor.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>13802731123</t>
+          <t>+86 19848080478, +44 7704 561086</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>https://taiyada1688.1688.com/</t>
+          <t>global.ptadoor.com</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>广东省丰顺县汤坑镇太平北路</t>
+          <t>Xincheng technology park, Yuelu Avenue, Changsha Hunan China</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Buyer: ¥17, Moq 50, good</t>
+          <t>Buyer: ¥3000, MoQ 1pcs, very good</t>
         </is>
       </c>
     </row>
@@ -2099,42 +2099,42 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>佛山市悠派家居科技有限公司</t>
+          <t>丰顺县泰雅达实业有限公司</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>黄伟业</t>
+          <t>徐小俊</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Yea@LGPKB.com</t>
+          <t>281431686@qq.com</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13825596371</t>
+          <t>13802731123</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>www.LGPKB.com</t>
+          <t>https://taiyada1688.1688.com/</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
+          <t>广东省丰顺县汤坑镇太平北路</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 600 RMB Great, very cheap</t>
+          <t>Buyer: ¥17, Moq 50, good</t>
         </is>
       </c>
     </row>
@@ -2144,18 +2144,34 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>艾锐特</t>
+          <t>佛山市悠派家居科技有限公司</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>冯蕾</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
+          <t>黄伟业</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Yea@LGPKB.com</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>13825596371</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>www.LGPKB.com</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市顺德区大良街道古鉴成展路3号</t>
+        </is>
+      </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2163,7 +2179,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 3400, Good price</t>
+          <t>Buyer: 600 RMB Great, very cheap</t>
         </is>
       </c>
     </row>
@@ -2173,30 +2189,18 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>常州市永春保温材料有限公司 (Changzhou Yongchun Thermal Insulation Materials Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>yc@ycbycl.com</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>0519-88931168</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>www.ycbycl.com</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>江苏省常州市天宁区郑陆镇工业集中区</t>
-        </is>
-      </c>
+          <t>艾锐特</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>冯蕾</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2204,7 +2208,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 10$</t>
+          <t>Buyer: 3400, Good price</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2218,28 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>诺奥(福建)环保家居用品有限公司</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>曾令贵</t>
-        </is>
-      </c>
+          <t>常州市永春保温材料有限公司 (Changzhou Yongchun Thermal Insulation Materials Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>513573190@qq.com</t>
+          <t>yc@ycbycl.com</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>86-13585642723 / 0596-8273388-8083</t>
+          <t>0519-88931168</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>www.fjnuoao.cn</t>
+          <t>www.ycbycl.com</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
+          <t>江苏省常州市天宁区郑陆镇工业集中区</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 69$</t>
+          <t>Buyer: 10$</t>
         </is>
       </c>
     </row>
@@ -2259,28 +2259,32 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>大音声学 (DAYIN ACOUSTICS)</t>
+          <t>诺奥(福建)环保家居用品有限公司</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>唐佳豪 (Vance)</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
+          <t>曾令贵</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>513573190@qq.com</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>+86 18925924350</t>
+          <t>86-13585642723 / 0596-8273388-8083</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>www.dayinacoustics.com</t>
+          <t>www.fjnuoao.cn</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>佛山市南海区里水镇赤山大道32号 (No.32 Chishan Avenue, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+          <t>福建省漳州市长泰区兴泰工业园区台湾工业园锦都路191号</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2290,7 +2294,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 50-85$</t>
+          <t>Buyer: 69$</t>
         </is>
       </c>
     </row>
@@ -2300,26 +2304,30 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>杭州班昇</t>
+          <t>大音声学 (DAYIN ACOUSTICS)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>陈卓敏 Ruby</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>295608376@qq.com</t>
-        </is>
-      </c>
+          <t>唐佳豪 (Vance)</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>+86 13556688832</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
+          <t>+86 18925924350</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>www.dayinacoustics.com</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>佛山市南海区里水镇赤山大道32号 (No.32 Chishan Avenue, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+        </is>
+      </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2327,7 +2335,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Buyer: ￥1000 good</t>
+          <t>Buyer: 50-85$</t>
         </is>
       </c>
     </row>
@@ -2337,34 +2345,26 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>FOSHAN SINCERE BUILDING MATERIALS CO., LTD.</t>
+          <t>杭州班昇</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Crystal 刘晓艺</t>
+          <t>陈卓敏 Ruby</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>crystal@sincerechina.net</t>
+          <t>295608376@qq.com</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>86-15815992213</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>www.sincerechina.net</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>佛山市禅城区南庄镇季华西路中国陶瓷产业总部基地西区C07-C08栋 (China Ceramics Industry Headquaters Block No.C07-08, West Area, West Jihua Road, Nanzhuang, Foshan, China)</t>
-        </is>
-      </c>
+          <t>+86 13556688832</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Buyer: ¥ 500 good</t>
+          <t>Buyer: ￥1000 good</t>
         </is>
       </c>
     </row>
@@ -2382,32 +2382,32 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Xiamen Golden Ricky Industry &amp; Trade Co.,Ltd</t>
+          <t>FOSHAN SINCERE BUILDING MATERIALS CO., LTD.</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Joan Liu</t>
+          <t>Crystal 刘晓艺</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>joan@goldenrickyhpl.com</t>
+          <t>crystal@sincerechina.net</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>+86 13599525074</t>
+          <t>86-15815992213</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Https://goldenrickyhpl.com</t>
+          <t>www.sincerechina.net</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Xiamen City, Fujian, China</t>
+          <t>佛山市禅城区南庄镇季华西路中国陶瓷产业总部基地西区C07-C08栋 (China Ceramics Industry Headquaters Block No.C07-08, West Area, West Jihua Road, Nanzhuang, Foshan, China)</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Buyer: ￥ 300 good</t>
+          <t>Buyer: ¥ 500 good</t>
         </is>
       </c>
     </row>
@@ -2427,30 +2427,42 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>江门市新阳刚智能科技有限公司</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
+          <t>Xiamen Golden Ricky Industry &amp; Trade Co.,Ltd</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Joan Liu</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>joan@goldenrickyhpl.com</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>135 3666 7789, 400-9090-518</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr"/>
+          <t>+86 13599525074</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Https://goldenrickyhpl.com</t>
+        </is>
+      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
+          <t>Xiamen City, Fujian, China</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 300 rmb and more. Good quality and good price. Small quantity</t>
+          <t>Buyer: ￥ 300 good</t>
         </is>
       </c>
     </row>
@@ -2460,42 +2472,30 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>河南蓝健陶瓷有限公司</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>王闻浠</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>lanjanweiyu@163.com</t>
-        </is>
-      </c>
+          <t>江门市新阳刚智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>+86-13569915996</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>www.lanjan.com</t>
-        </is>
-      </c>
+          <t>135 3666 7789, 400-9090-518</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>河南省长葛市石固镇梁庄工业园区</t>
+          <t>广东省江门市新会区大泽镇万洋众创城38-1号</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 33$ for 1 pcs. Good quality and quantity</t>
+          <t>Buyer: 300 rmb and more. Good quality and good price. Small quantity</t>
         </is>
       </c>
     </row>
@@ -2505,20 +2505,32 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>沃澜 (WOTUA)</t>
+          <t>河南蓝健陶瓷有限公司</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Dion Sun</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
+          <t>王闻浠</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>lanjanweiyu@163.com</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>+86-13569915996</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>www.lanjan.com</t>
+        </is>
+      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>3座104号</t>
+          <t>河南省长葛市石固镇梁庄工业园区</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2528,7 +2540,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Good quality and quantity. 140 rmb 1 pcs.</t>
+          <t>Buyer: 33$ for 1 pcs. Good quality and quantity</t>
         </is>
       </c>
     </row>
@@ -2538,22 +2550,22 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>三强地毯</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>hengsheng_carpet@163.com</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>0769-89807692</t>
-        </is>
-      </c>
+          <t>沃澜 (WOTUA)</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Dion Sun</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
       <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>3座104号</t>
+        </is>
+      </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2561,7 +2573,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Good 👍</t>
+          <t>Buyer: Good quality and quantity. 140 rmb 1 pcs.</t>
         </is>
       </c>
     </row>
@@ -2571,34 +2583,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Higold Group Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Willer Zhou</t>
-        </is>
-      </c>
+          <t>三强地毯</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>sale31@higold.com.cn</t>
+          <t>hengsheng_carpet@163.com</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>+86 158 2865 5891</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>www.higoldhardware.com</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>No.36 Shunye East Rd, Xingtan, Shunde, Foshan 528325, Guangdong, China</t>
-        </is>
-      </c>
+          <t>0769-89807692</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 5800</t>
+          <t>Buyer: Good 👍</t>
         </is>
       </c>
     </row>
@@ -2616,42 +2616,42 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Zhejiang Kehon Intelligent Science &amp; Technology Co., Ltd.</t>
+          <t>Higold Group Co., Ltd.</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Sammi Shi</t>
+          <t>Willer Zhou</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>sales01@kehon.cn</t>
+          <t>sale31@higold.com.cn</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>+86 156 8948 5097, 0578-3271096</t>
+          <t>+86 158 2865 5891</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>www.kehon.cn</t>
+          <t>www.higoldhardware.com</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
+          <t>No.36 Shunye East Rd, Xingtan, Shunde, Foshan 528325, Guangdong, China</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 130 yuan</t>
+          <t>Buyer: 5800</t>
         </is>
       </c>
     </row>
@@ -2661,42 +2661,42 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Guangdong Wanbang Modular Building Co., Ltd</t>
+          <t>Zhejiang Kehon Intelligent Science &amp; Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Richie Wang</t>
+          <t>Sammi Shi</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>richie.wang@wbhouse.com</t>
+          <t>sales01@kehon.cn</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>+86 137 1002 1675</t>
+          <t>+86 156 8948 5097, 0578-3271096</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>www.gdwbprefabhouse.com</t>
+          <t>www.kehon.cn</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Guangdong Factory: No.5, No. 161 Ganghe Avenue, Gaoming District, Foshan city, Guangdong, CHINA; Fujian Factory: Provincial Highway 308, Yunrong Township, Minqing County, Fuzhou City, Fujian Province, CHINA.</t>
+          <t>No.1 Hangchuan Rd., Huzhen Town, Jinyun County, Zhejiang, China</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 20000usd</t>
+          <t>Buyer: 130 yuan</t>
         </is>
       </c>
     </row>
@@ -2706,42 +2706,42 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Guhao Group | SEAJOIN</t>
+          <t>Guangdong Wanbang Modular Building Co., Ltd</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Owen Li</t>
+          <t>Richie Wang</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>owen.li@seajoinhouse.com</t>
+          <t>richie.wang@wbhouse.com</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>(86) 133 9501 1076</t>
+          <t>+86 137 1002 1675</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>www.seajoinhouse.com</t>
+          <t>www.gdwbprefabhouse.com</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Chongqing, China / Ho Chi Minh City, Vietnam</t>
+          <t>Guangdong Factory: No.5, No. 161 Ganghe Avenue, Gaoming District, Foshan city, Guangdong, CHINA; Fujian Factory: Provincial Highway 308, Yunrong Township, Minqing County, Fuzhou City, Fujian Province, CHINA.</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 500yuan</t>
+          <t>Buyer: 20000usd</t>
         </is>
       </c>
     </row>
@@ -2751,42 +2751,42 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CAE SANITARY FITTINGS INDUSTRY CO., LTD. GUANGDONG</t>
+          <t>Guhao Group | SEAJOIN</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Josie Guan</t>
+          <t>Owen Li</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>cae@china-cae.com</t>
+          <t>owen.li@seajoinhouse.com</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>+86-13702279135</t>
+          <t>(86) 133 9501 1076</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>www.china-cae.com</t>
+          <t>www.seajoinhouse.com</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>No.62-64, Xingda Rd., Shagang Dist., Shuikou Town, Kaiping, Guangdong, P.R.Of China.</t>
+          <t>Chongqing, China / Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 100, 47 rnb per piece</t>
+          <t>Buyer: 500yuan</t>
         </is>
       </c>
     </row>
@@ -2796,38 +2796,42 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>盐城格子匠家居有限公司</t>
+          <t>CAE SANITARY FITTINGS INDUSTRY CO., LTD. GUANGDONG</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>董华</t>
+          <t>Josie Guan</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>418897056@qq.com</t>
+          <t>cae@china-cae.com</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>13914649982, 18951488133</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr"/>
+          <t>+86-13702279135</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>www.china-cae.com</t>
+        </is>
+      </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
+          <t>No.62-64, Xingda Rd., Shagang Dist., Shuikou Town, Kaiping, Guangdong, P.R.Of China.</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 50, 200 rnb per</t>
+          <t>Buyer: MOQ 100, 47 rnb per piece</t>
         </is>
       </c>
     </row>
@@ -2837,32 +2841,28 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SUOFEIYA HOME COLLECTION CO., LTD</t>
+          <t>盐城格子匠家居有限公司</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Jasmine Guan 管敏秀</t>
+          <t>董华</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>jasmine@suofeiyahome.com</t>
+          <t>418897056@qq.com</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>+86 147 7520 2759</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sofeyiahome.com</t>
-        </is>
-      </c>
+          <t>13914649982, 18951488133</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
+          <t>江苏省盐城市亭湖区青墩头灶工业园全创路十号</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 10, 845 per piece</t>
+          <t>Buyer: MOQ 50, 200 rnb per</t>
         </is>
       </c>
     </row>
@@ -2882,32 +2882,32 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>利亚德光电股份有限公司 Leyard Optoelectronic Co., Ltd.</t>
+          <t>SUOFEIYA HOME COLLECTION CO., LTD</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>金厚强 Jin Houqiang</t>
+          <t>Jasmine Guan 管敏秀</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>jinhouqiang@leyard.com</t>
+          <t>jasmine@suofeiyahome.com</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>13510009569, 18829341125, 400-8592-666</t>
+          <t>+86 147 7520 2759</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>www.leyard.com</t>
+          <t>https://www.sofeyiahome.com</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋</t>
+          <t>SOFEYIA PLAZA, No. 87-89 Xingang East Road, Pazhou Street, Haizhu District, Guangzhou</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1pcs. Start from 60rmb. Novative technology</t>
+          <t>Buyer: MOQ 10, 845 per piece</t>
         </is>
       </c>
     </row>
@@ -2927,14 +2927,34 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>林商学社</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
+          <t>利亚德光电股份有限公司 Leyard Optoelectronic Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>金厚强 Jin Houqiang</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>jinhouqiang@leyard.com</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>13510009569, 18829341125, 400-8592-666</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>www.leyard.com</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>北京市海淀区颐和园北正红旗西街9号 / 深圳市龙华区观澜街道君子布社区观和路6号深圳利亚德微LED南方产业园A栋</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -2942,7 +2962,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Buyer: From 1pc. Natural materials.</t>
+          <t>Buyer: 1pcs. Start from 60rmb. Novative technology</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2972,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>佛山市威尔信保险柜有限公司 (Foshan Weierxin Safe Co., Ltd.)</t>
+          <t>林商学社</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr"/>
@@ -2967,7 +2987,7 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1250rmb. MOQ 1 pc</t>
+          <t>Buyer: From 1pc. Natural materials.</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2997,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SAKURA 樱花智能锁</t>
+          <t>佛山市威尔信保险柜有限公司 (Foshan Weierxin Safe Co., Ltd.)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr"/>
@@ -2992,7 +3012,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 199</t>
+          <t>Buyer: 1250rmb. MOQ 1 pc</t>
         </is>
       </c>
     </row>
@@ -3002,38 +3022,22 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>JNOD 基诺德</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>周信朋 Joe Zhou</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>sales02@jnodwater.com</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>+86 199 2825 2201, +86-757-2361 7920</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>www.jnodwater.com</t>
-        </is>
-      </c>
+          <t>SAKURA 樱花智能锁</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" s="3" t="inlineStr"/>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1410</t>
+          <t>Buyer: 199</t>
         </is>
       </c>
     </row>
@@ -3043,34 +3047,30 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>广州传祺时代智能科技有限公司</t>
+          <t>JNOD 基诺德</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>洪美兰</t>
+          <t>周信朋 Joe Zhou</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>jiang@chuangqitimes.com</t>
+          <t>sales02@jnodwater.com</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>13450298606, 020-82511901</t>
+          <t>+86 199 2825 2201, +86-757-2361 7920</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>www.chuangqitimes.com</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
-        </is>
-      </c>
+          <t>www.jnodwater.com</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Hardware</t>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 329</t>
+          <t>Buyer: 1410</t>
         </is>
       </c>
     </row>
@@ -3088,28 +3088,32 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>RUIKANG</t>
+          <t>广州传祺时代智能科技有限公司</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Jacky</t>
+          <t>洪美兰</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>sales08@ruikang-cn.com</t>
+          <t>jiang@chuangqitimes.com</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>+86 18028330648, +86 18022073939</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr"/>
+          <t>13450298606, 020-82511901</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>www.chuangqitimes.com</t>
+        </is>
+      </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
+          <t>广州市黄埔区云埔工业区观达路20号密博科技园</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
@@ -3119,7 +3123,7 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 229</t>
+          <t>Buyer: 329</t>
         </is>
       </c>
     </row>
@@ -3129,34 +3133,38 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>松下电器设备(中国)有限公司</t>
+          <t>RUIKANG</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>潘禹</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>sales08@ruikang-cn.com</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>13691864691</t>
+          <t>+86 18028330648, +86 18022073939</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
+          <t>2nd Yongyi Industrial Area, Donghai 5th Road, Dongfeng Town, Zhongshan, Guangdong, China</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 680</t>
+          <t>Buyer: 229</t>
         </is>
       </c>
     </row>
@@ -3166,42 +3174,34 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>CAE</t>
+          <t>松下电器设备(中国)有限公司</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Jack Guan</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>jack@cae.cn</t>
-        </is>
-      </c>
+          <t>潘禹</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>+86-750-8119338</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>www.cae.cn</t>
-        </is>
-      </c>
+          <t>13691864691</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
+          <t>广东省惠州市惠城区演达大道19号国安居6楼</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 150 yuan, 100, good range of products</t>
+          <t>Buyer: 680</t>
         </is>
       </c>
     </row>
@@ -3211,42 +3211,42 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>广东富矿智能家居有限公司 (Guangdong Fukuang Intelligent Home Co., Ltd.)</t>
+          <t>CAE</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>余赛银 (Yu Saiyin)</t>
+          <t>Jack Guan</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>109786129@qq.com</t>
+          <t>jack@cae.cn</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>+86 13660529010</t>
+          <t>+86-750-8119338</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>kingliye.com</t>
+          <t>www.cae.cn</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>佛山市南海区里广路二号碧桂园金沙国际广场1201室 (Room 1201, Building 10, Jinsha International Plaza No.2 Liguang Road, Nanhai District, Foshan City)</t>
+          <t>No.128, Chenghuan Road, Shuikou Town, Kaiping City, Guangdong, China</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
+          <t>Buyer: 150 yuan, 100, good range of products</t>
         </is>
       </c>
     </row>
@@ -3256,22 +3256,42 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>THOR 索而</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" s="3" t="inlineStr"/>
-      <c r="G71" s="3" t="inlineStr"/>
+          <t>广东富矿智能家居有限公司 (Guangdong Fukuang Intelligent Home Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>余赛银 (Yu Saiyin)</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>109786129@qq.com</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>+86 13660529010</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>kingliye.com</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>佛山市南海区里广路二号碧桂园金沙国际广场1201室 (Room 1201, Building 10, Jinsha International Plaza No.2 Liguang Road, Nanhai District, Foshan City)</t>
+        </is>
+      </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Buyer: The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
+          <t>Buyer: Set of furniture is very good quality, I like the company has also a showroom in Guangzhou</t>
         </is>
       </c>
     </row>
@@ -3281,33 +3301,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>肇庆合生雅居智能家居有限公司 (Zhaoqing Hesheng Yaju Intelligent Home Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Winni 何玲玲</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>helingling@gdhsyj.com</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>+86 18924564942</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>WWW.HOPSOONER.COM</t>
-        </is>
-      </c>
+          <t>THOR 索而</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3322,38 +3326,38 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>视威电子科技（上海）有限公司</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr"/>
+          <t>肇庆合生雅居智能家居有限公司 (Zhaoqing Hesheng Yaju Intelligent Home Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Winni 何玲玲</t>
+        </is>
+      </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>service@3weitech.com</t>
+          <t>helingling@gdhsyj.com</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>021-57715805</t>
+          <t>+86 18924564942</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>www.3weitech.com</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>上海市闵行区新骏环路188号11号楼A座518室</t>
-        </is>
-      </c>
+          <t>WWW.HOPSOONER.COM</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет проблема синхронизации . Есть свой искусственный интеллект . Нужно тестировать . Купили ленту у него лед, на телевизор как образец</t>
+          <t>Buyer: The price starts from three thousand yuan, the consultant showed all the functionality and provided a catalogue</t>
         </is>
       </c>
     </row>
@@ -3363,30 +3367,30 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>爱舒床垫集团有限公司</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>王鹏</t>
-        </is>
-      </c>
+          <t>视威电子科技（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1319129904@qq.com</t>
+          <t>service@3weitech.com</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>189-2324-7677</t>
+          <t>021-57715805</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>www.asnug.com</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr"/>
+          <t>www.3weitech.com</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>上海市闵行区新骏环路188号11号楼A座518室</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3394,7 +3398,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
+          <t>Buyer: 167 юаней , 500 штук минималка . Продукт хороший но у них свое приложение , не работают с Туя и Яндекс Алисой . Будет проблема синхронизации . Есть свой искусственный интеллект . Нужно тестировать . Купили ленту у него лед, на телевизор как образец</t>
         </is>
       </c>
     </row>
@@ -3404,34 +3408,30 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Suzhou Acesound New Material Technology Inc.</t>
+          <t>爱舒床垫集团有限公司</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Yolanda He</t>
+          <t>王鹏</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>ecosound02@polyacoustic.com</t>
+          <t>1319129904@qq.com</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>+86-18018130150</t>
+          <t>189-2324-7677</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>www.polyacoustic.com</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>No.10 Jinxi Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
-        </is>
-      </c>
+          <t>www.asnug.com</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
       <c r="H75" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного метра 150 юаней сказала примерно. Не до конца поняла точность минимальной партии, но говорили часто 100 кВ метром</t>
+          <t>Buyer: 20000 юаней . Качественный продукт, есть свое приложение. Но цена значительно завышена для подобного рода сегмента.</t>
         </is>
       </c>
     </row>
@@ -3449,26 +3449,34 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>soundbox</t>
+          <t>Suzhou Acesound New Material Technology Inc.</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>劉奕紫 Cathy</t>
+          <t>Yolanda He</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>sales19@soundbox.hk</t>
+          <t>ecosound02@polyacoustic.com</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>+86 137 6339 3059</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
+          <t>+86-18018130150</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>No.10 Jinxi Road, Xiangcheng, Suzhou, Jiangsu, China 215152</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3476,7 +3484,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Buyer: От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккуратная комната, достаточно комфортная. Цена немного завышена, встречали на других выставках пониже стоимостью.</t>
+          <t>Buyer: Необычный вариант стены. Можно очень вариативно украсить. Стоимость квадратного метра 150 юаней сказала примерно. Не до конца поняла точность минимальной партии, но говорили часто 100 кВ метром</t>
         </is>
       </c>
     </row>
@@ -3486,12 +3494,24 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>顶固集团</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr"/>
-      <c r="D77" s="3" t="inlineStr"/>
-      <c r="E77" s="3" t="inlineStr"/>
+          <t>soundbox</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>劉奕紫 Cathy</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>sales19@soundbox.hk</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>+86 137 6339 3059</t>
+        </is>
+      </c>
       <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" s="3" t="inlineStr"/>
       <c r="H77" s="3" t="inlineStr">
@@ -3501,7 +3521,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Buyer: От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккуратно. Хорошее решение для сушки белья и экономии места. Стоимость чуть больше 200 юаней</t>
+          <t>Buyer: От одного Саунд Бокса. Стоимость 5000$. Есть возможность при увеличении количества заказа, получить скидку. Очень аккуратная комната, достаточно комфортная. Цена немного завышена, встречали на других выставках пониже стоимостью.</t>
         </is>
       </c>
     </row>
@@ -3511,42 +3531,22 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Shenzhen Kingston Sanitary Ware Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Felicity</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>sales09@spakingston.com</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>+86-18025851458</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>www.spakingston.com</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Kingston Company, JiangJun Road, Qiuchang, Huiyang, Huizhou, China</t>
-        </is>
-      </c>
+          <t>顶固集团</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 100</t>
+          <t>Buyer: От одной закути. Видела и раньше такие конструкции, но эти выглядели очень аккуратно. Хорошее решение для сушки белья и экономии места. Стоимость чуть больше 200 юаней</t>
         </is>
       </c>
     </row>
@@ -3556,32 +3556,32 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Guangzhou Sunrans Sanitary Ware Co., Ltd / Guangzhou Sunrans New Energy Technology Co., Ltd</t>
+          <t>Shenzhen Kingston Sanitary Ware Co., Ltd.</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Felicity</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>william@sunrans.com</t>
+          <t>sales09@spakingston.com</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>+86 134 1613 9887, +86-20-26231998</t>
+          <t>+86-18025851458</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>http://www.sunrans.com</t>
+          <t>www.spakingston.com</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
+          <t>Kingston Company, JiangJun Road, Qiuchang, Huiyang, Huizhou, China</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very good and good products.</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -3599,24 +3599,44 @@
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="inlineStr"/>
-      <c r="C80" s="2" t="inlineStr"/>
-      <c r="D80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou Sunrans Sanitary Ware Co., Ltd / Guangzhou Sunrans New Energy Technology Co., Ltd</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>william@sunrans.com</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>15916159866</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+          <t>+86 134 1613 9887, +86-20-26231998</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>http://www.sunrans.com</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Headquarter: No.38-4, Lisan Avenue, Zengjiang Street, Zengcheng, Guangzhou; Factory: Xiang 2 Road, Huizhou Industrial Transfer Park, Huizhou, China 516820</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
+          <t>Buyer: MOQ 5 pcs, I got sample price for 2400usd. They have a very innovative product and very trendy. Their service is very good and good products.</t>
         </is>
       </c>
     </row>
@@ -3624,36 +3644,16 @@
       <c r="A81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>IFUN PARK &amp; TIPTOPFUN AMUSEMENT</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>Ivy Zhou</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>ivy@ifunpark.com</t>
-        </is>
-      </c>
+      <c r="B81" s="3" t="inlineStr"/>
+      <c r="C81" s="3" t="inlineStr"/>
+      <c r="D81" s="3" t="inlineStr"/>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>+86 133 0238 5758</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>www.ifunpark.com / www.ifunamusement.com</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
-        </is>
-      </c>
+          <t>15916159866</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr"/>
       <c r="H81" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 600</t>
+          <t>Buyer: MOQ 3 for custom made. 800usd. Different sizes different prices. Very affordable and good designs.</t>
         </is>
       </c>
     </row>
@@ -3671,14 +3671,34 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Weyth 惠特</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr"/>
-      <c r="D82" s="2" t="inlineStr"/>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
+          <t>IFUN PARK &amp; TIPTOPFUN AMUSEMENT</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Ivy Zhou</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>ivy@ifunpark.com</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>+86 133 0238 5758</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>www.ifunpark.com / www.ifunamusement.com</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>No. 13, Wenqiao Road, Xinqiao Village, Shiji Town, Panyu District, Guangzhou City, China</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3686,7 +3706,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 500</t>
+          <t>Buyer: 600</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3716,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>D.DELI 德利智能门锁</t>
+          <t>Weyth 惠特</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr"/>
@@ -3711,7 +3731,7 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 43</t>
+          <t>Buyer: 500</t>
         </is>
       </c>
     </row>
@@ -3721,42 +3741,22 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>RENQIU TUOXIN BUILDING MATERIALS CO., LTD</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Emily Li</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>tuoxinlqm@outlook.com</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>+86 19831737599</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tuoxinfiberglassmesh.com/</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
-        </is>
-      </c>
+          <t>D.DELI 德利智能门锁</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 0.6 usd/m2</t>
+          <t>Buyer: 43</t>
         </is>
       </c>
     </row>
@@ -3766,42 +3766,42 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>河南威兰得建筑科技有限公司</t>
+          <t>RENQIU TUOXIN BUILDING MATERIALS CO., LTD</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>王虎旗</t>
+          <t>Emily Li</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>hectorwang1982@gmail.com</t>
+          <t>tuoxinlqm@outlook.com</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>86 18638546565</t>
+          <t>+86 19831737599</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>www.weilandeglobal.com</t>
+          <t>https://www.tuoxinfiberglassmesh.com/</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>河南省郑州市曲梁工业园188号</t>
+          <t>Yanling Industrial Park, Renqiu City, Hebei Province, China</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Under negotiation, great opportunities</t>
+          <t>Buyer: 0.6 usd/m2</t>
         </is>
       </c>
     </row>
@@ -3811,34 +3811,42 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>江门市新会区致恒科技材料有限公司</t>
+          <t>河南威兰得建筑科技有限公司</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>曹双林 (Edith Cao)</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr"/>
+          <t>王虎旗</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>hectorwang1982@gmail.com</t>
+        </is>
+      </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>13286132534, 400-0750-889</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr"/>
+          <t>86 18638546565</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>www.weilandeglobal.com</t>
+        </is>
+      </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>广东省江门市蓬江区迎宾大道西23号之129</t>
+          <t>河南省郑州市曲梁工业园188号</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1-5 usd/l</t>
+          <t>Buyer: Under negotiation, great opportunities</t>
         </is>
       </c>
     </row>
@@ -3848,30 +3856,34 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>安居福智能门 (ANJUFU INTELLIGENT GATE)</t>
+          <t>江门市新会区致恒科技材料有限公司</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>罗如玲</t>
+          <t>曹双林 (Edith Cao)</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr"/>
-      <c r="E87" s="3" t="inlineStr"/>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>13286132534, 400-0750-889</t>
+        </is>
+      </c>
       <c r="F87" s="3" t="inlineStr"/>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>广东省中山市东凤镇</t>
+          <t>广东省江门市蓬江区迎宾大道西23号之129</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 100</t>
+          <t>Buyer: 1-5 usd/l</t>
         </is>
       </c>
     </row>
@@ -3881,14 +3893,22 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>欧派</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr"/>
+          <t>安居福智能门 (ANJUFU INTELLIGENT GATE)</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>罗如玲</t>
+        </is>
+      </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>广东省中山市东凤镇</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3896,7 +3916,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 679 rmb</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -3906,18 +3926,14 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>永康市鸿钰门业有限公司</t>
+          <t>欧派</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr"/>
       <c r="D89" s="3" t="inlineStr"/>
       <c r="E89" s="3" t="inlineStr"/>
       <c r="F89" s="3" t="inlineStr"/>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>浙江省永康市长城工业区</t>
-        </is>
-      </c>
+      <c r="G89" s="3" t="inlineStr"/>
       <c r="H89" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3925,7 +3941,7 @@
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 59 rmb</t>
+          <t>Buyer: 679 rmb</t>
         </is>
       </c>
     </row>
@@ -3935,18 +3951,18 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>东方喜卡</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>果果</t>
-        </is>
-      </c>
+          <t>永康市鸿钰门业有限公司</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>浙江省永康市长城工业区</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -3954,7 +3970,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 249RMB</t>
+          <t>Buyer: 59 rmb</t>
         </is>
       </c>
     </row>
@@ -3964,38 +3980,26 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>优品声学 (YP ACOUSTICS)</t>
+          <t>东方喜卡</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>李尚声 (Shangsheng Li)</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>15915975597@163.com</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>15915974406</t>
-        </is>
-      </c>
+          <t>果果</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr"/>
+      <c r="E91" s="3" t="inlineStr"/>
       <c r="F91" s="3" t="inlineStr"/>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
-        </is>
-      </c>
+      <c r="G91" s="3" t="inlineStr"/>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 6000RMB</t>
+          <t>Buyer: 249RMB</t>
         </is>
       </c>
     </row>
@@ -4005,30 +4009,38 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>双龙智科</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr"/>
-      <c r="D92" s="2" t="inlineStr"/>
+          <t>优品声学 (YP ACOUSTICS)</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>李尚声 (Shangsheng Li)</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>15915975597@163.com</t>
+        </is>
+      </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
+          <t>15915974406</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>江苏省太仓市双凤镇陆江路1号</t>
+          <t>广东省广州市番禺区正营创意园2栋二楼 (Second floor, Building 2, Zhengying Creative Park, Panyu District, Guangzhou City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 2000RMB&amp;gt;</t>
+          <t>Buyer: 6000RMB</t>
         </is>
       </c>
     </row>
@@ -4038,38 +4050,30 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>GUANGDONG TUOXUN INTELLIGENT TECHNOLOGY CO., LTD</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>Wing</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>wuyunying08@gmail.com</t>
-        </is>
-      </c>
+          <t>双龙智科</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr"/>
+      <c r="D93" s="3" t="inlineStr"/>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>189-2984-9818, 0758-8578545</t>
+          <t>138 6227 5829, 138 6227 4458, 0512-5666 6666</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr"/>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>Buyer: MOQ - 5000 and price - 7000 dollars</t>
+          <t>Buyer: 2000RMB&amp;gt;</t>
         </is>
       </c>
     </row>
@@ -4079,32 +4083,28 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Suzhou Acousound New Material Technology Co., Ltd.</t>
+          <t>GUANGDONG TUOXUN INTELLIGENT TECHNOLOGY CO., LTD</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Susan Xia</t>
+          <t>Wing</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>acousound16@polyacoustic.com</t>
+          <t>wuyunying08@gmail.com</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>+86-15512435605</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>www.polyacoustic.com</t>
-        </is>
-      </c>
+          <t>189-2984-9818, 0758-8578545</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu 215152</t>
+          <t>Auto Parts Industrial Park, Jinli Town, Gaoyao District, Zhaoqing, Guangdong</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 4000$</t>
+          <t>Buyer: MOQ - 5000 and price - 7000 dollars</t>
         </is>
       </c>
     </row>
@@ -4124,28 +4124,32 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>佛山市方泓五金建材有限公司 (Foshan Fangheng Hardware Co., Ltd.)</t>
+          <t>Suzhou Acousound New Material Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>陈施志凯 (CHEN SHI ZHI KAI)</t>
+          <t>Susan Xia</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>108455453@qq.com</t>
+          <t>acousound16@polyacoustic.com</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>+86 134 3318 1558, 0757-8560 9159</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr"/>
+          <t>+86-15512435605</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>www.polyacoustic.com</t>
+        </is>
+      </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
+          <t>No.10 Aimin Road, Xiangcheng, Suzhou, Jiangsu 215152</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
@@ -4155,7 +4159,7 @@
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>Buyer: The price cheap, merchant very friendly</t>
+          <t>Buyer: 4000$</t>
         </is>
       </c>
     </row>
@@ -4165,38 +4169,38 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Countermast Technology (Dalian) Company Limited</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr"/>
+          <t>佛山市方泓五金建材有限公司 (Foshan Fangheng Hardware Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>陈施志凯 (CHEN SHI ZHI KAI)</t>
+        </is>
+      </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>sales.countermast.china@countermast.com</t>
+          <t>108455453@qq.com</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>400-100-2228</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>www.countermast.cn</t>
-        </is>
-      </c>
+          <t>+86 134 3318 1558, 0757-8560 9159</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Building No.7, Zhongqing Industrial Park, Dalian free trade zone, Liaoning, China</t>
+          <t>中国广东省佛山市南海区里水镇大步工业区13号 (No. 13, Dabu Industrial Zone, Lishui Town, Nanhai District, Foshan City, Guangdong Province, China)</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Buyer: The price more cheaper, good quality</t>
+          <t>Buyer: The price cheap, merchant very friendly</t>
         </is>
       </c>
     </row>
@@ -4206,42 +4210,38 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>广州蒙娜丽莎控股集团有限公司, 广州蒙娜丽莎卫浴股份有限公司</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>严金霞</t>
-        </is>
-      </c>
+          <t>Countermast Technology (Dalian) Company Limited</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr"/>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>monalisa38@monalisa.cn</t>
+          <t>sales.countermast.china@countermast.com</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>+86 13711113746, 400 020 1818, +86 20-28607711</t>
+          <t>400-100-2228</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>www.monalisa.cn</t>
+          <t>www.countermast.cn</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>广州市花都区花东镇港头工业区4号</t>
+          <t>Building No.7, Zhongqing Industrial Park, Dalian free trade zone, Liaoning, China</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Good merchant, perfect products</t>
+          <t>Buyer: The price more cheaper, good quality</t>
         </is>
       </c>
     </row>
@@ -4251,42 +4251,42 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>高成 (Gaocheng)</t>
+          <t>广州蒙娜丽莎控股集团有限公司, 广州蒙娜丽莎卫浴股份有限公司</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>叶小龙/Dustin Ye</t>
+          <t>严金霞</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>yedustin@gmail.com</t>
+          <t>monalisa38@monalisa.cn</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>+86-188 5861 0008</t>
+          <t>+86 13711113746, 400 020 1818, +86 20-28607711</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>www.cngaocheng.cn</t>
+          <t>www.monalisa.cn</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>浙江省三门县浦坝港镇沿海工业城 (COASTAL INDUSTRIAL CITY, PUBAGANG TOWN, SANMEN, TAIZHOU CITY, ZHEJIANG PRO., CHINA)</t>
+          <t>广州市花都区花东镇港头工业区4号</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
+          <t>Buyer: Good merchant, perfect products</t>
         </is>
       </c>
     </row>
@@ -4296,42 +4296,42 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD. / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
+          <t>高成 (Gaocheng)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Pacao Yin</t>
+          <t>叶小龙/Dustin Ye</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>pin@pingaolao.com</t>
+          <t>yedustin@gmail.com</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>(0086)13903035682, (0086)0769-86378283, (0086)0769-86377522</t>
+          <t>+86-188 5861 0008</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
+          <t>www.cngaocheng.cn</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+          <t>浙江省三门县浦坝港镇沿海工业城 (COASTAL INDUSTRIAL CITY, PUBAGANG TOWN, SANMEN, TAIZHOU CITY, ZHEJIANG PRO., CHINA)</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 15 RMB the product is interesting</t>
+          <t>Buyer: 160 RMB/ pcs The prices are attractive and he wants me to represent their products in my country.</t>
         </is>
       </c>
     </row>
@@ -4341,32 +4341,32 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>浙江瑞鑫环保设备有限公司</t>
+          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD. / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>吴仁余</t>
+          <t>Pacao Yin</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>294217488@qq.com</t>
+          <t>pin@pingaolao.com</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>13967444542, 0579-82889122</t>
+          <t>(0086)13903035682, (0086)0769-86378283, (0086)0769-86377522</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>www.jhrxhb.com</t>
+          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>浙江省金华市婺城区罗店镇北山路精工工业园</t>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Buyer: nearly $15,000 for this production line</t>
+          <t>Buyer: 15 RMB the product is interesting</t>
         </is>
       </c>
     </row>
@@ -4386,32 +4386,32 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>ZHEJIANG DOUBLE-LIN VALVES CO., LTD.</t>
+          <t>浙江瑞鑫环保设备有限公司</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Dream Lin</t>
+          <t>吴仁余</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>sale15@double-lin.com</t>
+          <t>294217488@qq.com</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>86-020-66837727, 86-13710718529</t>
+          <t>13967444542, 0579-82889122</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>www.double-lin.com</t>
+          <t>www.jhrxhb.com</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
+          <t>浙江省金华市婺城区罗店镇北山路精工工业园</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 149</t>
+          <t>Buyer: nearly $15,000 for this production line</t>
         </is>
       </c>
     </row>
@@ -4431,28 +4431,32 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>苏州市富尔达科技股份有限公司</t>
+          <t>ZHEJIANG DOUBLE-LIN VALVES CO., LTD.</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>袁佳磊</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr"/>
+          <t>Dream Lin</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>sale15@double-lin.com</t>
+        </is>
+      </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>18652449601</t>
+          <t>86-020-66837727, 86-13710718529</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>www.cnfrd.cn</t>
+          <t>www.double-lin.com</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>江苏省太仓市港区临江路1号</t>
+          <t>Yanpan Hardware Industrial Area, Ganjiang Town, Yuhuan, Zhejiang, China</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -4462,7 +4466,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 749</t>
+          <t>Buyer: 149</t>
         </is>
       </c>
     </row>
@@ -4472,42 +4476,38 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.,LTD.</t>
+          <t>苏州市富尔达科技股份有限公司</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Eric Huang</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>464565801@qq.com</t>
-        </is>
-      </c>
+          <t>袁佳磊</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr"/>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>13813551160 / 0519-88784050</t>
+          <t>18652449601</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>www.ycpanel.com</t>
+          <t>www.cnfrd.cn</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>No.28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
+          <t>江苏省太仓市港区临江路1号</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 5000 USD</t>
+          <t>Buyer: 749</t>
         </is>
       </c>
     </row>
@@ -4517,30 +4517,42 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>双龙中科</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr"/>
-      <c r="D104" s="2" t="inlineStr"/>
+          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Eric Huang</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>464565801@qq.com</t>
+        </is>
+      </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr"/>
+          <t>13813551160 / 0519-88784050</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>www.ycpanel.com</t>
+        </is>
+      </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>江苏省太仓市双凤镇陆江路1号</t>
+          <t>No.28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
+          <t>Buyer: 5000 USD</t>
         </is>
       </c>
     </row>
@@ -4550,30 +4562,30 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>深圳市家为安智能科技有限公司</t>
+          <t>双龙中科</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr"/>
       <c r="D105" s="3" t="inlineStr"/>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>186-0205-8898 / 400-608-0098</t>
+          <t>138 6227 5829 / 138 6227 4458 / 0512-5666 6666</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr"/>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市南海区里水镇</t>
+          <t>江苏省太仓市双凤镇陆江路1号</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 249 RMB. They have fully described their products.</t>
+          <t>Buyer: Smart home system 2000 RMB. They have showed us how the smart home system works. That’s amazing!</t>
         </is>
       </c>
     </row>
@@ -4583,30 +4595,30 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>广州市优品声学科技有限公司</t>
+          <t>深圳市家为安智能科技有限公司</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr"/>
       <c r="D106" s="2" t="inlineStr"/>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>www.gzypsx.com</t>
-        </is>
-      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>186-0205-8898 / 400-608-0098</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区南村镇南村西路138号德意创意园二层</t>
+          <t>广东省佛山市南海区里水镇</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 6000RMB，积极，详细地告诉了一切</t>
+          <t>Buyer: 249 RMB. They have fully described their products.</t>
         </is>
       </c>
     </row>
@@ -4616,26 +4628,30 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>科维尔 (VIR)</t>
+          <t>广州市优品声学科技有限公司</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr"/>
       <c r="D107" s="3" t="inlineStr"/>
       <c r="E107" s="3" t="inlineStr"/>
-      <c r="F107" s="3" t="inlineStr"/>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>www.gzypsx.com</t>
+        </is>
+      </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>市长城工业区</t>
+          <t>广东省广州市番禺区南村镇南村西路138号德意创意园二层</t>
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 2000 RMB</t>
+          <t>Buyer: 6000RMB，积极，详细地告诉了一切</t>
         </is>
       </c>
     </row>
@@ -4645,28 +4661,16 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>贵州佑远木业有限公司</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>颜加伟</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>1164199388@qq.com</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>133 9983 5678</t>
-        </is>
-      </c>
+          <t>科维尔 (VIR)</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr"/>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
+          <t>市长城工业区</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -4676,7 +4680,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 400rmb /m2 good meeting</t>
+          <t>Buyer: 2000 RMB</t>
         </is>
       </c>
     </row>
@@ -4686,34 +4690,38 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>广西豪庭家具有限公司 (Guangxi Haoting Furniture Co., Ltd.)</t>
+          <t>贵州佑远木业有限公司</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>高学梅</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr"/>
+          <t>颜加伟</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>1164199388@qq.com</t>
+        </is>
+      </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>17687627315</t>
+          <t>133 9983 5678</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr"/>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
+          <t>贵州省赤水市成渝(赤水)家具产业园A3-2</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>Home Furnishing</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 350 rmb/m2</t>
+          <t>Buyer: 400rmb /m2 good meeting</t>
         </is>
       </c>
     </row>
@@ -4723,42 +4731,34 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
+          <t>广西豪庭家具有限公司 (Guangxi Haoting Furniture Co., Ltd.)</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Pacao Yin</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>pin@pingaolao.com</t>
-        </is>
-      </c>
+          <t>高学梅</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Mobile: (0086)13903035682, Tel: (0086)0769-86378283</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
-        </is>
-      </c>
+          <t>17687627315</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
+          <t>广西南宁邕武路增创工业园区 (Zengchuang Ind Park, Yongwu Rd, Nanning, Guangxi, China)</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Home Furnishing</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Buyer: MOQ 5000 pieces</t>
+          <t>Buyer: 350 rmb/m2</t>
         </is>
       </c>
     </row>
@@ -4768,42 +4768,42 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Moershu (摩尔舒卫浴)</t>
+          <t>HONGKONG PINGAO INDUSTRIAL CO., LTD / PINGAO HARDWARE &amp; PLASTIC PRODUCTS FACTORY</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Thea</t>
+          <t>Pacao Yin</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>moershu3@moershu.com</t>
+          <t>pin@pingaolao.com</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>13957622087</t>
+          <t>Mobile: (0086)13903035682, Tel: (0086)0769-86378283</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>www.moershu.com</t>
+          <t>www.pingaolao.com, https://dgpingao.1688.com</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
+          <t>NO.5 JINTAN SECOND STREET, SHANGWU INDUSTRIAL, SHIJIE TOWN, DONGGUAN, GUANGDONG, CHINA</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
+          <t>Buyer: MOQ 5000 pieces</t>
         </is>
       </c>
     </row>
@@ -4813,38 +4813,42 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Hangzhou Sciener Smart Technology Co.,Ltd.</t>
+          <t>Moershu (摩尔舒卫浴)</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Zoey Zhang</t>
+          <t>Thea</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>zoey@sciener.com</t>
+          <t>moershu3@moershu.com</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>+86 178-5768-8782</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr"/>
+          <t>13957622087</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>www.moershu.com</t>
+        </is>
+      </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
+          <t>777 Shanzhuan Road, Zhujiajiao Industrial Park, Qingpu District, Shanghai, China; No. 399 Haiyun Road, Jiaojiang District, Taizhou City, Zhejiang Province, China; 88-3 East Taihe Road, Jiaojiang District, Taizhou City, Zhejiang Province, China</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 20 / MOQ 100 Nice worker answered all questions</t>
+          <t>Buyer: 194 / MOQ 1 Was surprised of price, low price for this beautiful staff</t>
         </is>
       </c>
     </row>
@@ -4854,38 +4858,38 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>江西荣科新型材料有限公司 / JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.</t>
+          <t>Hangzhou Sciener Smart Technology Co.,Ltd.</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Lucy Zeng (曾露)</t>
+          <t>Zoey Zhang</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>lucy@rongkedecor.com</t>
+          <t>zoey@sciener.com</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>+86-13134020034</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>https://www.amerdecor.com/</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="inlineStr"/>
+          <t>+86 178-5768-8782</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr"/>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>Room 1101, Building A2,2-150# Yunlian Road, Yuhang District, Hangzhou, Zhejiang, PRC 311121</t>
+        </is>
+      </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 80 rmb for 230 meter</t>
+          <t>Buyer: 20 / MOQ 100 Nice worker answered all questions</t>
         </is>
       </c>
     </row>
@@ -4895,30 +4899,30 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SANNORA</t>
+          <t>江西荣科新型材料有限公司 / JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>王冠</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr"/>
+          <t>Lucy Zeng (曾露)</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>lucy@rongkedecor.com</t>
+        </is>
+      </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>+86 13229297183</t>
+          <t>+86-13134020034</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>WWW.SANNORA.COM; WWW.SANNORA-BATH.COM</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区</t>
-        </is>
-      </c>
+          <t>https://www.amerdecor.com/</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -4926,7 +4930,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1560 rmb for whole item</t>
+          <t>Buyer: 80 rmb for 230 meter</t>
         </is>
       </c>
     </row>
@@ -4936,42 +4940,38 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Kaiping Gold Medal Sanitary Ware Co.,Ltd. / Guangdong Aosman Sanitary Ware Co.,Ltd</t>
+          <t>SANNORA</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Sophia Deng (邓小艳)</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>sophiadeng@china-gold.cn</t>
-        </is>
-      </c>
+          <t>王冠</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr"/>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>+181 3838 6948</t>
+          <t>+86 13229297183</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>http://www.china-gold.cn, http://www.aosman.cn</t>
+          <t>WWW.SANNORA.COM; WWW.SANNORA-BATH.COM</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>198 Siqian Xi Road, Shuikou, Kaiping 529300, Guangdong PR.China</t>
+          <t>展厅：佛山市禅城区季华西路68号中国陶瓷产业总部基地东区C03座；工厂：佛山市南海区狮山谭边工业二区</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 4600 rmb</t>
+          <t>Buyer: 1560 rmb for whole item</t>
         </is>
       </c>
     </row>
@@ -4981,22 +4981,42 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>东风汽车</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr"/>
-      <c r="D116" s="2" t="inlineStr"/>
-      <c r="E116" s="2" t="inlineStr"/>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
+          <t>Kaiping Gold Medal Sanitary Ware Co.,Ltd. / Guangdong Aosman Sanitary Ware Co.,Ltd</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Sophia Deng (邓小艳)</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>sophiadeng@china-gold.cn</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>+181 3838 6948</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>http://www.china-gold.cn, http://www.aosman.cn</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>198 Siqian Xi Road, Shuikou, Kaiping 529300, Guangdong PR.China</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 50 Yuan 50g (The taste is authentic and aroma is really good</t>
+          <t>Buyer: 4600 rmb</t>
         </is>
       </c>
     </row>
@@ -5006,34 +5026,14 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.LTD.</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>Eric Huang</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>464565801@qq.com</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>13813551160, 0519-88784050</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>www.ycpanel.com</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>#28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
-        </is>
-      </c>
+          <t>东风汽车</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr"/>
+      <c r="D117" s="3" t="inlineStr"/>
+      <c r="E117" s="3" t="inlineStr"/>
+      <c r="F117" s="3" t="inlineStr"/>
+      <c r="G117" s="3" t="inlineStr"/>
       <c r="H117" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 2085</t>
+          <t>Buyer: 50 Yuan 50g (The taste is authentic and aroma is really good</t>
         </is>
       </c>
     </row>
@@ -5051,28 +5051,32 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>江西瑞京鸿兴实业有限公司</t>
+          <t>CHANGZHOU YOUCARE DECORATION ENGINEERING CO.LTD.</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>朱支群</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr"/>
+          <t>Eric Huang</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>464565801@qq.com</t>
+        </is>
+      </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>13763963598</t>
+          <t>13813551160, 0519-88784050</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>www.jx-wpc.com</t>
+          <t>www.ycpanel.com</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>江西省瑞金市经济开发区创业一路东侧</t>
+          <t>#28, Changzhou East Road, Henglin Town, Changzhou City, Jiangsu, China</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -5082,7 +5086,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 250¥/м3</t>
+          <t>Buyer: 2085</t>
         </is>
       </c>
     </row>
@@ -5092,42 +5096,38 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd</t>
+          <t>江西瑞京鸿兴实业有限公司</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Anne</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>victor@ck-bath.com</t>
-        </is>
-      </c>
+          <t>朱支群</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr"/>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>18656330093</t>
+          <t>13763963598</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>https://ck-bath.com/</t>
+          <t>www.jx-wpc.com</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
+          <t>江西省瑞金市经济开发区创业一路东侧</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 4500¥</t>
+          <t>Buyer: 250¥/м3</t>
         </is>
       </c>
     </row>
@@ -5137,42 +5137,42 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>ciarra</t>
+          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>linda.lu@ciarrahome.com</t>
+          <t>victor@ck-bath.com</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>+86 1882 9964 960, +86 1343 2639 580</t>
+          <t>18656330093</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>www.ciarrahome.com</t>
+          <t>https://ck-bath.com/</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
+          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 300¥ 300pcs</t>
+          <t>Buyer: 4500¥</t>
         </is>
       </c>
     </row>
@@ -5182,28 +5182,32 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Yekalon Mills</t>
+          <t>ciarra</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Viola Liu</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>wood6@sennorwell.com</t>
+          <t>linda.lu@ciarrahome.com</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>(86) 158 8931 1832</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr"/>
+          <t>+86 1882 9964 960, +86 1343 2639 580</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>www.ciarrahome.com</t>
+        </is>
+      </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
+          <t>Poly Center, Room 1703, 5 Linjiang Avenue, Tianhe, Guangzhou, Guangdong, China, 510623</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
@@ -5213,7 +5217,7 @@
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 50¥ 1000pcs</t>
+          <t>Buyer: 300¥ 300pcs</t>
         </is>
       </c>
     </row>
@@ -5223,42 +5227,38 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Ideal Sanitary Ware Co., Ltd.</t>
+          <t>Yekalon Mills</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Amy Liu 刘建美</t>
+          <t>Viola Liu</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>export@ideal-china.net</t>
+          <t>wood6@sennorwell.com</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>+86 (0) 757 8558 9299</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>www.ideal-sanitary.com</t>
-        </is>
-      </c>
+          <t>(86) 158 8931 1832</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>No.3 Hexi Road of Shashui, Yanghe Town, Gaoming District, Foshan City, Guangdong Province, 528515 - P.R.China.</t>
+          <t>3rd Floor, Building C, Golden Apple Innovation Park, Ganli 2nd Road, Longgang District, Shenzhen, 518112, China</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 500$ 100psc</t>
+          <t>Buyer: 50¥ 1000pcs</t>
         </is>
       </c>
     </row>
@@ -5268,32 +5268,32 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd.</t>
+          <t>Ideal Sanitary Ware Co., Ltd.</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Amy Liu 刘建美</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>victor@ck-bath.com</t>
+          <t>export@ideal-china.net</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>18656330093</t>
+          <t>+86 (0) 757 8558 9299</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>https://ck-bath.com/</t>
+          <t>www.ideal-sanitary.com</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
+          <t>No.3 Hexi Road of Shashui, Yanghe Town, Gaoming District, Foshan City, Guangdong Province, 528515 - P.R.China.</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 4500¥</t>
+          <t>Buyer: 500$ 100psc</t>
         </is>
       </c>
     </row>
@@ -5313,38 +5313,42 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>佛山市旌晨铝门窗有限公司</t>
+          <t>Xuancheng Hengxin Sanitary Ware Co., Ltd.</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>胡光辉</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>1525423805@qq.com</t>
+          <t>victor@ck-bath.com</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>18128752879</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr"/>
+          <t>18656330093</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>https://ck-bath.com/</t>
+        </is>
+      </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>佛山狮山镇谭边工业区崩岗头路四号之一</t>
+          <t>Yangyin Avenue, Xiangyang Town, Xuanzhou District, Xuancheng City, Anhui Province</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 980y/m2, moq 1000p, like doors with Mosquito netting</t>
+          <t>Buyer: 4500¥</t>
         </is>
       </c>
     </row>
@@ -5354,42 +5358,38 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>佛山市乾泽科技有限公司</t>
+          <t>佛山市旌晨铝门窗有限公司</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>陈可樑</t>
+          <t>胡光辉</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>hw-hardware@qian-ze.com</t>
+          <t>1525423805@qq.com</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>180 3863 7238</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>www.honeywell-hardware.com</t>
-        </is>
-      </c>
+          <t>18128752879</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr"/>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市三水区云东海街道宝盛路2号1座三层（合和建筑五金园区北门）</t>
+          <t>佛山狮山镇谭边工业区崩岗头路四号之一</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1000-2000p, 1.7-7$, good beautiful doors handless</t>
+          <t>Buyer: 980y/m2, moq 1000p, like doors with Mosquito netting</t>
         </is>
       </c>
     </row>
@@ -5399,26 +5399,42 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>ARTY 艺和</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr"/>
-      <c r="D126" s="2" t="inlineStr"/>
-      <c r="E126" s="2" t="inlineStr"/>
-      <c r="F126" s="2" t="inlineStr"/>
+          <t>佛山市乾泽科技有限公司</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>陈可樑</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>hw-hardware@qian-ze.com</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>180 3863 7238</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>www.honeywell-hardware.com</t>
+        </is>
+      </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>广东 · 开平</t>
+          <t>广东省佛山市三水区云东海街道宝盛路2号1座三层（合和建筑五金园区北门）</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
+          <t>Buyer: 1000-2000p, 1.7-7$, good beautiful doors handless</t>
         </is>
       </c>
     </row>
@@ -5428,14 +5444,22 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>SUNHOHI 新豪轩门窗</t>
+          <t>知和香馆</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr"/>
       <c r="D127" s="3" t="inlineStr"/>
-      <c r="E127" s="3" t="inlineStr"/>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>15926183211</t>
+        </is>
+      </c>
       <c r="F127" s="3" t="inlineStr"/>
-      <c r="G127" s="3" t="inlineStr"/>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>福建永春达埔</t>
+        </is>
+      </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5443,7 +5467,7 @@
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Индивидуальный от размеров. Нет уен конкретных у всех поставщиков. Все делается под заказ и производится от 1 шт.</t>
+          <t>Buyer: They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
         </is>
       </c>
     </row>
@@ -5453,24 +5477,32 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>景德镇窑珍陶瓷</t>
+          <t>San Nora (聖羅蘭·衛浴)</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>徐云霞</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr"/>
+          <t>ALLEN XU (许熙平)</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>sales@sannora.com</t>
+        </is>
+      </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>13697981203</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr"/>
+          <t>+86 137 0263 0244, +86-757-86438259</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>WWW.SANNORA.COM, WWW.SANNORA-BATH.COM</t>
+        </is>
+      </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>店面地址：江西省景德镇市国贸广场国贸街1号；厂址：吕蒙高新工业园沟上008号</t>
+          <t>TANBIAN IND. ZONE, SHISHAN TOWN, NANHAI DIST., FOSHAN, GUANGDONG, CHINA</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -5480,7 +5512,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 100 RMB per sample. The taste is very good</t>
+          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -5490,26 +5522,30 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>苏州东山茶厂 (Suzhou Dongshan Biluochun Tea Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr"/>
-      <c r="D129" s="3" t="inlineStr"/>
+          <t>PTAT | 帕兰蒂诺</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Joy Yang</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>joy@rans.group</t>
+        </is>
+      </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>0512-66281146</t>
+          <t>+86-13757430301</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>www.dsteaf.com</t>
-        </is>
-      </c>
-      <c r="G129" s="3" t="inlineStr">
-        <is>
-          <t>江苏省苏州市吴中区东山镇 (Dongshan Town, Wuzhong District, Suzhou City)</t>
-        </is>
-      </c>
+          <t>www.ptat.cn</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr"/>
       <c r="H129" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5517,7 +5553,7 @@
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 150 RMB per sample. The taste is very good</t>
+          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -5527,14 +5563,30 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>武夷星</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr"/>
+          <t>万磊建筑涂料有限公司</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>万磊市场部</t>
+        </is>
+      </c>
       <c r="D130" s="2" t="inlineStr"/>
-      <c r="E130" s="2" t="inlineStr"/>
-      <c r="F130" s="2" t="inlineStr"/>
-      <c r="G130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>186-8825-1404, 4000-147-187</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>http://www.fswanlei.com</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区</t>
+        </is>
+      </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5542,7 +5594,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 250 RMB per sample. The taste is very good</t>
+          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
         </is>
       </c>
     </row>
@@ -5552,14 +5604,34 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>湖北龙王垭茶业有限公司</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr"/>
-      <c r="D131" s="3" t="inlineStr"/>
-      <c r="E131" s="3" t="inlineStr"/>
-      <c r="F131" s="3" t="inlineStr"/>
-      <c r="G131" s="3" t="inlineStr"/>
+          <t>ZHEJIANG SEATING TECHNOLOGY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>May Zhang</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>sales5@anjeurostilefurniture.com</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>+86 182 5727 1590</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>www.zjseating.com</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
+        </is>
+      </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5567,7 +5639,7 @@
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 498rmb/unit. I like the green tea in white color. First time to see colorless tea and it was amazing, i will recommend it to my country’s local market.</t>
+          <t>Buyer: 1100</t>
         </is>
       </c>
     </row>
@@ -5577,30 +5649,42 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>知和香馆</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr"/>
-      <c r="D132" s="2" t="inlineStr"/>
+          <t>Chaozhou Lefu Sanitary Ware Technology Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>lucy@lefucz.com</t>
+        </is>
+      </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>15926183211</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr"/>
+          <t>+0086 18098114370</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>www.lefucz.com</t>
+        </is>
+      </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>福建永春达埔</t>
+          <t>Lefu Sanitary Ware, Sheweikeng, Dengtang Town, Chaoan District, Chaozhou City, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Buyer: They have tea perfume bar, which was amazing, moreover, i also love their snacks idea with tea.</t>
+          <t>Buyer: 1050</t>
         </is>
       </c>
     </row>
@@ -5610,34 +5694,14 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>San Nora (聖羅蘭·衛浴)</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>ALLEN XU (许熙平)</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>sales@sannora.com</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>+86 137 0263 0244, +86-757-86438259</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>WWW.SANNORA.COM, WWW.SANNORA-BATH.COM</t>
-        </is>
-      </c>
-      <c r="G133" s="3" t="inlineStr">
-        <is>
-          <t>TANBIAN IND. ZONE, SHISHAN TOWN, NANHAI DIST., FOSHAN, GUANGDONG, CHINA</t>
-        </is>
-      </c>
+          <t>宜昌毛尖</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr"/>
+      <c r="D133" s="3" t="inlineStr"/>
+      <c r="E133" s="3" t="inlineStr"/>
+      <c r="F133" s="3" t="inlineStr"/>
+      <c r="G133" s="3" t="inlineStr"/>
       <c r="H133" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5645,7 +5709,7 @@
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>Buyer: Prices are go and packing and Verstaliy is more</t>
         </is>
       </c>
     </row>
@@ -5655,29 +5719,13 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>PTAT | 帕兰蒂诺</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Joy Yang</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>joy@rans.group</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>+86-13757430301</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>www.ptat.cn</t>
-        </is>
-      </c>
+          <t>湖北龙王娅茶业有限公司</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr"/>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5686,7 +5734,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>Buyer: The taste anaroma is good of this product then anyother</t>
         </is>
       </c>
     </row>
@@ -5696,30 +5744,14 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>万磊建筑涂料有限公司</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>万磊市场部</t>
-        </is>
-      </c>
+          <t>正山堂 (ZHENG SHAN TANG)</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr"/>
       <c r="D135" s="3" t="inlineStr"/>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>186-8825-1404, 4000-147-187</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t>http://www.fswanlei.com</t>
-        </is>
-      </c>
-      <c r="G135" s="3" t="inlineStr">
-        <is>
-          <t>总部：广东省佛山市南海区松岗万石工业区；分厂：广西省贵港市覃塘区产业园甘化园区</t>
-        </is>
-      </c>
+      <c r="E135" s="3" t="inlineStr"/>
+      <c r="F135" s="3" t="inlineStr"/>
+      <c r="G135" s="3" t="inlineStr"/>
       <c r="H135" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5727,7 +5759,7 @@
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>Buyer: I will explore their catalog and website, choose products, then'll make an inquire.</t>
+          <t>Buyer: the product prices are very good. looks attractive</t>
         </is>
       </c>
     </row>
@@ -5737,34 +5769,30 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>ZHEJIANG SEATING TECHNOLOGY CO., LTD.</t>
+          <t>江西荣科新型建材有限公司 (JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.)</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>May Zhang</t>
+          <t>Lucy Zeng (曾露)</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>sales5@anjeurostilefurniture.com</t>
+          <t>lucy@rongkedecor.com</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>+86 182 5727 1590</t>
+          <t>+86-13134020034</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>www.zjseating.com</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>150 Taining Road, TianZiHu Industrial Area, Anji, Huzhou, Zhejiang, China. Post Code: 313300</t>
-        </is>
-      </c>
+          <t>https://www.amerdecor.com/</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5772,7 +5800,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1100</t>
+          <t>Buyer: 650 moq 300</t>
         </is>
       </c>
     </row>
@@ -5782,42 +5810,38 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Chaozhou Lefu Sanitary Ware Technology Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>Ethan</t>
-        </is>
-      </c>
+          <t>浙江雅柔装饰材料有限公司 (Zhejiang Yarou Decoration Material Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr"/>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>lucy@lefucz.com</t>
+          <t>sale01@yarouwallpaper.com.cn</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>+0086 18098114370</t>
+          <t>+86-18069994326, +86-18069994377</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>www.lefucz.com</t>
+          <t>https://www.yarouwallpaper.com.cn/</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>Lefu Sanitary Ware, Sheweikeng, Dengtang Town, Chaoan District, Chaozhou City, Guangdong Province, China</t>
+          <t>浙江省金华市义乌市福田街道涌金大道87号厂房二楼 (No. 1, Factory 2, Yongjin Avenue 87, Futian Subdistrict, Yiwu City, Jinhua City, Zhejiang Province)</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1050</t>
+          <t>Buyer: 14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
         </is>
       </c>
     </row>
@@ -5827,22 +5851,34 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>宜昌毛尖</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr"/>
+          <t>淄博永顺装饰材料有限公司</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>戴艳辉</t>
+        </is>
+      </c>
       <c r="D138" s="2" t="inlineStr"/>
-      <c r="E138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>18830173388</t>
+        </is>
+      </c>
       <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>石家庄市正定县曙光路49号东标和聚居</t>
+        </is>
+      </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Prices are go and packing and Verstaliy is more</t>
+          <t>Buyer: 0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
         </is>
       </c>
     </row>
@@ -5852,14 +5888,34 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>湖北龙王娅茶业有限公司</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr"/>
-      <c r="D139" s="3" t="inlineStr"/>
-      <c r="E139" s="3" t="inlineStr"/>
-      <c r="F139" s="3" t="inlineStr"/>
-      <c r="G139" s="3" t="inlineStr"/>
+          <t>宏宇集团 (HONGYU GROUP)</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Melina 王玲</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>lina@hongyugroup.com</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>+86 13827702216</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>en.hongyugroup.com</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
+        </is>
+      </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5867,7 +5923,7 @@
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>Buyer: The taste anaroma is good of this product then anyother</t>
+          <t>Buyer: 20</t>
         </is>
       </c>
     </row>
@@ -5877,14 +5933,34 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>正山堂 (ZHENG SHAN TANG)</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr"/>
-      <c r="D140" s="2" t="inlineStr"/>
-      <c r="E140" s="2" t="inlineStr"/>
-      <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr"/>
+          <t>Chongnuo(Shandong)NewMaterial Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Daisy</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>sales06@chongnuo-floors.com</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>+86 19906379675</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>www.chongnuo-floors.com</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>QingyunCounty,DezhouCity,China</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Building Decoration</t>
@@ -5892,7 +5968,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Buyer: the product prices are very good. looks attractive</t>
+          <t>Buyer: 9$</t>
         </is>
       </c>
     </row>
@@ -5902,29 +5978,25 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>江西荣科新型建材有限公司 (JIANGXI RONGKE NEW BUILDING MATERIALS CO., LTD.)</t>
+          <t>上海德翔木业有限公司 (Shanghai Dexiang Wood Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Lucy Zeng (曾露)</t>
+          <t>崔强 (Cui Qiang)</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>lucy@rongkedecor.com</t>
+          <t>513437660@qq.com</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>+86-13134020034</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>https://www.amerdecor.com/</t>
-        </is>
-      </c>
+          <t>+8618901960431</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr"/>
       <c r="G141" s="3" t="inlineStr"/>
       <c r="H141" s="3" t="inlineStr">
         <is>
@@ -5933,7 +6005,7 @@
       </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 650 moq 300</t>
+          <t>Buyer: 13.25$</t>
         </is>
       </c>
     </row>
@@ -5943,28 +6015,28 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>浙江雅柔装饰材料有限公司 (Zhejiang Yarou Decoration Material Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr"/>
+          <t>中材(邯郸)新材料有限公司 (China National Building Materials (Handan) New Materials Co.,Ltd.)</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Wangfeng</t>
+        </is>
+      </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>sale01@yarouwallpaper.com.cn</t>
+          <t>2523911877@qq.com</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>+86-18069994326, +86-18069994377</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>https://www.yarouwallpaper.com.cn/</t>
-        </is>
-      </c>
+          <t>13233648687</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市福田街道涌金大道87号厂房二楼 (No. 1, Factory 2, Yongjin Avenue 87, Futian Subdistrict, Yiwu City, Jinhua City, Zhejiang Province)</t>
+          <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -5974,7 +6046,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 14 RMB per sheet, MOQ is 1000 sheets. The company was agreed to provide shipping services.</t>
+          <t>Buyer: 8.83$</t>
         </is>
       </c>
     </row>
@@ -5984,34 +6056,30 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>淄博永顺装饰材料有限公司</t>
+          <t>Zhejiang Tianyan Holding Ltd</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>戴艳辉</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr"/>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>18830173388</t>
-        </is>
-      </c>
+      <c r="E143" s="3" t="inlineStr"/>
       <c r="F143" s="3" t="inlineStr"/>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>石家庄市正定县曙光路49号东标和聚居</t>
+          <t>Taizhou, Zhejiang</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 0.35 RMB, MOQ is 1000 pieces. Secure packaging material manufactured by this company is good quality</t>
+          <t>Buyer: 640 PCs, 3.72 RMB very good</t>
         </is>
       </c>
     </row>
@@ -6021,42 +6089,38 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>宏宇集团 (HONGYU GROUP)</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Melina 王玲</t>
-        </is>
-      </c>
+          <t>Foshan Cofesu Sanitary Ware Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr"/>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>lina@hongyugroup.com</t>
+          <t>sales@cofesu.com</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>+86 13827702216</t>
+          <t>+86 181 2821 2128</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>en.hongyugroup.com</t>
+          <t>www.cofesu.com</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区江湾二路26号 (No.26 Jiangwan Second Road, Chancheng District, Foshan, Guangdong)</t>
+          <t>Foshan, Guangdong, China</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 20</t>
+          <t>Buyer: 30 PCs, 420 RMB, need check quality</t>
         </is>
       </c>
     </row>
@@ -6066,42 +6130,38 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Chongnuo(Shandong)NewMaterial Co.,Ltd.</t>
+          <t>中国广东柜邦精密金属制品有限公司 (China Guangdong Guibang Precision Metal Products Co.Ltd)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Daisy</t>
+          <t>唐一智 (JUNIOR)</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>sales06@chongnuo-floors.com</t>
+          <t>13621417@qq.com</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>+86 19906379675</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>www.chongnuo-floors.com</t>
-        </is>
-      </c>
+          <t>+86-156-2562-1155</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr"/>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>QingyunCounty,DezhouCity,China</t>
+          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 9$</t>
+          <t>Buyer: 10000</t>
         </is>
       </c>
     </row>
@@ -6111,34 +6171,38 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>上海德翔木业有限公司 (Shanghai Dexiang Wood Industry Co., Ltd.)</t>
+          <t>Jieyang Yagegu Hardware Products Co., LTD</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>崔强 (Cui Qiang)</t>
+          <t>Zoya</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>513437660@qq.com</t>
+          <t>2291828903@qq.com</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>+8618901960431</t>
+          <t>+86 132 8810 6615</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
-      <c r="G146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 13.25$</t>
+          <t>Buyer: 10000</t>
         </is>
       </c>
     </row>
@@ -6148,38 +6212,38 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>中材(邯郸)新材料有限公司 (China National Building Materials (Handan) New Materials Co.,Ltd.)</t>
+          <t>广东启宏盛精密五金制品有限公司 (GUANGDONG QIHONGSHENG PRECISION HARDWARE PRODUCTS CO., LTD)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Wangfeng</t>
+          <t>邓美君 Jessica</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>2523911877@qq.com</t>
+          <t>bailide_hinge@163.com</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>13233648687</t>
+          <t>+86 13823419116 / 0758-8565117</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr"/>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>298, Huobei Road, Fuxing Economic Development Zone, Fuxing District, Handan City, Hebei Province</t>
+          <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 8.83$</t>
+          <t>Buyer: 100</t>
         </is>
       </c>
     </row>
@@ -6189,30 +6253,42 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Zhejiang Tianyan Holding Ltd</t>
+          <t>广东亚当斯金属精密制造有限公司 (Guangdong Adams Metal Precision Manufacturing Co.,Ltd)</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Nicole</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr"/>
-      <c r="E148" s="2" t="inlineStr"/>
-      <c r="F148" s="2" t="inlineStr"/>
+          <t>Kelly Liang (梁凯莹)</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>kelly@adamsmetal.com.cn</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>+86-180-2935-2895 / +86-757-25331912</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>www.adamsmetal.com.cn</t>
+        </is>
+      </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Taizhou, Zhejiang</t>
+          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 640 PCs, 3.72 RMB very good</t>
+          <t>Buyer: Depend on item</t>
         </is>
       </c>
     </row>
@@ -6222,38 +6298,26 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Foshan Cofesu Sanitary Ware Co., Ltd.</t>
+          <t>明德 (Mingde)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr"/>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>sales@cofesu.com</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>+86 181 2821 2128</t>
-        </is>
-      </c>
+      <c r="D149" s="3" t="inlineStr"/>
+      <c r="E149" s="3" t="inlineStr"/>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>www.cofesu.com</t>
-        </is>
-      </c>
-      <c r="G149" s="3" t="inlineStr">
-        <is>
-          <t>Foshan, Guangdong, China</t>
-        </is>
-      </c>
+          <t>www.mingde-china.com</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr"/>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 30 PCs, 420 RMB, need check quality</t>
+          <t>Buyer: Depend of quantity</t>
         </is>
       </c>
     </row>
@@ -6263,38 +6327,42 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>中国广东柜邦精密金属制品有限公司 (China Guangdong Guibang Precision Metal Products Co.Ltd)</t>
+          <t>佛山市顺德区腾徽精密智造有限公司 (FoShan ShunDe TengHui Precision Intelligent Manufacturing Co., Ltd)</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>唐一智 (JUNIOR)</t>
+          <t>刘婉莹 Carol Liu</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>13621417@qq.com</t>
+          <t>tenghuihardware@126.com</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>+86-156-2562-1155</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr"/>
+          <t>+86 133 1836 4599</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>www.teehve.cn</t>
+        </is>
+      </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Jieyang City, Guangdong Province Jiedong Longwei high-tech Zone industrial Park</t>
+          <t>广东省佛山市顺德区勒流街道众涌村港口路以西8-9号之二 (No.8-9, West of GangKou Road, Zhongchong Village, Leliu Town, Shunde District, Foshan City, Guangdong, China)</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Smart Home &amp; Lighting</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 10000</t>
+          <t>Buyer: 100/square meter</t>
         </is>
       </c>
     </row>
@@ -6304,38 +6372,42 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Jieyang Yagegu Hardware Products Co., LTD</t>
+          <t>DUOCAI TENT (多彩帐蓬)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Zoya</t>
+          <t>Jimmy 黄锦民</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>2291828903@qq.com</t>
+          <t>sales003@sdduocaizp.com</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>+86 132 8810 6615</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="inlineStr"/>
+          <t>(86)133 2294 8506, +86-766-8298662</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>www.dc-tent.com, www.sdduocaizp.com</t>
+        </is>
+      </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>Jieyang jiedong district industrial park pandong southeast river science and technology avenue.</t>
+          <t>云浮市云安区佛山(云浮)产业转移工业园86号 (No.86 Foshan(Yunfu) Industrial transfer park, yunan, yunfu, Guangdong China)</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 10000</t>
+          <t>Buyer: RMB 15705 MOQ5; pleasant impression</t>
         </is>
       </c>
     </row>
@@ -6345,38 +6417,42 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>广东启宏盛精密五金制品有限公司 (GUANGDONG QIHONGSHENG PRECISION HARDWARE PRODUCTS CO., LTD)</t>
+          <t>佛山市路乐户外制品有限公司 (FOSHAN RULER OUTDOOR HARDWARES CO.,LTD)</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>邓美君 Jessica</t>
+          <t>Marco Lau (刘嘉乐)</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>bailide_hinge@163.com</t>
+          <t>RULERAWNING07@163.COM</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>+86 13823419116 / 0758-8565117</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr"/>
+          <t>+86 13129016338</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>WWW.RULER-AWNING.COM</t>
+        </is>
+      </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>广东省肇庆市高要区金利镇圩镇社区金灿北路3号 (No. 3 Jinchan North Road, Xuzhen Community, Jinli Town, Gaoyao District, Zhaoqing City, Guangdong China)</t>
+          <t>END OF ROAD SHATANXIAN, SHASHUI INDUSTRIAL ZONE, SONGGANG TOWN, SHISHAN DISTRICT, FOSHAN CITY, GUANGDONG PROVINCE, CHINA, 528200</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 100</t>
+          <t>Buyer: MOQ5 25799 RMB</t>
         </is>
       </c>
     </row>
@@ -6386,42 +6462,42 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>广东亚当斯金属精密制造有限公司 (Guangdong Adams Metal Precision Manufacturing Co.,Ltd)</t>
+          <t>Avant Sports Industrial Co., Ltd.</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Kelly Liang (梁凯莹)</t>
+          <t>Jay Zhou</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>kelly@adamsmetal.com.cn</t>
+          <t>jay@avant.com.cn</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>+86-180-2935-2895 / +86-757-25331912</t>
+          <t>+86-13128980150, +86-755-2968-8357</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>www.adamsmetal.com.cn</t>
+          <t>www.avantseating.com</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区勒流镇港口路10号 (No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province)</t>
+          <t>Avant Industrial Park, Zhoushi Road, Bao'an, Shenzhen, Guangdong Province, China</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Doors &amp; Windows</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>Buyer: Depend on item</t>
+          <t>Buyer: RMB 19479; MOQ 1</t>
         </is>
       </c>
     </row>
@@ -6431,26 +6507,42 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>明德 (Mingde)</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr"/>
-      <c r="D154" s="2" t="inlineStr"/>
-      <c r="E154" s="2" t="inlineStr"/>
+          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>孟少美 (Elite Meng)</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>ttf@hbtfjs.com</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>+86-13103196326</t>
+        </is>
+      </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>www.mingde-china.com</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr"/>
+          <t>www.hbtfjs.com</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>河北省隆尧县东谷子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
+        </is>
+      </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Buyer: Depend of quantity</t>
+          <t>Buyer: 1000</t>
         </is>
       </c>
     </row>
@@ -6460,42 +6552,42 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>佛山市顺德区腾徽精密智造有限公司 (FoShan ShunDe TengHui Precision Intelligent Manufacturing Co., Ltd)</t>
+          <t>揭阳市新骏业五金制品有限公司 (JIEYANG XINJUNYE HARDWARE PRODUCTS CO., LTD)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>刘婉莹 Carol Liu</t>
+          <t>林树丹 (Lin Shudan)</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>tenghuihardware@126.com</t>
+          <t>linshdong@qq.com</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>+86 133 1836 4599</t>
+          <t>13751676456</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>www.teehve.cn</t>
+          <t>www.xinjunye.com</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区勒流街道众涌村港口路以西8-9号之二 (No.8-9, West of GangKou Road, Zhongchong Village, Leliu Town, Shunde District, Foshan City, Guangdong, China)</t>
+          <t>广东省揭阳市揭东区锡场工业区 (Xichang Industrial Zone, Jiedong District, Jieyang City, Guangdong Province)</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>Smart Home &amp; Lighting</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 100/square meter</t>
+          <t>Buyer: 1000</t>
         </is>
       </c>
     </row>
@@ -6505,42 +6597,42 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>DUOCAI TENT (多彩帐蓬)</t>
+          <t>Guangdong Adams Metal Precision Manufacturing Co., Ltd (广东亚当斯金属精密制造有限公司)</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Jimmy 黄锦民</t>
+          <t>Kelly Liang (梁凯莹)</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>sales003@sdduocaizp.com</t>
+          <t>kelly@adamsmetal.com.cn</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>(86)133 2294 8506, +86-766-8298662</t>
+          <t>+86-180-2935-2895, +86-757-25331912</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>www.dc-tent.com, www.sdduocaizp.com</t>
+          <t>www.adamsmetal.com.cn</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>云浮市云安区佛山(云浮)产业转移工业园86号 (No.86 Foshan(Yunfu) Industrial transfer park, yunan, yunfu, Guangdong China)</t>
+          <t>No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province (广东省佛山市顺德区勒流镇港口路10号)</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Buyer: RMB 15705 MOQ5; pleasant impression</t>
+          <t>Buyer: 1000</t>
         </is>
       </c>
     </row>
@@ -6550,42 +6642,42 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>佛山市路乐户外制品有限公司 (FOSHAN RULER OUTDOOR HARDWARES CO.,LTD)</t>
+          <t>广州蒙娜丽莎控股集团有限公司 / 广州蒙娜丽莎卫浴股份有限公司</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Marco Lau (刘嘉乐)</t>
+          <t>伍乐彤</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>RULERAWNING07@163.COM</t>
+          <t>monalisa702@monalisa.cn</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>+86 13129016338</t>
+          <t>86 13711117863, 400 020 1818, 86 20-28607722, 86 20-28607788</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>WWW.RULER-AWNING.COM</t>
+          <t>www.monalisa.cn</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>END OF ROAD SHATANXIAN, SHASHUI INDUSTRIAL ZONE, SONGGANG TOWN, SHISHAN DISTRICT, FOSHAN CITY, GUANGDONG PROVINCE, CHINA, 528200</t>
+          <t>广州市花都区花东镇港头工业区4号</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
         <is>
-          <t>Buyer: MOQ5 25799 RMB</t>
+          <t>Buyer: 2000$, can be customized, very convenient</t>
         </is>
       </c>
     </row>
@@ -6595,42 +6687,42 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Avant Sports Industrial Co., Ltd.</t>
+          <t>中山藝進不銹鋼裝飾制品有限公司 (ZHONGSHAN YIJIN STAINLESS STEEL DECORATION CO., LTD.)</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Jay Zhou</t>
+          <t>Anson Yuen</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>jay@avant.com.cn</t>
+          <t>info@hugemount.com</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>+86-13128980150, +86-755-2968-8357</t>
+          <t>150 1954 6322 / 86-760-88702663</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>www.avantseating.com</t>
+          <t>www.yijin.com</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Avant Industrial Park, Zhoushi Road, Bao'an, Shenzhen, Guangdong Province, China</t>
+          <t>中国广东省中山市港口镇石特社区穗安工业区迎富2路1号 (NO.1, Ying Fu 2 Road, Sui An Gong Ye Qu, Gang Kou Zhen Shi Te She Qu, Zhongshan City, Guangdong Province, P.R.China)</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>Doors &amp; Windows</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Buyer: RMB 19479; MOQ 1</t>
+          <t>Buyer: 38$, very unique</t>
         </is>
       </c>
     </row>
@@ -6640,42 +6732,42 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>河北天丰金属制品有限公司 (Hebei Tianfeng Metal Products Co., Ltd.)</t>
+          <t>宣城市宠爱卫浴有限公司 (CHONGAI SANITARY WARE CO., LTD.)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>孟少美 (Elite Meng)</t>
+          <t>Lucy (卢美珍)</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>ttf@hbtfjs.com</t>
+          <t>export@vnsmilo.com</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>+86-13103196326</t>
+          <t>+86-13757322119</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>www.hbtfjs.com</t>
+          <t>www.vnsmilo.com</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>河北省隆尧县东谷子村工业区 (Gongzi Village Industry Zone, Longyao County, Xingtai City, Hebei, China)</t>
+          <t>Xuancheng City Anhui, CHINA</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>Building Decoration</t>
+          <t>Bath &amp; Sanitary</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1000</t>
+          <t>Buyer: 2050 rmb, very interesting, convenient to use for pets</t>
         </is>
       </c>
     </row>
@@ -6685,42 +6777,30 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>揭阳市新骏业五金制品有限公司 (JIEYANG XINJUNYE HARDWARE PRODUCTS CO., LTD)</t>
+          <t>广西中晨木业有限公司 (Guangxi Zhongchen Wood Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>林树丹 (Lin Shudan)</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>linshdong@qq.com</t>
-        </is>
-      </c>
+          <t>张爱彬 (Zhang Aibin)</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr"/>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>13751676456</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>www.xinjunye.com</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>广东省揭阳市揭东区锡场工业区 (Xichang Industrial Zone, Jiedong District, Jieyang City, Guangdong Province)</t>
-        </is>
-      </c>
+          <t>+86 18178085851</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 1000</t>
+          <t>Buyer: 25 rmb, 1 box, like this product</t>
         </is>
       </c>
     </row>
@@ -6730,42 +6810,42 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Guangdong Adams Metal Precision Manufacturing Co., Ltd (广东亚当斯金属精密制造有限公司)</t>
+          <t>NINGBO YUSHENG HOME TECH CO., LTD. (宁波裕盛家居科技有限公司)</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Kelly Liang (梁凯莹)</t>
+          <t>Tequila Xu (徐孟杰)</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>kelly@adamsmetal.com.cn</t>
+          <t>marketing@cxyushun.com, tequila8xu@gmail.com</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>+86-180-2935-2895, +86-757-25331912</t>
+          <t>0086-13819449988, +86 574 63190388</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>www.adamsmetal.com.cn</t>
+          <t>www.cxys8.com</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>No.10, Gangkou Road, Leliu Town, Shunde District, Foshan City, Guangdong Province (广东省佛山市顺德区勒流镇港口路10号)</t>
+          <t>中国浙江慈溪市杨梅大道南路1518号 (NO.1518, YANGMEI AVENUE SOUTH ROAD, CIXI CITY, ZHEJIANG, CHINA)</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Building Decoration</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 1000</t>
+          <t>Buyer: 34 rmb, 1000, normal</t>
         </is>
       </c>
     </row>
@@ -6775,42 +6855,42 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>广州蒙娜丽莎控股集团有限公司 / 广州蒙娜丽莎卫浴股份有限公司</t>
+          <t>河北建华锁业有限公司 (Hebei Jianhua Lock Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>伍乐彤</t>
+          <t>刘芳 (Jane Liu)</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>monalisa702@monalisa.cn</t>
+          <t>jane@dirock.cn</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>86 13711117863, 400 020 1818, 86 20-28607722, 86 20-28607788</t>
+          <t>187 1377 2087</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>www.monalisa.cn</t>
+          <t>http://www.dirock.cn</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区花东镇港头工业区4号</t>
+          <t>河北省泊头市寺门村镇后牛屯</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Bath &amp; Sanitary</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>Buyer: 2000$, can be customized, very convenient</t>
+          <t>Buyer: 40 rmb, 2000, very good</t>
         </is>
       </c>
     </row>
@@ -6820,32 +6900,32 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>中山藝進不銹鋼裝飾制品有限公司 (ZHONGSHAN YIJIN STAINLESS STEEL DECORATION CO., LTD.)</t>
+          <t>浙江安吉双虎竹木业有限公司 / 安吉诺迪新材料有限公司</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Anson Yuen</t>
+          <t>周瑶琳</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>info@hugemount.com</t>
+          <t>lisa.nordi@nuodibm.com</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>150 1954 6322 / 86-760-88702663</t>
+          <t>+86-137 3822 8209</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>www.yijin.com</t>
+          <t>www.tigerbamboo.com / www.nuodibm.com</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>中国广东省中山市港口镇石特社区穗安工业区迎富2路1号 (NO.1, Ying Fu 2 Road, Sui An Gong Ye Qu, Gang Kou Zhen Shi Te She Qu, Zhongshan City, Guangdong Province, P.R.China)</t>
+          <t>浙江省湖州市安吉县孝丰镇大竹村</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
@@ -6855,7 +6935,7 @@
       </c>
       <c r="I163" s="3" t="inlineStr">
         <is>
-          <t>Buyer: 38$, very unique</t>
+          <t>Buyer: 1 container 250 rmb</t>
         </is>
       </c>
     </row>
@@ -6865,42 +6945,42 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>宣城市宠爱卫浴有限公司 (CHONGAI SANITARY WARE CO., LTD.)</t>
+          <t>宏宇集团 HONGYU GROUP</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Lucy (卢美珍)</t>
+          <t>Melina 王玲</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>export@vnsmilo.com</t>
+          <t>lina@hongyugroup.com</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>+86-13757322119</t>
+          <t>+86 13827702216</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>www.vnsmilo.com</t>
+          <t>en.hongyugroup.com</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Xuancheng City Anhui, CHINA</t>
+          <t>广东省佛山市禅城区江湾二